--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="131">
   <si>
     <t>League</t>
   </si>
@@ -259,7 +259,7 @@
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
-    <t>Argentinian Primera Division</t>
+    <t>Colombian Primera B</t>
   </si>
   <si>
     <t>South Korean K1 League</t>
@@ -268,6 +268,9 @@
     <t>Latvian Virsliga</t>
   </si>
   <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
@@ -277,13 +280,16 @@
     <t>Spanish La Liga</t>
   </si>
   <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
     <t>2026-08-25</t>
   </si>
   <si>
     <t>00:00:00</t>
   </si>
   <si>
-    <t>00:15:00</t>
+    <t>00:45:00</t>
   </si>
   <si>
     <t>10:30:00</t>
@@ -304,13 +310,16 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>Libertad FC</t>
   </si>
   <si>
-    <t>Lanus</t>
-  </si>
-  <si>
-    <t>Talleres</t>
+    <t>Internacional de Palmira</t>
   </si>
   <si>
     <t>Gimcheon Sangmu</t>
@@ -325,12 +334,18 @@
     <t>FK Auda</t>
   </si>
   <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
     <t>Al-Taawoun Buraidah</t>
   </si>
   <si>
     <t>Osters</t>
   </si>
   <si>
+    <t>Orebro</t>
+  </si>
+  <si>
     <t>Al-Ettifaq</t>
   </si>
   <si>
@@ -340,13 +355,16 @@
     <t>Valencia</t>
   </si>
   <si>
+    <t>Afturelding</t>
+  </si>
+  <si>
+    <t>Boca Juniors de Cali</t>
+  </si>
+  <si>
     <t>Macara</t>
   </si>
   <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Rosario Central</t>
+    <t>Barranquilla</t>
   </si>
   <si>
     <t>Jeonbuk Motors</t>
@@ -361,12 +379,18 @@
     <t>Liepajas Metalurgs</t>
   </si>
   <si>
+    <t>FC Metaloglobus Bucuresti</t>
+  </si>
+  <si>
     <t>Al-Feiha</t>
   </si>
   <si>
     <t>Sundsvall</t>
   </si>
   <si>
+    <t>Varbergs BoIS</t>
+  </si>
+  <si>
     <t>Al Nassr</t>
   </si>
   <si>
@@ -376,7 +400,13 @@
     <t>Betis</t>
   </si>
   <si>
-    <t>2026-08-23 12:49:28</t>
+    <t>Grotta</t>
+  </si>
+  <si>
+    <t>Bogota</t>
+  </si>
+  <si>
+    <t>2026-08-23 17:36:55</t>
   </si>
 </sst>
 </file>
@@ -708,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -958,16 +988,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F2">
         <v>3.1</v>
@@ -985,7 +1015,7 @@
         <v>3.1</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
         <v>1.47</v>
@@ -1024,118 +1054,118 @@
         <v>1.39</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH2">
         <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
@@ -1192,7 +1222,7 @@
         <v>8.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1200,178 +1230,178 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F3">
-        <v>2.74</v>
+        <v>1.36</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>110</v>
       </c>
       <c r="J3">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>3.15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="P3">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="Q3">
-        <v>2.74</v>
+        <v>1.75</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.5</v>
+        <v>2.54</v>
       </c>
       <c r="X3">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR3">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS3">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT3">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW3">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA3">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BB3">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC3">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD3">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE3">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF3">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1434,249 +1464,249 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F4">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="G4">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="H4">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="J4">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
+        <v>1.98</v>
+      </c>
+      <c r="R4">
+        <v>1.34</v>
+      </c>
+      <c r="S4">
+        <v>3.5</v>
+      </c>
+      <c r="T4">
+        <v>1.8</v>
+      </c>
+      <c r="U4">
+        <v>2.12</v>
+      </c>
+      <c r="V4">
+        <v>1.75</v>
+      </c>
+      <c r="W4">
+        <v>1.35</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>4.1</v>
+      </c>
+      <c r="BI4">
         <v>2.68</v>
       </c>
-      <c r="R4">
-        <v>1.19</v>
-      </c>
-      <c r="S4">
-        <v>5.3</v>
-      </c>
-      <c r="T4">
-        <v>2.06</v>
-      </c>
-      <c r="U4">
-        <v>1.79</v>
-      </c>
-      <c r="V4">
-        <v>1.44</v>
-      </c>
-      <c r="W4">
-        <v>1.52</v>
-      </c>
-      <c r="X4">
-        <v>9</v>
-      </c>
-      <c r="Y4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z4">
-        <v>24</v>
-      </c>
-      <c r="AA4">
-        <v>80</v>
-      </c>
-      <c r="AB4">
-        <v>8.6</v>
-      </c>
-      <c r="AC4">
-        <v>7.4</v>
-      </c>
-      <c r="AD4">
-        <v>15</v>
-      </c>
-      <c r="AE4">
-        <v>60</v>
-      </c>
-      <c r="AF4">
-        <v>18</v>
-      </c>
-      <c r="AG4">
-        <v>14</v>
-      </c>
-      <c r="AH4">
-        <v>27</v>
-      </c>
-      <c r="AI4">
-        <v>95</v>
-      </c>
-      <c r="AJ4">
-        <v>60</v>
-      </c>
-      <c r="AK4">
-        <v>50</v>
-      </c>
-      <c r="AL4">
-        <v>85</v>
-      </c>
-      <c r="AM4">
-        <v>210</v>
-      </c>
-      <c r="AN4">
-        <v>60</v>
-      </c>
-      <c r="AO4">
-        <v>80</v>
-      </c>
-      <c r="AP4">
-        <v>7.4</v>
-      </c>
-      <c r="AQ4">
-        <v>7.6</v>
-      </c>
-      <c r="AR4">
-        <v>16.5</v>
-      </c>
-      <c r="AS4">
-        <v>6.8</v>
-      </c>
-      <c r="AT4">
-        <v>7.2</v>
-      </c>
-      <c r="AU4">
-        <v>6</v>
-      </c>
-      <c r="AV4">
-        <v>12</v>
-      </c>
-      <c r="AW4">
-        <v>6.8</v>
-      </c>
-      <c r="AX4">
-        <v>15</v>
-      </c>
-      <c r="AY4">
-        <v>11</v>
-      </c>
-      <c r="AZ4">
-        <v>18.5</v>
-      </c>
-      <c r="BA4">
-        <v>7</v>
-      </c>
-      <c r="BB4">
-        <v>6.8</v>
-      </c>
-      <c r="BC4">
-        <v>6.4</v>
-      </c>
-      <c r="BD4">
-        <v>7</v>
-      </c>
-      <c r="BE4">
-        <v>7.2</v>
-      </c>
-      <c r="BF4">
-        <v>6.8</v>
-      </c>
-      <c r="BG4">
-        <v>6.8</v>
-      </c>
-      <c r="BH4">
-        <v>3.1</v>
-      </c>
-      <c r="BI4">
-        <v>2.22</v>
-      </c>
       <c r="BJ4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>4</v>
+        <v>1.33</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5.5</v>
+        <v>1.33</v>
       </c>
       <c r="BN4">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>1.33</v>
       </c>
       <c r="BP4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>4.8</v>
+        <v>1.33</v>
       </c>
       <c r="BR4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>5.2</v>
+        <v>1.33</v>
       </c>
       <c r="BT4">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="BV4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>4.9</v>
+        <v>1.33</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>5.2</v>
+        <v>1.33</v>
       </c>
       <c r="BZ4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="CB4" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1684,241 +1714,241 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F5">
-        <v>3.45</v>
+        <v>2.52</v>
       </c>
       <c r="G5">
-        <v>3.8</v>
+        <v>2.72</v>
       </c>
       <c r="H5">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>2.32</v>
+        <v>3.35</v>
       </c>
       <c r="J5">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="O5">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="P5">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="Q5">
-        <v>1.96</v>
+        <v>2.36</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="S5">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="T5">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="U5">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="V5">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="X5">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="Y5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z5">
+        <v>24</v>
+      </c>
+      <c r="AA5">
+        <v>70</v>
+      </c>
+      <c r="AB5">
+        <v>8.6</v>
+      </c>
+      <c r="AC5">
+        <v>7.4</v>
+      </c>
+      <c r="AD5">
         <v>16.5</v>
       </c>
-      <c r="AA5">
-        <v>34</v>
-      </c>
-      <c r="AB5">
-        <v>15.5</v>
-      </c>
-      <c r="AC5">
-        <v>8.4</v>
-      </c>
-      <c r="AD5">
-        <v>13</v>
-      </c>
       <c r="AE5">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AG5">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AI5">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AK5">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AL5">
         <v>65</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AO5">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
         <v>8.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AS5">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AT5">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AU5">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AW5">
-        <v>21</v>
+        <v>5.8</v>
       </c>
       <c r="AX5">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AY5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB5">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD5">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BE5">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BG5">
-        <v>14</v>
+        <v>5.9</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1926,524 +1956,524 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F6">
-        <v>2.52</v>
+        <v>1.56</v>
       </c>
       <c r="G6">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="H6">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="I6">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="L6">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="O6">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="P6">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="S6">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="W6">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y6">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="Z6">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="AA6">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="AB6">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AE6">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AF6">
-        <v>18.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AJ6">
-        <v>48</v>
+        <v>17.5</v>
       </c>
       <c r="AK6">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AL6">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AM6">
         <v>170</v>
       </c>
       <c r="AN6">
-        <v>38</v>
+        <v>9.6</v>
       </c>
       <c r="AO6">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="AP6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AR6">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="AS6">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU6">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV6">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AW6">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX6">
+        <v>8</v>
+      </c>
+      <c r="AY6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6">
+        <v>18</v>
+      </c>
+      <c r="BA6">
+        <v>7.4</v>
+      </c>
+      <c r="BB6">
+        <v>12.5</v>
+      </c>
+      <c r="BC6">
         <v>13.5</v>
       </c>
-      <c r="AY6">
-        <v>10.5</v>
-      </c>
-      <c r="AZ6">
-        <v>17</v>
-      </c>
-      <c r="BA6">
-        <v>6</v>
-      </c>
-      <c r="BB6">
-        <v>5.8</v>
-      </c>
-      <c r="BC6">
-        <v>5.5</v>
-      </c>
       <c r="BD6">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE6">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF6">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG6">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="CB6" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F7">
-        <v>1.56</v>
+        <v>1.05</v>
       </c>
       <c r="G7">
-        <v>1.64</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>6.4</v>
+        <v>1.05</v>
       </c>
       <c r="I7">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>1.08</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.94</v>
+        <v>1.19</v>
       </c>
       <c r="R7">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>3.4</v>
+        <v>1.19</v>
       </c>
       <c r="T7">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7">
+        <v>1.03</v>
+      </c>
+      <c r="AR7">
+        <v>1.03</v>
+      </c>
+      <c r="AS7">
+        <v>1.03</v>
+      </c>
+      <c r="AT7">
+        <v>1.03</v>
+      </c>
+      <c r="AU7">
+        <v>1.03</v>
+      </c>
+      <c r="AV7">
+        <v>1.03</v>
+      </c>
+      <c r="AW7">
+        <v>1.03</v>
+      </c>
+      <c r="AX7">
+        <v>1.03</v>
+      </c>
+      <c r="AY7">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7">
+        <v>1.03</v>
+      </c>
+      <c r="BA7">
+        <v>1.03</v>
+      </c>
+      <c r="BB7">
+        <v>1.03</v>
+      </c>
+      <c r="BC7">
+        <v>1.03</v>
+      </c>
+      <c r="BD7">
+        <v>1.03</v>
+      </c>
+      <c r="BE7">
+        <v>1.03</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.01</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.01</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
         <v>130</v>
-      </c>
-      <c r="AF7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG7">
-        <v>10.5</v>
-      </c>
-      <c r="AH7">
-        <v>28</v>
-      </c>
-      <c r="AI7">
-        <v>120</v>
-      </c>
-      <c r="AJ7">
-        <v>17.5</v>
-      </c>
-      <c r="AK7">
-        <v>18.5</v>
-      </c>
-      <c r="AL7">
-        <v>46</v>
-      </c>
-      <c r="AM7">
-        <v>170</v>
-      </c>
-      <c r="AN7">
-        <v>9.6</v>
-      </c>
-      <c r="AO7">
-        <v>180</v>
-      </c>
-      <c r="AP7">
-        <v>12.5</v>
-      </c>
-      <c r="AQ7">
-        <v>18</v>
-      </c>
-      <c r="AR7">
-        <v>7</v>
-      </c>
-      <c r="AS7">
-        <v>7.6</v>
-      </c>
-      <c r="AT7">
-        <v>6.8</v>
-      </c>
-      <c r="AU7">
-        <v>8.6</v>
-      </c>
-      <c r="AV7">
-        <v>20</v>
-      </c>
-      <c r="AW7">
-        <v>7.4</v>
-      </c>
-      <c r="AX7">
-        <v>8</v>
-      </c>
-      <c r="AY7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7">
-        <v>18</v>
-      </c>
-      <c r="BA7">
-        <v>7.4</v>
-      </c>
-      <c r="BB7">
-        <v>12.5</v>
-      </c>
-      <c r="BC7">
-        <v>13.5</v>
-      </c>
-      <c r="BD7">
-        <v>6.8</v>
-      </c>
-      <c r="BE7">
-        <v>7.6</v>
-      </c>
-      <c r="BF7">
-        <v>8.4</v>
-      </c>
-      <c r="BG7">
-        <v>7.6</v>
-      </c>
-      <c r="BH7">
-        <v>0</v>
-      </c>
-      <c r="BI7">
-        <v>0</v>
-      </c>
-      <c r="BJ7">
-        <v>0</v>
-      </c>
-      <c r="BK7">
-        <v>0</v>
-      </c>
-      <c r="BL7">
-        <v>0</v>
-      </c>
-      <c r="BM7">
-        <v>0</v>
-      </c>
-      <c r="BN7">
-        <v>0</v>
-      </c>
-      <c r="BO7">
-        <v>0</v>
-      </c>
-      <c r="BP7">
-        <v>0</v>
-      </c>
-      <c r="BQ7">
-        <v>0</v>
-      </c>
-      <c r="BR7">
-        <v>0</v>
-      </c>
-      <c r="BS7">
-        <v>0</v>
-      </c>
-      <c r="BT7">
-        <v>0</v>
-      </c>
-      <c r="BU7">
-        <v>0</v>
-      </c>
-      <c r="BV7">
-        <v>0</v>
-      </c>
-      <c r="BW7">
-        <v>0</v>
-      </c>
-      <c r="BX7">
-        <v>0</v>
-      </c>
-      <c r="BY7">
-        <v>0</v>
-      </c>
-      <c r="BZ7">
-        <v>0</v>
-      </c>
-      <c r="CA7">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2452,216 +2482,216 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F9">
         <v>1.55</v>
@@ -2670,28 +2700,28 @@
         <v>1.71</v>
       </c>
       <c r="H9">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P9">
         <v>1.92</v>
@@ -2700,213 +2730,213 @@
         <v>1.81</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F10">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G10">
         <v>1.91</v>
@@ -2924,202 +2954,202 @@
         <v>4.5</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q10">
         <v>1.63</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3128,240 +3158,240 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F11">
+        <v>2.76</v>
+      </c>
+      <c r="G11">
+        <v>3.1</v>
+      </c>
+      <c r="H11">
+        <v>2.52</v>
+      </c>
+      <c r="I11">
+        <v>2.86</v>
+      </c>
+      <c r="J11">
+        <v>3.5</v>
+      </c>
+      <c r="K11">
+        <v>3.85</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.06</v>
+      </c>
+      <c r="N11">
+        <v>3.95</v>
+      </c>
+      <c r="O11">
+        <v>1.29</v>
+      </c>
+      <c r="P11">
+        <v>1.98</v>
+      </c>
+      <c r="Q11">
+        <v>1.85</v>
+      </c>
+      <c r="R11">
+        <v>1.37</v>
+      </c>
+      <c r="S11">
+        <v>3.1</v>
+      </c>
+      <c r="T11">
+        <v>1.69</v>
+      </c>
+      <c r="U11">
+        <v>2.22</v>
+      </c>
+      <c r="V11">
+        <v>1.55</v>
+      </c>
+      <c r="W11">
+        <v>1.47</v>
+      </c>
+      <c r="X11">
+        <v>18</v>
+      </c>
+      <c r="Y11">
+        <v>12.5</v>
+      </c>
+      <c r="Z11">
+        <v>19</v>
+      </c>
+      <c r="AA11">
+        <v>40</v>
+      </c>
+      <c r="AB11">
+        <v>14.5</v>
+      </c>
+      <c r="AC11">
         <v>8.6</v>
       </c>
-      <c r="G11">
+      <c r="AD11">
+        <v>14</v>
+      </c>
+      <c r="AE11">
+        <v>30</v>
+      </c>
+      <c r="AF11">
+        <v>21</v>
+      </c>
+      <c r="AG11">
+        <v>13.5</v>
+      </c>
+      <c r="AH11">
+        <v>17.5</v>
+      </c>
+      <c r="AI11">
+        <v>40</v>
+      </c>
+      <c r="AJ11">
+        <v>65</v>
+      </c>
+      <c r="AK11">
+        <v>36</v>
+      </c>
+      <c r="AL11">
+        <v>42</v>
+      </c>
+      <c r="AM11">
+        <v>100</v>
+      </c>
+      <c r="AN11">
+        <v>29</v>
+      </c>
+      <c r="AO11">
+        <v>23</v>
+      </c>
+      <c r="AP11">
         <v>12</v>
       </c>
-      <c r="H11">
-        <v>1.32</v>
-      </c>
-      <c r="I11">
-        <v>1.38</v>
-      </c>
-      <c r="J11">
-        <v>6</v>
-      </c>
-      <c r="K11">
-        <v>8</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
+      <c r="AQ11">
+        <v>10</v>
+      </c>
+      <c r="AR11">
+        <v>15.5</v>
+      </c>
+      <c r="AS11">
+        <v>24</v>
+      </c>
+      <c r="AT11">
+        <v>10.5</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>9.4</v>
+      </c>
+      <c r="AW11">
+        <v>21</v>
+      </c>
+      <c r="AX11">
+        <v>17</v>
+      </c>
+      <c r="AY11">
+        <v>10</v>
+      </c>
+      <c r="AZ11">
+        <v>12.5</v>
+      </c>
+      <c r="BA11">
+        <v>24</v>
+      </c>
+      <c r="BB11">
+        <v>27</v>
+      </c>
+      <c r="BC11">
+        <v>19</v>
+      </c>
+      <c r="BD11">
+        <v>25</v>
+      </c>
+      <c r="BE11">
+        <v>1.01</v>
+      </c>
+      <c r="BF11">
+        <v>21</v>
+      </c>
+      <c r="BG11">
+        <v>18.5</v>
+      </c>
+      <c r="BH11">
+        <v>4.3</v>
+      </c>
+      <c r="BI11">
+        <v>2.86</v>
+      </c>
+      <c r="BJ11">
+        <v>12.5</v>
+      </c>
+      <c r="BK11">
+        <v>2.68</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
         <v>3.4</v>
       </c>
-      <c r="Q11">
-        <v>1.34</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>0</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>0</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-      <c r="BD11">
-        <v>0</v>
-      </c>
-      <c r="BE11">
-        <v>0</v>
-      </c>
-      <c r="BF11">
-        <v>0</v>
-      </c>
-      <c r="BG11">
-        <v>0</v>
-      </c>
-      <c r="BH11">
-        <v>0</v>
-      </c>
-      <c r="BI11">
-        <v>0</v>
-      </c>
-      <c r="BJ11">
-        <v>0</v>
-      </c>
-      <c r="BK11">
-        <v>0</v>
-      </c>
-      <c r="BL11">
-        <v>0</v>
-      </c>
-      <c r="BM11">
-        <v>0</v>
-      </c>
       <c r="BN11">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3370,491 +3400,1217 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F12">
-        <v>1.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G12">
-        <v>1.93</v>
+        <v>12.5</v>
       </c>
       <c r="H12">
+        <v>1.31</v>
+      </c>
+      <c r="I12">
+        <v>1.37</v>
+      </c>
+      <c r="J12">
+        <v>6.2</v>
+      </c>
+      <c r="K12">
+        <v>7.2</v>
+      </c>
+      <c r="L12">
+        <v>1.15</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>8.4</v>
+      </c>
+      <c r="O12">
+        <v>1.11</v>
+      </c>
+      <c r="P12">
+        <v>3.45</v>
+      </c>
+      <c r="Q12">
+        <v>1.34</v>
+      </c>
+      <c r="R12">
+        <v>2.02</v>
+      </c>
+      <c r="S12">
+        <v>1.85</v>
+      </c>
+      <c r="T12">
+        <v>1.67</v>
+      </c>
+      <c r="U12">
+        <v>2.28</v>
+      </c>
+      <c r="V12">
+        <v>3.7</v>
+      </c>
+      <c r="W12">
+        <v>1.1</v>
+      </c>
+      <c r="X12">
+        <v>60</v>
+      </c>
+      <c r="Y12">
+        <v>19.5</v>
+      </c>
+      <c r="Z12">
+        <v>15</v>
+      </c>
+      <c r="AA12">
+        <v>15.5</v>
+      </c>
+      <c r="AB12">
+        <v>60</v>
+      </c>
+      <c r="AC12">
+        <v>21</v>
+      </c>
+      <c r="AD12">
+        <v>14.5</v>
+      </c>
+      <c r="AE12">
+        <v>16.5</v>
+      </c>
+      <c r="AF12">
+        <v>120</v>
+      </c>
+      <c r="AG12">
+        <v>44</v>
+      </c>
+      <c r="AH12">
+        <v>28</v>
+      </c>
+      <c r="AI12">
+        <v>32</v>
+      </c>
+      <c r="AJ12">
+        <v>310</v>
+      </c>
+      <c r="AK12">
+        <v>130</v>
+      </c>
+      <c r="AL12">
+        <v>95</v>
+      </c>
+      <c r="AM12">
+        <v>95</v>
+      </c>
+      <c r="AN12">
+        <v>100</v>
+      </c>
+      <c r="AO12">
+        <v>4</v>
+      </c>
+      <c r="AP12">
+        <v>4.3</v>
+      </c>
+      <c r="AQ12">
+        <v>11.5</v>
+      </c>
+      <c r="AR12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS12">
+        <v>11</v>
+      </c>
+      <c r="AT12">
+        <v>4.3</v>
+      </c>
+      <c r="AU12">
+        <v>12</v>
+      </c>
+      <c r="AV12">
+        <v>10.5</v>
+      </c>
+      <c r="AW12">
+        <v>11.5</v>
+      </c>
+      <c r="AX12">
+        <v>4.4</v>
+      </c>
+      <c r="AY12">
         <v>4.2</v>
       </c>
-      <c r="I12">
-        <v>5.5</v>
-      </c>
-      <c r="J12">
-        <v>3.9</v>
-      </c>
-      <c r="K12">
-        <v>4.7</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>2.32</v>
-      </c>
-      <c r="Q12">
-        <v>1.62</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="CB12" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13">
+        <v>1.75</v>
+      </c>
+      <c r="G13">
+        <v>1.93</v>
+      </c>
+      <c r="H13">
+        <v>4.2</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>3.9</v>
+      </c>
+      <c r="K13">
+        <v>4.6</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.04</v>
+      </c>
+      <c r="N13">
+        <v>4.7</v>
+      </c>
+      <c r="O13">
+        <v>1.21</v>
+      </c>
+      <c r="P13">
+        <v>2.32</v>
+      </c>
+      <c r="Q13">
+        <v>1.62</v>
+      </c>
+      <c r="R13">
+        <v>1.51</v>
+      </c>
+      <c r="S13">
+        <v>2.56</v>
+      </c>
+      <c r="T13">
+        <v>1.63</v>
+      </c>
+      <c r="U13">
+        <v>2.28</v>
+      </c>
+      <c r="V13">
+        <v>1.25</v>
+      </c>
+      <c r="W13">
+        <v>2.06</v>
+      </c>
+      <c r="X13">
+        <v>25</v>
+      </c>
+      <c r="Y13">
+        <v>24</v>
+      </c>
+      <c r="Z13">
+        <v>44</v>
+      </c>
+      <c r="AA13">
+        <v>110</v>
+      </c>
+      <c r="AB13">
+        <v>13.5</v>
+      </c>
+      <c r="AC13">
+        <v>11.5</v>
+      </c>
+      <c r="AD13">
+        <v>19</v>
+      </c>
+      <c r="AE13">
+        <v>60</v>
+      </c>
+      <c r="AF13">
+        <v>14</v>
+      </c>
+      <c r="AG13">
+        <v>12</v>
+      </c>
+      <c r="AH13">
+        <v>18</v>
+      </c>
+      <c r="AI13">
+        <v>60</v>
+      </c>
+      <c r="AJ13">
+        <v>24</v>
+      </c>
+      <c r="AK13">
+        <v>18.5</v>
+      </c>
+      <c r="AL13">
+        <v>36</v>
+      </c>
+      <c r="AM13">
+        <v>90</v>
+      </c>
+      <c r="AN13">
+        <v>9.4</v>
+      </c>
+      <c r="AO13">
+        <v>50</v>
+      </c>
+      <c r="AP13">
+        <v>16.5</v>
+      </c>
+      <c r="AQ13">
+        <v>17</v>
+      </c>
+      <c r="AR13">
+        <v>27</v>
+      </c>
+      <c r="AS13">
+        <v>6</v>
+      </c>
+      <c r="AT13">
+        <v>9</v>
+      </c>
+      <c r="AU13">
+        <v>8.4</v>
+      </c>
+      <c r="AV13">
+        <v>14</v>
+      </c>
+      <c r="AW13">
+        <v>38</v>
+      </c>
+      <c r="AX13">
+        <v>11</v>
+      </c>
+      <c r="AY13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ13">
+        <v>13</v>
+      </c>
+      <c r="BA13">
+        <v>36</v>
+      </c>
+      <c r="BB13">
+        <v>17</v>
+      </c>
+      <c r="BC13">
+        <v>13.5</v>
+      </c>
+      <c r="BD13">
+        <v>21</v>
+      </c>
+      <c r="BE13">
+        <v>5.8</v>
+      </c>
+      <c r="BF13">
+        <v>7</v>
+      </c>
+      <c r="BG13">
+        <v>5.6</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.01</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.01</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.01</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.01</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
         <v>87</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14">
+        <v>2.9</v>
+      </c>
+      <c r="G14">
+        <v>2.94</v>
+      </c>
+      <c r="H14">
+        <v>2.66</v>
+      </c>
+      <c r="I14">
+        <v>2.7</v>
+      </c>
+      <c r="J14">
+        <v>3.45</v>
+      </c>
+      <c r="K14">
+        <v>3.5</v>
+      </c>
+      <c r="L14">
+        <v>1.41</v>
+      </c>
+      <c r="M14">
+        <v>1.08</v>
+      </c>
+      <c r="N14">
+        <v>3.75</v>
+      </c>
+      <c r="O14">
+        <v>1.35</v>
+      </c>
+      <c r="P14">
+        <v>1.92</v>
+      </c>
+      <c r="Q14">
+        <v>2.02</v>
+      </c>
+      <c r="R14">
+        <v>1.35</v>
+      </c>
+      <c r="S14">
+        <v>3.65</v>
+      </c>
+      <c r="T14">
+        <v>1.8</v>
+      </c>
+      <c r="U14">
+        <v>2.2</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>13</v>
+      </c>
+      <c r="Y14">
+        <v>11</v>
+      </c>
+      <c r="Z14">
+        <v>17.5</v>
+      </c>
+      <c r="AA14">
+        <v>40</v>
+      </c>
+      <c r="AB14">
+        <v>11.5</v>
+      </c>
+      <c r="AC14">
+        <v>7.8</v>
+      </c>
+      <c r="AD14">
+        <v>12</v>
+      </c>
+      <c r="AE14">
+        <v>30</v>
+      </c>
+      <c r="AF14">
+        <v>20</v>
+      </c>
+      <c r="AG14">
+        <v>13</v>
+      </c>
+      <c r="AH14">
+        <v>17.5</v>
+      </c>
+      <c r="AI14">
+        <v>44</v>
+      </c>
+      <c r="AJ14">
+        <v>46</v>
+      </c>
+      <c r="AK14">
+        <v>34</v>
+      </c>
+      <c r="AL14">
+        <v>46</v>
+      </c>
+      <c r="AM14">
         <v>95</v>
       </c>
-      <c r="D13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" t="s">
-        <v>119</v>
-      </c>
-      <c r="F13">
-        <v>2.88</v>
-      </c>
-      <c r="G13">
-        <v>2.96</v>
-      </c>
-      <c r="H13">
-        <v>2.7</v>
-      </c>
-      <c r="I13">
-        <v>2.74</v>
-      </c>
-      <c r="J13">
+      <c r="AN14">
+        <v>29</v>
+      </c>
+      <c r="AO14">
+        <v>26</v>
+      </c>
+      <c r="AP14">
+        <v>12</v>
+      </c>
+      <c r="AQ14">
+        <v>10</v>
+      </c>
+      <c r="AR14">
+        <v>16</v>
+      </c>
+      <c r="AS14">
+        <v>36</v>
+      </c>
+      <c r="AT14">
+        <v>10.5</v>
+      </c>
+      <c r="AU14">
+        <v>7.2</v>
+      </c>
+      <c r="AV14">
+        <v>11</v>
+      </c>
+      <c r="AW14">
+        <v>27</v>
+      </c>
+      <c r="AX14">
+        <v>17.5</v>
+      </c>
+      <c r="AY14">
+        <v>11.5</v>
+      </c>
+      <c r="AZ14">
+        <v>16</v>
+      </c>
+      <c r="BA14">
+        <v>36</v>
+      </c>
+      <c r="BB14">
+        <v>42</v>
+      </c>
+      <c r="BC14">
+        <v>27</v>
+      </c>
+      <c r="BD14">
+        <v>38</v>
+      </c>
+      <c r="BE14">
+        <v>75</v>
+      </c>
+      <c r="BF14">
+        <v>25</v>
+      </c>
+      <c r="BG14">
+        <v>22</v>
+      </c>
+      <c r="BH14">
         <v>3.45</v>
       </c>
-      <c r="K13">
-        <v>3.5</v>
-      </c>
-      <c r="L13">
-        <v>1.41</v>
-      </c>
-      <c r="M13">
-        <v>1.08</v>
-      </c>
-      <c r="N13">
-        <v>3.65</v>
-      </c>
-      <c r="O13">
-        <v>1.35</v>
-      </c>
-      <c r="P13">
-        <v>1.91</v>
-      </c>
-      <c r="Q13">
-        <v>2.06</v>
-      </c>
-      <c r="R13">
-        <v>1.35</v>
-      </c>
-      <c r="S13">
-        <v>3.75</v>
-      </c>
-      <c r="T13">
-        <v>1.8</v>
-      </c>
-      <c r="U13">
+      <c r="BI14">
+        <v>2.76</v>
+      </c>
+      <c r="BJ14">
+        <v>10</v>
+      </c>
+      <c r="BK14">
+        <v>7.4</v>
+      </c>
+      <c r="BL14">
+        <v>130</v>
+      </c>
+      <c r="BM14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN14">
+        <v>6.2</v>
+      </c>
+      <c r="BO14">
+        <v>5.1</v>
+      </c>
+      <c r="BP14">
+        <v>24</v>
+      </c>
+      <c r="BQ14">
+        <v>7.2</v>
+      </c>
+      <c r="BR14">
+        <v>38</v>
+      </c>
+      <c r="BS14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT14">
+        <v>5.8</v>
+      </c>
+      <c r="BU14">
+        <v>4.8</v>
+      </c>
+      <c r="BV14">
+        <v>22</v>
+      </c>
+      <c r="BW14">
+        <v>7</v>
+      </c>
+      <c r="BX14">
+        <v>36</v>
+      </c>
+      <c r="BY14">
+        <v>8</v>
+      </c>
+      <c r="BZ14">
+        <v>30</v>
+      </c>
+      <c r="CA14">
+        <v>7.8</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15">
+        <v>1.32</v>
+      </c>
+      <c r="G15">
+        <v>1.48</v>
+      </c>
+      <c r="H15">
+        <v>6.4</v>
+      </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
+      <c r="J15">
+        <v>5.8</v>
+      </c>
+      <c r="K15">
+        <v>11.5</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.52</v>
+      </c>
+      <c r="O15">
+        <v>1.04</v>
+      </c>
+      <c r="P15">
+        <v>2.52</v>
+      </c>
+      <c r="Q15">
+        <v>1.04</v>
+      </c>
+      <c r="R15">
         <v>2.16</v>
       </c>
-      <c r="V13">
-        <v>1.57</v>
-      </c>
-      <c r="W13">
-        <v>1.51</v>
-      </c>
-      <c r="X13">
-        <v>13.5</v>
-      </c>
-      <c r="Y13">
-        <v>11</v>
-      </c>
-      <c r="Z13">
-        <v>18.5</v>
-      </c>
-      <c r="AA13">
-        <v>42</v>
-      </c>
-      <c r="AB13">
-        <v>11.5</v>
-      </c>
-      <c r="AC13">
-        <v>7.8</v>
-      </c>
-      <c r="AD13">
-        <v>12.5</v>
-      </c>
-      <c r="AE13">
-        <v>32</v>
-      </c>
-      <c r="AF13">
-        <v>19.5</v>
-      </c>
-      <c r="AG13">
-        <v>13</v>
-      </c>
-      <c r="AH13">
-        <v>17.5</v>
-      </c>
-      <c r="AI13">
-        <v>44</v>
-      </c>
-      <c r="AJ13">
-        <v>46</v>
-      </c>
-      <c r="AK13">
-        <v>34</v>
-      </c>
-      <c r="AL13">
-        <v>46</v>
-      </c>
-      <c r="AM13">
-        <v>95</v>
-      </c>
-      <c r="AN13">
-        <v>29</v>
-      </c>
-      <c r="AO13">
-        <v>26</v>
-      </c>
-      <c r="AP13">
-        <v>12</v>
-      </c>
-      <c r="AQ13">
-        <v>10</v>
-      </c>
-      <c r="AR13">
-        <v>15.5</v>
-      </c>
-      <c r="AS13">
-        <v>34</v>
-      </c>
-      <c r="AT13">
-        <v>10.5</v>
-      </c>
-      <c r="AU13">
-        <v>7</v>
-      </c>
-      <c r="AV13">
-        <v>11</v>
-      </c>
-      <c r="AW13">
-        <v>19.5</v>
-      </c>
-      <c r="AX13">
-        <v>16</v>
-      </c>
-      <c r="AY13">
-        <v>11.5</v>
-      </c>
-      <c r="AZ13">
-        <v>15.5</v>
-      </c>
-      <c r="BA13">
-        <v>30</v>
-      </c>
-      <c r="BB13">
-        <v>36</v>
-      </c>
-      <c r="BC13">
-        <v>21</v>
-      </c>
-      <c r="BD13">
-        <v>34</v>
-      </c>
-      <c r="BE13">
-        <v>36</v>
-      </c>
-      <c r="BF13">
-        <v>18.5</v>
-      </c>
-      <c r="BG13">
-        <v>21</v>
-      </c>
-      <c r="BH13">
-        <v>0</v>
-      </c>
-      <c r="BI13">
-        <v>0</v>
-      </c>
-      <c r="BJ13">
-        <v>0</v>
-      </c>
-      <c r="BK13">
-        <v>0</v>
-      </c>
-      <c r="BL13">
-        <v>0</v>
-      </c>
-      <c r="BM13">
-        <v>0</v>
-      </c>
-      <c r="BN13">
-        <v>0</v>
-      </c>
-      <c r="BO13">
-        <v>0</v>
-      </c>
-      <c r="BP13">
-        <v>0</v>
-      </c>
-      <c r="BQ13">
-        <v>0</v>
-      </c>
-      <c r="BR13">
-        <v>0</v>
-      </c>
-      <c r="BS13">
-        <v>0</v>
-      </c>
-      <c r="BT13">
-        <v>0</v>
-      </c>
-      <c r="BU13">
-        <v>0</v>
-      </c>
-      <c r="BV13">
-        <v>0</v>
-      </c>
-      <c r="BW13">
-        <v>0</v>
-      </c>
-      <c r="BX13">
-        <v>0</v>
-      </c>
-      <c r="BY13">
-        <v>0</v>
-      </c>
-      <c r="BZ13">
-        <v>0</v>
-      </c>
-      <c r="CA13">
-        <v>0</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>120</v>
+      <c r="S15">
+        <v>1.62</v>
+      </c>
+      <c r="T15">
+        <v>1.5</v>
+      </c>
+      <c r="U15">
+        <v>1.01</v>
+      </c>
+      <c r="V15">
+        <v>1.07</v>
+      </c>
+      <c r="W15">
+        <v>3.1</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15">
+        <v>1.03</v>
+      </c>
+      <c r="AR15">
+        <v>1.03</v>
+      </c>
+      <c r="AS15">
+        <v>1.03</v>
+      </c>
+      <c r="AT15">
+        <v>1.03</v>
+      </c>
+      <c r="AU15">
+        <v>1.03</v>
+      </c>
+      <c r="AV15">
+        <v>1.03</v>
+      </c>
+      <c r="AW15">
+        <v>1.03</v>
+      </c>
+      <c r="AX15">
+        <v>1.03</v>
+      </c>
+      <c r="AY15">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15">
+        <v>1.03</v>
+      </c>
+      <c r="BA15">
+        <v>1.03</v>
+      </c>
+      <c r="BB15">
+        <v>1.03</v>
+      </c>
+      <c r="BC15">
+        <v>1.03</v>
+      </c>
+      <c r="BD15">
+        <v>1.03</v>
+      </c>
+      <c r="BE15">
+        <v>1.03</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" t="s">
+        <v>129</v>
+      </c>
+      <c r="F16">
+        <v>1.04</v>
+      </c>
+      <c r="G16">
+        <v>1000</v>
+      </c>
+      <c r="H16">
+        <v>1.04</v>
+      </c>
+      <c r="I16">
+        <v>1000</v>
+      </c>
+      <c r="J16">
+        <v>1.04</v>
+      </c>
+      <c r="K16">
+        <v>950</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.24</v>
+      </c>
+      <c r="Q16">
+        <v>1.01</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="168">
   <si>
     <t>League</t>
   </si>
@@ -259,12 +259,18 @@
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
     <t>Colombian Primera B</t>
   </si>
   <si>
     <t>South Korean K1 League</t>
   </si>
   <si>
+    <t>Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Latvian Virsliga</t>
   </si>
   <si>
@@ -277,33 +283,57 @@
     <t>Swedish Superettan</t>
   </si>
   <si>
+    <t>South African Premier Division</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
     <t>2026-08-25</t>
   </si>
   <si>
     <t>00:00:00</t>
   </si>
   <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
     <t>00:45:00</t>
   </si>
   <si>
     <t>10:30:00</t>
   </si>
   <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
     <t>16:00:00</t>
   </si>
   <si>
+    <t>16:05:00</t>
+  </si>
+  <si>
     <t>16:10:00</t>
   </si>
   <si>
     <t>17:00:00</t>
   </si>
   <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
     <t>18:00:00</t>
   </si>
   <si>
@@ -316,9 +346,24 @@
     <t>20:30:00</t>
   </si>
   <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Libertad FC</t>
   </si>
   <si>
+    <t>Lanus</t>
+  </si>
+  <si>
+    <t>Talleres</t>
+  </si>
+  <si>
     <t>Internacional de Palmira</t>
   </si>
   <si>
@@ -331,19 +376,37 @@
     <t>FC Seoul</t>
   </si>
   <si>
+    <t>Tobol Kostanay</t>
+  </si>
+  <si>
     <t>FK Auda</t>
   </si>
   <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
+    <t>Abha</t>
+  </si>
+  <si>
     <t>Al-Taawoun Buraidah</t>
   </si>
   <si>
+    <t>Orebro</t>
+  </si>
+  <si>
     <t>Osters</t>
   </si>
   <si>
-    <t>Orebro</t>
+    <t>Siwelele FC</t>
+  </si>
+  <si>
+    <t>Orlando Pirates (SA)</t>
+  </si>
+  <si>
+    <t>Kruger United FC</t>
+  </si>
+  <si>
+    <t>Marumo Gallants FC</t>
   </si>
   <si>
     <t>Al-Ettifaq</t>
@@ -361,9 +424,27 @@
     <t>Boca Juniors de Cali</t>
   </si>
   <si>
+    <t>Club 2 de Mayo de Pedro Juan Cab</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Atletico GO</t>
+  </si>
+  <si>
+    <t>Atletico Bucaramanga</t>
+  </si>
+  <si>
     <t>Macara</t>
   </si>
   <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
     <t>Barranquilla</t>
   </si>
   <si>
@@ -376,19 +457,37 @@
     <t>Bucheon FC 1995</t>
   </si>
   <si>
+    <t>FK Kaisar</t>
+  </si>
+  <si>
     <t>Liepajas Metalurgs</t>
   </si>
   <si>
     <t>FC Metaloglobus Bucuresti</t>
   </si>
   <si>
+    <t>Al-Khaleej Saihat</t>
+  </si>
+  <si>
     <t>Al-Feiha</t>
   </si>
   <si>
+    <t>Varbergs BoIS</t>
+  </si>
+  <si>
     <t>Sundsvall</t>
   </si>
   <si>
-    <t>Varbergs BoIS</t>
+    <t>Chippa Utd</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>TS Galaxy FC</t>
   </si>
   <si>
     <t>Al Nassr</t>
@@ -406,7 +505,19 @@
     <t>Bogota</t>
   </si>
   <si>
-    <t>2026-08-23 17:36:55</t>
+    <t>Guarani (Par)</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Aguilas Doradas</t>
+  </si>
+  <si>
+    <t>2026-08-24 10:29:12</t>
   </si>
 </sst>
 </file>
@@ -738,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -988,241 +1099,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="F2">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H2">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I2">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P2">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="Q2">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AF2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG2">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI2">
+        <v>50</v>
+      </c>
+      <c r="AJ2">
+        <v>80</v>
+      </c>
+      <c r="AK2">
+        <v>48</v>
+      </c>
+      <c r="AL2">
         <v>60</v>
-      </c>
-      <c r="AJ2">
-        <v>75</v>
-      </c>
-      <c r="AK2">
-        <v>55</v>
-      </c>
-      <c r="AL2">
-        <v>70</v>
       </c>
       <c r="AM2">
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AP2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS2">
-        <v>4.5</v>
+        <v>26</v>
       </c>
       <c r="AT2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AU2">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="AX2">
+        <v>20</v>
+      </c>
+      <c r="AY2">
+        <v>12.5</v>
+      </c>
+      <c r="AZ2">
         <v>17</v>
       </c>
-      <c r="AY2">
-        <v>11</v>
-      </c>
-      <c r="AZ2">
-        <v>14.5</v>
-      </c>
       <c r="BA2">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="BB2">
-        <v>4.8</v>
+        <v>46</v>
       </c>
       <c r="BC2">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="BD2">
-        <v>4.7</v>
+        <v>44</v>
       </c>
       <c r="BE2">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>4.7</v>
+        <v>38</v>
       </c>
       <c r="BG2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BH2">
         <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO2">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BP2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BU2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1230,483 +1341,483 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="F3">
-        <v>1.36</v>
+        <v>2.8</v>
       </c>
       <c r="G3">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
-        <v>110</v>
+        <v>3.15</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="O3">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
-        <v>1.75</v>
+        <v>2.76</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>2.54</v>
+        <v>1.52</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP3">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR3">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS3">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="AT3">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU3">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="AX3">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY3">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA3">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BB3">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BC3">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BD3">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BE3">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="F4">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="G4">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="H4">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="I4">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="Q4">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="R4">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="S4">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BH4">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>1.33</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM4">
-        <v>1.33</v>
+        <v>7.6</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO4">
-        <v>1.33</v>
+        <v>4.8</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ4">
-        <v>1.33</v>
+        <v>6</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS4">
-        <v>1.33</v>
+        <v>6.6</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU4">
-        <v>1.33</v>
+        <v>4.5</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW4">
-        <v>1.33</v>
+        <v>6</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY4">
-        <v>1.33</v>
+        <v>6.6</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA4">
-        <v>1.33</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1714,483 +1825,483 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="F5">
-        <v>2.52</v>
+        <v>1.45</v>
       </c>
       <c r="G5">
-        <v>2.72</v>
+        <v>1.49</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>4.8</v>
+      </c>
+      <c r="K5">
+        <v>5.6</v>
+      </c>
+      <c r="L5">
+        <v>1.31</v>
+      </c>
+      <c r="M5">
+        <v>1.04</v>
+      </c>
+      <c r="N5">
+        <v>5.1</v>
+      </c>
+      <c r="O5">
+        <v>1.21</v>
+      </c>
+      <c r="P5">
+        <v>2.42</v>
+      </c>
+      <c r="Q5">
+        <v>1.64</v>
+      </c>
+      <c r="R5">
+        <v>1.58</v>
+      </c>
+      <c r="S5">
+        <v>2.56</v>
+      </c>
+      <c r="T5">
+        <v>1.84</v>
+      </c>
+      <c r="U5">
+        <v>1.98</v>
+      </c>
+      <c r="V5">
+        <v>1.12</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <v>950</v>
+      </c>
+      <c r="Y5">
+        <v>32</v>
+      </c>
+      <c r="Z5">
+        <v>75</v>
+      </c>
+      <c r="AA5">
+        <v>270</v>
+      </c>
+      <c r="AB5">
+        <v>10.5</v>
+      </c>
+      <c r="AC5">
+        <v>12.5</v>
+      </c>
+      <c r="AD5">
+        <v>32</v>
+      </c>
+      <c r="AE5">
+        <v>120</v>
+      </c>
+      <c r="AF5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG5">
+        <v>970</v>
+      </c>
+      <c r="AH5">
+        <v>25</v>
+      </c>
+      <c r="AI5">
+        <v>100</v>
+      </c>
+      <c r="AJ5">
+        <v>13</v>
+      </c>
+      <c r="AK5">
+        <v>15.5</v>
+      </c>
+      <c r="AL5">
+        <v>34</v>
+      </c>
+      <c r="AM5">
+        <v>120</v>
+      </c>
+      <c r="AN5">
+        <v>6</v>
+      </c>
+      <c r="AO5">
+        <v>140</v>
+      </c>
+      <c r="AP5">
+        <v>19.5</v>
+      </c>
+      <c r="AQ5">
+        <v>7.8</v>
+      </c>
+      <c r="AR5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS5">
+        <v>10</v>
+      </c>
+      <c r="AT5">
+        <v>8.6</v>
+      </c>
+      <c r="AU5">
+        <v>10</v>
+      </c>
+      <c r="AV5">
+        <v>7.8</v>
+      </c>
+      <c r="AW5">
+        <v>9.6</v>
+      </c>
+      <c r="AX5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5">
+        <v>20</v>
+      </c>
+      <c r="BA5">
+        <v>9.4</v>
+      </c>
+      <c r="BB5">
+        <v>10.5</v>
+      </c>
+      <c r="BC5">
+        <v>12</v>
+      </c>
+      <c r="BD5">
+        <v>26</v>
+      </c>
+      <c r="BE5">
+        <v>9.6</v>
+      </c>
+      <c r="BF5">
+        <v>5.1</v>
+      </c>
+      <c r="BG5">
+        <v>9.6</v>
+      </c>
+      <c r="BH5">
+        <v>4.4</v>
+      </c>
+      <c r="BI5">
+        <v>3.45</v>
+      </c>
+      <c r="BJ5">
+        <v>11</v>
+      </c>
+      <c r="BK5">
+        <v>5.7</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>10.5</v>
+      </c>
+      <c r="BN5">
+        <v>4.2</v>
+      </c>
+      <c r="BO5">
         <v>3.35</v>
       </c>
-      <c r="J5">
-        <v>3.2</v>
-      </c>
-      <c r="K5">
-        <v>3.35</v>
-      </c>
-      <c r="L5">
-        <v>1.46</v>
-      </c>
-      <c r="M5">
-        <v>1.11</v>
-      </c>
-      <c r="N5">
-        <v>2.88</v>
-      </c>
-      <c r="O5">
-        <v>1.46</v>
-      </c>
-      <c r="P5">
-        <v>1.64</v>
-      </c>
-      <c r="Q5">
-        <v>2.36</v>
-      </c>
-      <c r="R5">
-        <v>1.23</v>
-      </c>
-      <c r="S5">
-        <v>4.7</v>
-      </c>
-      <c r="T5">
-        <v>1.98</v>
-      </c>
-      <c r="U5">
-        <v>1.9</v>
-      </c>
-      <c r="V5">
-        <v>1.43</v>
-      </c>
-      <c r="W5">
-        <v>1.58</v>
-      </c>
-      <c r="X5">
-        <v>11.5</v>
-      </c>
-      <c r="Y5">
+      <c r="BP5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ5">
+        <v>5</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>7.6</v>
+      </c>
+      <c r="BT5">
         <v>12</v>
       </c>
-      <c r="Z5">
-        <v>24</v>
-      </c>
-      <c r="AA5">
-        <v>70</v>
-      </c>
-      <c r="AB5">
-        <v>8.6</v>
-      </c>
-      <c r="AC5">
-        <v>7.4</v>
-      </c>
-      <c r="AD5">
-        <v>16.5</v>
-      </c>
-      <c r="AE5">
-        <v>55</v>
-      </c>
-      <c r="AF5">
-        <v>18.5</v>
-      </c>
-      <c r="AG5">
-        <v>14.5</v>
-      </c>
-      <c r="AH5">
-        <v>24</v>
-      </c>
-      <c r="AI5">
-        <v>75</v>
-      </c>
-      <c r="AJ5">
-        <v>48</v>
-      </c>
-      <c r="AK5">
-        <v>36</v>
-      </c>
-      <c r="AL5">
-        <v>65</v>
-      </c>
-      <c r="AM5">
-        <v>170</v>
-      </c>
-      <c r="AN5">
-        <v>38</v>
-      </c>
-      <c r="AO5">
-        <v>65</v>
-      </c>
-      <c r="AP5">
-        <v>9</v>
-      </c>
-      <c r="AQ5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR5">
-        <v>17.5</v>
-      </c>
-      <c r="AS5">
+      <c r="BU5">
         <v>5.9</v>
       </c>
-      <c r="AT5">
-        <v>7.8</v>
-      </c>
-      <c r="AU5">
-        <v>6.6</v>
-      </c>
-      <c r="AV5">
-        <v>12</v>
-      </c>
-      <c r="AW5">
-        <v>5.8</v>
-      </c>
-      <c r="AX5">
-        <v>13.5</v>
-      </c>
-      <c r="AY5">
-        <v>10.5</v>
-      </c>
-      <c r="AZ5">
-        <v>17</v>
-      </c>
-      <c r="BA5">
-        <v>6</v>
-      </c>
-      <c r="BB5">
-        <v>5.7</v>
-      </c>
-      <c r="BC5">
-        <v>5.5</v>
-      </c>
-      <c r="BD5">
-        <v>5.9</v>
-      </c>
-      <c r="BE5">
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>10</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ5">
+        <v>13</v>
+      </c>
+      <c r="CA5">
         <v>6.2</v>
       </c>
-      <c r="BF5">
-        <v>5.5</v>
-      </c>
-      <c r="BG5">
-        <v>5.9</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.01</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.01</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.01</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.01</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.01</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.01</v>
-      </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
-        <v>1.01</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>1.01</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>1.01</v>
-      </c>
-      <c r="BZ5">
-        <v>1000</v>
-      </c>
-      <c r="CA5">
-        <v>1.01</v>
-      </c>
       <c r="CB5" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="F6">
-        <v>1.56</v>
+        <v>3.55</v>
       </c>
       <c r="G6">
-        <v>1.64</v>
+        <v>3.7</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>2.22</v>
       </c>
       <c r="I6">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K6">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M6">
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O6">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q6">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="R6">
+        <v>1.35</v>
+      </c>
+      <c r="S6">
+        <v>3.6</v>
+      </c>
+      <c r="T6">
+        <v>1.82</v>
+      </c>
+      <c r="U6">
+        <v>2.12</v>
+      </c>
+      <c r="V6">
+        <v>1.76</v>
+      </c>
+      <c r="W6">
         <v>1.37</v>
       </c>
-      <c r="S6">
-        <v>3.4</v>
-      </c>
-      <c r="T6">
-        <v>2</v>
-      </c>
-      <c r="U6">
-        <v>1.89</v>
-      </c>
-      <c r="V6">
-        <v>1.15</v>
-      </c>
-      <c r="W6">
-        <v>2.56</v>
-      </c>
       <c r="X6">
+        <v>16</v>
+      </c>
+      <c r="Y6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z6">
+        <v>16.5</v>
+      </c>
+      <c r="AA6">
+        <v>34</v>
+      </c>
+      <c r="AB6">
+        <v>15.5</v>
+      </c>
+      <c r="AC6">
+        <v>8</v>
+      </c>
+      <c r="AD6">
+        <v>11.5</v>
+      </c>
+      <c r="AE6">
+        <v>29</v>
+      </c>
+      <c r="AF6">
+        <v>30</v>
+      </c>
+      <c r="AG6">
         <v>17.5</v>
       </c>
-      <c r="Y6">
+      <c r="AH6">
+        <v>19</v>
+      </c>
+      <c r="AI6">
+        <v>46</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>55</v>
+      </c>
+      <c r="AL6">
+        <v>55</v>
+      </c>
+      <c r="AM6">
+        <v>120</v>
+      </c>
+      <c r="AN6">
+        <v>55</v>
+      </c>
+      <c r="AO6">
+        <v>20</v>
+      </c>
+      <c r="AP6">
+        <v>12.5</v>
+      </c>
+      <c r="AQ6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR6">
+        <v>12.5</v>
+      </c>
+      <c r="AS6">
+        <v>19</v>
+      </c>
+      <c r="AT6">
+        <v>11.5</v>
+      </c>
+      <c r="AU6">
+        <v>7.2</v>
+      </c>
+      <c r="AV6">
+        <v>10</v>
+      </c>
+      <c r="AW6">
+        <v>21</v>
+      </c>
+      <c r="AX6">
+        <v>21</v>
+      </c>
+      <c r="AY6">
+        <v>13.5</v>
+      </c>
+      <c r="AZ6">
+        <v>16</v>
+      </c>
+      <c r="BA6">
+        <v>28</v>
+      </c>
+      <c r="BB6">
+        <v>32</v>
+      </c>
+      <c r="BC6">
+        <v>32</v>
+      </c>
+      <c r="BD6">
+        <v>29</v>
+      </c>
+      <c r="BE6">
+        <v>38</v>
+      </c>
+      <c r="BF6">
         <v>25</v>
       </c>
-      <c r="Z6">
-        <v>70</v>
-      </c>
-      <c r="AA6">
-        <v>260</v>
-      </c>
-      <c r="AB6">
-        <v>8</v>
-      </c>
-      <c r="AC6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD6">
+      <c r="BG6">
+        <v>16</v>
+      </c>
+      <c r="BH6">
+        <v>3.35</v>
+      </c>
+      <c r="BI6">
+        <v>3.05</v>
+      </c>
+      <c r="BJ6">
+        <v>9.6</v>
+      </c>
+      <c r="BK6">
+        <v>6</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>15</v>
+      </c>
+      <c r="BN6">
+        <v>6.8</v>
+      </c>
+      <c r="BO6">
+        <v>5.3</v>
+      </c>
+      <c r="BP6">
+        <v>29</v>
+      </c>
+      <c r="BQ6">
+        <v>10.5</v>
+      </c>
+      <c r="BR6">
+        <v>40</v>
+      </c>
+      <c r="BS6">
+        <v>12</v>
+      </c>
+      <c r="BT6">
+        <v>5.1</v>
+      </c>
+      <c r="BU6">
+        <v>4</v>
+      </c>
+      <c r="BV6">
+        <v>16.5</v>
+      </c>
+      <c r="BW6">
+        <v>8.4</v>
+      </c>
+      <c r="BX6">
         <v>32</v>
       </c>
-      <c r="AE6">
-        <v>130</v>
-      </c>
-      <c r="AF6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG6">
+      <c r="BY6">
+        <v>11</v>
+      </c>
+      <c r="BZ6">
+        <v>27</v>
+      </c>
+      <c r="CA6">
         <v>10.5</v>
       </c>
-      <c r="AH6">
-        <v>28</v>
-      </c>
-      <c r="AI6">
-        <v>120</v>
-      </c>
-      <c r="AJ6">
-        <v>17.5</v>
-      </c>
-      <c r="AK6">
-        <v>19.5</v>
-      </c>
-      <c r="AL6">
-        <v>46</v>
-      </c>
-      <c r="AM6">
-        <v>170</v>
-      </c>
-      <c r="AN6">
-        <v>9.6</v>
-      </c>
-      <c r="AO6">
-        <v>180</v>
-      </c>
-      <c r="AP6">
-        <v>13</v>
-      </c>
-      <c r="AQ6">
-        <v>17</v>
-      </c>
-      <c r="AR6">
-        <v>7</v>
-      </c>
-      <c r="AS6">
-        <v>7.6</v>
-      </c>
-      <c r="AT6">
-        <v>6.8</v>
-      </c>
-      <c r="AU6">
-        <v>8.6</v>
-      </c>
-      <c r="AV6">
-        <v>20</v>
-      </c>
-      <c r="AW6">
-        <v>7.4</v>
-      </c>
-      <c r="AX6">
-        <v>8</v>
-      </c>
-      <c r="AY6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6">
-        <v>18</v>
-      </c>
-      <c r="BA6">
-        <v>7.4</v>
-      </c>
-      <c r="BB6">
-        <v>12.5</v>
-      </c>
-      <c r="BC6">
-        <v>13.5</v>
-      </c>
-      <c r="BD6">
-        <v>6.8</v>
-      </c>
-      <c r="BE6">
-        <v>7.6</v>
-      </c>
-      <c r="BF6">
-        <v>8.4</v>
-      </c>
-      <c r="BG6">
-        <v>7.6</v>
-      </c>
-      <c r="BH6">
-        <v>4.2</v>
-      </c>
-      <c r="BI6">
-        <v>2.74</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>1.32</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.32</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>1.32</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>1.32</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>1.32</v>
-      </c>
-      <c r="BT6">
-        <v>1000</v>
-      </c>
-      <c r="BU6">
-        <v>1.32</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>1.32</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>1.32</v>
-      </c>
-      <c r="BZ6">
-        <v>1000</v>
-      </c>
-      <c r="CA6">
-        <v>1.32</v>
-      </c>
       <c r="CB6" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2198,518 +2309,518 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="F7">
-        <v>1.05</v>
+        <v>2.5</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="H7">
-        <v>1.05</v>
+        <v>3.2</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J7">
-        <v>1.08</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N7">
+        <v>2.94</v>
+      </c>
+      <c r="O7">
+        <v>1.48</v>
+      </c>
+      <c r="P7">
+        <v>1.66</v>
+      </c>
+      <c r="Q7">
+        <v>2.44</v>
+      </c>
+      <c r="R7">
         <v>1.25</v>
       </c>
-      <c r="O7">
-        <v>1.19</v>
-      </c>
-      <c r="P7">
-        <v>1.25</v>
-      </c>
-      <c r="Q7">
-        <v>1.19</v>
-      </c>
-      <c r="R7">
-        <v>1.18</v>
-      </c>
       <c r="S7">
-        <v>1.19</v>
+        <v>4.8</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM7">
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="F8">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="G8">
-        <v>990</v>
+        <v>1.62</v>
       </c>
       <c r="H8">
-        <v>1.08</v>
+        <v>6.4</v>
       </c>
       <c r="I8">
-        <v>990</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.37</v>
+        <v>1.88</v>
       </c>
       <c r="R8">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>1.37</v>
+        <v>3.25</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>2.6</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB8" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>1.71</v>
+        <v>990</v>
       </c>
       <c r="H9">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>9.800000000000001</v>
+        <v>990</v>
       </c>
       <c r="J9">
-        <v>3.85</v>
+        <v>1.06</v>
       </c>
       <c r="K9">
-        <v>6.6</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2718,22 +2829,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="P9">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q9">
-        <v>1.81</v>
+        <v>1.17</v>
       </c>
       <c r="R9">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2742,10 +2853,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2859,297 +2970,297 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="F10">
-        <v>1.81</v>
+        <v>1.13</v>
       </c>
       <c r="G10">
-        <v>1.91</v>
+        <v>990</v>
       </c>
       <c r="H10">
-        <v>4.2</v>
+        <v>1.12</v>
       </c>
       <c r="I10">
-        <v>4.8</v>
+        <v>990</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>1.24</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.26</v>
+      </c>
+      <c r="O10">
+        <v>1.2</v>
+      </c>
+      <c r="P10">
+        <v>1.25</v>
+      </c>
+      <c r="Q10">
+        <v>1.19</v>
+      </c>
+      <c r="R10">
+        <v>1.18</v>
+      </c>
+      <c r="S10">
+        <v>1.2</v>
+      </c>
+      <c r="T10">
+        <v>1.11</v>
+      </c>
+      <c r="U10">
+        <v>1.11</v>
+      </c>
+      <c r="V10">
+        <v>1.11</v>
+      </c>
+      <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10">
+        <v>1.01</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>1.01</v>
+      </c>
+      <c r="AU10">
+        <v>1.01</v>
+      </c>
+      <c r="AV10">
+        <v>1.01</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>1.01</v>
+      </c>
+      <c r="AY10">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10">
+        <v>1.01</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
         <v>1.04</v>
       </c>
-      <c r="N10">
-        <v>5</v>
-      </c>
-      <c r="O10">
-        <v>1.21</v>
-      </c>
-      <c r="P10">
-        <v>2.36</v>
-      </c>
-      <c r="Q10">
-        <v>1.63</v>
-      </c>
-      <c r="R10">
-        <v>1.54</v>
-      </c>
-      <c r="S10">
-        <v>2.56</v>
-      </c>
-      <c r="T10">
-        <v>1.64</v>
-      </c>
-      <c r="U10">
-        <v>2.34</v>
-      </c>
-      <c r="V10">
-        <v>1.27</v>
-      </c>
-      <c r="W10">
-        <v>2.1</v>
-      </c>
-      <c r="X10">
-        <v>26</v>
-      </c>
-      <c r="Y10">
-        <v>24</v>
-      </c>
-      <c r="Z10">
-        <v>38</v>
-      </c>
-      <c r="AA10">
-        <v>110</v>
-      </c>
-      <c r="AB10">
-        <v>13.5</v>
-      </c>
-      <c r="AC10">
-        <v>11.5</v>
-      </c>
-      <c r="AD10">
-        <v>18.5</v>
-      </c>
-      <c r="AE10">
-        <v>60</v>
-      </c>
-      <c r="AF10">
-        <v>15</v>
-      </c>
-      <c r="AG10">
-        <v>12</v>
-      </c>
-      <c r="AH10">
-        <v>19.5</v>
-      </c>
-      <c r="AI10">
-        <v>60</v>
-      </c>
-      <c r="AJ10">
-        <v>23</v>
-      </c>
-      <c r="AK10">
-        <v>18</v>
-      </c>
-      <c r="AL10">
-        <v>36</v>
-      </c>
-      <c r="AM10">
-        <v>70</v>
-      </c>
-      <c r="AN10">
-        <v>9</v>
-      </c>
-      <c r="AO10">
-        <v>48</v>
-      </c>
-      <c r="AP10">
-        <v>16.5</v>
-      </c>
-      <c r="AQ10">
-        <v>16</v>
-      </c>
-      <c r="AR10">
-        <v>1.01</v>
-      </c>
-      <c r="AS10">
-        <v>1.01</v>
-      </c>
-      <c r="AT10">
-        <v>10</v>
-      </c>
-      <c r="AU10">
-        <v>8.6</v>
-      </c>
-      <c r="AV10">
-        <v>14</v>
-      </c>
-      <c r="AW10">
-        <v>1.01</v>
-      </c>
-      <c r="AX10">
-        <v>10</v>
-      </c>
-      <c r="AY10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ10">
-        <v>12.5</v>
-      </c>
-      <c r="BA10">
-        <v>34</v>
-      </c>
-      <c r="BB10">
-        <v>15.5</v>
-      </c>
-      <c r="BC10">
-        <v>13.5</v>
-      </c>
-      <c r="BD10">
-        <v>1.03</v>
-      </c>
-      <c r="BE10">
-        <v>1.01</v>
-      </c>
-      <c r="BF10">
-        <v>6.8</v>
-      </c>
-      <c r="BG10">
-        <v>1.01</v>
-      </c>
-      <c r="BH10">
-        <v>5.5</v>
-      </c>
-      <c r="BI10">
-        <v>2.94</v>
-      </c>
       <c r="BJ10">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3158,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3166,850 +3277,850 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="F11">
-        <v>2.76</v>
+        <v>1.12</v>
       </c>
       <c r="G11">
-        <v>3.1</v>
+        <v>990</v>
       </c>
       <c r="H11">
-        <v>2.52</v>
+        <v>1.12</v>
       </c>
       <c r="I11">
-        <v>2.86</v>
+        <v>990</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>1.27</v>
       </c>
       <c r="K11">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>1.98</v>
+        <v>1.41</v>
       </c>
       <c r="Q11">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="R11">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="S11">
-        <v>3.1</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="W11">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
         <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F12">
+        <v>2.96</v>
+      </c>
+      <c r="G12">
+        <v>3.45</v>
+      </c>
+      <c r="H12">
+        <v>2.3</v>
+      </c>
+      <c r="I12">
+        <v>2.6</v>
+      </c>
+      <c r="J12">
+        <v>3.4</v>
+      </c>
+      <c r="K12">
+        <v>3.8</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.06</v>
+      </c>
+      <c r="N12">
+        <v>3.7</v>
+      </c>
+      <c r="O12">
+        <v>1.29</v>
+      </c>
+      <c r="P12">
+        <v>1.96</v>
+      </c>
+      <c r="Q12">
+        <v>1.85</v>
+      </c>
+      <c r="R12">
+        <v>1.37</v>
+      </c>
+      <c r="S12">
+        <v>3.15</v>
+      </c>
+      <c r="T12">
+        <v>1.69</v>
+      </c>
+      <c r="U12">
+        <v>2.18</v>
+      </c>
+      <c r="V12">
+        <v>1.62</v>
+      </c>
+      <c r="W12">
+        <v>1.41</v>
+      </c>
+      <c r="X12">
+        <v>16.5</v>
+      </c>
+      <c r="Y12">
+        <v>13</v>
+      </c>
+      <c r="Z12">
+        <v>19</v>
+      </c>
+      <c r="AA12">
+        <v>38</v>
+      </c>
+      <c r="AB12">
+        <v>14</v>
+      </c>
+      <c r="AC12">
         <v>8.800000000000001</v>
       </c>
-      <c r="G12">
-        <v>12.5</v>
-      </c>
-      <c r="H12">
-        <v>1.31</v>
-      </c>
-      <c r="I12">
-        <v>1.37</v>
-      </c>
-      <c r="J12">
-        <v>6.2</v>
-      </c>
-      <c r="K12">
-        <v>7.2</v>
-      </c>
-      <c r="L12">
-        <v>1.15</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>8.4</v>
-      </c>
-      <c r="O12">
-        <v>1.11</v>
-      </c>
-      <c r="P12">
-        <v>3.45</v>
-      </c>
-      <c r="Q12">
-        <v>1.34</v>
-      </c>
-      <c r="R12">
-        <v>2.02</v>
-      </c>
-      <c r="S12">
-        <v>1.85</v>
-      </c>
-      <c r="T12">
-        <v>1.67</v>
-      </c>
-      <c r="U12">
-        <v>2.28</v>
-      </c>
-      <c r="V12">
-        <v>3.7</v>
-      </c>
-      <c r="W12">
-        <v>1.1</v>
-      </c>
-      <c r="X12">
+      <c r="AD12">
+        <v>13.5</v>
+      </c>
+      <c r="AE12">
+        <v>30</v>
+      </c>
+      <c r="AF12">
+        <v>26</v>
+      </c>
+      <c r="AG12">
+        <v>16</v>
+      </c>
+      <c r="AH12">
+        <v>17.5</v>
+      </c>
+      <c r="AI12">
+        <v>42</v>
+      </c>
+      <c r="AJ12">
         <v>60</v>
       </c>
-      <c r="Y12">
-        <v>19.5</v>
-      </c>
-      <c r="Z12">
-        <v>15</v>
-      </c>
-      <c r="AA12">
-        <v>15.5</v>
-      </c>
-      <c r="AB12">
-        <v>60</v>
-      </c>
-      <c r="AC12">
-        <v>21</v>
-      </c>
-      <c r="AD12">
-        <v>14.5</v>
-      </c>
-      <c r="AE12">
-        <v>16.5</v>
-      </c>
-      <c r="AF12">
-        <v>120</v>
-      </c>
-      <c r="AG12">
-        <v>44</v>
-      </c>
-      <c r="AH12">
-        <v>28</v>
-      </c>
-      <c r="AI12">
-        <v>32</v>
-      </c>
-      <c r="AJ12">
-        <v>310</v>
-      </c>
       <c r="AK12">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AL12">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AM12">
         <v>95</v>
       </c>
       <c r="AN12">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AO12">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AP12">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="AQ12">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR12">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AS12">
+        <v>5.4</v>
+      </c>
+      <c r="AT12">
         <v>11</v>
       </c>
-      <c r="AT12">
-        <v>4.3</v>
-      </c>
       <c r="AU12">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="AV12">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX12">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AY12">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AZ12">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="BA12">
-        <v>18.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB12">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC12">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BD12">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE12">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF12">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="BG12">
-        <v>3.1</v>
+        <v>14.5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.94</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="F13">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G13">
+        <v>1.89</v>
+      </c>
+      <c r="H13">
+        <v>4.6</v>
+      </c>
+      <c r="I13">
+        <v>5.5</v>
+      </c>
+      <c r="J13">
+        <v>3.8</v>
+      </c>
+      <c r="K13">
+        <v>4.2</v>
+      </c>
+      <c r="L13">
+        <v>1.32</v>
+      </c>
+      <c r="M13">
+        <v>1.06</v>
+      </c>
+      <c r="N13">
+        <v>3.7</v>
+      </c>
+      <c r="O13">
+        <v>1.3</v>
+      </c>
+      <c r="P13">
         <v>1.93</v>
       </c>
-      <c r="H13">
-        <v>4.2</v>
-      </c>
-      <c r="I13">
-        <v>5</v>
-      </c>
-      <c r="J13">
-        <v>3.9</v>
-      </c>
-      <c r="K13">
-        <v>4.6</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.04</v>
-      </c>
-      <c r="N13">
-        <v>4.7</v>
-      </c>
-      <c r="O13">
-        <v>1.21</v>
-      </c>
-      <c r="P13">
-        <v>2.32</v>
-      </c>
       <c r="Q13">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="R13">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="S13">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="T13">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="U13">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="V13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X13">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Y13">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Z13">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA13">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AB13">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AC13">
+        <v>10</v>
+      </c>
+      <c r="AD13">
+        <v>27</v>
+      </c>
+      <c r="AE13">
+        <v>80</v>
+      </c>
+      <c r="AF13">
         <v>11.5</v>
-      </c>
-      <c r="AD13">
-        <v>19</v>
-      </c>
-      <c r="AE13">
-        <v>60</v>
-      </c>
-      <c r="AF13">
-        <v>14</v>
       </c>
       <c r="AG13">
         <v>12</v>
       </c>
       <c r="AH13">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AI13">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AJ13">
         <v>24</v>
       </c>
       <c r="AK13">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AL13">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM13">
+        <v>130</v>
+      </c>
+      <c r="AN13">
+        <v>14</v>
+      </c>
+      <c r="AO13">
         <v>90</v>
       </c>
-      <c r="AN13">
-        <v>9.4</v>
-      </c>
-      <c r="AO13">
-        <v>50</v>
-      </c>
       <c r="AP13">
+        <v>13</v>
+      </c>
+      <c r="AQ13">
+        <v>15</v>
+      </c>
+      <c r="AR13">
+        <v>5.7</v>
+      </c>
+      <c r="AS13">
+        <v>6.2</v>
+      </c>
+      <c r="AT13">
+        <v>7.4</v>
+      </c>
+      <c r="AU13">
+        <v>7.8</v>
+      </c>
+      <c r="AV13">
         <v>16.5</v>
       </c>
-      <c r="AQ13">
-        <v>17</v>
-      </c>
-      <c r="AR13">
-        <v>27</v>
-      </c>
-      <c r="AS13">
+      <c r="AW13">
         <v>6</v>
       </c>
-      <c r="AT13">
+      <c r="AX13">
+        <v>8.6</v>
+      </c>
+      <c r="AY13">
+        <v>8.4</v>
+      </c>
+      <c r="AZ13">
+        <v>16.5</v>
+      </c>
+      <c r="BA13">
+        <v>6</v>
+      </c>
+      <c r="BB13">
+        <v>13.5</v>
+      </c>
+      <c r="BC13">
+        <v>14.5</v>
+      </c>
+      <c r="BD13">
+        <v>5.6</v>
+      </c>
+      <c r="BE13">
+        <v>6.2</v>
+      </c>
+      <c r="BF13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG13">
+        <v>6</v>
+      </c>
+      <c r="BH13">
+        <v>3.6</v>
+      </c>
+      <c r="BI13">
+        <v>3.1</v>
+      </c>
+      <c r="BJ13">
+        <v>10.5</v>
+      </c>
+      <c r="BK13">
+        <v>5.4</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>10.5</v>
+      </c>
+      <c r="BN13">
+        <v>4.6</v>
+      </c>
+      <c r="BO13">
+        <v>3.45</v>
+      </c>
+      <c r="BP13">
+        <v>13</v>
+      </c>
+      <c r="BQ13">
+        <v>6</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>8</v>
+      </c>
+      <c r="BT13">
+        <v>8.6</v>
+      </c>
+      <c r="BU13">
+        <v>4.9</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
         <v>9</v>
       </c>
-      <c r="AU13">
-        <v>8.4</v>
-      </c>
-      <c r="AV13">
-        <v>14</v>
-      </c>
-      <c r="AW13">
-        <v>38</v>
-      </c>
-      <c r="AX13">
-        <v>11</v>
-      </c>
-      <c r="AY13">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ13">
-        <v>13</v>
-      </c>
-      <c r="BA13">
-        <v>36</v>
-      </c>
-      <c r="BB13">
-        <v>17</v>
-      </c>
-      <c r="BC13">
-        <v>13.5</v>
-      </c>
-      <c r="BD13">
-        <v>21</v>
-      </c>
-      <c r="BE13">
-        <v>5.8</v>
-      </c>
-      <c r="BF13">
-        <v>7</v>
-      </c>
-      <c r="BG13">
-        <v>5.6</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
-        <v>1.01</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>1.01</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.01</v>
-      </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
-        <v>1.01</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>1.01</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.01</v>
-      </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
-        <v>1.01</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>1.01</v>
-      </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB13" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="F14">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="G14">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="I14">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J14">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K14">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="L14">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="M14">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="O14">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="P14">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S14">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="T14">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="U14">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Y14">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z14">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AA14">
         <v>40</v>
       </c>
       <c r="AB14">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC14">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE14">
         <v>30</v>
       </c>
       <c r="AF14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH14">
         <v>17.5</v>
       </c>
       <c r="AI14">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ14">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AK14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL14">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AP14">
         <v>12</v>
@@ -4018,115 +4129,115 @@
         <v>10</v>
       </c>
       <c r="AR14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS14">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AT14">
         <v>10.5</v>
       </c>
       <c r="AU14">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV14">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AW14">
+        <v>21</v>
+      </c>
+      <c r="AX14">
+        <v>17</v>
+      </c>
+      <c r="AY14">
+        <v>10</v>
+      </c>
+      <c r="AZ14">
+        <v>12.5</v>
+      </c>
+      <c r="BA14">
+        <v>24</v>
+      </c>
+      <c r="BB14">
         <v>27</v>
       </c>
-      <c r="AX14">
-        <v>17.5</v>
-      </c>
-      <c r="AY14">
-        <v>11.5</v>
-      </c>
-      <c r="AZ14">
-        <v>16</v>
-      </c>
-      <c r="BA14">
-        <v>36</v>
-      </c>
-      <c r="BB14">
-        <v>42</v>
-      </c>
       <c r="BC14">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="BD14">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BE14">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="BF14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BG14">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BH14">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BI14">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BJ14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK14">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BL14">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BM14">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BN14">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO14">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BQ14">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BR14">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BS14">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BT14">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BU14">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BV14">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BW14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BX14">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BY14">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BZ14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4134,232 +4245,232 @@
         <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="F15">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="G15">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="H15">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="I15">
+        <v>4.9</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15">
+        <v>4.5</v>
+      </c>
+      <c r="L15">
+        <v>1.26</v>
+      </c>
+      <c r="M15">
+        <v>1.04</v>
+      </c>
+      <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15">
+        <v>1.21</v>
+      </c>
+      <c r="P15">
+        <v>2.4</v>
+      </c>
+      <c r="Q15">
+        <v>1.62</v>
+      </c>
+      <c r="R15">
+        <v>1.57</v>
+      </c>
+      <c r="S15">
+        <v>2.52</v>
+      </c>
+      <c r="T15">
+        <v>1.63</v>
+      </c>
+      <c r="U15">
+        <v>2.38</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>25</v>
+      </c>
+      <c r="Y15">
+        <v>24</v>
+      </c>
+      <c r="Z15">
+        <v>38</v>
+      </c>
+      <c r="AA15">
+        <v>110</v>
+      </c>
+      <c r="AB15">
+        <v>13.5</v>
+      </c>
+      <c r="AC15">
+        <v>10</v>
+      </c>
+      <c r="AD15">
+        <v>22</v>
+      </c>
+      <c r="AE15">
+        <v>60</v>
+      </c>
+      <c r="AF15">
+        <v>15</v>
+      </c>
+      <c r="AG15">
+        <v>11</v>
+      </c>
+      <c r="AH15">
+        <v>19</v>
+      </c>
+      <c r="AI15">
+        <v>55</v>
+      </c>
+      <c r="AJ15">
+        <v>21</v>
+      </c>
+      <c r="AK15">
+        <v>17.5</v>
+      </c>
+      <c r="AL15">
+        <v>28</v>
+      </c>
+      <c r="AM15">
+        <v>70</v>
+      </c>
+      <c r="AN15">
+        <v>8.6</v>
+      </c>
+      <c r="AO15">
+        <v>46</v>
+      </c>
+      <c r="AP15">
+        <v>19</v>
+      </c>
+      <c r="AQ15">
+        <v>18.5</v>
+      </c>
+      <c r="AR15">
+        <v>6.6</v>
+      </c>
+      <c r="AS15">
+        <v>7.4</v>
+      </c>
+      <c r="AT15">
+        <v>10</v>
+      </c>
+      <c r="AU15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV15">
         <v>14</v>
       </c>
-      <c r="J15">
-        <v>5.8</v>
-      </c>
-      <c r="K15">
+      <c r="AW15">
+        <v>7</v>
+      </c>
+      <c r="AX15">
         <v>11.5</v>
       </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.01</v>
-      </c>
-      <c r="N15">
-        <v>2.52</v>
-      </c>
-      <c r="O15">
-        <v>1.04</v>
-      </c>
-      <c r="P15">
-        <v>2.52</v>
-      </c>
-      <c r="Q15">
-        <v>1.04</v>
-      </c>
-      <c r="R15">
-        <v>2.16</v>
-      </c>
-      <c r="S15">
-        <v>1.62</v>
-      </c>
-      <c r="T15">
-        <v>1.5</v>
-      </c>
-      <c r="U15">
-        <v>1.01</v>
-      </c>
-      <c r="V15">
-        <v>1.07</v>
-      </c>
-      <c r="W15">
-        <v>3.1</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>1000</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>1000</v>
-      </c>
-      <c r="AC15">
-        <v>1000</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.03</v>
-      </c>
-      <c r="AQ15">
-        <v>1.03</v>
-      </c>
-      <c r="AR15">
-        <v>1.03</v>
-      </c>
-      <c r="AS15">
-        <v>1.03</v>
-      </c>
-      <c r="AT15">
-        <v>1.03</v>
-      </c>
-      <c r="AU15">
-        <v>1.03</v>
-      </c>
-      <c r="AV15">
-        <v>1.03</v>
-      </c>
-      <c r="AW15">
-        <v>1.03</v>
-      </c>
-      <c r="AX15">
-        <v>1.03</v>
-      </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4368,249 +4479,3153 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" t="s">
+        <v>154</v>
+      </c>
+      <c r="F16">
+        <v>1.76</v>
+      </c>
+      <c r="G16">
+        <v>2.2</v>
+      </c>
+      <c r="H16">
+        <v>4.2</v>
+      </c>
+      <c r="I16">
+        <v>7.4</v>
+      </c>
+      <c r="J16">
+        <v>2.84</v>
+      </c>
+      <c r="K16">
+        <v>3.6</v>
+      </c>
+      <c r="L16">
+        <v>1.44</v>
+      </c>
+      <c r="M16">
+        <v>1.06</v>
+      </c>
+      <c r="N16">
+        <v>2.14</v>
+      </c>
+      <c r="O16">
+        <v>1.22</v>
+      </c>
+      <c r="P16">
+        <v>1.43</v>
+      </c>
+      <c r="Q16">
+        <v>2.18</v>
+      </c>
+      <c r="R16">
+        <v>1.13</v>
+      </c>
+      <c r="S16">
+        <v>2.6</v>
+      </c>
+      <c r="T16">
+        <v>1.11</v>
+      </c>
+      <c r="U16">
+        <v>1.11</v>
+      </c>
+      <c r="V16">
+        <v>1.15</v>
+      </c>
+      <c r="W16">
+        <v>1.84</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>1000</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16">
+        <v>1.01</v>
+      </c>
+      <c r="AR16">
+        <v>1.01</v>
+      </c>
+      <c r="AS16">
+        <v>1.01</v>
+      </c>
+      <c r="AT16">
+        <v>1.01</v>
+      </c>
+      <c r="AU16">
+        <v>1.01</v>
+      </c>
+      <c r="AV16">
+        <v>1.01</v>
+      </c>
+      <c r="AW16">
+        <v>1.01</v>
+      </c>
+      <c r="AX16">
+        <v>1.01</v>
+      </c>
+      <c r="AY16">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16">
+        <v>1.01</v>
+      </c>
+      <c r="BA16">
+        <v>1.01</v>
+      </c>
+      <c r="BB16">
+        <v>1.01</v>
+      </c>
+      <c r="BC16">
+        <v>1.01</v>
+      </c>
+      <c r="BD16">
+        <v>1.01</v>
+      </c>
+      <c r="BE16">
+        <v>1.01</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.04</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.04</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.04</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.04</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.04</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.04</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.04</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.04</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.04</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.04</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
         <v>89</v>
       </c>
-      <c r="C16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17">
+        <v>1.34</v>
+      </c>
+      <c r="G17">
+        <v>1.42</v>
+      </c>
+      <c r="H17">
+        <v>8.6</v>
+      </c>
+      <c r="I17">
+        <v>19</v>
+      </c>
+      <c r="J17">
+        <v>4.2</v>
+      </c>
+      <c r="K17">
+        <v>5.2</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.08</v>
+      </c>
+      <c r="N17">
+        <v>2.72</v>
+      </c>
+      <c r="O17">
+        <v>1.4</v>
+      </c>
+      <c r="P17">
+        <v>1.83</v>
+      </c>
+      <c r="Q17">
+        <v>2</v>
+      </c>
+      <c r="R17">
+        <v>1.22</v>
+      </c>
+      <c r="S17">
+        <v>3.3</v>
+      </c>
+      <c r="T17">
+        <v>2.66</v>
+      </c>
+      <c r="U17">
+        <v>1.48</v>
+      </c>
+      <c r="V17">
+        <v>1.06</v>
+      </c>
+      <c r="W17">
+        <v>3.35</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>1000</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17">
+        <v>1.01</v>
+      </c>
+      <c r="AR17">
+        <v>1.01</v>
+      </c>
+      <c r="AS17">
+        <v>1.01</v>
+      </c>
+      <c r="AT17">
+        <v>1.01</v>
+      </c>
+      <c r="AU17">
+        <v>1.01</v>
+      </c>
+      <c r="AV17">
+        <v>1.01</v>
+      </c>
+      <c r="AW17">
+        <v>1.01</v>
+      </c>
+      <c r="AX17">
+        <v>1.01</v>
+      </c>
+      <c r="AY17">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17">
+        <v>1.01</v>
+      </c>
+      <c r="BA17">
+        <v>1.01</v>
+      </c>
+      <c r="BB17">
+        <v>1.01</v>
+      </c>
+      <c r="BC17">
+        <v>1.01</v>
+      </c>
+      <c r="BD17">
+        <v>1.01</v>
+      </c>
+      <c r="BE17">
+        <v>1.01</v>
+      </c>
+      <c r="BF17">
+        <v>1.01</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17">
+        <v>4.2</v>
+      </c>
+      <c r="BI17">
+        <v>2.34</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.32</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.32</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.32</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.32</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.32</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.32</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.32</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.32</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.32</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" t="s">
         <v>129</v>
       </c>
-      <c r="F16">
+      <c r="E18" t="s">
+        <v>156</v>
+      </c>
+      <c r="F18">
+        <v>3.15</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18">
+        <v>2.48</v>
+      </c>
+      <c r="I18">
+        <v>2.84</v>
+      </c>
+      <c r="J18">
+        <v>2.66</v>
+      </c>
+      <c r="K18">
+        <v>3.25</v>
+      </c>
+      <c r="L18">
+        <v>1.55</v>
+      </c>
+      <c r="M18">
+        <v>1.12</v>
+      </c>
+      <c r="N18">
+        <v>2.6</v>
+      </c>
+      <c r="O18">
+        <v>1.53</v>
+      </c>
+      <c r="P18">
+        <v>1.52</v>
+      </c>
+      <c r="Q18">
+        <v>2.52</v>
+      </c>
+      <c r="R18">
+        <v>1.18</v>
+      </c>
+      <c r="S18">
+        <v>3.95</v>
+      </c>
+      <c r="T18">
+        <v>2.08</v>
+      </c>
+      <c r="U18">
+        <v>1.79</v>
+      </c>
+      <c r="V18">
+        <v>1.54</v>
+      </c>
+      <c r="W18">
+        <v>1.33</v>
+      </c>
+      <c r="X18">
+        <v>9</v>
+      </c>
+      <c r="Y18">
+        <v>9</v>
+      </c>
+      <c r="Z18">
+        <v>16.5</v>
+      </c>
+      <c r="AA18">
+        <v>55</v>
+      </c>
+      <c r="AB18">
+        <v>11</v>
+      </c>
+      <c r="AC18">
+        <v>8.4</v>
+      </c>
+      <c r="AD18">
+        <v>13.5</v>
+      </c>
+      <c r="AE18">
+        <v>46</v>
+      </c>
+      <c r="AF18">
+        <v>27</v>
+      </c>
+      <c r="AG18">
+        <v>16</v>
+      </c>
+      <c r="AH18">
+        <v>24</v>
+      </c>
+      <c r="AI18">
+        <v>80</v>
+      </c>
+      <c r="AJ18">
+        <v>85</v>
+      </c>
+      <c r="AK18">
+        <v>65</v>
+      </c>
+      <c r="AL18">
+        <v>95</v>
+      </c>
+      <c r="AM18">
+        <v>220</v>
+      </c>
+      <c r="AN18">
+        <v>85</v>
+      </c>
+      <c r="AO18">
+        <v>55</v>
+      </c>
+      <c r="AP18">
+        <v>3.55</v>
+      </c>
+      <c r="AQ18">
+        <v>3.55</v>
+      </c>
+      <c r="AR18">
+        <v>4.3</v>
+      </c>
+      <c r="AS18">
+        <v>5.3</v>
+      </c>
+      <c r="AT18">
+        <v>3.85</v>
+      </c>
+      <c r="AU18">
+        <v>5.3</v>
+      </c>
+      <c r="AV18">
+        <v>4.1</v>
+      </c>
+      <c r="AW18">
+        <v>5.2</v>
+      </c>
+      <c r="AX18">
+        <v>4.8</v>
+      </c>
+      <c r="AY18">
+        <v>4.3</v>
+      </c>
+      <c r="AZ18">
+        <v>4.7</v>
+      </c>
+      <c r="BA18">
+        <v>5.5</v>
+      </c>
+      <c r="BB18">
+        <v>5.5</v>
+      </c>
+      <c r="BC18">
+        <v>5.4</v>
+      </c>
+      <c r="BD18">
+        <v>5.6</v>
+      </c>
+      <c r="BE18">
+        <v>5.8</v>
+      </c>
+      <c r="BF18">
+        <v>5.5</v>
+      </c>
+      <c r="BG18">
+        <v>5.3</v>
+      </c>
+      <c r="BH18">
+        <v>2.8</v>
+      </c>
+      <c r="BI18">
+        <v>2.22</v>
+      </c>
+      <c r="BJ18">
+        <v>11.5</v>
+      </c>
+      <c r="BK18">
+        <v>5.6</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>2.22</v>
+      </c>
+      <c r="BN18">
+        <v>6.6</v>
+      </c>
+      <c r="BO18">
+        <v>4.1</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>2.1</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>2.14</v>
+      </c>
+      <c r="BT18">
+        <v>5.5</v>
+      </c>
+      <c r="BU18">
+        <v>3.65</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>2.04</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>2.14</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>2.14</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F19">
+        <v>2.54</v>
+      </c>
+      <c r="G19">
+        <v>2.88</v>
+      </c>
+      <c r="H19">
+        <v>3.1</v>
+      </c>
+      <c r="I19">
+        <v>3.8</v>
+      </c>
+      <c r="J19">
+        <v>2.8</v>
+      </c>
+      <c r="K19">
+        <v>3.25</v>
+      </c>
+      <c r="L19">
+        <v>1.5</v>
+      </c>
+      <c r="M19">
+        <v>1.11</v>
+      </c>
+      <c r="N19">
+        <v>2.42</v>
+      </c>
+      <c r="O19">
+        <v>1.55</v>
+      </c>
+      <c r="P19">
+        <v>1.48</v>
+      </c>
+      <c r="Q19">
+        <v>2.64</v>
+      </c>
+      <c r="R19">
+        <v>1.17</v>
+      </c>
+      <c r="S19">
+        <v>1.05</v>
+      </c>
+      <c r="T19">
+        <v>2.08</v>
+      </c>
+      <c r="U19">
+        <v>1.73</v>
+      </c>
+      <c r="V19">
+        <v>1.37</v>
+      </c>
+      <c r="W19">
+        <v>1.53</v>
+      </c>
+      <c r="X19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y19">
+        <v>11</v>
+      </c>
+      <c r="Z19">
+        <v>26</v>
+      </c>
+      <c r="AA19">
+        <v>85</v>
+      </c>
+      <c r="AB19">
+        <v>9.4</v>
+      </c>
+      <c r="AC19">
+        <v>8.4</v>
+      </c>
+      <c r="AD19">
+        <v>18.5</v>
+      </c>
+      <c r="AE19">
+        <v>65</v>
+      </c>
+      <c r="AF19">
+        <v>19.5</v>
+      </c>
+      <c r="AG19">
+        <v>16</v>
+      </c>
+      <c r="AH19">
+        <v>29</v>
+      </c>
+      <c r="AI19">
+        <v>100</v>
+      </c>
+      <c r="AJ19">
+        <v>60</v>
+      </c>
+      <c r="AK19">
+        <v>50</v>
+      </c>
+      <c r="AL19">
+        <v>85</v>
+      </c>
+      <c r="AM19">
+        <v>240</v>
+      </c>
+      <c r="AN19">
+        <v>60</v>
+      </c>
+      <c r="AO19">
+        <v>90</v>
+      </c>
+      <c r="AP19">
+        <v>3.05</v>
+      </c>
+      <c r="AQ19">
+        <v>3.15</v>
+      </c>
+      <c r="AR19">
+        <v>3.8</v>
+      </c>
+      <c r="AS19">
+        <v>4.2</v>
+      </c>
+      <c r="AT19">
+        <v>3</v>
+      </c>
+      <c r="AU19">
+        <v>2.92</v>
+      </c>
+      <c r="AV19">
+        <v>3.6</v>
+      </c>
+      <c r="AW19">
+        <v>4.1</v>
+      </c>
+      <c r="AX19">
+        <v>3.6</v>
+      </c>
+      <c r="AY19">
+        <v>3.45</v>
+      </c>
+      <c r="AZ19">
+        <v>3.85</v>
+      </c>
+      <c r="BA19">
+        <v>4.2</v>
+      </c>
+      <c r="BB19">
+        <v>4.1</v>
+      </c>
+      <c r="BC19">
+        <v>4.1</v>
+      </c>
+      <c r="BD19">
+        <v>4.2</v>
+      </c>
+      <c r="BE19">
+        <v>4.3</v>
+      </c>
+      <c r="BF19">
+        <v>4.1</v>
+      </c>
+      <c r="BG19">
+        <v>4.2</v>
+      </c>
+      <c r="BH19">
+        <v>2.72</v>
+      </c>
+      <c r="BI19">
+        <v>2.2</v>
+      </c>
+      <c r="BJ19">
+        <v>12</v>
+      </c>
+      <c r="BK19">
+        <v>5.8</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>2.16</v>
+      </c>
+      <c r="BN19">
+        <v>5.6</v>
+      </c>
+      <c r="BO19">
+        <v>3.7</v>
+      </c>
+      <c r="BP19">
+        <v>26</v>
+      </c>
+      <c r="BQ19">
+        <v>2.02</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>2.1</v>
+      </c>
+      <c r="BT19">
+        <v>6.4</v>
+      </c>
+      <c r="BU19">
+        <v>4</v>
+      </c>
+      <c r="BV19">
+        <v>34</v>
+      </c>
+      <c r="BW19">
+        <v>2.06</v>
+      </c>
+      <c r="BX19">
+        <v>60</v>
+      </c>
+      <c r="BY19">
+        <v>2.1</v>
+      </c>
+      <c r="BZ19">
+        <v>60</v>
+      </c>
+      <c r="CA19">
+        <v>2.1</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G20">
+        <v>11.5</v>
+      </c>
+      <c r="H20">
+        <v>1.31</v>
+      </c>
+      <c r="I20">
+        <v>1.37</v>
+      </c>
+      <c r="J20">
+        <v>6.2</v>
+      </c>
+      <c r="K20">
+        <v>7.2</v>
+      </c>
+      <c r="L20">
+        <v>1.17</v>
+      </c>
+      <c r="M20">
+        <v>1.02</v>
+      </c>
+      <c r="N20">
+        <v>8.4</v>
+      </c>
+      <c r="O20">
+        <v>1.11</v>
+      </c>
+      <c r="P20">
+        <v>3.45</v>
+      </c>
+      <c r="Q20">
+        <v>1.34</v>
+      </c>
+      <c r="R20">
+        <v>2.02</v>
+      </c>
+      <c r="S20">
+        <v>1.9</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>3.7</v>
+      </c>
+      <c r="W20">
+        <v>1.1</v>
+      </c>
+      <c r="X20">
+        <v>55</v>
+      </c>
+      <c r="Y20">
+        <v>19</v>
+      </c>
+      <c r="Z20">
+        <v>15</v>
+      </c>
+      <c r="AA20">
+        <v>15</v>
+      </c>
+      <c r="AB20">
+        <v>60</v>
+      </c>
+      <c r="AC20">
+        <v>21</v>
+      </c>
+      <c r="AD20">
+        <v>13.5</v>
+      </c>
+      <c r="AE20">
+        <v>16</v>
+      </c>
+      <c r="AF20">
+        <v>120</v>
+      </c>
+      <c r="AG20">
+        <v>44</v>
+      </c>
+      <c r="AH20">
+        <v>28</v>
+      </c>
+      <c r="AI20">
+        <v>32</v>
+      </c>
+      <c r="AJ20">
+        <v>310</v>
+      </c>
+      <c r="AK20">
+        <v>130</v>
+      </c>
+      <c r="AL20">
+        <v>80</v>
+      </c>
+      <c r="AM20">
+        <v>95</v>
+      </c>
+      <c r="AN20">
+        <v>100</v>
+      </c>
+      <c r="AO20">
+        <v>3.5</v>
+      </c>
+      <c r="AP20">
+        <v>5.5</v>
+      </c>
+      <c r="AQ20">
+        <v>14</v>
+      </c>
+      <c r="AR20">
+        <v>11</v>
+      </c>
+      <c r="AS20">
+        <v>11</v>
+      </c>
+      <c r="AT20">
+        <v>5.5</v>
+      </c>
+      <c r="AU20">
+        <v>12</v>
+      </c>
+      <c r="AV20">
+        <v>10.5</v>
+      </c>
+      <c r="AW20">
+        <v>11.5</v>
+      </c>
+      <c r="AX20">
+        <v>5.8</v>
+      </c>
+      <c r="AY20">
+        <v>30</v>
+      </c>
+      <c r="AZ20">
+        <v>20</v>
+      </c>
+      <c r="BA20">
+        <v>5.1</v>
+      </c>
+      <c r="BB20">
+        <v>6</v>
+      </c>
+      <c r="BC20">
+        <v>5.9</v>
+      </c>
+      <c r="BD20">
+        <v>5.7</v>
+      </c>
+      <c r="BE20">
+        <v>5.7</v>
+      </c>
+      <c r="BF20">
+        <v>5.8</v>
+      </c>
+      <c r="BG20">
+        <v>3.1</v>
+      </c>
+      <c r="BH20">
+        <v>5.9</v>
+      </c>
+      <c r="BI20">
+        <v>4.4</v>
+      </c>
+      <c r="BJ20">
+        <v>10.5</v>
+      </c>
+      <c r="BK20">
+        <v>5.8</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>11</v>
+      </c>
+      <c r="BN20">
+        <v>13.5</v>
+      </c>
+      <c r="BO20">
+        <v>6.6</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>10.5</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>10</v>
+      </c>
+      <c r="BT20">
+        <v>4.6</v>
+      </c>
+      <c r="BU20">
+        <v>3.5</v>
+      </c>
+      <c r="BV20">
+        <v>7.6</v>
+      </c>
+      <c r="BW20">
+        <v>5.6</v>
+      </c>
+      <c r="BX20">
+        <v>17</v>
+      </c>
+      <c r="BY20">
+        <v>7.4</v>
+      </c>
+      <c r="BZ20">
+        <v>7.8</v>
+      </c>
+      <c r="CA20">
+        <v>5.7</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21">
+        <v>1.75</v>
+      </c>
+      <c r="G21">
+        <v>1.93</v>
+      </c>
+      <c r="H21">
+        <v>4.2</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>3.95</v>
+      </c>
+      <c r="K21">
+        <v>4.5</v>
+      </c>
+      <c r="L21">
+        <v>1.3</v>
+      </c>
+      <c r="M21">
         <v>1.04</v>
       </c>
-      <c r="G16">
-        <v>1000</v>
-      </c>
-      <c r="H16">
+      <c r="N21">
+        <v>4.7</v>
+      </c>
+      <c r="O21">
+        <v>1.21</v>
+      </c>
+      <c r="P21">
+        <v>2.32</v>
+      </c>
+      <c r="Q21">
+        <v>1.62</v>
+      </c>
+      <c r="R21">
+        <v>1.51</v>
+      </c>
+      <c r="S21">
+        <v>2.56</v>
+      </c>
+      <c r="T21">
+        <v>1.63</v>
+      </c>
+      <c r="U21">
+        <v>2.26</v>
+      </c>
+      <c r="V21">
+        <v>1.25</v>
+      </c>
+      <c r="W21">
+        <v>2.08</v>
+      </c>
+      <c r="X21">
+        <v>25</v>
+      </c>
+      <c r="Y21">
+        <v>24</v>
+      </c>
+      <c r="Z21">
+        <v>42</v>
+      </c>
+      <c r="AA21">
+        <v>110</v>
+      </c>
+      <c r="AB21">
+        <v>12</v>
+      </c>
+      <c r="AC21">
+        <v>10.5</v>
+      </c>
+      <c r="AD21">
+        <v>19</v>
+      </c>
+      <c r="AE21">
+        <v>60</v>
+      </c>
+      <c r="AF21">
+        <v>13.5</v>
+      </c>
+      <c r="AG21">
+        <v>11</v>
+      </c>
+      <c r="AH21">
+        <v>18</v>
+      </c>
+      <c r="AI21">
+        <v>60</v>
+      </c>
+      <c r="AJ21">
+        <v>21</v>
+      </c>
+      <c r="AK21">
+        <v>18.5</v>
+      </c>
+      <c r="AL21">
+        <v>34</v>
+      </c>
+      <c r="AM21">
+        <v>85</v>
+      </c>
+      <c r="AN21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO21">
+        <v>48</v>
+      </c>
+      <c r="AP21">
+        <v>18</v>
+      </c>
+      <c r="AQ21">
+        <v>17</v>
+      </c>
+      <c r="AR21">
+        <v>6.6</v>
+      </c>
+      <c r="AS21">
+        <v>7.4</v>
+      </c>
+      <c r="AT21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU21">
+        <v>4.5</v>
+      </c>
+      <c r="AV21">
+        <v>15</v>
+      </c>
+      <c r="AW21">
+        <v>7</v>
+      </c>
+      <c r="AX21">
+        <v>11</v>
+      </c>
+      <c r="AY21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ21">
+        <v>14</v>
+      </c>
+      <c r="BA21">
+        <v>7</v>
+      </c>
+      <c r="BB21">
+        <v>16.5</v>
+      </c>
+      <c r="BC21">
+        <v>14.5</v>
+      </c>
+      <c r="BD21">
+        <v>6.4</v>
+      </c>
+      <c r="BE21">
+        <v>7.2</v>
+      </c>
+      <c r="BF21">
+        <v>7</v>
+      </c>
+      <c r="BG21">
+        <v>6.8</v>
+      </c>
+      <c r="BH21">
+        <v>4.3</v>
+      </c>
+      <c r="BI21">
+        <v>3.35</v>
+      </c>
+      <c r="BJ21">
+        <v>9.6</v>
+      </c>
+      <c r="BK21">
+        <v>4.8</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>8.6</v>
+      </c>
+      <c r="BN21">
+        <v>5</v>
+      </c>
+      <c r="BO21">
+        <v>3.85</v>
+      </c>
+      <c r="BP21">
+        <v>12.5</v>
+      </c>
+      <c r="BQ21">
+        <v>5.4</v>
+      </c>
+      <c r="BR21">
+        <v>24</v>
+      </c>
+      <c r="BS21">
+        <v>6.8</v>
+      </c>
+      <c r="BT21">
+        <v>8.6</v>
+      </c>
+      <c r="BU21">
+        <v>4.5</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>7.6</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>7.8</v>
+      </c>
+      <c r="BZ21">
+        <v>17</v>
+      </c>
+      <c r="CA21">
+        <v>6</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>3.05</v>
+      </c>
+      <c r="H22">
+        <v>2.62</v>
+      </c>
+      <c r="I22">
+        <v>2.66</v>
+      </c>
+      <c r="J22">
+        <v>3.45</v>
+      </c>
+      <c r="K22">
+        <v>3.5</v>
+      </c>
+      <c r="L22">
+        <v>1.44</v>
+      </c>
+      <c r="M22">
+        <v>1.08</v>
+      </c>
+      <c r="N22">
+        <v>3.75</v>
+      </c>
+      <c r="O22">
+        <v>1.35</v>
+      </c>
+      <c r="P22">
+        <v>1.91</v>
+      </c>
+      <c r="Q22">
+        <v>2.06</v>
+      </c>
+      <c r="R22">
+        <v>1.35</v>
+      </c>
+      <c r="S22">
+        <v>3.75</v>
+      </c>
+      <c r="T22">
+        <v>1.81</v>
+      </c>
+      <c r="U22">
+        <v>2.18</v>
+      </c>
+      <c r="V22">
+        <v>1.6</v>
+      </c>
+      <c r="W22">
+        <v>1.49</v>
+      </c>
+      <c r="X22">
+        <v>13</v>
+      </c>
+      <c r="Y22">
+        <v>11</v>
+      </c>
+      <c r="Z22">
+        <v>17</v>
+      </c>
+      <c r="AA22">
+        <v>40</v>
+      </c>
+      <c r="AB22">
+        <v>11.5</v>
+      </c>
+      <c r="AC22">
+        <v>7.6</v>
+      </c>
+      <c r="AD22">
+        <v>12</v>
+      </c>
+      <c r="AE22">
+        <v>30</v>
+      </c>
+      <c r="AF22">
+        <v>20</v>
+      </c>
+      <c r="AG22">
+        <v>13</v>
+      </c>
+      <c r="AH22">
+        <v>17.5</v>
+      </c>
+      <c r="AI22">
+        <v>42</v>
+      </c>
+      <c r="AJ22">
+        <v>48</v>
+      </c>
+      <c r="AK22">
+        <v>34</v>
+      </c>
+      <c r="AL22">
+        <v>46</v>
+      </c>
+      <c r="AM22">
+        <v>95</v>
+      </c>
+      <c r="AN22">
+        <v>32</v>
+      </c>
+      <c r="AO22">
+        <v>25</v>
+      </c>
+      <c r="AP22">
+        <v>12</v>
+      </c>
+      <c r="AQ22">
+        <v>10</v>
+      </c>
+      <c r="AR22">
+        <v>15.5</v>
+      </c>
+      <c r="AS22">
+        <v>34</v>
+      </c>
+      <c r="AT22">
+        <v>10.5</v>
+      </c>
+      <c r="AU22">
+        <v>7.2</v>
+      </c>
+      <c r="AV22">
+        <v>11</v>
+      </c>
+      <c r="AW22">
+        <v>27</v>
+      </c>
+      <c r="AX22">
+        <v>17.5</v>
+      </c>
+      <c r="AY22">
+        <v>12</v>
+      </c>
+      <c r="AZ22">
+        <v>16</v>
+      </c>
+      <c r="BA22">
+        <v>36</v>
+      </c>
+      <c r="BB22">
+        <v>42</v>
+      </c>
+      <c r="BC22">
+        <v>30</v>
+      </c>
+      <c r="BD22">
+        <v>38</v>
+      </c>
+      <c r="BE22">
+        <v>75</v>
+      </c>
+      <c r="BF22">
+        <v>28</v>
+      </c>
+      <c r="BG22">
+        <v>22</v>
+      </c>
+      <c r="BH22">
+        <v>3.25</v>
+      </c>
+      <c r="BI22">
+        <v>3.05</v>
+      </c>
+      <c r="BJ22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK22">
+        <v>8.4</v>
+      </c>
+      <c r="BL22">
+        <v>120</v>
+      </c>
+      <c r="BM22">
+        <v>15.5</v>
+      </c>
+      <c r="BN22">
+        <v>5.9</v>
+      </c>
+      <c r="BO22">
+        <v>5.4</v>
+      </c>
+      <c r="BP22">
+        <v>24</v>
+      </c>
+      <c r="BQ22">
+        <v>10</v>
+      </c>
+      <c r="BR22">
+        <v>38</v>
+      </c>
+      <c r="BS22">
+        <v>12</v>
+      </c>
+      <c r="BT22">
+        <v>5.6</v>
+      </c>
+      <c r="BU22">
+        <v>5.1</v>
+      </c>
+      <c r="BV22">
+        <v>21</v>
+      </c>
+      <c r="BW22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX22">
+        <v>34</v>
+      </c>
+      <c r="BY22">
+        <v>11.5</v>
+      </c>
+      <c r="BZ22">
+        <v>29</v>
+      </c>
+      <c r="CA22">
+        <v>11</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23">
+        <v>1.35</v>
+      </c>
+      <c r="G23">
+        <v>1.36</v>
+      </c>
+      <c r="H23">
+        <v>7.8</v>
+      </c>
+      <c r="I23">
+        <v>9.6</v>
+      </c>
+      <c r="J23">
+        <v>6.2</v>
+      </c>
+      <c r="K23">
+        <v>7.2</v>
+      </c>
+      <c r="L23">
+        <v>1.14</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>1.1</v>
+      </c>
+      <c r="O23">
+        <v>1.09</v>
+      </c>
+      <c r="P23">
+        <v>3.9</v>
+      </c>
+      <c r="Q23">
+        <v>1.27</v>
+      </c>
+      <c r="R23">
+        <v>2.2</v>
+      </c>
+      <c r="S23">
+        <v>1.66</v>
+      </c>
+      <c r="T23">
+        <v>1.5</v>
+      </c>
+      <c r="U23">
+        <v>2.62</v>
+      </c>
+      <c r="V23">
+        <v>1.11</v>
+      </c>
+      <c r="W23">
+        <v>3.75</v>
+      </c>
+      <c r="X23">
+        <v>70</v>
+      </c>
+      <c r="Y23">
+        <v>60</v>
+      </c>
+      <c r="Z23">
+        <v>110</v>
+      </c>
+      <c r="AA23">
+        <v>230</v>
+      </c>
+      <c r="AB23">
+        <v>23</v>
+      </c>
+      <c r="AC23">
+        <v>22</v>
+      </c>
+      <c r="AD23">
+        <v>38</v>
+      </c>
+      <c r="AE23">
+        <v>95</v>
+      </c>
+      <c r="AF23">
+        <v>19</v>
+      </c>
+      <c r="AG23">
+        <v>15</v>
+      </c>
+      <c r="AH23">
+        <v>25</v>
+      </c>
+      <c r="AI23">
+        <v>70</v>
+      </c>
+      <c r="AJ23">
+        <v>19</v>
+      </c>
+      <c r="AK23">
+        <v>17</v>
+      </c>
+      <c r="AL23">
+        <v>27</v>
+      </c>
+      <c r="AM23">
+        <v>70</v>
+      </c>
+      <c r="AN23">
+        <v>3.45</v>
+      </c>
+      <c r="AO23">
+        <v>55</v>
+      </c>
+      <c r="AP23">
+        <v>5</v>
+      </c>
+      <c r="AQ23">
+        <v>5</v>
+      </c>
+      <c r="AR23">
+        <v>5.2</v>
+      </c>
+      <c r="AS23">
+        <v>5.3</v>
+      </c>
+      <c r="AT23">
+        <v>4.4</v>
+      </c>
+      <c r="AU23">
+        <v>4.3</v>
+      </c>
+      <c r="AV23">
+        <v>4.7</v>
+      </c>
+      <c r="AW23">
+        <v>5.1</v>
+      </c>
+      <c r="AX23">
+        <v>4.2</v>
+      </c>
+      <c r="AY23">
+        <v>4</v>
+      </c>
+      <c r="AZ23">
+        <v>4.4</v>
+      </c>
+      <c r="BA23">
+        <v>5</v>
+      </c>
+      <c r="BB23">
+        <v>4.2</v>
+      </c>
+      <c r="BC23">
+        <v>4.1</v>
+      </c>
+      <c r="BD23">
+        <v>4.5</v>
+      </c>
+      <c r="BE23">
+        <v>5</v>
+      </c>
+      <c r="BF23">
+        <v>2.96</v>
+      </c>
+      <c r="BG23">
+        <v>4.9</v>
+      </c>
+      <c r="BH23">
+        <v>7</v>
+      </c>
+      <c r="BI23">
+        <v>4</v>
+      </c>
+      <c r="BJ23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK23">
+        <v>4.8</v>
+      </c>
+      <c r="BL23">
+        <v>65</v>
+      </c>
+      <c r="BM23">
+        <v>8.4</v>
+      </c>
+      <c r="BN23">
+        <v>5.2</v>
+      </c>
+      <c r="BO23">
+        <v>3.35</v>
+      </c>
+      <c r="BP23">
+        <v>8.4</v>
+      </c>
+      <c r="BQ23">
+        <v>4.5</v>
+      </c>
+      <c r="BR23">
+        <v>16</v>
+      </c>
+      <c r="BS23">
+        <v>6</v>
+      </c>
+      <c r="BT23">
+        <v>13</v>
+      </c>
+      <c r="BU23">
+        <v>5.5</v>
+      </c>
+      <c r="BV23">
+        <v>48</v>
+      </c>
+      <c r="BW23">
+        <v>8</v>
+      </c>
+      <c r="BX23">
+        <v>38</v>
+      </c>
+      <c r="BY23">
+        <v>7.6</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" t="s">
+        <v>162</v>
+      </c>
+      <c r="F24">
+        <v>2.12</v>
+      </c>
+      <c r="G24">
+        <v>2.88</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>4.6</v>
+      </c>
+      <c r="J24">
+        <v>2.86</v>
+      </c>
+      <c r="K24">
+        <v>5.1</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>2.58</v>
+      </c>
+      <c r="O24">
+        <v>1.27</v>
+      </c>
+      <c r="P24">
+        <v>1.4</v>
+      </c>
+      <c r="Q24">
+        <v>2.48</v>
+      </c>
+      <c r="R24">
+        <v>1.13</v>
+      </c>
+      <c r="S24">
+        <v>2.8</v>
+      </c>
+      <c r="T24">
+        <v>2.1</v>
+      </c>
+      <c r="U24">
+        <v>1.76</v>
+      </c>
+      <c r="V24">
+        <v>1.28</v>
+      </c>
+      <c r="W24">
+        <v>1.53</v>
+      </c>
+      <c r="X24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y24">
+        <v>10.5</v>
+      </c>
+      <c r="Z24">
+        <v>29</v>
+      </c>
+      <c r="AA24">
+        <v>100</v>
+      </c>
+      <c r="AB24">
+        <v>7.6</v>
+      </c>
+      <c r="AC24">
+        <v>7.2</v>
+      </c>
+      <c r="AD24">
+        <v>19.5</v>
+      </c>
+      <c r="AE24">
+        <v>90</v>
+      </c>
+      <c r="AF24">
+        <v>16.5</v>
+      </c>
+      <c r="AG24">
+        <v>14.5</v>
+      </c>
+      <c r="AH24">
+        <v>32</v>
+      </c>
+      <c r="AI24">
+        <v>100</v>
+      </c>
+      <c r="AJ24">
+        <v>50</v>
+      </c>
+      <c r="AK24">
+        <v>50</v>
+      </c>
+      <c r="AL24">
+        <v>90</v>
+      </c>
+      <c r="AM24">
+        <v>220</v>
+      </c>
+      <c r="AN24">
+        <v>42</v>
+      </c>
+      <c r="AO24">
+        <v>110</v>
+      </c>
+      <c r="AP24">
+        <v>4.2</v>
+      </c>
+      <c r="AQ24">
+        <v>4.4</v>
+      </c>
+      <c r="AR24">
+        <v>6</v>
+      </c>
+      <c r="AS24">
+        <v>7</v>
+      </c>
+      <c r="AT24">
+        <v>3.75</v>
+      </c>
+      <c r="AU24">
+        <v>3.65</v>
+      </c>
+      <c r="AV24">
+        <v>5.4</v>
+      </c>
+      <c r="AW24">
+        <v>6.6</v>
+      </c>
+      <c r="AX24">
+        <v>5.1</v>
+      </c>
+      <c r="AY24">
+        <v>4.9</v>
+      </c>
+      <c r="AZ24">
+        <v>5.7</v>
+      </c>
+      <c r="BA24">
+        <v>7</v>
+      </c>
+      <c r="BB24">
+        <v>6.2</v>
+      </c>
+      <c r="BC24">
+        <v>6.2</v>
+      </c>
+      <c r="BD24">
+        <v>6.6</v>
+      </c>
+      <c r="BE24">
+        <v>7.2</v>
+      </c>
+      <c r="BF24">
+        <v>6.2</v>
+      </c>
+      <c r="BG24">
+        <v>7</v>
+      </c>
+      <c r="BH24">
+        <v>2.72</v>
+      </c>
+      <c r="BI24">
+        <v>2.28</v>
+      </c>
+      <c r="BJ24">
+        <v>11.5</v>
+      </c>
+      <c r="BK24">
+        <v>6.4</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>2.26</v>
+      </c>
+      <c r="BN24">
+        <v>5.1</v>
+      </c>
+      <c r="BO24">
+        <v>3.75</v>
+      </c>
+      <c r="BP24">
+        <v>22</v>
+      </c>
+      <c r="BQ24">
+        <v>2.08</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>2.18</v>
+      </c>
+      <c r="BT24">
+        <v>6.8</v>
+      </c>
+      <c r="BU24">
+        <v>4.6</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>2.16</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>2.2</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>1.1</v>
+      </c>
+      <c r="O25">
+        <v>1.02</v>
+      </c>
+      <c r="P25">
+        <v>1.25</v>
+      </c>
+      <c r="Q25">
+        <v>1.5</v>
+      </c>
+      <c r="R25">
+        <v>1.18</v>
+      </c>
+      <c r="S25">
+        <v>1.5</v>
+      </c>
+      <c r="T25">
+        <v>1.11</v>
+      </c>
+      <c r="U25">
+        <v>1.11</v>
+      </c>
+      <c r="V25">
+        <v>1.01</v>
+      </c>
+      <c r="W25">
+        <v>1.01</v>
+      </c>
+      <c r="X25">
+        <v>1000</v>
+      </c>
+      <c r="Y25">
+        <v>1000</v>
+      </c>
+      <c r="Z25">
+        <v>1000</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>1000</v>
+      </c>
+      <c r="AC25">
+        <v>1000</v>
+      </c>
+      <c r="AD25">
+        <v>1000</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>1000</v>
+      </c>
+      <c r="AG25">
+        <v>1000</v>
+      </c>
+      <c r="AH25">
+        <v>1000</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25">
+        <v>1.01</v>
+      </c>
+      <c r="AR25">
+        <v>1.01</v>
+      </c>
+      <c r="AS25">
+        <v>1.01</v>
+      </c>
+      <c r="AT25">
+        <v>1.01</v>
+      </c>
+      <c r="AU25">
+        <v>1.01</v>
+      </c>
+      <c r="AV25">
+        <v>1.01</v>
+      </c>
+      <c r="AW25">
+        <v>1.01</v>
+      </c>
+      <c r="AX25">
+        <v>1.01</v>
+      </c>
+      <c r="AY25">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25">
+        <v>1.01</v>
+      </c>
+      <c r="BA25">
+        <v>1.01</v>
+      </c>
+      <c r="BB25">
+        <v>1.01</v>
+      </c>
+      <c r="BC25">
+        <v>1.01</v>
+      </c>
+      <c r="BD25">
+        <v>1.01</v>
+      </c>
+      <c r="BE25">
+        <v>1.01</v>
+      </c>
+      <c r="BF25">
+        <v>1.01</v>
+      </c>
+      <c r="BG25">
+        <v>1.01</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
         <v>1.04</v>
       </c>
-      <c r="I16">
-        <v>1000</v>
-      </c>
-      <c r="J16">
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
         <v>1.04</v>
       </c>
-      <c r="K16">
-        <v>950</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.04</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.04</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.04</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.04</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.04</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.04</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.04</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.04</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" t="s">
+        <v>164</v>
+      </c>
+      <c r="F26">
+        <v>1.98</v>
+      </c>
+      <c r="G26">
+        <v>2.1</v>
+      </c>
+      <c r="H26">
+        <v>4.4</v>
+      </c>
+      <c r="I26">
+        <v>5.2</v>
+      </c>
+      <c r="J26">
+        <v>3.2</v>
+      </c>
+      <c r="K26">
+        <v>3.45</v>
+      </c>
+      <c r="L26">
+        <v>1.46</v>
+      </c>
+      <c r="M26">
+        <v>1.11</v>
+      </c>
+      <c r="N26">
+        <v>2.72</v>
+      </c>
+      <c r="O26">
+        <v>1.44</v>
+      </c>
+      <c r="P26">
+        <v>1.57</v>
+      </c>
+      <c r="Q26">
+        <v>2.44</v>
+      </c>
+      <c r="R26">
+        <v>1.22</v>
+      </c>
+      <c r="S26">
+        <v>4.7</v>
+      </c>
+      <c r="T26">
+        <v>2.06</v>
+      </c>
+      <c r="U26">
+        <v>1.78</v>
+      </c>
+      <c r="V26">
         <v>1.24</v>
       </c>
-      <c r="Q16">
-        <v>1.01</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>0</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>0</v>
-      </c>
-      <c r="BC16">
-        <v>0</v>
-      </c>
-      <c r="BD16">
-        <v>0</v>
-      </c>
-      <c r="BE16">
-        <v>0</v>
-      </c>
-      <c r="BF16">
-        <v>0</v>
-      </c>
-      <c r="BG16">
-        <v>0</v>
-      </c>
-      <c r="BH16">
-        <v>0</v>
-      </c>
-      <c r="BI16">
-        <v>0</v>
-      </c>
-      <c r="BJ16">
-        <v>0</v>
-      </c>
-      <c r="BK16">
-        <v>0</v>
-      </c>
-      <c r="BL16">
-        <v>0</v>
-      </c>
-      <c r="BM16">
-        <v>0</v>
-      </c>
-      <c r="BN16">
-        <v>0</v>
-      </c>
-      <c r="BO16">
-        <v>0</v>
-      </c>
-      <c r="BP16">
-        <v>0</v>
-      </c>
-      <c r="BQ16">
-        <v>0</v>
-      </c>
-      <c r="BR16">
-        <v>0</v>
-      </c>
-      <c r="BS16">
-        <v>0</v>
-      </c>
-      <c r="BT16">
-        <v>0</v>
-      </c>
-      <c r="BU16">
-        <v>0</v>
-      </c>
-      <c r="BV16">
-        <v>0</v>
-      </c>
-      <c r="BW16">
-        <v>0</v>
-      </c>
-      <c r="BX16">
-        <v>0</v>
-      </c>
-      <c r="BY16">
-        <v>0</v>
-      </c>
-      <c r="BZ16">
-        <v>0</v>
-      </c>
-      <c r="CA16">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="s">
+      <c r="W26">
+        <v>1.91</v>
+      </c>
+      <c r="X26">
+        <v>10.5</v>
+      </c>
+      <c r="Y26">
+        <v>13.5</v>
+      </c>
+      <c r="Z26">
+        <v>34</v>
+      </c>
+      <c r="AA26">
         <v>130</v>
+      </c>
+      <c r="AB26">
+        <v>7.2</v>
+      </c>
+      <c r="AC26">
+        <v>8</v>
+      </c>
+      <c r="AD26">
+        <v>21</v>
+      </c>
+      <c r="AE26">
+        <v>95</v>
+      </c>
+      <c r="AF26">
+        <v>12</v>
+      </c>
+      <c r="AG26">
+        <v>11.5</v>
+      </c>
+      <c r="AH26">
+        <v>24</v>
+      </c>
+      <c r="AI26">
+        <v>110</v>
+      </c>
+      <c r="AJ26">
+        <v>27</v>
+      </c>
+      <c r="AK26">
+        <v>28</v>
+      </c>
+      <c r="AL26">
+        <v>60</v>
+      </c>
+      <c r="AM26">
+        <v>200</v>
+      </c>
+      <c r="AN26">
+        <v>24</v>
+      </c>
+      <c r="AO26">
+        <v>120</v>
+      </c>
+      <c r="AP26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ26">
+        <v>11</v>
+      </c>
+      <c r="AR26">
+        <v>7.4</v>
+      </c>
+      <c r="AS26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT26">
+        <v>6</v>
+      </c>
+      <c r="AU26">
+        <v>6.6</v>
+      </c>
+      <c r="AV26">
+        <v>17</v>
+      </c>
+      <c r="AW26">
+        <v>8.4</v>
+      </c>
+      <c r="AX26">
+        <v>9.4</v>
+      </c>
+      <c r="AY26">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26">
+        <v>20</v>
+      </c>
+      <c r="BA26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB26">
+        <v>21</v>
+      </c>
+      <c r="BC26">
+        <v>7</v>
+      </c>
+      <c r="BD26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE26">
+        <v>9</v>
+      </c>
+      <c r="BF26">
+        <v>19</v>
+      </c>
+      <c r="BG26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH26">
+        <v>3.2</v>
+      </c>
+      <c r="BI26">
+        <v>2.42</v>
+      </c>
+      <c r="BJ26">
+        <v>13</v>
+      </c>
+      <c r="BK26">
+        <v>4.1</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>5.8</v>
+      </c>
+      <c r="BN26">
+        <v>5.1</v>
+      </c>
+      <c r="BO26">
+        <v>3.65</v>
+      </c>
+      <c r="BP26">
+        <v>18.5</v>
+      </c>
+      <c r="BQ26">
+        <v>4.5</v>
+      </c>
+      <c r="BR26">
+        <v>44</v>
+      </c>
+      <c r="BS26">
+        <v>5.3</v>
+      </c>
+      <c r="BT26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU26">
+        <v>6</v>
+      </c>
+      <c r="BV26">
+        <v>55</v>
+      </c>
+      <c r="BW26">
+        <v>5.4</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>5.5</v>
+      </c>
+      <c r="BZ26">
+        <v>44</v>
+      </c>
+      <c r="CA26">
+        <v>5.3</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27">
+        <v>2.16</v>
+      </c>
+      <c r="G27">
+        <v>2.26</v>
+      </c>
+      <c r="H27">
+        <v>3.95</v>
+      </c>
+      <c r="I27">
+        <v>4.4</v>
+      </c>
+      <c r="J27">
+        <v>3</v>
+      </c>
+      <c r="K27">
+        <v>3.35</v>
+      </c>
+      <c r="L27">
+        <v>1.49</v>
+      </c>
+      <c r="M27">
+        <v>1.12</v>
+      </c>
+      <c r="N27">
+        <v>2.66</v>
+      </c>
+      <c r="O27">
+        <v>1.52</v>
+      </c>
+      <c r="P27">
+        <v>1.55</v>
+      </c>
+      <c r="Q27">
+        <v>2.52</v>
+      </c>
+      <c r="R27">
+        <v>1.2</v>
+      </c>
+      <c r="S27">
+        <v>5.1</v>
+      </c>
+      <c r="T27">
+        <v>2.08</v>
+      </c>
+      <c r="U27">
+        <v>1.8</v>
+      </c>
+      <c r="V27">
+        <v>1.3</v>
+      </c>
+      <c r="W27">
+        <v>1.79</v>
+      </c>
+      <c r="X27">
+        <v>9</v>
+      </c>
+      <c r="Y27">
+        <v>11.5</v>
+      </c>
+      <c r="Z27">
+        <v>29</v>
+      </c>
+      <c r="AA27">
+        <v>120</v>
+      </c>
+      <c r="AB27">
+        <v>7.2</v>
+      </c>
+      <c r="AC27">
+        <v>7.4</v>
+      </c>
+      <c r="AD27">
+        <v>21</v>
+      </c>
+      <c r="AE27">
+        <v>80</v>
+      </c>
+      <c r="AF27">
+        <v>15</v>
+      </c>
+      <c r="AG27">
+        <v>12</v>
+      </c>
+      <c r="AH27">
+        <v>27</v>
+      </c>
+      <c r="AI27">
+        <v>100</v>
+      </c>
+      <c r="AJ27">
+        <v>42</v>
+      </c>
+      <c r="AK27">
+        <v>42</v>
+      </c>
+      <c r="AL27">
+        <v>80</v>
+      </c>
+      <c r="AM27">
+        <v>210</v>
+      </c>
+      <c r="AN27">
+        <v>40</v>
+      </c>
+      <c r="AO27">
+        <v>120</v>
+      </c>
+      <c r="AP27">
+        <v>7.8</v>
+      </c>
+      <c r="AQ27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR27">
+        <v>20</v>
+      </c>
+      <c r="AS27">
+        <v>10</v>
+      </c>
+      <c r="AT27">
+        <v>6.4</v>
+      </c>
+      <c r="AU27">
+        <v>6.4</v>
+      </c>
+      <c r="AV27">
+        <v>7</v>
+      </c>
+      <c r="AW27">
+        <v>9.6</v>
+      </c>
+      <c r="AX27">
+        <v>11</v>
+      </c>
+      <c r="AY27">
+        <v>10</v>
+      </c>
+      <c r="AZ27">
+        <v>7.6</v>
+      </c>
+      <c r="BA27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC27">
+        <v>22</v>
+      </c>
+      <c r="BD27">
+        <v>36</v>
+      </c>
+      <c r="BE27">
+        <v>10</v>
+      </c>
+      <c r="BF27">
+        <v>8</v>
+      </c>
+      <c r="BG27">
+        <v>10</v>
+      </c>
+      <c r="BH27">
+        <v>2.78</v>
+      </c>
+      <c r="BI27">
+        <v>2.54</v>
+      </c>
+      <c r="BJ27">
+        <v>13</v>
+      </c>
+      <c r="BK27">
+        <v>4.8</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>7.2</v>
+      </c>
+      <c r="BN27">
+        <v>5.4</v>
+      </c>
+      <c r="BO27">
+        <v>3.85</v>
+      </c>
+      <c r="BP27">
+        <v>22</v>
+      </c>
+      <c r="BQ27">
+        <v>5.6</v>
+      </c>
+      <c r="BR27">
+        <v>48</v>
+      </c>
+      <c r="BS27">
+        <v>6.4</v>
+      </c>
+      <c r="BT27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU27">
+        <v>5.6</v>
+      </c>
+      <c r="BV27">
+        <v>46</v>
+      </c>
+      <c r="BW27">
+        <v>6.4</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>6.8</v>
+      </c>
+      <c r="BZ27">
+        <v>55</v>
+      </c>
+      <c r="CA27">
+        <v>6.6</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F28">
+        <v>2.06</v>
+      </c>
+      <c r="G28">
+        <v>2.12</v>
+      </c>
+      <c r="H28">
+        <v>4.2</v>
+      </c>
+      <c r="I28">
+        <v>4.4</v>
+      </c>
+      <c r="J28">
+        <v>3.35</v>
+      </c>
+      <c r="K28">
+        <v>3.5</v>
+      </c>
+      <c r="L28">
+        <v>1.44</v>
+      </c>
+      <c r="M28">
+        <v>1.1</v>
+      </c>
+      <c r="N28">
+        <v>2.94</v>
+      </c>
+      <c r="O28">
+        <v>1.45</v>
+      </c>
+      <c r="P28">
+        <v>1.67</v>
+      </c>
+      <c r="Q28">
+        <v>2.3</v>
+      </c>
+      <c r="R28">
+        <v>1.23</v>
+      </c>
+      <c r="S28">
+        <v>4.5</v>
+      </c>
+      <c r="T28">
+        <v>2.04</v>
+      </c>
+      <c r="U28">
+        <v>1.85</v>
+      </c>
+      <c r="V28">
+        <v>1.3</v>
+      </c>
+      <c r="W28">
+        <v>1.89</v>
+      </c>
+      <c r="X28">
+        <v>12</v>
+      </c>
+      <c r="Y28">
+        <v>13.5</v>
+      </c>
+      <c r="Z28">
+        <v>36</v>
+      </c>
+      <c r="AA28">
+        <v>130</v>
+      </c>
+      <c r="AB28">
+        <v>7.8</v>
+      </c>
+      <c r="AC28">
+        <v>8</v>
+      </c>
+      <c r="AD28">
+        <v>21</v>
+      </c>
+      <c r="AE28">
+        <v>80</v>
+      </c>
+      <c r="AF28">
+        <v>12.5</v>
+      </c>
+      <c r="AG28">
+        <v>12.5</v>
+      </c>
+      <c r="AH28">
+        <v>23</v>
+      </c>
+      <c r="AI28">
+        <v>95</v>
+      </c>
+      <c r="AJ28">
+        <v>30</v>
+      </c>
+      <c r="AK28">
+        <v>30</v>
+      </c>
+      <c r="AL28">
+        <v>60</v>
+      </c>
+      <c r="AM28">
+        <v>180</v>
+      </c>
+      <c r="AN28">
+        <v>25</v>
+      </c>
+      <c r="AO28">
+        <v>110</v>
+      </c>
+      <c r="AP28">
+        <v>4.4</v>
+      </c>
+      <c r="AQ28">
+        <v>11</v>
+      </c>
+      <c r="AR28">
+        <v>5.8</v>
+      </c>
+      <c r="AS28">
+        <v>6.6</v>
+      </c>
+      <c r="AT28">
+        <v>3.7</v>
+      </c>
+      <c r="AU28">
+        <v>3.7</v>
+      </c>
+      <c r="AV28">
+        <v>15.5</v>
+      </c>
+      <c r="AW28">
+        <v>6.4</v>
+      </c>
+      <c r="AX28">
+        <v>10</v>
+      </c>
+      <c r="AY28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28">
+        <v>18.5</v>
+      </c>
+      <c r="BA28">
+        <v>6.4</v>
+      </c>
+      <c r="BB28">
+        <v>21</v>
+      </c>
+      <c r="BC28">
+        <v>21</v>
+      </c>
+      <c r="BD28">
+        <v>6.2</v>
+      </c>
+      <c r="BE28">
+        <v>6.6</v>
+      </c>
+      <c r="BF28">
+        <v>18</v>
+      </c>
+      <c r="BG28">
+        <v>6.6</v>
+      </c>
+      <c r="BH28">
+        <v>3.05</v>
+      </c>
+      <c r="BI28">
+        <v>2.46</v>
+      </c>
+      <c r="BJ28">
+        <v>11.5</v>
+      </c>
+      <c r="BK28">
+        <v>5.5</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>10</v>
+      </c>
+      <c r="BN28">
+        <v>4.8</v>
+      </c>
+      <c r="BO28">
+        <v>3.7</v>
+      </c>
+      <c r="BP28">
+        <v>17</v>
+      </c>
+      <c r="BQ28">
+        <v>6.6</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>8.4</v>
+      </c>
+      <c r="BT28">
+        <v>7.8</v>
+      </c>
+      <c r="BU28">
+        <v>5.9</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>8.6</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>9</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>8.4</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="170">
   <si>
     <t>League</t>
   </si>
@@ -286,6 +286,9 @@
     <t>South African Premier Division</t>
   </si>
   <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -325,9 +328,6 @@
     <t>16:05:00</t>
   </si>
   <si>
-    <t>16:10:00</t>
-  </si>
-  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -388,13 +388,16 @@
     <t>Abha</t>
   </si>
   <si>
-    <t>Al-Taawoun Buraidah</t>
+    <t>Osters</t>
   </si>
   <si>
     <t>Orebro</t>
   </si>
   <si>
-    <t>Osters</t>
+    <t>Marumo Gallants FC</t>
+  </si>
+  <si>
+    <t>Kruger United FC</t>
   </si>
   <si>
     <t>Siwelele FC</t>
@@ -403,18 +406,15 @@
     <t>Orlando Pirates (SA)</t>
   </si>
   <si>
-    <t>Kruger United FC</t>
-  </si>
-  <si>
-    <t>Marumo Gallants FC</t>
-  </si>
-  <si>
     <t>Al-Ettifaq</t>
   </si>
   <si>
     <t>Al-Shabab (KSA)</t>
   </si>
   <si>
+    <t>CD Gualberto Villarroel</t>
+  </si>
+  <si>
     <t>Valencia</t>
   </si>
   <si>
@@ -427,10 +427,13 @@
     <t>Club 2 de Mayo de Pedro Juan Cab</t>
   </si>
   <si>
+    <t>Atletico GO</t>
+  </si>
+  <si>
     <t>Juventude</t>
   </si>
   <si>
-    <t>Atletico GO</t>
+    <t>Universitario de Vinto</t>
   </si>
   <si>
     <t>Atletico Bucaramanga</t>
@@ -469,13 +472,16 @@
     <t>Al-Khaleej Saihat</t>
   </si>
   <si>
-    <t>Al-Feiha</t>
+    <t>Sundsvall</t>
   </si>
   <si>
     <t>Varbergs BoIS</t>
   </si>
   <si>
-    <t>Sundsvall</t>
+    <t>TS Galaxy FC</t>
+  </si>
+  <si>
+    <t>Durban City</t>
   </si>
   <si>
     <t>Chippa Utd</t>
@@ -484,18 +490,15 @@
     <t>Sekhukhune United</t>
   </si>
   <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>TS Galaxy FC</t>
-  </si>
-  <si>
     <t>Al Nassr</t>
   </si>
   <si>
     <t>Al Riyadh SC</t>
   </si>
   <si>
+    <t>Oriente Petrolero</t>
+  </si>
+  <si>
     <t>Betis</t>
   </si>
   <si>
@@ -508,16 +511,19 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>CRB</t>
   </si>
   <si>
-    <t>Botafogo SP</t>
+    <t>Nacional Potosi</t>
   </si>
   <si>
     <t>Aguilas Doradas</t>
   </si>
   <si>
-    <t>2026-08-24 10:29:12</t>
+    <t>2026-08-24 12:49:40</t>
   </si>
 </sst>
 </file>
@@ -849,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB28"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1099,85 +1105,85 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
         <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F2">
         <v>3.5</v>
       </c>
       <c r="G2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="H2">
+        <v>2.28</v>
+      </c>
+      <c r="I2">
         <v>2.36</v>
       </c>
-      <c r="I2">
-        <v>2.42</v>
-      </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T2">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U2">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="V2">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA2">
         <v>38</v>
       </c>
       <c r="AB2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
@@ -1186,67 +1192,67 @@
         <v>12.5</v>
       </c>
       <c r="AE2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
+        <v>85</v>
+      </c>
+      <c r="AK2">
+        <v>55</v>
+      </c>
+      <c r="AL2">
+        <v>70</v>
+      </c>
+      <c r="AM2">
+        <v>160</v>
+      </c>
+      <c r="AN2">
         <v>80</v>
       </c>
-      <c r="AK2">
-        <v>48</v>
-      </c>
-      <c r="AL2">
-        <v>60</v>
-      </c>
-      <c r="AM2">
-        <v>150</v>
-      </c>
-      <c r="AN2">
-        <v>55</v>
-      </c>
       <c r="AO2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AT2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2">
         <v>17</v>
@@ -1258,82 +1264,82 @@
         <v>46</v>
       </c>
       <c r="BC2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BG2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BH2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI2">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BO2">
         <v>5.3</v>
       </c>
       <c r="BP2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BR2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BS2">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT2">
         <v>5.2</v>
       </c>
       <c r="BU2">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BV2">
         <v>19</v>
       </c>
       <c r="BW2">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1341,28 +1347,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
         <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F3">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G3">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -1371,211 +1377,211 @@
         <v>3.1</v>
       </c>
       <c r="L3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M3">
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="P3">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA3">
-        <v>480</v>
+        <v>70</v>
       </c>
       <c r="AB3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC3">
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG3">
         <v>13.5</v>
       </c>
       <c r="AH3">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AI3">
+        <v>110</v>
+      </c>
+      <c r="AJ3">
+        <v>50</v>
+      </c>
+      <c r="AK3">
+        <v>44</v>
+      </c>
+      <c r="AL3">
         <v>90</v>
       </c>
-      <c r="AJ3">
-        <v>60</v>
-      </c>
-      <c r="AK3">
-        <v>50</v>
-      </c>
-      <c r="AL3">
-        <v>80</v>
-      </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>670</v>
       </c>
       <c r="AN3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO3">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR3">
         <v>17.5</v>
       </c>
       <c r="AS3">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AT3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU3">
         <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AX3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY3">
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BB3">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BC3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BD3">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BE3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BF3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG3">
+        <v>32</v>
+      </c>
+      <c r="BH3">
+        <v>3.05</v>
+      </c>
+      <c r="BI3">
+        <v>2.18</v>
+      </c>
+      <c r="BJ3">
+        <v>13.5</v>
+      </c>
+      <c r="BK3">
+        <v>4.2</v>
+      </c>
+      <c r="BL3">
+        <v>260</v>
+      </c>
+      <c r="BM3">
+        <v>5.9</v>
+      </c>
+      <c r="BN3">
+        <v>5.5</v>
+      </c>
+      <c r="BO3">
+        <v>4.2</v>
+      </c>
+      <c r="BP3">
         <v>30</v>
       </c>
-      <c r="BH3">
-        <v>3</v>
-      </c>
-      <c r="BI3">
-        <v>2.24</v>
-      </c>
-      <c r="BJ3">
-        <v>11.5</v>
-      </c>
-      <c r="BK3">
+      <c r="BQ3">
         <v>5</v>
-      </c>
-      <c r="BL3">
-        <v>240</v>
-      </c>
-      <c r="BM3">
-        <v>8.4</v>
-      </c>
-      <c r="BN3">
-        <v>5.6</v>
-      </c>
-      <c r="BO3">
-        <v>5</v>
-      </c>
-      <c r="BP3">
-        <v>27</v>
-      </c>
-      <c r="BQ3">
-        <v>6.6</v>
       </c>
       <c r="BR3">
         <v>60</v>
       </c>
       <c r="BS3">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BT3">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW3">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="CA3">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1583,28 +1589,28 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
         <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F4">
         <v>2.84</v>
       </c>
       <c r="G4">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J4">
         <v>3.05</v>
@@ -1622,13 +1628,13 @@
         <v>2.92</v>
       </c>
       <c r="O4">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P4">
         <v>1.63</v>
       </c>
       <c r="Q4">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R4">
         <v>1.23</v>
@@ -1637,10 +1643,10 @@
         <v>5</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
         <v>1.47</v>
@@ -1652,40 +1658,40 @@
         <v>9.4</v>
       </c>
       <c r="Y4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA4">
         <v>55</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
         <v>14</v>
       </c>
       <c r="AE4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG4">
         <v>13.5</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK4">
         <v>40</v>
@@ -1694,13 +1700,13 @@
         <v>65</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN4">
         <v>55</v>
       </c>
       <c r="AO4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP4">
         <v>8.4</v>
@@ -1709,13 +1715,13 @@
         <v>8.4</v>
       </c>
       <c r="AR4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS4">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AT4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4">
         <v>6.4</v>
@@ -1724,10 +1730,10 @@
         <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY4">
         <v>12</v>
@@ -1736,7 +1742,7 @@
         <v>19</v>
       </c>
       <c r="BA4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB4">
         <v>40</v>
@@ -1757,67 +1763,67 @@
         <v>40</v>
       </c>
       <c r="BH4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>3.75</v>
       </c>
       <c r="BL4">
         <v>210</v>
       </c>
       <c r="BM4">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BN4">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO4">
+        <v>4.3</v>
+      </c>
+      <c r="BP4">
+        <v>26</v>
+      </c>
+      <c r="BQ4">
+        <v>4.4</v>
+      </c>
+      <c r="BR4">
+        <v>55</v>
+      </c>
+      <c r="BS4">
         <v>4.8</v>
       </c>
-      <c r="BP4">
-        <v>25</v>
-      </c>
-      <c r="BQ4">
-        <v>6</v>
-      </c>
-      <c r="BR4">
+      <c r="BT4">
+        <v>7</v>
+      </c>
+      <c r="BU4">
+        <v>5</v>
+      </c>
+      <c r="BV4">
+        <v>32</v>
+      </c>
+      <c r="BW4">
+        <v>4.5</v>
+      </c>
+      <c r="BX4">
+        <v>55</v>
+      </c>
+      <c r="BY4">
+        <v>4.8</v>
+      </c>
+      <c r="BZ4">
         <v>46</v>
       </c>
-      <c r="BS4">
-        <v>6.6</v>
-      </c>
-      <c r="BT4">
-        <v>6.2</v>
-      </c>
-      <c r="BU4">
-        <v>4.5</v>
-      </c>
-      <c r="BV4">
-        <v>28</v>
-      </c>
-      <c r="BW4">
-        <v>6</v>
-      </c>
-      <c r="BX4">
-        <v>48</v>
-      </c>
-      <c r="BY4">
-        <v>6.6</v>
-      </c>
-      <c r="BZ4">
-        <v>44</v>
-      </c>
       <c r="CA4">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1825,16 +1831,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
         <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F5">
         <v>1.45</v>
@@ -1843,22 +1849,22 @@
         <v>1.49</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>9</v>
       </c>
       <c r="J5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L5">
         <v>1.31</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
         <v>5.1</v>
@@ -1873,28 +1879,28 @@
         <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S5">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T5">
         <v>1.84</v>
       </c>
       <c r="U5">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V5">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Y5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z5">
         <v>75</v>
@@ -1906,28 +1912,28 @@
         <v>10.5</v>
       </c>
       <c r="AC5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD5">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AE5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF5">
         <v>9.800000000000001</v>
       </c>
       <c r="AG5">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
         <v>25</v>
       </c>
       <c r="AI5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AK5">
         <v>15.5</v>
@@ -1936,37 +1942,37 @@
         <v>34</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN5">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AO5">
         <v>140</v>
       </c>
       <c r="AP5">
-        <v>19.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ5">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AR5">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
         <v>10</v>
       </c>
       <c r="AV5">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX5">
         <v>8.199999999999999</v>
@@ -1975,28 +1981,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="BA5">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>26</v>
+        <v>5.8</v>
       </c>
       <c r="BE5">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH5">
         <v>4.4</v>
@@ -2008,13 +2014,13 @@
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN5">
         <v>4.2</v>
@@ -2026,40 +2032,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BQ5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT5">
         <v>12</v>
       </c>
       <c r="BU5">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CA5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2067,19 +2073,19 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
         <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G6">
         <v>3.7</v>
@@ -2091,13 +2097,13 @@
         <v>2.3</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M6">
         <v>1.07</v>
@@ -2109,7 +2115,7 @@
         <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q6">
         <v>2.04</v>
@@ -2118,73 +2124,73 @@
         <v>1.35</v>
       </c>
       <c r="S6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T6">
         <v>1.82</v>
       </c>
       <c r="U6">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V6">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W6">
         <v>1.37</v>
       </c>
       <c r="X6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y6">
         <v>9.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AA6">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AB6">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC6">
         <v>8</v>
       </c>
       <c r="AD6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE6">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AF6">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG6">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="AM6">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AO6">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AP6">
         <v>12.5</v>
@@ -2199,10 +2205,10 @@
         <v>19</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV6">
         <v>10</v>
@@ -2211,7 +2217,7 @@
         <v>21</v>
       </c>
       <c r="AX6">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AY6">
         <v>13.5</v>
@@ -2220,7 +2226,7 @@
         <v>16</v>
       </c>
       <c r="BA6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB6">
         <v>32</v>
@@ -2229,10 +2235,10 @@
         <v>32</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE6">
-        <v>38</v>
+        <v>13.5</v>
       </c>
       <c r="BF6">
         <v>25</v>
@@ -2241,67 +2247,67 @@
         <v>16</v>
       </c>
       <c r="BH6">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2309,22 +2315,22 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
         <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F7">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G7">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H7">
         <v>3.2</v>
@@ -2333,22 +2339,22 @@
         <v>3.35</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O7">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P7">
         <v>1.66</v>
@@ -2363,7 +2369,7 @@
         <v>4.8</v>
       </c>
       <c r="T7">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U7">
         <v>1.92</v>
@@ -2372,19 +2378,19 @@
         <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X7">
         <v>10.5</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA7">
-        <v>550</v>
+        <v>70</v>
       </c>
       <c r="AB7">
         <v>8.4</v>
@@ -2396,10 +2402,10 @@
         <v>14.5</v>
       </c>
       <c r="AE7">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AF7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG7">
         <v>13</v>
@@ -2414,7 +2420,7 @@
         <v>42</v>
       </c>
       <c r="AK7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL7">
         <v>60</v>
@@ -2423,7 +2429,7 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO7">
         <v>60</v>
@@ -2435,16 +2441,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT7">
         <v>7.6</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
         <v>13</v>
@@ -2453,7 +2459,7 @@
         <v>25</v>
       </c>
       <c r="AX7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY7">
         <v>11</v>
@@ -2468,82 +2474,82 @@
         <v>23</v>
       </c>
       <c r="BC7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD7">
         <v>29</v>
       </c>
       <c r="BE7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BF7">
         <v>21</v>
       </c>
       <c r="BG7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BH7">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2551,19 +2557,19 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F8">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G8">
         <v>1.62</v>
@@ -2572,16 +2578,16 @@
         <v>6.4</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M8">
         <v>1.06</v>
@@ -2599,13 +2605,13 @@
         <v>1.88</v>
       </c>
       <c r="R8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S8">
         <v>3.25</v>
       </c>
       <c r="T8">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U8">
         <v>1.93</v>
@@ -2617,13 +2623,13 @@
         <v>2.6</v>
       </c>
       <c r="X8">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Y8">
         <v>23</v>
       </c>
       <c r="Z8">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA8">
         <v>240</v>
@@ -2632,7 +2638,7 @@
         <v>8.4</v>
       </c>
       <c r="AC8">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
         <v>27</v>
@@ -2647,52 +2653,52 @@
         <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI8">
         <v>110</v>
       </c>
       <c r="AJ8">
+        <v>15</v>
+      </c>
+      <c r="AK8">
+        <v>18</v>
+      </c>
+      <c r="AL8">
+        <v>44</v>
+      </c>
+      <c r="AM8">
+        <v>160</v>
+      </c>
+      <c r="AN8">
+        <v>8.6</v>
+      </c>
+      <c r="AO8">
+        <v>160</v>
+      </c>
+      <c r="AP8">
         <v>14.5</v>
-      </c>
-      <c r="AK8">
-        <v>17.5</v>
-      </c>
-      <c r="AL8">
-        <v>40</v>
-      </c>
-      <c r="AM8">
-        <v>150</v>
-      </c>
-      <c r="AN8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO8">
-        <v>150</v>
-      </c>
-      <c r="AP8">
-        <v>14</v>
       </c>
       <c r="AQ8">
         <v>18</v>
       </c>
       <c r="AR8">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS8">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU8">
         <v>8.800000000000001</v>
       </c>
       <c r="AV8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW8">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AX8">
         <v>8.199999999999999</v>
@@ -2701,10 +2707,10 @@
         <v>9</v>
       </c>
       <c r="AZ8">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8">
         <v>12.5</v>
@@ -2713,22 +2719,22 @@
         <v>15</v>
       </c>
       <c r="BD8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BE8">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF8">
         <v>7.8</v>
       </c>
       <c r="BG8">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH8">
         <v>3.7</v>
       </c>
       <c r="BI8">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
@@ -2740,19 +2746,19 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8">
         <v>4.2</v>
       </c>
       <c r="BO8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP8">
         <v>10.5</v>
       </c>
       <c r="BQ8">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR8">
         <v>27</v>
@@ -2770,7 +2776,7 @@
         <v>65</v>
       </c>
       <c r="BW8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX8">
         <v>70</v>
@@ -2779,13 +2785,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BZ8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA8">
         <v>6.8</v>
       </c>
       <c r="CB8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2793,178 +2799,178 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="G9">
-        <v>990</v>
+        <v>1.81</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
-        <v>1.06</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="O9">
+        <v>1.27</v>
+      </c>
+      <c r="P9">
+        <v>2.02</v>
+      </c>
+      <c r="Q9">
+        <v>1.78</v>
+      </c>
+      <c r="R9">
+        <v>1.4</v>
+      </c>
+      <c r="S9">
+        <v>2.88</v>
+      </c>
+      <c r="T9">
+        <v>1.81</v>
+      </c>
+      <c r="U9">
+        <v>2</v>
+      </c>
+      <c r="V9">
         <v>1.17</v>
       </c>
-      <c r="P9">
-        <v>1.24</v>
-      </c>
-      <c r="Q9">
-        <v>1.17</v>
-      </c>
-      <c r="R9">
-        <v>1.18</v>
-      </c>
-      <c r="S9">
-        <v>1.31</v>
-      </c>
-      <c r="T9">
-        <v>1.11</v>
-      </c>
-      <c r="U9">
-        <v>1.11</v>
-      </c>
-      <c r="V9">
-        <v>1.01</v>
-      </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3027,7 +3033,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3035,31 +3041,31 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
         <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F10">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="G10">
-        <v>990</v>
+        <v>3.75</v>
       </c>
       <c r="H10">
-        <v>1.12</v>
+        <v>2.2</v>
       </c>
       <c r="I10">
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.24</v>
+        <v>3.6</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3071,7 +3077,7 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.26</v>
+        <v>1.82</v>
       </c>
       <c r="O10">
         <v>1.2</v>
@@ -3098,7 +3104,7 @@
         <v>1.11</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3269,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3277,58 +3283,58 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
         <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F11">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
       <c r="G11">
         <v>990</v>
       </c>
       <c r="H11">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>990</v>
       </c>
       <c r="J11">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P11">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="Q11">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="R11">
         <v>1.15</v>
       </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>3.3</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3337,10 +3343,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3511,7 +3517,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3519,175 +3525,175 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
         <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F12">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H12">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I12">
         <v>2.6</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12">
+        <v>4.2</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.04</v>
+      </c>
+      <c r="N12">
         <v>3.8</v>
       </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.06</v>
-      </c>
-      <c r="N12">
-        <v>3.7</v>
-      </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P12">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R12">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T12">
-        <v>1.69</v>
+        <v>1.12</v>
       </c>
       <c r="U12">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W12">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>19.5</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>16</v>
+      </c>
+      <c r="AC12">
+        <v>9.6</v>
+      </c>
+      <c r="AD12">
+        <v>14</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>27</v>
+      </c>
+      <c r="AG12">
         <v>16.5</v>
       </c>
-      <c r="Y12">
-        <v>13</v>
-      </c>
-      <c r="Z12">
+      <c r="AH12">
+        <v>20</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.77</v>
+      </c>
+      <c r="AQ12">
+        <v>1.77</v>
+      </c>
+      <c r="AR12">
+        <v>1.63</v>
+      </c>
+      <c r="AS12">
+        <v>1.78</v>
+      </c>
+      <c r="AT12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU12">
+        <v>1.5</v>
+      </c>
+      <c r="AV12">
+        <v>1.58</v>
+      </c>
+      <c r="AW12">
         <v>19</v>
       </c>
-      <c r="AA12">
-        <v>38</v>
-      </c>
-      <c r="AB12">
-        <v>14</v>
-      </c>
-      <c r="AC12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12">
-        <v>13.5</v>
-      </c>
-      <c r="AE12">
-        <v>30</v>
-      </c>
-      <c r="AF12">
-        <v>26</v>
-      </c>
-      <c r="AG12">
-        <v>16</v>
-      </c>
-      <c r="AH12">
-        <v>17.5</v>
-      </c>
-      <c r="AI12">
-        <v>42</v>
-      </c>
-      <c r="AJ12">
-        <v>60</v>
-      </c>
-      <c r="AK12">
-        <v>40</v>
-      </c>
-      <c r="AL12">
-        <v>46</v>
-      </c>
-      <c r="AM12">
-        <v>95</v>
-      </c>
-      <c r="AN12">
-        <v>32</v>
-      </c>
-      <c r="AO12">
-        <v>22</v>
-      </c>
-      <c r="AP12">
-        <v>13</v>
-      </c>
-      <c r="AQ12">
-        <v>9.6</v>
-      </c>
-      <c r="AR12">
-        <v>13.5</v>
-      </c>
-      <c r="AS12">
-        <v>5.4</v>
-      </c>
-      <c r="AT12">
-        <v>11</v>
-      </c>
-      <c r="AU12">
-        <v>3.65</v>
-      </c>
-      <c r="AV12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW12">
-        <v>5.2</v>
-      </c>
       <c r="AX12">
-        <v>5</v>
+        <v>1.67</v>
       </c>
       <c r="AY12">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="AZ12">
-        <v>4.6</v>
+        <v>1.63</v>
       </c>
       <c r="BA12">
-        <v>5.4</v>
+        <v>1.78</v>
       </c>
       <c r="BB12">
-        <v>5.7</v>
+        <v>1.78</v>
       </c>
       <c r="BC12">
-        <v>5.4</v>
+        <v>1.78</v>
       </c>
       <c r="BD12">
-        <v>5.5</v>
+        <v>1.78</v>
       </c>
       <c r="BE12">
-        <v>5.9</v>
+        <v>1.78</v>
       </c>
       <c r="BF12">
-        <v>19</v>
+        <v>1.78</v>
       </c>
       <c r="BG12">
         <v>14.5</v>
@@ -3753,249 +3759,249 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
         <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F13">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G13">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="H13">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I13">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="J13">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L13">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="P13">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="Q13">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="R13">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="S13">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="T13">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="U13">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="V13">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W13">
         <v>2.12</v>
       </c>
       <c r="X13">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="Y13">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Z13">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA13">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD13">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AE13">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AF13">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI13">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AJ13">
         <v>24</v>
       </c>
       <c r="AK13">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AM13">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AN13">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO13">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AP13">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AQ13">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR13">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS13">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT13">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13">
         <v>7.8</v>
       </c>
       <c r="AV13">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AW13">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AX13">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ13">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BB13">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC13">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BD13">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="BE13">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF13">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BG13">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BH13">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CA13">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4003,7 +4009,7 @@
         <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
         <v>104</v>
@@ -4012,94 +4018,94 @@
         <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F14">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H14">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I14">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J14">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
         <v>3.85</v>
       </c>
       <c r="L14">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M14">
         <v>1.06</v>
       </c>
       <c r="N14">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O14">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P14">
         <v>2</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="R14">
         <v>1.39</v>
       </c>
       <c r="S14">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T14">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="U14">
         <v>2.22</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z14">
         <v>19</v>
       </c>
       <c r="AA14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AB14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC14">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14">
         <v>13</v>
       </c>
       <c r="AE14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG14">
         <v>13.5</v>
       </c>
       <c r="AH14">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI14">
         <v>40</v>
@@ -4108,10 +4114,10 @@
         <v>65</v>
       </c>
       <c r="AK14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL14">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AM14">
         <v>100</v>
@@ -4120,31 +4126,31 @@
         <v>26</v>
       </c>
       <c r="AO14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ14">
         <v>10</v>
       </c>
       <c r="AR14">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AS14">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="AT14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV14">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW14">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="AX14">
         <v>17</v>
@@ -4153,82 +4159,82 @@
         <v>10</v>
       </c>
       <c r="AZ14">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB14">
         <v>27</v>
       </c>
       <c r="BC14">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="BD14">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="BE14">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG14">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4237,249 +4243,249 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
         <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F15">
-        <v>1.79</v>
+        <v>2.54</v>
       </c>
       <c r="G15">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="H15">
+        <v>3.1</v>
+      </c>
+      <c r="I15">
+        <v>3.8</v>
+      </c>
+      <c r="J15">
+        <v>2.8</v>
+      </c>
+      <c r="K15">
+        <v>3.25</v>
+      </c>
+      <c r="L15">
+        <v>1.5</v>
+      </c>
+      <c r="M15">
+        <v>1.13</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.48</v>
+      </c>
+      <c r="Q15">
+        <v>2.62</v>
+      </c>
+      <c r="R15">
+        <v>1.19</v>
+      </c>
+      <c r="S15">
+        <v>1.05</v>
+      </c>
+      <c r="T15">
+        <v>2.08</v>
+      </c>
+      <c r="U15">
+        <v>1.73</v>
+      </c>
+      <c r="V15">
+        <v>1.33</v>
+      </c>
+      <c r="W15">
+        <v>1.52</v>
+      </c>
+      <c r="X15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y15">
+        <v>11</v>
+      </c>
+      <c r="Z15">
+        <v>23</v>
+      </c>
+      <c r="AA15">
+        <v>85</v>
+      </c>
+      <c r="AB15">
+        <v>9.4</v>
+      </c>
+      <c r="AC15">
+        <v>7.4</v>
+      </c>
+      <c r="AD15">
+        <v>16</v>
+      </c>
+      <c r="AE15">
+        <v>65</v>
+      </c>
+      <c r="AF15">
+        <v>19.5</v>
+      </c>
+      <c r="AG15">
+        <v>14</v>
+      </c>
+      <c r="AH15">
+        <v>29</v>
+      </c>
+      <c r="AI15">
+        <v>100</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>50</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>60</v>
+      </c>
+      <c r="AO15">
+        <v>90</v>
+      </c>
+      <c r="AP15">
+        <v>3.1</v>
+      </c>
+      <c r="AQ15">
+        <v>3.2</v>
+      </c>
+      <c r="AR15">
+        <v>3.8</v>
+      </c>
+      <c r="AS15">
         <v>4.3</v>
       </c>
-      <c r="I15">
-        <v>4.9</v>
-      </c>
-      <c r="J15">
-        <v>4</v>
-      </c>
-      <c r="K15">
+      <c r="AT15">
+        <v>3.05</v>
+      </c>
+      <c r="AU15">
+        <v>2.82</v>
+      </c>
+      <c r="AV15">
+        <v>3.55</v>
+      </c>
+      <c r="AW15">
+        <v>4.2</v>
+      </c>
+      <c r="AX15">
+        <v>3.7</v>
+      </c>
+      <c r="AY15">
+        <v>3.45</v>
+      </c>
+      <c r="AZ15">
+        <v>3.95</v>
+      </c>
+      <c r="BA15">
+        <v>4.3</v>
+      </c>
+      <c r="BB15">
         <v>4.5</v>
       </c>
-      <c r="L15">
-        <v>1.26</v>
-      </c>
-      <c r="M15">
-        <v>1.04</v>
-      </c>
-      <c r="N15">
-        <v>5</v>
-      </c>
-      <c r="O15">
-        <v>1.21</v>
-      </c>
-      <c r="P15">
-        <v>2.4</v>
-      </c>
-      <c r="Q15">
-        <v>1.62</v>
-      </c>
-      <c r="R15">
-        <v>1.57</v>
-      </c>
-      <c r="S15">
-        <v>2.52</v>
-      </c>
-      <c r="T15">
-        <v>1.63</v>
-      </c>
-      <c r="U15">
-        <v>2.38</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>25</v>
-      </c>
-      <c r="Y15">
-        <v>24</v>
-      </c>
-      <c r="Z15">
-        <v>38</v>
-      </c>
-      <c r="AA15">
-        <v>110</v>
-      </c>
-      <c r="AB15">
-        <v>13.5</v>
-      </c>
-      <c r="AC15">
-        <v>10</v>
-      </c>
-      <c r="AD15">
-        <v>22</v>
-      </c>
-      <c r="AE15">
-        <v>60</v>
-      </c>
-      <c r="AF15">
-        <v>15</v>
-      </c>
-      <c r="AG15">
-        <v>11</v>
-      </c>
-      <c r="AH15">
-        <v>19</v>
-      </c>
-      <c r="AI15">
-        <v>55</v>
-      </c>
-      <c r="AJ15">
-        <v>21</v>
-      </c>
-      <c r="AK15">
-        <v>17.5</v>
-      </c>
-      <c r="AL15">
-        <v>28</v>
-      </c>
-      <c r="AM15">
-        <v>70</v>
-      </c>
-      <c r="AN15">
-        <v>8.6</v>
-      </c>
-      <c r="AO15">
-        <v>46</v>
-      </c>
-      <c r="AP15">
-        <v>19</v>
-      </c>
-      <c r="AQ15">
-        <v>18.5</v>
-      </c>
-      <c r="AR15">
-        <v>6.6</v>
-      </c>
-      <c r="AS15">
-        <v>7.4</v>
-      </c>
-      <c r="AT15">
-        <v>10</v>
-      </c>
-      <c r="AU15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV15">
-        <v>14</v>
-      </c>
-      <c r="AW15">
-        <v>7</v>
-      </c>
-      <c r="AX15">
-        <v>11.5</v>
-      </c>
-      <c r="AY15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15">
-        <v>12.5</v>
-      </c>
-      <c r="BA15">
-        <v>7</v>
-      </c>
-      <c r="BB15">
-        <v>17.5</v>
-      </c>
       <c r="BC15">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD15">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE15">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF15">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="BG15">
-        <v>32</v>
+        <v>4.3</v>
       </c>
       <c r="BH15">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4487,7 +4493,7 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
         <v>105</v>
@@ -4496,169 +4502,169 @@
         <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F16">
+        <v>3.1</v>
+      </c>
+      <c r="G16">
+        <v>3.85</v>
+      </c>
+      <c r="H16">
+        <v>2.46</v>
+      </c>
+      <c r="I16">
+        <v>2.86</v>
+      </c>
+      <c r="J16">
+        <v>2.82</v>
+      </c>
+      <c r="K16">
+        <v>3.7</v>
+      </c>
+      <c r="L16">
+        <v>1.47</v>
+      </c>
+      <c r="M16">
+        <v>1.12</v>
+      </c>
+      <c r="N16">
+        <v>2.48</v>
+      </c>
+      <c r="O16">
+        <v>1.5</v>
+      </c>
+      <c r="P16">
+        <v>1.52</v>
+      </c>
+      <c r="Q16">
+        <v>2.54</v>
+      </c>
+      <c r="R16">
+        <v>1.15</v>
+      </c>
+      <c r="S16">
+        <v>4.5</v>
+      </c>
+      <c r="T16">
+        <v>2.04</v>
+      </c>
+      <c r="U16">
         <v>1.76</v>
       </c>
-      <c r="G16">
-        <v>2.2</v>
-      </c>
-      <c r="H16">
-        <v>4.2</v>
-      </c>
-      <c r="I16">
-        <v>7.4</v>
-      </c>
-      <c r="J16">
-        <v>2.84</v>
-      </c>
-      <c r="K16">
-        <v>3.6</v>
-      </c>
-      <c r="L16">
-        <v>1.44</v>
-      </c>
-      <c r="M16">
-        <v>1.06</v>
-      </c>
-      <c r="N16">
-        <v>2.14</v>
-      </c>
-      <c r="O16">
-        <v>1.22</v>
-      </c>
-      <c r="P16">
-        <v>1.43</v>
-      </c>
-      <c r="Q16">
-        <v>2.18</v>
-      </c>
-      <c r="R16">
-        <v>1.13</v>
-      </c>
-      <c r="S16">
-        <v>2.6</v>
-      </c>
-      <c r="T16">
-        <v>1.11</v>
-      </c>
-      <c r="U16">
-        <v>1.11</v>
-      </c>
       <c r="V16">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
+        <v>1.35</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z16">
+        <v>19.5</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>8.6</v>
+      </c>
+      <c r="AD16">
+        <v>16</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>28</v>
+      </c>
+      <c r="AG16">
+        <v>19</v>
+      </c>
+      <c r="AH16">
+        <v>950</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.83</v>
+      </c>
+      <c r="AQ16">
+        <v>1.55</v>
+      </c>
+      <c r="AR16">
+        <v>1.68</v>
+      </c>
+      <c r="AS16">
         <v>1.84</v>
       </c>
-      <c r="X16">
-        <v>1000</v>
-      </c>
-      <c r="Y16">
-        <v>1000</v>
-      </c>
-      <c r="Z16">
-        <v>1000</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>1000</v>
-      </c>
-      <c r="AC16">
-        <v>1000</v>
-      </c>
-      <c r="AD16">
-        <v>1000</v>
-      </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>1000</v>
-      </c>
-      <c r="AG16">
-        <v>1000</v>
-      </c>
-      <c r="AH16">
-        <v>1000</v>
-      </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
-        <v>1000</v>
-      </c>
-      <c r="AK16">
-        <v>1000</v>
-      </c>
-      <c r="AL16">
-        <v>1000</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>1000</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>1.01</v>
-      </c>
-      <c r="AQ16">
-        <v>1.01</v>
-      </c>
-      <c r="AR16">
-        <v>1.01</v>
-      </c>
-      <c r="AS16">
-        <v>1.01</v>
-      </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4721,7 +4727,7 @@
         <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4729,7 +4735,7 @@
         <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
         <v>105</v>
@@ -4738,61 +4744,61 @@
         <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F17">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M17">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N17">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="O17">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="P17">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="R17">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="S17">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="T17">
-        <v>2.66</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="W17">
-        <v>3.35</v>
+        <v>1.84</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4903,67 +4909,67 @@
         <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4971,7 +4977,7 @@
         <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
         <v>105</v>
@@ -4980,420 +4986,420 @@
         <v>129</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F18">
+        <v>1.33</v>
+      </c>
+      <c r="G18">
+        <v>1.41</v>
+      </c>
+      <c r="H18">
+        <v>9.6</v>
+      </c>
+      <c r="I18">
+        <v>19</v>
+      </c>
+      <c r="J18">
+        <v>4.4</v>
+      </c>
+      <c r="K18">
+        <v>5.3</v>
+      </c>
+      <c r="L18">
+        <v>1.36</v>
+      </c>
+      <c r="M18">
+        <v>1.08</v>
+      </c>
+      <c r="N18">
+        <v>2.74</v>
+      </c>
+      <c r="O18">
+        <v>1.39</v>
+      </c>
+      <c r="P18">
+        <v>1.83</v>
+      </c>
+      <c r="Q18">
+        <v>1.99</v>
+      </c>
+      <c r="R18">
+        <v>1.25</v>
+      </c>
+      <c r="S18">
+        <v>3.25</v>
+      </c>
+      <c r="T18">
+        <v>2.66</v>
+      </c>
+      <c r="U18">
+        <v>1.47</v>
+      </c>
+      <c r="V18">
+        <v>1.05</v>
+      </c>
+      <c r="W18">
+        <v>3.3</v>
+      </c>
+      <c r="X18">
+        <v>15</v>
+      </c>
+      <c r="Y18">
+        <v>38</v>
+      </c>
+      <c r="Z18">
+        <v>190</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>6.8</v>
+      </c>
+      <c r="AC18">
+        <v>14.5</v>
+      </c>
+      <c r="AD18">
+        <v>950</v>
+      </c>
+      <c r="AE18">
+        <v>530</v>
+      </c>
+      <c r="AF18">
+        <v>7.8</v>
+      </c>
+      <c r="AG18">
+        <v>14</v>
+      </c>
+      <c r="AH18">
+        <v>60</v>
+      </c>
+      <c r="AI18">
+        <v>430</v>
+      </c>
+      <c r="AJ18">
+        <v>12.5</v>
+      </c>
+      <c r="AK18">
+        <v>24</v>
+      </c>
+      <c r="AL18">
+        <v>85</v>
+      </c>
+      <c r="AM18">
+        <v>530</v>
+      </c>
+      <c r="AN18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>3.6</v>
+      </c>
+      <c r="AQ18">
+        <v>4.2</v>
+      </c>
+      <c r="AR18">
+        <v>4.6</v>
+      </c>
+      <c r="AS18">
+        <v>4.8</v>
+      </c>
+      <c r="AT18">
+        <v>2.8</v>
+      </c>
+      <c r="AU18">
+        <v>3.6</v>
+      </c>
+      <c r="AV18">
+        <v>4.5</v>
+      </c>
+      <c r="AW18">
+        <v>4.7</v>
+      </c>
+      <c r="AX18">
+        <v>2.96</v>
+      </c>
+      <c r="AY18">
+        <v>3.55</v>
+      </c>
+      <c r="AZ18">
+        <v>4.4</v>
+      </c>
+      <c r="BA18">
+        <v>4.7</v>
+      </c>
+      <c r="BB18">
+        <v>3.45</v>
+      </c>
+      <c r="BC18">
+        <v>4</v>
+      </c>
+      <c r="BD18">
+        <v>4.5</v>
+      </c>
+      <c r="BE18">
+        <v>4.7</v>
+      </c>
+      <c r="BF18">
         <v>3.15</v>
       </c>
-      <c r="G18">
-        <v>4</v>
-      </c>
-      <c r="H18">
-        <v>2.48</v>
-      </c>
-      <c r="I18">
-        <v>2.84</v>
-      </c>
-      <c r="J18">
-        <v>2.66</v>
-      </c>
-      <c r="K18">
-        <v>3.25</v>
-      </c>
-      <c r="L18">
-        <v>1.55</v>
-      </c>
-      <c r="M18">
-        <v>1.12</v>
-      </c>
-      <c r="N18">
-        <v>2.6</v>
-      </c>
-      <c r="O18">
-        <v>1.53</v>
-      </c>
-      <c r="P18">
-        <v>1.52</v>
-      </c>
-      <c r="Q18">
-        <v>2.52</v>
-      </c>
-      <c r="R18">
-        <v>1.18</v>
-      </c>
-      <c r="S18">
-        <v>3.95</v>
-      </c>
-      <c r="T18">
-        <v>2.08</v>
-      </c>
-      <c r="U18">
-        <v>1.79</v>
-      </c>
-      <c r="V18">
-        <v>1.54</v>
-      </c>
-      <c r="W18">
-        <v>1.33</v>
-      </c>
-      <c r="X18">
-        <v>9</v>
-      </c>
-      <c r="Y18">
-        <v>9</v>
-      </c>
-      <c r="Z18">
-        <v>16.5</v>
-      </c>
-      <c r="AA18">
-        <v>55</v>
-      </c>
-      <c r="AB18">
-        <v>11</v>
-      </c>
-      <c r="AC18">
-        <v>8.4</v>
-      </c>
-      <c r="AD18">
-        <v>13.5</v>
-      </c>
-      <c r="AE18">
-        <v>46</v>
-      </c>
-      <c r="AF18">
-        <v>27</v>
-      </c>
-      <c r="AG18">
-        <v>16</v>
-      </c>
-      <c r="AH18">
-        <v>24</v>
-      </c>
-      <c r="AI18">
-        <v>80</v>
-      </c>
-      <c r="AJ18">
-        <v>85</v>
-      </c>
-      <c r="AK18">
-        <v>65</v>
-      </c>
-      <c r="AL18">
-        <v>95</v>
-      </c>
-      <c r="AM18">
-        <v>220</v>
-      </c>
-      <c r="AN18">
-        <v>85</v>
-      </c>
-      <c r="AO18">
-        <v>55</v>
-      </c>
-      <c r="AP18">
-        <v>3.55</v>
-      </c>
-      <c r="AQ18">
-        <v>3.55</v>
-      </c>
-      <c r="AR18">
-        <v>4.3</v>
-      </c>
-      <c r="AS18">
-        <v>5.3</v>
-      </c>
-      <c r="AT18">
-        <v>3.85</v>
-      </c>
-      <c r="AU18">
-        <v>5.3</v>
-      </c>
-      <c r="AV18">
-        <v>4.1</v>
-      </c>
-      <c r="AW18">
-        <v>5.2</v>
-      </c>
-      <c r="AX18">
+      <c r="BG18">
         <v>4.8</v>
       </c>
-      <c r="AY18">
-        <v>4.3</v>
-      </c>
-      <c r="AZ18">
-        <v>4.7</v>
-      </c>
-      <c r="BA18">
-        <v>5.5</v>
-      </c>
-      <c r="BB18">
-        <v>5.5</v>
-      </c>
-      <c r="BC18">
-        <v>5.4</v>
-      </c>
-      <c r="BD18">
-        <v>5.6</v>
-      </c>
-      <c r="BE18">
-        <v>5.8</v>
-      </c>
-      <c r="BF18">
-        <v>5.5</v>
-      </c>
-      <c r="BG18">
-        <v>5.3</v>
-      </c>
       <c r="BH18">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
         <v>130</v>
       </c>
       <c r="E19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F19">
-        <v>2.54</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G19">
-        <v>2.88</v>
+        <v>11.5</v>
       </c>
       <c r="H19">
+        <v>1.31</v>
+      </c>
+      <c r="I19">
+        <v>1.37</v>
+      </c>
+      <c r="J19">
+        <v>6.2</v>
+      </c>
+      <c r="K19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L19">
+        <v>1.17</v>
+      </c>
+      <c r="M19">
+        <v>1.02</v>
+      </c>
+      <c r="N19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O19">
+        <v>1.11</v>
+      </c>
+      <c r="P19">
+        <v>3.45</v>
+      </c>
+      <c r="Q19">
+        <v>1.34</v>
+      </c>
+      <c r="R19">
+        <v>2.02</v>
+      </c>
+      <c r="S19">
+        <v>1.9</v>
+      </c>
+      <c r="T19">
+        <v>1.66</v>
+      </c>
+      <c r="U19">
+        <v>2.28</v>
+      </c>
+      <c r="V19">
+        <v>3.7</v>
+      </c>
+      <c r="W19">
+        <v>1.1</v>
+      </c>
+      <c r="X19">
+        <v>950</v>
+      </c>
+      <c r="Y19">
+        <v>16.5</v>
+      </c>
+      <c r="Z19">
+        <v>13</v>
+      </c>
+      <c r="AA19">
+        <v>13</v>
+      </c>
+      <c r="AB19">
+        <v>950</v>
+      </c>
+      <c r="AC19">
+        <v>17</v>
+      </c>
+      <c r="AD19">
+        <v>12</v>
+      </c>
+      <c r="AE19">
+        <v>14</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>950</v>
+      </c>
+      <c r="AH19">
+        <v>24</v>
+      </c>
+      <c r="AI19">
+        <v>26</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>80</v>
+      </c>
+      <c r="AM19">
+        <v>80</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>3.5</v>
+      </c>
+      <c r="AP19">
+        <v>7.4</v>
+      </c>
+      <c r="AQ19">
+        <v>14</v>
+      </c>
+      <c r="AR19">
+        <v>11</v>
+      </c>
+      <c r="AS19">
+        <v>11</v>
+      </c>
+      <c r="AT19">
+        <v>7.4</v>
+      </c>
+      <c r="AU19">
+        <v>14.5</v>
+      </c>
+      <c r="AV19">
+        <v>10</v>
+      </c>
+      <c r="AW19">
+        <v>11.5</v>
+      </c>
+      <c r="AX19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY19">
+        <v>7</v>
+      </c>
+      <c r="AZ19">
+        <v>20</v>
+      </c>
+      <c r="BA19">
+        <v>6.6</v>
+      </c>
+      <c r="BB19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD19">
+        <v>7.8</v>
+      </c>
+      <c r="BE19">
+        <v>7.8</v>
+      </c>
+      <c r="BF19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG19">
         <v>3.1</v>
       </c>
-      <c r="I19">
-        <v>3.8</v>
-      </c>
-      <c r="J19">
-        <v>2.8</v>
-      </c>
-      <c r="K19">
-        <v>3.25</v>
-      </c>
-      <c r="L19">
-        <v>1.5</v>
-      </c>
-      <c r="M19">
-        <v>1.11</v>
-      </c>
-      <c r="N19">
-        <v>2.42</v>
-      </c>
-      <c r="O19">
-        <v>1.55</v>
-      </c>
-      <c r="P19">
-        <v>1.48</v>
-      </c>
-      <c r="Q19">
-        <v>2.64</v>
-      </c>
-      <c r="R19">
-        <v>1.17</v>
-      </c>
-      <c r="S19">
-        <v>1.05</v>
-      </c>
-      <c r="T19">
-        <v>2.08</v>
-      </c>
-      <c r="U19">
-        <v>1.73</v>
-      </c>
-      <c r="V19">
-        <v>1.37</v>
-      </c>
-      <c r="W19">
-        <v>1.53</v>
-      </c>
-      <c r="X19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y19">
-        <v>11</v>
-      </c>
-      <c r="Z19">
-        <v>26</v>
-      </c>
-      <c r="AA19">
-        <v>85</v>
-      </c>
-      <c r="AB19">
-        <v>9.4</v>
-      </c>
-      <c r="AC19">
-        <v>8.4</v>
-      </c>
-      <c r="AD19">
-        <v>18.5</v>
-      </c>
-      <c r="AE19">
-        <v>65</v>
-      </c>
-      <c r="AF19">
-        <v>19.5</v>
-      </c>
-      <c r="AG19">
-        <v>16</v>
-      </c>
-      <c r="AH19">
-        <v>29</v>
-      </c>
-      <c r="AI19">
-        <v>100</v>
-      </c>
-      <c r="AJ19">
-        <v>60</v>
-      </c>
-      <c r="AK19">
-        <v>50</v>
-      </c>
-      <c r="AL19">
-        <v>85</v>
-      </c>
-      <c r="AM19">
-        <v>240</v>
-      </c>
-      <c r="AN19">
-        <v>60</v>
-      </c>
-      <c r="AO19">
-        <v>90</v>
-      </c>
-      <c r="AP19">
-        <v>3.05</v>
-      </c>
-      <c r="AQ19">
-        <v>3.15</v>
-      </c>
-      <c r="AR19">
-        <v>3.8</v>
-      </c>
-      <c r="AS19">
-        <v>4.2</v>
-      </c>
-      <c r="AT19">
-        <v>3</v>
-      </c>
-      <c r="AU19">
-        <v>2.92</v>
-      </c>
-      <c r="AV19">
-        <v>3.6</v>
-      </c>
-      <c r="AW19">
-        <v>4.1</v>
-      </c>
-      <c r="AX19">
-        <v>3.6</v>
-      </c>
-      <c r="AY19">
-        <v>3.45</v>
-      </c>
-      <c r="AZ19">
-        <v>3.85</v>
-      </c>
-      <c r="BA19">
-        <v>4.2</v>
-      </c>
-      <c r="BB19">
-        <v>4.1</v>
-      </c>
-      <c r="BC19">
-        <v>4.1</v>
-      </c>
-      <c r="BD19">
-        <v>4.2</v>
-      </c>
-      <c r="BE19">
-        <v>4.3</v>
-      </c>
-      <c r="BF19">
-        <v>4.1</v>
-      </c>
-      <c r="BG19">
-        <v>4.2</v>
-      </c>
       <c r="BH19">
-        <v>2.72</v>
+        <v>5.9</v>
       </c>
       <c r="BI19">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="BJ19">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK19">
         <v>5.8</v>
@@ -5402,52 +5408,52 @@
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>2.16</v>
+        <v>11</v>
       </c>
       <c r="BN19">
+        <v>13.5</v>
+      </c>
+      <c r="BO19">
+        <v>6.6</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>10.5</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>10</v>
+      </c>
+      <c r="BT19">
+        <v>4.6</v>
+      </c>
+      <c r="BU19">
+        <v>3.5</v>
+      </c>
+      <c r="BV19">
+        <v>7.6</v>
+      </c>
+      <c r="BW19">
         <v>5.6</v>
       </c>
-      <c r="BO19">
-        <v>3.7</v>
-      </c>
-      <c r="BP19">
-        <v>26</v>
-      </c>
-      <c r="BQ19">
-        <v>2.02</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>2.1</v>
-      </c>
-      <c r="BT19">
-        <v>6.4</v>
-      </c>
-      <c r="BU19">
-        <v>4</v>
-      </c>
-      <c r="BV19">
-        <v>34</v>
-      </c>
-      <c r="BW19">
-        <v>2.06</v>
-      </c>
       <c r="BX19">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="BY19">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="BZ19">
-        <v>60</v>
+        <v>7.8</v>
       </c>
       <c r="CA19">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="CB19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5455,7 +5461,7 @@
         <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
         <v>106</v>
@@ -5464,482 +5470,482 @@
         <v>131</v>
       </c>
       <c r="E20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F20">
+        <v>1.73</v>
+      </c>
+      <c r="G20">
+        <v>1.86</v>
+      </c>
+      <c r="H20">
+        <v>4.4</v>
+      </c>
+      <c r="I20">
+        <v>5.1</v>
+      </c>
+      <c r="J20">
+        <v>4</v>
+      </c>
+      <c r="K20">
+        <v>4.7</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.04</v>
+      </c>
+      <c r="N20">
+        <v>4.7</v>
+      </c>
+      <c r="O20">
+        <v>1.21</v>
+      </c>
+      <c r="P20">
+        <v>2.32</v>
+      </c>
+      <c r="Q20">
+        <v>1.61</v>
+      </c>
+      <c r="R20">
+        <v>1.49</v>
+      </c>
+      <c r="S20">
+        <v>2.52</v>
+      </c>
+      <c r="T20">
+        <v>1.63</v>
+      </c>
+      <c r="U20">
+        <v>2.26</v>
+      </c>
+      <c r="V20">
+        <v>1.24</v>
+      </c>
+      <c r="W20">
+        <v>2.16</v>
+      </c>
+      <c r="X20">
+        <v>23</v>
+      </c>
+      <c r="Y20">
+        <v>24</v>
+      </c>
+      <c r="Z20">
+        <v>44</v>
+      </c>
+      <c r="AA20">
+        <v>110</v>
+      </c>
+      <c r="AB20">
+        <v>13.5</v>
+      </c>
+      <c r="AC20">
+        <v>11.5</v>
+      </c>
+      <c r="AD20">
+        <v>22</v>
+      </c>
+      <c r="AE20">
+        <v>60</v>
+      </c>
+      <c r="AF20">
+        <v>13.5</v>
+      </c>
+      <c r="AG20">
+        <v>12</v>
+      </c>
+      <c r="AH20">
+        <v>20</v>
+      </c>
+      <c r="AI20">
+        <v>60</v>
+      </c>
+      <c r="AJ20">
+        <v>23</v>
+      </c>
+      <c r="AK20">
+        <v>20</v>
+      </c>
+      <c r="AL20">
+        <v>34</v>
+      </c>
+      <c r="AM20">
+        <v>85</v>
+      </c>
+      <c r="AN20">
+        <v>10</v>
+      </c>
+      <c r="AO20">
+        <v>55</v>
+      </c>
+      <c r="AP20">
+        <v>18.5</v>
+      </c>
+      <c r="AQ20">
+        <v>17.5</v>
+      </c>
+      <c r="AR20">
+        <v>4.8</v>
+      </c>
+      <c r="AS20">
+        <v>5.2</v>
+      </c>
+      <c r="AT20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU20">
+        <v>8.4</v>
+      </c>
+      <c r="AV20">
+        <v>15.5</v>
+      </c>
+      <c r="AW20">
+        <v>5</v>
+      </c>
+      <c r="AX20">
+        <v>10.5</v>
+      </c>
+      <c r="AY20">
         <v>8.800000000000001</v>
       </c>
-      <c r="G20">
-        <v>11.5</v>
-      </c>
-      <c r="H20">
-        <v>1.31</v>
-      </c>
-      <c r="I20">
-        <v>1.37</v>
-      </c>
-      <c r="J20">
-        <v>6.2</v>
-      </c>
-      <c r="K20">
-        <v>7.2</v>
-      </c>
-      <c r="L20">
-        <v>1.17</v>
-      </c>
-      <c r="M20">
-        <v>1.02</v>
-      </c>
-      <c r="N20">
-        <v>8.4</v>
-      </c>
-      <c r="O20">
-        <v>1.11</v>
-      </c>
-      <c r="P20">
-        <v>3.45</v>
-      </c>
-      <c r="Q20">
-        <v>1.34</v>
-      </c>
-      <c r="R20">
-        <v>2.02</v>
-      </c>
-      <c r="S20">
-        <v>1.9</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>3.7</v>
-      </c>
-      <c r="W20">
-        <v>1.1</v>
-      </c>
-      <c r="X20">
-        <v>55</v>
-      </c>
-      <c r="Y20">
-        <v>19</v>
-      </c>
-      <c r="Z20">
-        <v>15</v>
-      </c>
-      <c r="AA20">
-        <v>15</v>
-      </c>
-      <c r="AB20">
-        <v>60</v>
-      </c>
-      <c r="AC20">
-        <v>21</v>
-      </c>
-      <c r="AD20">
-        <v>13.5</v>
-      </c>
-      <c r="AE20">
-        <v>16</v>
-      </c>
-      <c r="AF20">
-        <v>120</v>
-      </c>
-      <c r="AG20">
-        <v>44</v>
-      </c>
-      <c r="AH20">
-        <v>28</v>
-      </c>
-      <c r="AI20">
-        <v>32</v>
-      </c>
-      <c r="AJ20">
-        <v>310</v>
-      </c>
-      <c r="AK20">
-        <v>130</v>
-      </c>
-      <c r="AL20">
-        <v>80</v>
-      </c>
-      <c r="AM20">
-        <v>95</v>
-      </c>
-      <c r="AN20">
-        <v>100</v>
-      </c>
-      <c r="AO20">
-        <v>3.5</v>
-      </c>
-      <c r="AP20">
-        <v>5.5</v>
-      </c>
-      <c r="AQ20">
-        <v>14</v>
-      </c>
-      <c r="AR20">
-        <v>11</v>
-      </c>
-      <c r="AS20">
-        <v>11</v>
-      </c>
-      <c r="AT20">
-        <v>5.5</v>
-      </c>
-      <c r="AU20">
-        <v>12</v>
-      </c>
-      <c r="AV20">
-        <v>10.5</v>
-      </c>
-      <c r="AW20">
-        <v>11.5</v>
-      </c>
-      <c r="AX20">
-        <v>5.8</v>
-      </c>
-      <c r="AY20">
-        <v>30</v>
-      </c>
       <c r="AZ20">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BA20">
+        <v>5</v>
+      </c>
+      <c r="BB20">
+        <v>16.5</v>
+      </c>
+      <c r="BC20">
+        <v>14.5</v>
+      </c>
+      <c r="BD20">
+        <v>6.4</v>
+      </c>
+      <c r="BE20">
         <v>5.1</v>
       </c>
-      <c r="BB20">
-        <v>6</v>
-      </c>
-      <c r="BC20">
-        <v>5.9</v>
-      </c>
-      <c r="BD20">
-        <v>5.7</v>
-      </c>
-      <c r="BE20">
-        <v>5.7</v>
-      </c>
       <c r="BF20">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG20">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH20">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
         <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F21">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="G21">
-        <v>1.93</v>
+        <v>990</v>
       </c>
       <c r="H21">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>990</v>
       </c>
       <c r="J21">
-        <v>3.95</v>
+        <v>1.06</v>
       </c>
       <c r="K21">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L21">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>4.7</v>
+        <v>1.25</v>
       </c>
       <c r="O21">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="P21">
-        <v>2.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q21">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="R21">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="S21">
-        <v>2.56</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="U21">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="V21">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W21">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CA21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
         <v>107</v>
@@ -5948,25 +5954,25 @@
         <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G22">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H22">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I22">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J22">
+        <v>3.4</v>
+      </c>
+      <c r="K22">
         <v>3.45</v>
-      </c>
-      <c r="K22">
-        <v>3.5</v>
       </c>
       <c r="L22">
         <v>1.44</v>
@@ -5978,13 +5984,13 @@
         <v>3.75</v>
       </c>
       <c r="O22">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P22">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q22">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R22">
         <v>1.35</v>
@@ -5996,22 +6002,22 @@
         <v>1.81</v>
       </c>
       <c r="U22">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V22">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W22">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X22">
         <v>13</v>
       </c>
       <c r="Y22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z22">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA22">
         <v>40</v>
@@ -6020,7 +6026,7 @@
         <v>11.5</v>
       </c>
       <c r="AC22">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD22">
         <v>12</v>
@@ -6029,7 +6035,7 @@
         <v>30</v>
       </c>
       <c r="AF22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG22">
         <v>13</v>
@@ -6038,37 +6044,37 @@
         <v>17.5</v>
       </c>
       <c r="AI22">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ22">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK22">
         <v>34</v>
       </c>
       <c r="AL22">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM22">
         <v>95</v>
       </c>
       <c r="AN22">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO22">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP22">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ22">
         <v>10</v>
       </c>
       <c r="AR22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT22">
         <v>10.5</v>
@@ -6083,7 +6089,7 @@
         <v>27</v>
       </c>
       <c r="AX22">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY22">
         <v>12</v>
@@ -6101,16 +6107,16 @@
         <v>30</v>
       </c>
       <c r="BD22">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE22">
         <v>75</v>
       </c>
       <c r="BF22">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BG22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH22">
         <v>3.25</v>
@@ -6119,34 +6125,34 @@
         <v>3.05</v>
       </c>
       <c r="BJ22">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK22">
         <v>8.4</v>
       </c>
       <c r="BL22">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM22">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN22">
         <v>5.9</v>
       </c>
       <c r="BO22">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP22">
         <v>24</v>
       </c>
       <c r="BQ22">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BR22">
         <v>38</v>
       </c>
       <c r="BS22">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT22">
         <v>5.6</v>
@@ -6155,33 +6161,33 @@
         <v>5.1</v>
       </c>
       <c r="BV22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW22">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BX22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY22">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ22">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CA22">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CB22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
         <v>108</v>
@@ -6190,7 +6196,7 @@
         <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F23">
         <v>1.35</v>
@@ -6202,46 +6208,46 @@
         <v>7.8</v>
       </c>
       <c r="I23">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="J23">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="K23">
         <v>7.2</v>
       </c>
       <c r="L23">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O23">
         <v>1.09</v>
       </c>
       <c r="P23">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="Q23">
         <v>1.27</v>
       </c>
       <c r="R23">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S23">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="T23">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U23">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="V23">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W23">
         <v>3.75</v>
@@ -6262,19 +6268,19 @@
         <v>23</v>
       </c>
       <c r="AC23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD23">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE23">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF23">
         <v>19</v>
       </c>
       <c r="AG23">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH23">
         <v>25</v>
@@ -6298,7 +6304,7 @@
         <v>3.45</v>
       </c>
       <c r="AO23">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP23">
         <v>5</v>
@@ -6307,7 +6313,7 @@
         <v>5</v>
       </c>
       <c r="AR23">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS23">
         <v>5.3</v>
@@ -6316,10 +6322,10 @@
         <v>4.4</v>
       </c>
       <c r="AU23">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV23">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW23">
         <v>5.1</v>
@@ -6349,64 +6355,64 @@
         <v>5</v>
       </c>
       <c r="BF23">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="BG23">
         <v>4.9</v>
       </c>
       <c r="BH23">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6415,7 +6421,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6423,7 +6429,7 @@
         <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
         <v>109</v>
@@ -6432,43 +6438,43 @@
         <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F24">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="G24">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I24">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J24">
         <v>2.86</v>
       </c>
       <c r="K24">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="L24">
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N24">
         <v>2.58</v>
       </c>
       <c r="O24">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="P24">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q24">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R24">
         <v>1.13</v>
@@ -6477,178 +6483,178 @@
         <v>2.8</v>
       </c>
       <c r="T24">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U24">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W24">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="X24">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6657,15 +6663,15 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
         <v>110</v>
@@ -6674,7 +6680,7 @@
         <v>136</v>
       </c>
       <c r="E25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -6899,15 +6905,15 @@
         <v>1.04</v>
       </c>
       <c r="CB25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
         <v>111</v>
@@ -6916,175 +6922,175 @@
         <v>137</v>
       </c>
       <c r="E26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F26">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="G26">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="H26">
+        <v>3.9</v>
+      </c>
+      <c r="I26">
         <v>4.4</v>
       </c>
-      <c r="I26">
-        <v>5.2</v>
-      </c>
       <c r="J26">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K26">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L26">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M26">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N26">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="O26">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P26">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q26">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R26">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S26">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T26">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="U26">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V26">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W26">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="X26">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL26">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AN26">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AO26">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ26">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AR26">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AS26">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AT26">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AU26">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV26">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AW26">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AX26">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AY26">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ26">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BA26">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB26">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BC26">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BD26">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BE26">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BF26">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BG26">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BH26">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BI26">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="BJ26">
         <v>13</v>
@@ -7096,34 +7102,34 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN26">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BO26">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BP26">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BQ26">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR26">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BS26">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT26">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU26">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV26">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BW26">
         <v>5.4</v>
@@ -7132,24 +7138,24 @@
         <v>1000</v>
       </c>
       <c r="BY26">
+        <v>5.6</v>
+      </c>
+      <c r="BZ26">
+        <v>55</v>
+      </c>
+      <c r="CA26">
         <v>5.5</v>
       </c>
-      <c r="BZ26">
-        <v>44</v>
-      </c>
-      <c r="CA26">
-        <v>5.3</v>
-      </c>
       <c r="CB26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
         <v>111</v>
@@ -7158,240 +7164,240 @@
         <v>138</v>
       </c>
       <c r="E27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F27">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="G27">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="H27">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="I27">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="J27">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="K27">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L27">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N27">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="O27">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="P27">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q27">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="R27">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S27">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="T27">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U27">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="Y27">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="Z27">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA27">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB27">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC27">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD27">
         <v>21</v>
       </c>
       <c r="AE27">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF27">
+        <v>13</v>
+      </c>
+      <c r="AG27">
+        <v>12.5</v>
+      </c>
+      <c r="AH27">
+        <v>1000</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>27</v>
+      </c>
+      <c r="AK27">
+        <v>28</v>
+      </c>
+      <c r="AL27">
+        <v>60</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>24</v>
+      </c>
+      <c r="AO27">
+        <v>130</v>
+      </c>
+      <c r="AP27">
+        <v>3.5</v>
+      </c>
+      <c r="AQ27">
+        <v>11</v>
+      </c>
+      <c r="AR27">
+        <v>4.4</v>
+      </c>
+      <c r="AS27">
+        <v>4.8</v>
+      </c>
+      <c r="AT27">
+        <v>6</v>
+      </c>
+      <c r="AU27">
+        <v>6.6</v>
+      </c>
+      <c r="AV27">
+        <v>16.5</v>
+      </c>
+      <c r="AW27">
+        <v>4.7</v>
+      </c>
+      <c r="AX27">
+        <v>9.6</v>
+      </c>
+      <c r="AY27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ27">
+        <v>19.5</v>
+      </c>
+      <c r="BA27">
+        <v>5</v>
+      </c>
+      <c r="BB27">
+        <v>21</v>
+      </c>
+      <c r="BC27">
+        <v>4.2</v>
+      </c>
+      <c r="BD27">
+        <v>4.6</v>
+      </c>
+      <c r="BE27">
+        <v>5</v>
+      </c>
+      <c r="BF27">
+        <v>17</v>
+      </c>
+      <c r="BG27">
+        <v>4.8</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.37</v>
+      </c>
+      <c r="BJ27">
         <v>15</v>
       </c>
-      <c r="AG27">
-        <v>12</v>
-      </c>
-      <c r="AH27">
-        <v>27</v>
-      </c>
-      <c r="AI27">
-        <v>100</v>
-      </c>
-      <c r="AJ27">
-        <v>42</v>
-      </c>
-      <c r="AK27">
-        <v>42</v>
-      </c>
-      <c r="AL27">
-        <v>80</v>
-      </c>
-      <c r="AM27">
-        <v>210</v>
-      </c>
-      <c r="AN27">
-        <v>40</v>
-      </c>
-      <c r="AO27">
-        <v>120</v>
-      </c>
-      <c r="AP27">
-        <v>7.8</v>
-      </c>
-      <c r="AQ27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR27">
-        <v>20</v>
-      </c>
-      <c r="AS27">
+      <c r="BK27">
+        <v>1.26</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.37</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>3.3</v>
+      </c>
+      <c r="BP27">
+        <v>21</v>
+      </c>
+      <c r="BQ27">
+        <v>1.29</v>
+      </c>
+      <c r="BR27">
+        <v>50</v>
+      </c>
+      <c r="BS27">
+        <v>1.34</v>
+      </c>
+      <c r="BT27">
         <v>10</v>
       </c>
-      <c r="AT27">
-        <v>6.4</v>
-      </c>
-      <c r="AU27">
-        <v>6.4</v>
-      </c>
-      <c r="AV27">
-        <v>7</v>
-      </c>
-      <c r="AW27">
-        <v>9.6</v>
-      </c>
-      <c r="AX27">
-        <v>11</v>
-      </c>
-      <c r="AY27">
-        <v>10</v>
-      </c>
-      <c r="AZ27">
-        <v>7.6</v>
-      </c>
-      <c r="BA27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB27">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC27">
-        <v>22</v>
-      </c>
-      <c r="BD27">
-        <v>36</v>
-      </c>
-      <c r="BE27">
-        <v>10</v>
-      </c>
-      <c r="BF27">
-        <v>8</v>
-      </c>
-      <c r="BG27">
-        <v>10</v>
-      </c>
-      <c r="BH27">
-        <v>2.78</v>
-      </c>
-      <c r="BI27">
-        <v>2.54</v>
-      </c>
-      <c r="BJ27">
-        <v>13</v>
-      </c>
-      <c r="BK27">
-        <v>4.8</v>
-      </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
-        <v>7.2</v>
-      </c>
-      <c r="BN27">
-        <v>5.4</v>
-      </c>
-      <c r="BO27">
-        <v>3.85</v>
-      </c>
-      <c r="BP27">
-        <v>22</v>
-      </c>
-      <c r="BQ27">
-        <v>5.6</v>
-      </c>
-      <c r="BR27">
-        <v>48</v>
-      </c>
-      <c r="BS27">
-        <v>6.4</v>
-      </c>
-      <c r="BT27">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BU27">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV27">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>6.4</v>
+        <v>1.34</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>6.8</v>
+        <v>1.37</v>
       </c>
       <c r="BZ27">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="CA27">
-        <v>6.6</v>
+        <v>1.34</v>
       </c>
       <c r="CB27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
         <v>112</v>
@@ -7400,232 +7406,474 @@
         <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F28">
+        <v>1.7</v>
+      </c>
+      <c r="G28">
+        <v>990</v>
+      </c>
+      <c r="H28">
+        <v>1.75</v>
+      </c>
+      <c r="I28">
+        <v>600</v>
+      </c>
+      <c r="J28">
+        <v>1.06</v>
+      </c>
+      <c r="K28">
+        <v>950</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.01</v>
+      </c>
+      <c r="N28">
+        <v>1.26</v>
+      </c>
+      <c r="O28">
+        <v>1.16</v>
+      </c>
+      <c r="P28">
+        <v>1.26</v>
+      </c>
+      <c r="Q28">
+        <v>1.16</v>
+      </c>
+      <c r="R28">
+        <v>1.18</v>
+      </c>
+      <c r="S28">
+        <v>1.05</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>1.01</v>
+      </c>
+      <c r="W28">
+        <v>1.01</v>
+      </c>
+      <c r="X28">
+        <v>1000</v>
+      </c>
+      <c r="Y28">
+        <v>1000</v>
+      </c>
+      <c r="Z28">
+        <v>1000</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
+        <v>1000</v>
+      </c>
+      <c r="AC28">
+        <v>1000</v>
+      </c>
+      <c r="AD28">
+        <v>1000</v>
+      </c>
+      <c r="AE28">
+        <v>1000</v>
+      </c>
+      <c r="AF28">
+        <v>1000</v>
+      </c>
+      <c r="AG28">
+        <v>1000</v>
+      </c>
+      <c r="AH28">
+        <v>1000</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>1000</v>
+      </c>
+      <c r="AK28">
+        <v>1000</v>
+      </c>
+      <c r="AL28">
+        <v>1000</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>1000</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28">
+        <v>1.01</v>
+      </c>
+      <c r="AR28">
+        <v>1.01</v>
+      </c>
+      <c r="AS28">
+        <v>1.01</v>
+      </c>
+      <c r="AT28">
+        <v>1.01</v>
+      </c>
+      <c r="AU28">
+        <v>1.01</v>
+      </c>
+      <c r="AV28">
+        <v>1.01</v>
+      </c>
+      <c r="AW28">
+        <v>1.01</v>
+      </c>
+      <c r="AX28">
+        <v>1.01</v>
+      </c>
+      <c r="AY28">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28">
+        <v>1.01</v>
+      </c>
+      <c r="BA28">
+        <v>1.01</v>
+      </c>
+      <c r="BB28">
+        <v>1.01</v>
+      </c>
+      <c r="BC28">
+        <v>1.01</v>
+      </c>
+      <c r="BD28">
+        <v>1.01</v>
+      </c>
+      <c r="BE28">
+        <v>1.01</v>
+      </c>
+      <c r="BF28">
+        <v>1.01</v>
+      </c>
+      <c r="BG28">
+        <v>1.01</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>1.04</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>1.04</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.04</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>1.04</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.04</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.04</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>1.04</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.04</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.04</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" t="s">
+        <v>168</v>
+      </c>
+      <c r="F29">
         <v>2.06</v>
       </c>
-      <c r="G28">
-        <v>2.12</v>
-      </c>
-      <c r="H28">
+      <c r="G29">
+        <v>2.14</v>
+      </c>
+      <c r="H29">
         <v>4.2</v>
       </c>
-      <c r="I28">
-        <v>4.4</v>
-      </c>
-      <c r="J28">
-        <v>3.35</v>
-      </c>
-      <c r="K28">
-        <v>3.5</v>
-      </c>
-      <c r="L28">
-        <v>1.44</v>
-      </c>
-      <c r="M28">
+      <c r="I29">
+        <v>4.7</v>
+      </c>
+      <c r="J29">
+        <v>3.2</v>
+      </c>
+      <c r="K29">
+        <v>3.6</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
         <v>1.1</v>
       </c>
-      <c r="N28">
+      <c r="N29">
         <v>2.94</v>
       </c>
-      <c r="O28">
+      <c r="O29">
         <v>1.45</v>
       </c>
-      <c r="P28">
-        <v>1.67</v>
-      </c>
-      <c r="Q28">
-        <v>2.3</v>
-      </c>
-      <c r="R28">
-        <v>1.23</v>
-      </c>
-      <c r="S28">
+      <c r="P29">
+        <v>1.64</v>
+      </c>
+      <c r="Q29">
+        <v>2.32</v>
+      </c>
+      <c r="R29">
+        <v>1.24</v>
+      </c>
+      <c r="S29">
         <v>4.5</v>
       </c>
-      <c r="T28">
+      <c r="T29">
         <v>2.04</v>
       </c>
-      <c r="U28">
-        <v>1.85</v>
-      </c>
-      <c r="V28">
-        <v>1.3</v>
-      </c>
-      <c r="W28">
-        <v>1.89</v>
-      </c>
-      <c r="X28">
+      <c r="U29">
+        <v>1.83</v>
+      </c>
+      <c r="V29">
+        <v>1.27</v>
+      </c>
+      <c r="W29">
+        <v>1.87</v>
+      </c>
+      <c r="X29">
         <v>12</v>
       </c>
-      <c r="Y28">
+      <c r="Y29">
+        <v>15</v>
+      </c>
+      <c r="Z29">
+        <v>38</v>
+      </c>
+      <c r="AA29">
+        <v>130</v>
+      </c>
+      <c r="AB29">
+        <v>8.6</v>
+      </c>
+      <c r="AC29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD29">
+        <v>22</v>
+      </c>
+      <c r="AE29">
+        <v>70</v>
+      </c>
+      <c r="AF29">
         <v>13.5</v>
       </c>
-      <c r="Z28">
-        <v>36</v>
-      </c>
-      <c r="AA28">
-        <v>130</v>
-      </c>
-      <c r="AB28">
-        <v>7.8</v>
-      </c>
-      <c r="AC28">
-        <v>8</v>
-      </c>
-      <c r="AD28">
+      <c r="AG29">
+        <v>12.5</v>
+      </c>
+      <c r="AH29">
+        <v>26</v>
+      </c>
+      <c r="AI29">
+        <v>95</v>
+      </c>
+      <c r="AJ29">
+        <v>30</v>
+      </c>
+      <c r="AK29">
+        <v>30</v>
+      </c>
+      <c r="AL29">
+        <v>60</v>
+      </c>
+      <c r="AM29">
+        <v>180</v>
+      </c>
+      <c r="AN29">
+        <v>25</v>
+      </c>
+      <c r="AO29">
+        <v>120</v>
+      </c>
+      <c r="AP29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ29">
+        <v>11</v>
+      </c>
+      <c r="AR29">
+        <v>4.7</v>
+      </c>
+      <c r="AS29">
+        <v>5.1</v>
+      </c>
+      <c r="AT29">
+        <v>6.4</v>
+      </c>
+      <c r="AU29">
+        <v>6.6</v>
+      </c>
+      <c r="AV29">
+        <v>15.5</v>
+      </c>
+      <c r="AW29">
+        <v>4.9</v>
+      </c>
+      <c r="AX29">
+        <v>10</v>
+      </c>
+      <c r="AY29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ29">
+        <v>18.5</v>
+      </c>
+      <c r="BA29">
+        <v>5</v>
+      </c>
+      <c r="BB29">
         <v>21</v>
       </c>
-      <c r="AE28">
-        <v>80</v>
-      </c>
-      <c r="AF28">
-        <v>12.5</v>
-      </c>
-      <c r="AG28">
-        <v>12.5</v>
-      </c>
-      <c r="AH28">
-        <v>23</v>
-      </c>
-      <c r="AI28">
-        <v>95</v>
-      </c>
-      <c r="AJ28">
-        <v>30</v>
-      </c>
-      <c r="AK28">
-        <v>30</v>
-      </c>
-      <c r="AL28">
-        <v>60</v>
-      </c>
-      <c r="AM28">
-        <v>180</v>
-      </c>
-      <c r="AN28">
-        <v>25</v>
-      </c>
-      <c r="AO28">
-        <v>110</v>
-      </c>
-      <c r="AP28">
-        <v>4.4</v>
-      </c>
-      <c r="AQ28">
-        <v>11</v>
-      </c>
-      <c r="AR28">
-        <v>5.8</v>
-      </c>
-      <c r="AS28">
-        <v>6.6</v>
-      </c>
-      <c r="AT28">
-        <v>3.7</v>
-      </c>
-      <c r="AU28">
-        <v>3.7</v>
-      </c>
-      <c r="AV28">
-        <v>15.5</v>
-      </c>
-      <c r="AW28">
-        <v>6.4</v>
-      </c>
-      <c r="AX28">
-        <v>10</v>
-      </c>
-      <c r="AY28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ28">
-        <v>18.5</v>
-      </c>
-      <c r="BA28">
-        <v>6.4</v>
-      </c>
-      <c r="BB28">
+      <c r="BC29">
         <v>21</v>
       </c>
-      <c r="BC28">
-        <v>21</v>
-      </c>
-      <c r="BD28">
-        <v>6.2</v>
-      </c>
-      <c r="BE28">
-        <v>6.6</v>
-      </c>
-      <c r="BF28">
-        <v>18</v>
-      </c>
-      <c r="BG28">
-        <v>6.6</v>
-      </c>
-      <c r="BH28">
-        <v>3.05</v>
-      </c>
-      <c r="BI28">
-        <v>2.46</v>
-      </c>
-      <c r="BJ28">
-        <v>11.5</v>
-      </c>
-      <c r="BK28">
-        <v>5.5</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>10</v>
-      </c>
-      <c r="BN28">
-        <v>4.8</v>
-      </c>
-      <c r="BO28">
-        <v>3.7</v>
-      </c>
-      <c r="BP28">
-        <v>17</v>
-      </c>
-      <c r="BQ28">
-        <v>6.6</v>
-      </c>
-      <c r="BR28">
-        <v>1000</v>
-      </c>
-      <c r="BS28">
-        <v>8.4</v>
-      </c>
-      <c r="BT28">
-        <v>7.8</v>
-      </c>
-      <c r="BU28">
-        <v>5.9</v>
-      </c>
-      <c r="BV28">
-        <v>1000</v>
-      </c>
-      <c r="BW28">
-        <v>8.6</v>
-      </c>
-      <c r="BX28">
-        <v>1000</v>
-      </c>
-      <c r="BY28">
-        <v>9</v>
-      </c>
-      <c r="BZ28">
-        <v>1000</v>
-      </c>
-      <c r="CA28">
-        <v>8.4</v>
-      </c>
-      <c r="CB28" t="s">
-        <v>167</v>
+      <c r="BD29">
+        <v>4.9</v>
+      </c>
+      <c r="BE29">
+        <v>5.2</v>
+      </c>
+      <c r="BF29">
+        <v>16.5</v>
+      </c>
+      <c r="BG29">
+        <v>5.1</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>1.04</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>1.04</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.04</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>1.04</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>1.04</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>1.04</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>1.04</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.04</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.04</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>1.04</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="181">
   <si>
     <t>League</t>
   </si>
@@ -271,15 +271,18 @@
     <t>Kazakhstan Premier League</t>
   </si>
   <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
     <t>Latvian Virsliga</t>
   </si>
   <si>
-    <t>Romanian Liga II</t>
-  </si>
-  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>UEFA Champions League Qualifiers</t>
+  </si>
+  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
@@ -328,6 +331,12 @@
     <t>16:05:00</t>
   </si>
   <si>
+    <t>16:10:00</t>
+  </si>
+  <si>
+    <t>16:45:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -379,15 +388,21 @@
     <t>Tobol Kostanay</t>
   </si>
   <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
     <t>FK Auda</t>
   </si>
   <si>
-    <t>Unirea Slobozia</t>
-  </si>
-  <si>
     <t>Abha</t>
   </si>
   <si>
+    <t>Al-Taawoun Buraidah</t>
+  </si>
+  <si>
+    <t>FC Sabah</t>
+  </si>
+  <si>
     <t>Osters</t>
   </si>
   <si>
@@ -418,6 +433,12 @@
     <t>Valencia</t>
   </si>
   <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Bodo Glimt</t>
+  </si>
+  <si>
     <t>Afturelding</t>
   </si>
   <si>
@@ -463,15 +484,21 @@
     <t>FK Kaisar</t>
   </si>
   <si>
+    <t>FC Metaloglobus Bucuresti</t>
+  </si>
+  <si>
     <t>Liepajas Metalurgs</t>
   </si>
   <si>
-    <t>FC Metaloglobus Bucuresti</t>
-  </si>
-  <si>
     <t>Al-Khaleej Saihat</t>
   </si>
   <si>
+    <t>Al-Feiha</t>
+  </si>
+  <si>
+    <t>Hapoel Beer Sheva</t>
+  </si>
+  <si>
     <t>Sundsvall</t>
   </si>
   <si>
@@ -502,6 +529,12 @@
     <t>Betis</t>
   </si>
   <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>NEC Nijmegen</t>
+  </si>
+  <si>
     <t>Grotta</t>
   </si>
   <si>
@@ -523,7 +556,7 @@
     <t>Aguilas Doradas</t>
   </si>
   <si>
-    <t>2026-08-24 12:49:40</t>
+    <t>2026-08-24 14:54:40</t>
   </si>
 </sst>
 </file>
@@ -855,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB29"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1105,31 +1138,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G2">
         <v>3.75</v>
       </c>
       <c r="H2">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I2">
         <v>2.36</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
         <v>3.45</v>
@@ -1141,28 +1174,28 @@
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R2">
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
+        <v>1.96</v>
+      </c>
+      <c r="U2">
         <v>1.91</v>
-      </c>
-      <c r="U2">
-        <v>1.9</v>
       </c>
       <c r="V2">
         <v>1.73</v>
@@ -1171,13 +1204,13 @@
         <v>1.37</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA2">
         <v>38</v>
@@ -1195,7 +1228,7 @@
         <v>29</v>
       </c>
       <c r="AF2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG2">
         <v>15.5</v>
@@ -1228,16 +1261,16 @@
         <v>9.4</v>
       </c>
       <c r="AQ2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR2">
         <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1246,7 +1279,7 @@
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX2">
         <v>21</v>
@@ -1264,13 +1297,13 @@
         <v>46</v>
       </c>
       <c r="BC2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD2">
         <v>46</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF2">
         <v>42</v>
@@ -1279,7 +1312,7 @@
         <v>21</v>
       </c>
       <c r="BH2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI2">
         <v>2.52</v>
@@ -1288,58 +1321,58 @@
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
         <v>7.2</v>
       </c>
       <c r="BO2">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BP2">
         <v>36</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU2">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BV2">
         <v>19</v>
       </c>
       <c r="BW2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2">
         <v>38</v>
       </c>
       <c r="CA2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1347,19 +1380,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F3">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G3">
         <v>2.78</v>
@@ -1368,16 +1401,16 @@
         <v>3.2</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
       <c r="K3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M3">
         <v>1.14</v>
@@ -1389,7 +1422,7 @@
         <v>1.6</v>
       </c>
       <c r="P3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q3">
         <v>2.84</v>
@@ -1401,7 +1434,7 @@
         <v>6</v>
       </c>
       <c r="T3">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
         <v>1.77</v>
@@ -1413,7 +1446,7 @@
         <v>1.56</v>
       </c>
       <c r="X3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y3">
         <v>9</v>
@@ -1422,10 +1455,10 @@
         <v>21</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC3">
         <v>7</v>
@@ -1458,7 +1491,7 @@
         <v>90</v>
       </c>
       <c r="AM3">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="AN3">
         <v>55</v>
@@ -1467,7 +1500,7 @@
         <v>95</v>
       </c>
       <c r="AP3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3">
         <v>8</v>
@@ -1479,7 +1512,7 @@
         <v>48</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU3">
         <v>6.2</v>
@@ -1488,7 +1521,7 @@
         <v>13</v>
       </c>
       <c r="AW3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AX3">
         <v>14</v>
@@ -1500,7 +1533,7 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="BB3">
         <v>25</v>
@@ -1512,16 +1545,16 @@
         <v>60</v>
       </c>
       <c r="BE3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BF3">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BG3">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BH3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI3">
         <v>2.18</v>
@@ -1530,16 +1563,16 @@
         <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3">
         <v>260</v>
       </c>
       <c r="BM3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO3">
         <v>4.2</v>
@@ -1548,40 +1581,40 @@
         <v>30</v>
       </c>
       <c r="BQ3">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BR3">
         <v>60</v>
       </c>
       <c r="BS3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BT3">
         <v>7.2</v>
       </c>
       <c r="BU3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BX3">
         <v>55</v>
       </c>
       <c r="BY3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BZ3">
         <v>65</v>
       </c>
       <c r="CA3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1589,19 +1622,19 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F4">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G4">
         <v>2.9</v>
@@ -1625,7 +1658,7 @@
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O4">
         <v>1.49</v>
@@ -1634,19 +1667,19 @@
         <v>1.63</v>
       </c>
       <c r="Q4">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R4">
         <v>1.23</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T4">
         <v>2</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V4">
         <v>1.47</v>
@@ -1655,7 +1688,7 @@
         <v>1.52</v>
       </c>
       <c r="X4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y4">
         <v>9.4</v>
@@ -1667,10 +1700,10 @@
         <v>55</v>
       </c>
       <c r="AB4">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
         <v>14</v>
@@ -1679,7 +1712,7 @@
         <v>42</v>
       </c>
       <c r="AF4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG4">
         <v>13.5</v>
@@ -1688,7 +1721,7 @@
         <v>21</v>
       </c>
       <c r="AI4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ4">
         <v>48</v>
@@ -1706,10 +1739,10 @@
         <v>55</v>
       </c>
       <c r="AO4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4">
         <v>8.4</v>
@@ -1718,7 +1751,7 @@
         <v>17</v>
       </c>
       <c r="AS4">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AT4">
         <v>8.199999999999999</v>
@@ -1739,7 +1772,7 @@
         <v>12</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA4">
         <v>55</v>
@@ -1772,13 +1805,13 @@
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BL4">
         <v>210</v>
       </c>
       <c r="BM4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BN4">
         <v>6.6</v>
@@ -1796,7 +1829,7 @@
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BT4">
         <v>7</v>
@@ -1805,7 +1838,7 @@
         <v>5</v>
       </c>
       <c r="BV4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW4">
         <v>4.5</v>
@@ -1814,16 +1847,16 @@
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ4">
         <v>46</v>
       </c>
       <c r="CA4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB4" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1831,19 +1864,19 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G5">
         <v>1.49</v>
@@ -1858,10 +1891,10 @@
         <v>4.7</v>
       </c>
       <c r="K5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.03</v>
@@ -1882,49 +1915,49 @@
         <v>1.56</v>
       </c>
       <c r="S5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T5">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U5">
         <v>1.96</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X5">
         <v>24</v>
       </c>
       <c r="Y5">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Z5">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AA5">
         <v>270</v>
       </c>
       <c r="AB5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD5">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AE5">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AF5">
         <v>9.800000000000001</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
         <v>25</v>
@@ -1933,34 +1966,34 @@
         <v>110</v>
       </c>
       <c r="AJ5">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AK5">
         <v>15.5</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM5">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN5">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO5">
         <v>140</v>
       </c>
       <c r="AP5">
-        <v>5.4</v>
+        <v>17</v>
       </c>
       <c r="AQ5">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="AR5">
-        <v>6.4</v>
+        <v>55</v>
       </c>
       <c r="AS5">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -1969,10 +2002,10 @@
         <v>10</v>
       </c>
       <c r="AV5">
-        <v>5.8</v>
+        <v>22</v>
       </c>
       <c r="AW5">
-        <v>6.6</v>
+        <v>55</v>
       </c>
       <c r="AX5">
         <v>8.199999999999999</v>
@@ -1981,10 +2014,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>6.6</v>
+        <v>46</v>
       </c>
       <c r="BB5">
         <v>11</v>
@@ -1993,79 +2026,79 @@
         <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>5.8</v>
+        <v>22</v>
       </c>
       <c r="BE5">
-        <v>6.6</v>
+        <v>65</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5">
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
         <v>4.2</v>
       </c>
       <c r="BO5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP5">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR5">
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT5">
         <v>12</v>
       </c>
       <c r="BU5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5">
         <v>13.5</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2073,22 +2106,22 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F6">
         <v>3.5</v>
       </c>
       <c r="G6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H6">
         <v>2.22</v>
@@ -2118,13 +2151,13 @@
         <v>1.9</v>
       </c>
       <c r="Q6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R6">
         <v>1.35</v>
       </c>
       <c r="S6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T6">
         <v>1.82</v>
@@ -2187,7 +2220,7 @@
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO6">
         <v>18.5</v>
@@ -2307,7 +2340,7 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2315,16 +2348,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F7">
         <v>2.52</v>
@@ -2351,16 +2384,16 @@
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O7">
         <v>1.47</v>
       </c>
       <c r="P7">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q7">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R7">
         <v>1.25</v>
@@ -2402,7 +2435,7 @@
         <v>14.5</v>
       </c>
       <c r="AE7">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF7">
         <v>15.5</v>
@@ -2444,7 +2477,7 @@
         <v>18</v>
       </c>
       <c r="AS7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT7">
         <v>7.6</v>
@@ -2456,7 +2489,7 @@
         <v>13</v>
       </c>
       <c r="AW7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AX7">
         <v>13</v>
@@ -2468,13 +2501,13 @@
         <v>19</v>
       </c>
       <c r="BA7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB7">
+        <v>27</v>
+      </c>
+      <c r="BC7">
         <v>23</v>
-      </c>
-      <c r="BC7">
-        <v>21</v>
       </c>
       <c r="BD7">
         <v>29</v>
@@ -2549,7 +2582,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2557,28 +2590,28 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F8">
         <v>1.56</v>
       </c>
       <c r="G8">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="H8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
         <v>4.3</v>
@@ -2596,16 +2629,16 @@
         <v>4</v>
       </c>
       <c r="O8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P8">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q8">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
         <v>3.25</v>
@@ -2620,10 +2653,10 @@
         <v>1.16</v>
       </c>
       <c r="W8">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="X8">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y8">
         <v>23</v>
@@ -2638,7 +2671,7 @@
         <v>8.4</v>
       </c>
       <c r="AC8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD8">
         <v>27</v>
@@ -2659,13 +2692,13 @@
         <v>110</v>
       </c>
       <c r="AJ8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK8">
         <v>18</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM8">
         <v>160</v>
@@ -2683,10 +2716,10 @@
         <v>18</v>
       </c>
       <c r="AR8">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="AS8">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT8">
         <v>7.4</v>
@@ -2698,7 +2731,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX8">
         <v>8.199999999999999</v>
@@ -2707,10 +2740,10 @@
         <v>9</v>
       </c>
       <c r="AZ8">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>9.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BB8">
         <v>12.5</v>
@@ -2719,22 +2752,22 @@
         <v>15</v>
       </c>
       <c r="BD8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE8">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF8">
         <v>7.8</v>
       </c>
       <c r="BG8">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH8">
         <v>3.7</v>
       </c>
       <c r="BI8">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
@@ -2752,7 +2785,7 @@
         <v>4.2</v>
       </c>
       <c r="BO8">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BP8">
         <v>10.5</v>
@@ -2791,7 +2824,7 @@
         <v>6.8</v>
       </c>
       <c r="CB8" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2799,25 +2832,25 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F9">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G9">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H9">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I9">
         <v>6.6</v>
@@ -2826,34 +2859,34 @@
         <v>3.85</v>
       </c>
       <c r="K9">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9">
         <v>1.3</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Q9">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S9">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U9">
         <v>2</v>
@@ -2865,10 +2898,10 @@
         <v>2.24</v>
       </c>
       <c r="X9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z9">
         <v>65</v>
@@ -2877,100 +2910,100 @@
         <v>180</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9">
         <v>24</v>
       </c>
       <c r="AE9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF9">
         <v>11</v>
       </c>
       <c r="AG9">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI9">
         <v>100</v>
       </c>
       <c r="AJ9">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK9">
         <v>18.5</v>
       </c>
       <c r="AL9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM9">
         <v>130</v>
       </c>
       <c r="AN9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO9">
         <v>110</v>
       </c>
       <c r="AP9">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ9">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AR9">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS9">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AU9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV9">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AW9">
+        <v>7.8</v>
+      </c>
+      <c r="AX9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY9">
+        <v>8.6</v>
+      </c>
+      <c r="AZ9">
+        <v>15.5</v>
+      </c>
+      <c r="BA9">
+        <v>7.8</v>
+      </c>
+      <c r="BB9">
         <v>5.8</v>
       </c>
-      <c r="AX9">
-        <v>4</v>
-      </c>
-      <c r="AY9">
-        <v>4</v>
-      </c>
-      <c r="AZ9">
-        <v>5</v>
-      </c>
-      <c r="BA9">
-        <v>5.8</v>
-      </c>
-      <c r="BB9">
+      <c r="BC9">
+        <v>5.9</v>
+      </c>
+      <c r="BD9">
+        <v>7</v>
+      </c>
+      <c r="BE9">
+        <v>8</v>
+      </c>
+      <c r="BF9">
         <v>4.7</v>
       </c>
-      <c r="BC9">
-        <v>4.7</v>
-      </c>
-      <c r="BD9">
-        <v>5.4</v>
-      </c>
-      <c r="BE9">
-        <v>6</v>
-      </c>
-      <c r="BF9">
-        <v>3.8</v>
-      </c>
       <c r="BG9">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3033,7 +3066,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3041,178 +3074,178 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F10">
-        <v>1.4</v>
+        <v>2.68</v>
       </c>
       <c r="G10">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="H10">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="I10">
-        <v>990</v>
+        <v>3.1</v>
       </c>
       <c r="J10">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
-        <v>1.82</v>
+        <v>3.05</v>
       </c>
       <c r="O10">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q10">
-        <v>1.19</v>
+        <v>2.12</v>
       </c>
       <c r="R10">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="W10">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3269,13 +3302,13 @@
         <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3283,241 +3316,241 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F11">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="G11">
-        <v>990</v>
+        <v>2.06</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="I11">
-        <v>990</v>
+        <v>4.4</v>
       </c>
       <c r="J11">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>1.42</v>
+        <v>4.6</v>
       </c>
       <c r="O11">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="P11">
+        <v>2.24</v>
+      </c>
+      <c r="Q11">
+        <v>1.62</v>
+      </c>
+      <c r="R11">
+        <v>1.49</v>
+      </c>
+      <c r="S11">
+        <v>2.62</v>
+      </c>
+      <c r="T11">
+        <v>1.62</v>
+      </c>
+      <c r="U11">
+        <v>2.32</v>
+      </c>
+      <c r="V11">
         <v>1.29</v>
       </c>
-      <c r="Q11">
-        <v>1.98</v>
-      </c>
-      <c r="R11">
-        <v>1.15</v>
-      </c>
-      <c r="S11">
-        <v>3.3</v>
-      </c>
-      <c r="T11">
-        <v>1.11</v>
-      </c>
-      <c r="U11">
-        <v>1.11</v>
-      </c>
-      <c r="V11">
-        <v>1.12</v>
-      </c>
       <c r="W11">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3525,34 +3558,34 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H12">
         <v>2.34</v>
       </c>
       <c r="I12">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3567,19 +3600,19 @@
         <v>1.27</v>
       </c>
       <c r="P12">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q12">
         <v>1.86</v>
       </c>
       <c r="R12">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S12">
         <v>3.1</v>
       </c>
       <c r="T12">
-        <v>1.12</v>
+        <v>1.64</v>
       </c>
       <c r="U12">
         <v>1.11</v>
@@ -3588,7 +3621,7 @@
         <v>1.63</v>
       </c>
       <c r="W12">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3597,31 +3630,31 @@
         <v>1000</v>
       </c>
       <c r="Z12">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD12">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
         <v>1000</v>
       </c>
       <c r="AF12">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
         <v>1000</v>
@@ -3645,58 +3678,58 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.77</v>
+        <v>1.13</v>
       </c>
       <c r="AQ12">
-        <v>1.77</v>
+        <v>1.13</v>
       </c>
       <c r="AR12">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AS12">
-        <v>1.78</v>
+        <v>1.14</v>
       </c>
       <c r="AT12">
+        <v>1.13</v>
+      </c>
+      <c r="AU12">
+        <v>1.01</v>
+      </c>
+      <c r="AV12">
         <v>9.800000000000001</v>
       </c>
-      <c r="AU12">
-        <v>1.5</v>
-      </c>
-      <c r="AV12">
-        <v>1.58</v>
-      </c>
       <c r="AW12">
-        <v>19</v>
+        <v>1.14</v>
       </c>
       <c r="AX12">
-        <v>1.67</v>
+        <v>1.14</v>
       </c>
       <c r="AY12">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AZ12">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="BA12">
-        <v>1.78</v>
+        <v>1.14</v>
       </c>
       <c r="BB12">
-        <v>1.78</v>
+        <v>1.14</v>
       </c>
       <c r="BC12">
-        <v>1.78</v>
+        <v>1.14</v>
       </c>
       <c r="BD12">
-        <v>1.78</v>
+        <v>1.14</v>
       </c>
       <c r="BE12">
-        <v>1.78</v>
+        <v>1.14</v>
       </c>
       <c r="BF12">
-        <v>1.78</v>
+        <v>1.14</v>
       </c>
       <c r="BG12">
-        <v>14.5</v>
+        <v>1.14</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3759,186 +3792,186 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F13">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G13">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="H13">
         <v>4.4</v>
       </c>
       <c r="I13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K13">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="O13">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="P13">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="Q13">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="R13">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S13">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="T13">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="U13">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="V13">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W13">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="X13">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="Y13">
+        <v>21</v>
+      </c>
+      <c r="Z13">
+        <v>40</v>
+      </c>
+      <c r="AA13">
+        <v>130</v>
+      </c>
+      <c r="AB13">
+        <v>9.4</v>
+      </c>
+      <c r="AC13">
+        <v>10.5</v>
+      </c>
+      <c r="AD13">
+        <v>23</v>
+      </c>
+      <c r="AE13">
+        <v>75</v>
+      </c>
+      <c r="AF13">
+        <v>12</v>
+      </c>
+      <c r="AG13">
+        <v>10.5</v>
+      </c>
+      <c r="AH13">
+        <v>21</v>
+      </c>
+      <c r="AI13">
+        <v>80</v>
+      </c>
+      <c r="AJ13">
         <v>25</v>
       </c>
-      <c r="Z13">
-        <v>44</v>
-      </c>
-      <c r="AA13">
-        <v>110</v>
-      </c>
-      <c r="AB13">
+      <c r="AK13">
+        <v>21</v>
+      </c>
+      <c r="AL13">
+        <v>40</v>
+      </c>
+      <c r="AM13">
+        <v>130</v>
+      </c>
+      <c r="AN13">
+        <v>13</v>
+      </c>
+      <c r="AO13">
+        <v>80</v>
+      </c>
+      <c r="AP13">
+        <v>13</v>
+      </c>
+      <c r="AQ13">
         <v>14</v>
       </c>
-      <c r="AC13">
-        <v>12</v>
-      </c>
-      <c r="AD13">
-        <v>22</v>
-      </c>
-      <c r="AE13">
-        <v>60</v>
-      </c>
-      <c r="AF13">
-        <v>14</v>
-      </c>
-      <c r="AG13">
-        <v>12.5</v>
-      </c>
-      <c r="AH13">
-        <v>17</v>
-      </c>
-      <c r="AI13">
-        <v>55</v>
-      </c>
-      <c r="AJ13">
-        <v>24</v>
-      </c>
-      <c r="AK13">
+      <c r="AR13">
+        <v>6.8</v>
+      </c>
+      <c r="AS13">
+        <v>7.8</v>
+      </c>
+      <c r="AT13">
+        <v>7.8</v>
+      </c>
+      <c r="AU13">
+        <v>7.4</v>
+      </c>
+      <c r="AV13">
+        <v>16</v>
+      </c>
+      <c r="AW13">
+        <v>7.4</v>
+      </c>
+      <c r="AX13">
+        <v>10</v>
+      </c>
+      <c r="AY13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ13">
+        <v>16</v>
+      </c>
+      <c r="BA13">
+        <v>7.6</v>
+      </c>
+      <c r="BB13">
         <v>17.5</v>
       </c>
-      <c r="AL13">
-        <v>28</v>
-      </c>
-      <c r="AM13">
-        <v>80</v>
-      </c>
-      <c r="AN13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO13">
-        <v>46</v>
-      </c>
-      <c r="AP13">
-        <v>17</v>
-      </c>
-      <c r="AQ13">
+      <c r="BC13">
         <v>16.5</v>
       </c>
-      <c r="AR13">
-        <v>5.1</v>
-      </c>
-      <c r="AS13">
-        <v>5.4</v>
-      </c>
-      <c r="AT13">
+      <c r="BD13">
+        <v>6.8</v>
+      </c>
+      <c r="BE13">
+        <v>7.8</v>
+      </c>
+      <c r="BF13">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU13">
-        <v>7.8</v>
-      </c>
-      <c r="AV13">
-        <v>14</v>
-      </c>
-      <c r="AW13">
-        <v>5.2</v>
-      </c>
-      <c r="AX13">
-        <v>10.5</v>
-      </c>
-      <c r="AY13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ13">
-        <v>12.5</v>
-      </c>
-      <c r="BA13">
-        <v>5.2</v>
-      </c>
-      <c r="BB13">
-        <v>15.5</v>
-      </c>
-      <c r="BC13">
-        <v>13</v>
-      </c>
-      <c r="BD13">
-        <v>20</v>
-      </c>
-      <c r="BE13">
-        <v>5.3</v>
-      </c>
-      <c r="BF13">
-        <v>6.6</v>
-      </c>
       <c r="BG13">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3995,13 +4028,13 @@
         <v>1.04</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4009,178 +4042,178 @@
         <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F14">
-        <v>2.72</v>
+        <v>1.98</v>
       </c>
       <c r="G14">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="K14">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M14">
         <v>1.06</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P14">
+        <v>2.08</v>
+      </c>
+      <c r="Q14">
+        <v>1.83</v>
+      </c>
+      <c r="R14">
+        <v>1.42</v>
+      </c>
+      <c r="S14">
+        <v>3.1</v>
+      </c>
+      <c r="T14">
+        <v>1.76</v>
+      </c>
+      <c r="U14">
+        <v>2.16</v>
+      </c>
+      <c r="V14">
+        <v>1.31</v>
+      </c>
+      <c r="W14">
         <v>2</v>
       </c>
-      <c r="Q14">
-        <v>1.79</v>
-      </c>
-      <c r="R14">
-        <v>1.39</v>
-      </c>
-      <c r="S14">
-        <v>3</v>
-      </c>
-      <c r="T14">
-        <v>1.64</v>
-      </c>
-      <c r="U14">
-        <v>2.22</v>
-      </c>
-      <c r="V14">
-        <v>1.55</v>
-      </c>
-      <c r="W14">
-        <v>1.47</v>
-      </c>
       <c r="X14">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y14">
+        <v>16.5</v>
+      </c>
+      <c r="Z14">
+        <v>30</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>10.5</v>
+      </c>
+      <c r="AC14">
+        <v>9</v>
+      </c>
+      <c r="AD14">
+        <v>16.5</v>
+      </c>
+      <c r="AE14">
+        <v>48</v>
+      </c>
+      <c r="AF14">
         <v>13</v>
       </c>
-      <c r="Z14">
-        <v>19</v>
-      </c>
-      <c r="AA14">
-        <v>50</v>
-      </c>
-      <c r="AB14">
-        <v>14</v>
-      </c>
-      <c r="AC14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD14">
+      <c r="AG14">
+        <v>10.5</v>
+      </c>
+      <c r="AH14">
+        <v>18.5</v>
+      </c>
+      <c r="AI14">
+        <v>55</v>
+      </c>
+      <c r="AJ14">
+        <v>24</v>
+      </c>
+      <c r="AK14">
+        <v>21</v>
+      </c>
+      <c r="AL14">
+        <v>34</v>
+      </c>
+      <c r="AM14">
+        <v>90</v>
+      </c>
+      <c r="AN14">
         <v>13</v>
       </c>
-      <c r="AE14">
+      <c r="AO14">
+        <v>46</v>
+      </c>
+      <c r="AP14">
+        <v>14.5</v>
+      </c>
+      <c r="AQ14">
+        <v>15</v>
+      </c>
+      <c r="AR14">
+        <v>25</v>
+      </c>
+      <c r="AS14">
+        <v>36</v>
+      </c>
+      <c r="AT14">
+        <v>9.6</v>
+      </c>
+      <c r="AU14">
+        <v>8</v>
+      </c>
+      <c r="AV14">
+        <v>14.5</v>
+      </c>
+      <c r="AW14">
+        <v>38</v>
+      </c>
+      <c r="AX14">
+        <v>11.5</v>
+      </c>
+      <c r="AY14">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14">
+        <v>16</v>
+      </c>
+      <c r="BA14">
+        <v>44</v>
+      </c>
+      <c r="BB14">
+        <v>21</v>
+      </c>
+      <c r="BC14">
+        <v>18</v>
+      </c>
+      <c r="BD14">
         <v>29</v>
       </c>
-      <c r="AF14">
-        <v>22</v>
-      </c>
-      <c r="AG14">
-        <v>13.5</v>
-      </c>
-      <c r="AH14">
-        <v>17</v>
-      </c>
-      <c r="AI14">
-        <v>40</v>
-      </c>
-      <c r="AJ14">
-        <v>65</v>
-      </c>
-      <c r="AK14">
+      <c r="BE14">
         <v>36</v>
       </c>
-      <c r="AL14">
-        <v>55</v>
-      </c>
-      <c r="AM14">
-        <v>100</v>
-      </c>
-      <c r="AN14">
-        <v>26</v>
-      </c>
-      <c r="AO14">
-        <v>22</v>
-      </c>
-      <c r="AP14">
-        <v>12.5</v>
-      </c>
-      <c r="AQ14">
-        <v>10</v>
-      </c>
-      <c r="AR14">
-        <v>14</v>
-      </c>
-      <c r="AS14">
-        <v>6.6</v>
-      </c>
-      <c r="AT14">
-        <v>10</v>
-      </c>
-      <c r="AU14">
-        <v>7.2</v>
-      </c>
-      <c r="AV14">
-        <v>10</v>
-      </c>
-      <c r="AW14">
-        <v>6.2</v>
-      </c>
-      <c r="AX14">
-        <v>17</v>
-      </c>
-      <c r="AY14">
-        <v>10</v>
-      </c>
-      <c r="AZ14">
-        <v>13.5</v>
-      </c>
-      <c r="BA14">
-        <v>23</v>
-      </c>
-      <c r="BB14">
-        <v>27</v>
-      </c>
-      <c r="BC14">
-        <v>6.6</v>
-      </c>
-      <c r="BD14">
-        <v>6.8</v>
-      </c>
-      <c r="BE14">
-        <v>7.2</v>
-      </c>
       <c r="BF14">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BG14">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4237,13 +4270,13 @@
         <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4251,241 +4284,241 @@
         <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="F15">
-        <v>2.54</v>
+        <v>1.79</v>
       </c>
       <c r="G15">
-        <v>2.9</v>
+        <v>1.87</v>
       </c>
       <c r="H15">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="I15">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="J15">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="L15">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15">
+        <v>1.21</v>
+      </c>
+      <c r="P15">
+        <v>2.42</v>
+      </c>
+      <c r="Q15">
+        <v>1.62</v>
+      </c>
+      <c r="R15">
+        <v>1.58</v>
+      </c>
+      <c r="S15">
+        <v>2.5</v>
+      </c>
+      <c r="T15">
+        <v>1.64</v>
+      </c>
+      <c r="U15">
+        <v>2.38</v>
+      </c>
+      <c r="V15">
+        <v>1.26</v>
+      </c>
+      <c r="W15">
+        <v>2.14</v>
+      </c>
+      <c r="X15">
+        <v>26</v>
+      </c>
+      <c r="Y15">
+        <v>25</v>
+      </c>
+      <c r="Z15">
+        <v>44</v>
+      </c>
+      <c r="AA15">
+        <v>110</v>
+      </c>
+      <c r="AB15">
+        <v>13.5</v>
+      </c>
+      <c r="AC15">
+        <v>11.5</v>
+      </c>
+      <c r="AD15">
+        <v>22</v>
+      </c>
+      <c r="AE15">
+        <v>60</v>
+      </c>
+      <c r="AF15">
+        <v>13.5</v>
+      </c>
+      <c r="AG15">
+        <v>12</v>
+      </c>
+      <c r="AH15">
+        <v>16.5</v>
+      </c>
+      <c r="AI15">
+        <v>55</v>
+      </c>
+      <c r="AJ15">
+        <v>21</v>
+      </c>
+      <c r="AK15">
+        <v>17.5</v>
+      </c>
+      <c r="AL15">
+        <v>27</v>
+      </c>
+      <c r="AM15">
+        <v>80</v>
+      </c>
+      <c r="AN15">
+        <v>8.6</v>
+      </c>
+      <c r="AO15">
+        <v>46</v>
+      </c>
+      <c r="AP15">
+        <v>19.5</v>
+      </c>
+      <c r="AQ15">
+        <v>16.5</v>
+      </c>
+      <c r="AR15">
+        <v>32</v>
+      </c>
+      <c r="AS15">
+        <v>7</v>
+      </c>
+      <c r="AT15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV15">
+        <v>14</v>
+      </c>
+      <c r="AW15">
+        <v>6.6</v>
+      </c>
+      <c r="AX15">
+        <v>10.5</v>
+      </c>
+      <c r="AY15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15">
+        <v>12.5</v>
+      </c>
+      <c r="BA15">
+        <v>6.6</v>
+      </c>
+      <c r="BB15">
+        <v>15.5</v>
+      </c>
+      <c r="BC15">
+        <v>13</v>
+      </c>
+      <c r="BD15">
+        <v>20</v>
+      </c>
+      <c r="BE15">
+        <v>6.8</v>
+      </c>
+      <c r="BF15">
+        <v>7.4</v>
+      </c>
+      <c r="BG15">
+        <v>6.4</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.04</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.04</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.04</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.04</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.04</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.04</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.04</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15">
         <v>0</v>
       </c>
-      <c r="O15">
+      <c r="CA15">
         <v>0</v>
       </c>
-      <c r="P15">
-        <v>1.48</v>
-      </c>
-      <c r="Q15">
-        <v>2.62</v>
-      </c>
-      <c r="R15">
-        <v>1.19</v>
-      </c>
-      <c r="S15">
-        <v>1.05</v>
-      </c>
-      <c r="T15">
-        <v>2.08</v>
-      </c>
-      <c r="U15">
-        <v>1.73</v>
-      </c>
-      <c r="V15">
-        <v>1.33</v>
-      </c>
-      <c r="W15">
-        <v>1.52</v>
-      </c>
-      <c r="X15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y15">
-        <v>11</v>
-      </c>
-      <c r="Z15">
-        <v>23</v>
-      </c>
-      <c r="AA15">
-        <v>85</v>
-      </c>
-      <c r="AB15">
-        <v>9.4</v>
-      </c>
-      <c r="AC15">
-        <v>7.4</v>
-      </c>
-      <c r="AD15">
-        <v>16</v>
-      </c>
-      <c r="AE15">
-        <v>65</v>
-      </c>
-      <c r="AF15">
-        <v>19.5</v>
-      </c>
-      <c r="AG15">
-        <v>14</v>
-      </c>
-      <c r="AH15">
-        <v>29</v>
-      </c>
-      <c r="AI15">
-        <v>100</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>50</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>60</v>
-      </c>
-      <c r="AO15">
-        <v>90</v>
-      </c>
-      <c r="AP15">
-        <v>3.1</v>
-      </c>
-      <c r="AQ15">
-        <v>3.2</v>
-      </c>
-      <c r="AR15">
-        <v>3.8</v>
-      </c>
-      <c r="AS15">
-        <v>4.3</v>
-      </c>
-      <c r="AT15">
-        <v>3.05</v>
-      </c>
-      <c r="AU15">
-        <v>2.82</v>
-      </c>
-      <c r="AV15">
-        <v>3.55</v>
-      </c>
-      <c r="AW15">
-        <v>4.2</v>
-      </c>
-      <c r="AX15">
-        <v>3.7</v>
-      </c>
-      <c r="AY15">
-        <v>3.45</v>
-      </c>
-      <c r="AZ15">
-        <v>3.95</v>
-      </c>
-      <c r="BA15">
-        <v>4.3</v>
-      </c>
-      <c r="BB15">
-        <v>4.5</v>
-      </c>
-      <c r="BC15">
-        <v>4.2</v>
-      </c>
-      <c r="BD15">
-        <v>4.5</v>
-      </c>
-      <c r="BE15">
-        <v>4.5</v>
-      </c>
-      <c r="BF15">
-        <v>4.2</v>
-      </c>
-      <c r="BG15">
-        <v>4.3</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.04</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.04</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.04</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>1.04</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>1.04</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>1.04</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
-      <c r="BU15">
-        <v>1.04</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>1.04</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>1.04</v>
-      </c>
-      <c r="BZ15">
-        <v>1000</v>
-      </c>
-      <c r="CA15">
-        <v>1.04</v>
-      </c>
       <c r="CB15" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4493,178 +4526,178 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F16">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="G16">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="H16">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="I16">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="J16">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="K16">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L16">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="M16">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N16">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="O16">
+        <v>1.27</v>
+      </c>
+      <c r="P16">
+        <v>2.04</v>
+      </c>
+      <c r="Q16">
+        <v>1.81</v>
+      </c>
+      <c r="R16">
+        <v>1.41</v>
+      </c>
+      <c r="S16">
+        <v>3</v>
+      </c>
+      <c r="T16">
+        <v>1.67</v>
+      </c>
+      <c r="U16">
+        <v>2.26</v>
+      </c>
+      <c r="V16">
+        <v>1.58</v>
+      </c>
+      <c r="W16">
         <v>1.5</v>
       </c>
-      <c r="P16">
-        <v>1.52</v>
-      </c>
-      <c r="Q16">
-        <v>2.54</v>
-      </c>
-      <c r="R16">
-        <v>1.15</v>
-      </c>
-      <c r="S16">
-        <v>4.5</v>
-      </c>
-      <c r="T16">
-        <v>2.04</v>
-      </c>
-      <c r="U16">
-        <v>1.76</v>
-      </c>
-      <c r="V16">
-        <v>1.53</v>
-      </c>
-      <c r="W16">
-        <v>1.35</v>
-      </c>
       <c r="X16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y16">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="Z16">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD16">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF16">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AG16">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP16">
-        <v>1.83</v>
+        <v>12.5</v>
       </c>
       <c r="AQ16">
-        <v>1.55</v>
+        <v>10</v>
       </c>
       <c r="AR16">
-        <v>1.68</v>
+        <v>14</v>
       </c>
       <c r="AS16">
-        <v>1.84</v>
+        <v>7</v>
       </c>
       <c r="AT16">
-        <v>1.83</v>
+        <v>10</v>
       </c>
       <c r="AU16">
-        <v>1.51</v>
+        <v>7.2</v>
       </c>
       <c r="AV16">
-        <v>1.65</v>
+        <v>10</v>
       </c>
       <c r="AW16">
-        <v>1.84</v>
+        <v>6.6</v>
       </c>
       <c r="AX16">
-        <v>1.72</v>
+        <v>17</v>
       </c>
       <c r="AY16">
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
-        <v>1.73</v>
+        <v>13.5</v>
       </c>
       <c r="BA16">
-        <v>1.84</v>
+        <v>23</v>
       </c>
       <c r="BB16">
-        <v>1.84</v>
+        <v>27</v>
       </c>
       <c r="BC16">
-        <v>1.84</v>
+        <v>6.8</v>
       </c>
       <c r="BD16">
-        <v>1.84</v>
+        <v>7</v>
       </c>
       <c r="BE16">
-        <v>1.84</v>
+        <v>7.8</v>
       </c>
       <c r="BF16">
-        <v>1.84</v>
+        <v>20</v>
       </c>
       <c r="BG16">
-        <v>1.84</v>
+        <v>17.5</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4721,192 +4754,192 @@
         <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L17">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M17">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="N17">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="O17">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="P17">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q17">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="S17">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="T17">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U17">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V17">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4969,186 +5002,186 @@
         <v>1.04</v>
       </c>
       <c r="CB17" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F18">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="G18">
-        <v>1.41</v>
+        <v>3.6</v>
       </c>
       <c r="H18">
-        <v>9.6</v>
+        <v>2.48</v>
       </c>
       <c r="I18">
-        <v>19</v>
+        <v>2.84</v>
       </c>
       <c r="J18">
+        <v>2.84</v>
+      </c>
+      <c r="K18">
+        <v>3.3</v>
+      </c>
+      <c r="L18">
+        <v>1.47</v>
+      </c>
+      <c r="M18">
+        <v>1.12</v>
+      </c>
+      <c r="N18">
+        <v>2.48</v>
+      </c>
+      <c r="O18">
+        <v>1.53</v>
+      </c>
+      <c r="P18">
+        <v>1.52</v>
+      </c>
+      <c r="Q18">
+        <v>2.54</v>
+      </c>
+      <c r="R18">
+        <v>1.18</v>
+      </c>
+      <c r="S18">
+        <v>4.5</v>
+      </c>
+      <c r="T18">
+        <v>2.08</v>
+      </c>
+      <c r="U18">
+        <v>1.78</v>
+      </c>
+      <c r="V18">
+        <v>1.54</v>
+      </c>
+      <c r="W18">
+        <v>1.39</v>
+      </c>
+      <c r="X18">
+        <v>10.5</v>
+      </c>
+      <c r="Y18">
+        <v>8.4</v>
+      </c>
+      <c r="Z18">
+        <v>16.5</v>
+      </c>
+      <c r="AA18">
+        <v>55</v>
+      </c>
+      <c r="AB18">
+        <v>11.5</v>
+      </c>
+      <c r="AC18">
+        <v>7.4</v>
+      </c>
+      <c r="AD18">
+        <v>13.5</v>
+      </c>
+      <c r="AE18">
+        <v>48</v>
+      </c>
+      <c r="AF18">
+        <v>27</v>
+      </c>
+      <c r="AG18">
+        <v>18.5</v>
+      </c>
+      <c r="AH18">
+        <v>24</v>
+      </c>
+      <c r="AI18">
+        <v>80</v>
+      </c>
+      <c r="AJ18">
+        <v>85</v>
+      </c>
+      <c r="AK18">
+        <v>65</v>
+      </c>
+      <c r="AL18">
+        <v>95</v>
+      </c>
+      <c r="AM18">
+        <v>220</v>
+      </c>
+      <c r="AN18">
+        <v>85</v>
+      </c>
+      <c r="AO18">
+        <v>55</v>
+      </c>
+      <c r="AP18">
+        <v>3.7</v>
+      </c>
+      <c r="AQ18">
+        <v>3.4</v>
+      </c>
+      <c r="AR18">
+        <v>4.2</v>
+      </c>
+      <c r="AS18">
+        <v>5.2</v>
+      </c>
+      <c r="AT18">
+        <v>3.85</v>
+      </c>
+      <c r="AU18">
+        <v>5.2</v>
+      </c>
+      <c r="AV18">
+        <v>4</v>
+      </c>
+      <c r="AW18">
+        <v>5.1</v>
+      </c>
+      <c r="AX18">
+        <v>4.7</v>
+      </c>
+      <c r="AY18">
         <v>4.4</v>
       </c>
-      <c r="K18">
+      <c r="AZ18">
+        <v>4.6</v>
+      </c>
+      <c r="BA18">
+        <v>5.4</v>
+      </c>
+      <c r="BB18">
+        <v>5.4</v>
+      </c>
+      <c r="BC18">
         <v>5.3</v>
       </c>
-      <c r="L18">
-        <v>1.36</v>
-      </c>
-      <c r="M18">
-        <v>1.08</v>
-      </c>
-      <c r="N18">
-        <v>2.74</v>
-      </c>
-      <c r="O18">
-        <v>1.39</v>
-      </c>
-      <c r="P18">
-        <v>1.83</v>
-      </c>
-      <c r="Q18">
-        <v>1.99</v>
-      </c>
-      <c r="R18">
-        <v>1.25</v>
-      </c>
-      <c r="S18">
-        <v>3.25</v>
-      </c>
-      <c r="T18">
-        <v>2.66</v>
-      </c>
-      <c r="U18">
-        <v>1.47</v>
-      </c>
-      <c r="V18">
-        <v>1.05</v>
-      </c>
-      <c r="W18">
-        <v>3.3</v>
-      </c>
-      <c r="X18">
-        <v>15</v>
-      </c>
-      <c r="Y18">
-        <v>38</v>
-      </c>
-      <c r="Z18">
-        <v>190</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>6.8</v>
-      </c>
-      <c r="AC18">
-        <v>14.5</v>
-      </c>
-      <c r="AD18">
-        <v>950</v>
-      </c>
-      <c r="AE18">
-        <v>530</v>
-      </c>
-      <c r="AF18">
-        <v>7.8</v>
-      </c>
-      <c r="AG18">
-        <v>14</v>
-      </c>
-      <c r="AH18">
-        <v>60</v>
-      </c>
-      <c r="AI18">
-        <v>430</v>
-      </c>
-      <c r="AJ18">
-        <v>12.5</v>
-      </c>
-      <c r="AK18">
-        <v>24</v>
-      </c>
-      <c r="AL18">
-        <v>85</v>
-      </c>
-      <c r="AM18">
-        <v>530</v>
-      </c>
-      <c r="AN18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>3.6</v>
-      </c>
-      <c r="AQ18">
-        <v>4.2</v>
-      </c>
-      <c r="AR18">
-        <v>4.6</v>
-      </c>
-      <c r="AS18">
-        <v>4.8</v>
-      </c>
-      <c r="AT18">
-        <v>2.8</v>
-      </c>
-      <c r="AU18">
-        <v>3.6</v>
-      </c>
-      <c r="AV18">
-        <v>4.5</v>
-      </c>
-      <c r="AW18">
-        <v>4.7</v>
-      </c>
-      <c r="AX18">
-        <v>2.96</v>
-      </c>
-      <c r="AY18">
-        <v>3.55</v>
-      </c>
-      <c r="AZ18">
-        <v>4.4</v>
-      </c>
-      <c r="BA18">
-        <v>4.7</v>
-      </c>
-      <c r="BB18">
-        <v>3.45</v>
-      </c>
-      <c r="BC18">
-        <v>4</v>
-      </c>
       <c r="BD18">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE18">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF18">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="BG18">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5211,114 +5244,114 @@
         <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="F19">
-        <v>8.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="G19">
-        <v>11.5</v>
+        <v>2.18</v>
       </c>
       <c r="H19">
-        <v>1.31</v>
+        <v>4.4</v>
       </c>
       <c r="I19">
-        <v>1.37</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="K19">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="L19">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="M19">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N19">
-        <v>8.199999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="O19">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="P19">
-        <v>3.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q19">
-        <v>1.34</v>
+        <v>2.18</v>
       </c>
       <c r="R19">
-        <v>2.02</v>
+        <v>1.13</v>
       </c>
       <c r="S19">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="T19">
-        <v>1.66</v>
+        <v>2.04</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>1.55</v>
       </c>
       <c r="V19">
-        <v>3.7</v>
+        <v>1.16</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
         <v>950</v>
       </c>
-      <c r="Y19">
-        <v>16.5</v>
-      </c>
-      <c r="Z19">
-        <v>13</v>
-      </c>
-      <c r="AA19">
-        <v>13</v>
-      </c>
-      <c r="AB19">
-        <v>950</v>
-      </c>
-      <c r="AC19">
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
         <v>17</v>
-      </c>
-      <c r="AD19">
-        <v>12</v>
-      </c>
-      <c r="AE19">
-        <v>14</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
       </c>
       <c r="AG19">
         <v>950</v>
       </c>
       <c r="AH19">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
         <v>1000</v>
@@ -5327,313 +5360,313 @@
         <v>1000</v>
       </c>
       <c r="AL19">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
         <v>1000</v>
       </c>
       <c r="AO19">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>7.4</v>
+        <v>1.23</v>
       </c>
       <c r="AQ19">
+        <v>7.8</v>
+      </c>
+      <c r="AR19">
+        <v>19.5</v>
+      </c>
+      <c r="AS19">
+        <v>1.23</v>
+      </c>
+      <c r="AT19">
+        <v>4.4</v>
+      </c>
+      <c r="AU19">
+        <v>5.1</v>
+      </c>
+      <c r="AV19">
         <v>14</v>
       </c>
-      <c r="AR19">
-        <v>11</v>
-      </c>
-      <c r="AS19">
-        <v>11</v>
-      </c>
-      <c r="AT19">
-        <v>7.4</v>
-      </c>
-      <c r="AU19">
-        <v>14.5</v>
-      </c>
-      <c r="AV19">
-        <v>10</v>
-      </c>
       <c r="AW19">
-        <v>11.5</v>
+        <v>1.23</v>
       </c>
       <c r="AX19">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="AY19">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AZ19">
-        <v>20</v>
+        <v>1.23</v>
       </c>
       <c r="BA19">
-        <v>6.6</v>
+        <v>1.23</v>
       </c>
       <c r="BB19">
-        <v>8.800000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="BC19">
-        <v>8.800000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="BD19">
-        <v>7.8</v>
+        <v>1.23</v>
       </c>
       <c r="BE19">
-        <v>7.8</v>
+        <v>1.23</v>
       </c>
       <c r="BF19">
-        <v>8.800000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="BG19">
-        <v>3.1</v>
+        <v>1.23</v>
       </c>
       <c r="BH19">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F20">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="G20">
-        <v>1.86</v>
+        <v>1.41</v>
       </c>
       <c r="H20">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>5.1</v>
+        <v>16.5</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M20">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N20">
-        <v>4.7</v>
+        <v>2.94</v>
       </c>
       <c r="O20">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="P20">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="Q20">
-        <v>1.61</v>
+        <v>2.14</v>
       </c>
       <c r="R20">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="S20">
-        <v>2.52</v>
+        <v>3.7</v>
       </c>
       <c r="T20">
-        <v>1.63</v>
+        <v>2.68</v>
       </c>
       <c r="U20">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="V20">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="W20">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="X20">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Y20">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Z20">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="AA20">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD20">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE20">
-        <v>60</v>
+        <v>530</v>
       </c>
       <c r="AF20">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="AG20">
         <v>12</v>
       </c>
       <c r="AH20">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AI20">
-        <v>60</v>
+        <v>430</v>
       </c>
       <c r="AJ20">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AK20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL20">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AM20">
-        <v>85</v>
+        <v>530</v>
       </c>
       <c r="AN20">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO20">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>18.5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ20">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AR20">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="AS20">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT20">
-        <v>9.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="AU20">
+        <v>5</v>
+      </c>
+      <c r="AV20">
+        <v>18</v>
+      </c>
+      <c r="AW20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX20">
+        <v>3.75</v>
+      </c>
+      <c r="AY20">
+        <v>4.9</v>
+      </c>
+      <c r="AZ20">
+        <v>15</v>
+      </c>
+      <c r="BA20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB20">
+        <v>4.7</v>
+      </c>
+      <c r="BC20">
+        <v>6</v>
+      </c>
+      <c r="BD20">
+        <v>19.5</v>
+      </c>
+      <c r="BE20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF20">
+        <v>4.3</v>
+      </c>
+      <c r="BG20">
         <v>8.4</v>
       </c>
-      <c r="AV20">
-        <v>15.5</v>
-      </c>
-      <c r="AW20">
-        <v>5</v>
-      </c>
-      <c r="AX20">
-        <v>10.5</v>
-      </c>
-      <c r="AY20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ20">
-        <v>14.5</v>
-      </c>
-      <c r="BA20">
-        <v>5</v>
-      </c>
-      <c r="BB20">
-        <v>16.5</v>
-      </c>
-      <c r="BC20">
-        <v>14.5</v>
-      </c>
-      <c r="BD20">
-        <v>6.4</v>
-      </c>
-      <c r="BE20">
-        <v>5.1</v>
-      </c>
-      <c r="BF20">
-        <v>7.4</v>
-      </c>
-      <c r="BG20">
-        <v>4.9</v>
-      </c>
       <c r="BH20">
         <v>1000</v>
       </c>
@@ -5695,526 +5728,526 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E21" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F21">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G21">
-        <v>990</v>
+        <v>12</v>
       </c>
       <c r="H21">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="I21">
-        <v>990</v>
+        <v>1.37</v>
       </c>
       <c r="J21">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="K21">
+        <v>7.2</v>
+      </c>
+      <c r="L21">
+        <v>1.17</v>
+      </c>
+      <c r="M21">
+        <v>1.02</v>
+      </c>
+      <c r="N21">
+        <v>8.4</v>
+      </c>
+      <c r="O21">
+        <v>1.12</v>
+      </c>
+      <c r="P21">
+        <v>3.45</v>
+      </c>
+      <c r="Q21">
+        <v>1.34</v>
+      </c>
+      <c r="R21">
+        <v>2.02</v>
+      </c>
+      <c r="S21">
+        <v>1.9</v>
+      </c>
+      <c r="T21">
+        <v>1.66</v>
+      </c>
+      <c r="U21">
+        <v>2.28</v>
+      </c>
+      <c r="V21">
+        <v>3.7</v>
+      </c>
+      <c r="W21">
+        <v>1.1</v>
+      </c>
+      <c r="X21">
+        <v>48</v>
+      </c>
+      <c r="Y21">
+        <v>16.5</v>
+      </c>
+      <c r="Z21">
+        <v>13</v>
+      </c>
+      <c r="AA21">
+        <v>13</v>
+      </c>
+      <c r="AB21">
         <v>950</v>
       </c>
-      <c r="L21">
-        <v>1.01</v>
-      </c>
-      <c r="M21">
-        <v>1.01</v>
-      </c>
-      <c r="N21">
-        <v>1.25</v>
-      </c>
-      <c r="O21">
-        <v>1.14</v>
-      </c>
-      <c r="P21">
-        <v>1.25</v>
-      </c>
-      <c r="Q21">
-        <v>1.13</v>
-      </c>
-      <c r="R21">
-        <v>1.18</v>
-      </c>
-      <c r="S21">
-        <v>1.14</v>
-      </c>
-      <c r="T21">
-        <v>1.11</v>
-      </c>
-      <c r="U21">
-        <v>1.11</v>
-      </c>
-      <c r="V21">
-        <v>1.01</v>
-      </c>
-      <c r="W21">
-        <v>1.01</v>
-      </c>
-      <c r="X21">
-        <v>1000</v>
-      </c>
-      <c r="Y21">
-        <v>1000</v>
-      </c>
-      <c r="Z21">
-        <v>1000</v>
-      </c>
-      <c r="AA21">
-        <v>1000</v>
-      </c>
-      <c r="AB21">
-        <v>1000</v>
-      </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="AP21">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB21">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC21">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD21">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="CB21" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E22" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F22">
-        <v>2.96</v>
+        <v>1.73</v>
       </c>
       <c r="G22">
-        <v>2.98</v>
+        <v>1.86</v>
       </c>
       <c r="H22">
-        <v>2.66</v>
+        <v>4.4</v>
       </c>
       <c r="I22">
-        <v>2.68</v>
+        <v>5.1</v>
       </c>
       <c r="J22">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N22">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="O22">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="P22">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="Q22">
-        <v>2.08</v>
+        <v>1.61</v>
       </c>
       <c r="R22">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="S22">
-        <v>3.75</v>
+        <v>2.52</v>
       </c>
       <c r="T22">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="U22">
+        <v>2.28</v>
+      </c>
+      <c r="V22">
+        <v>1.24</v>
+      </c>
+      <c r="W22">
         <v>2.16</v>
       </c>
-      <c r="V22">
-        <v>1.59</v>
-      </c>
-      <c r="W22">
-        <v>1.5</v>
-      </c>
       <c r="X22">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Y22">
+        <v>24</v>
+      </c>
+      <c r="Z22">
+        <v>42</v>
+      </c>
+      <c r="AA22">
+        <v>110</v>
+      </c>
+      <c r="AB22">
+        <v>13.5</v>
+      </c>
+      <c r="AC22">
         <v>10.5</v>
       </c>
-      <c r="Z22">
+      <c r="AD22">
+        <v>22</v>
+      </c>
+      <c r="AE22">
+        <v>55</v>
+      </c>
+      <c r="AF22">
+        <v>13.5</v>
+      </c>
+      <c r="AG22">
+        <v>11</v>
+      </c>
+      <c r="AH22">
+        <v>18</v>
+      </c>
+      <c r="AI22">
+        <v>60</v>
+      </c>
+      <c r="AJ22">
+        <v>21</v>
+      </c>
+      <c r="AK22">
+        <v>18</v>
+      </c>
+      <c r="AL22">
+        <v>34</v>
+      </c>
+      <c r="AM22">
+        <v>85</v>
+      </c>
+      <c r="AN22">
+        <v>9</v>
+      </c>
+      <c r="AO22">
+        <v>50</v>
+      </c>
+      <c r="AP22">
+        <v>18.5</v>
+      </c>
+      <c r="AQ22">
         <v>17.5</v>
       </c>
-      <c r="AA22">
-        <v>40</v>
-      </c>
-      <c r="AB22">
-        <v>11.5</v>
-      </c>
-      <c r="AC22">
+      <c r="AR22">
+        <v>6.2</v>
+      </c>
+      <c r="AS22">
+        <v>7</v>
+      </c>
+      <c r="AT22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU22">
+        <v>8.4</v>
+      </c>
+      <c r="AV22">
+        <v>15.5</v>
+      </c>
+      <c r="AW22">
+        <v>6.4</v>
+      </c>
+      <c r="AX22">
+        <v>10.5</v>
+      </c>
+      <c r="AY22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ22">
+        <v>14.5</v>
+      </c>
+      <c r="BA22">
+        <v>6.6</v>
+      </c>
+      <c r="BB22">
+        <v>16.5</v>
+      </c>
+      <c r="BC22">
+        <v>14.5</v>
+      </c>
+      <c r="BD22">
+        <v>6</v>
+      </c>
+      <c r="BE22">
+        <v>6.8</v>
+      </c>
+      <c r="BF22">
         <v>7.4</v>
       </c>
-      <c r="AD22">
-        <v>12</v>
-      </c>
-      <c r="AE22">
-        <v>30</v>
-      </c>
-      <c r="AF22">
-        <v>19.5</v>
-      </c>
-      <c r="AG22">
-        <v>13</v>
-      </c>
-      <c r="AH22">
-        <v>17.5</v>
-      </c>
-      <c r="AI22">
-        <v>44</v>
-      </c>
-      <c r="AJ22">
-        <v>46</v>
-      </c>
-      <c r="AK22">
-        <v>34</v>
-      </c>
-      <c r="AL22">
-        <v>44</v>
-      </c>
-      <c r="AM22">
-        <v>95</v>
-      </c>
-      <c r="AN22">
-        <v>30</v>
-      </c>
-      <c r="AO22">
-        <v>26</v>
-      </c>
-      <c r="AP22">
-        <v>11.5</v>
-      </c>
-      <c r="AQ22">
-        <v>10</v>
-      </c>
-      <c r="AR22">
-        <v>16</v>
-      </c>
-      <c r="AS22">
-        <v>36</v>
-      </c>
-      <c r="AT22">
-        <v>10.5</v>
-      </c>
-      <c r="AU22">
-        <v>7.2</v>
-      </c>
-      <c r="AV22">
-        <v>11</v>
-      </c>
-      <c r="AW22">
-        <v>27</v>
-      </c>
-      <c r="AX22">
-        <v>18</v>
-      </c>
-      <c r="AY22">
-        <v>12</v>
-      </c>
-      <c r="AZ22">
-        <v>16</v>
-      </c>
-      <c r="BA22">
-        <v>36</v>
-      </c>
-      <c r="BB22">
-        <v>42</v>
-      </c>
-      <c r="BC22">
-        <v>30</v>
-      </c>
-      <c r="BD22">
-        <v>40</v>
-      </c>
-      <c r="BE22">
-        <v>75</v>
-      </c>
-      <c r="BF22">
-        <v>27</v>
-      </c>
       <c r="BG22">
-        <v>23</v>
+        <v>6.4</v>
       </c>
       <c r="BH22">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>17.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F23">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="G23">
-        <v>1.36</v>
+        <v>990</v>
       </c>
       <c r="H23">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="I23">
-        <v>8.4</v>
+        <v>990</v>
       </c>
       <c r="J23">
-        <v>6.8</v>
+        <v>1.09</v>
       </c>
       <c r="K23">
-        <v>7.2</v>
+        <v>950</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6223,142 +6256,142 @@
         <v>1.01</v>
       </c>
       <c r="N23">
+        <v>1.28</v>
+      </c>
+      <c r="O23">
+        <v>1.14</v>
+      </c>
+      <c r="P23">
+        <v>1.28</v>
+      </c>
+      <c r="Q23">
+        <v>1.13</v>
+      </c>
+      <c r="R23">
+        <v>1.18</v>
+      </c>
+      <c r="S23">
+        <v>1.14</v>
+      </c>
+      <c r="T23">
         <v>1.11</v>
       </c>
-      <c r="O23">
-        <v>1.09</v>
-      </c>
-      <c r="P23">
-        <v>1.25</v>
-      </c>
-      <c r="Q23">
-        <v>1.27</v>
-      </c>
-      <c r="R23">
-        <v>2.14</v>
-      </c>
-      <c r="S23">
-        <v>1.57</v>
-      </c>
-      <c r="T23">
-        <v>1.51</v>
-      </c>
       <c r="U23">
-        <v>2.58</v>
+        <v>1.11</v>
       </c>
       <c r="V23">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W23">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6421,1046 +6454,1046 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F24">
-        <v>2.28</v>
+        <v>2.98</v>
       </c>
       <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
         <v>2.64</v>
       </c>
-      <c r="H24">
-        <v>3.3</v>
-      </c>
       <c r="I24">
-        <v>4.5</v>
+        <v>2.68</v>
       </c>
       <c r="J24">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="K24">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M24">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N24">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="O24">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="P24">
-        <v>1.39</v>
+        <v>1.9</v>
       </c>
       <c r="Q24">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="R24">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="S24">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="T24">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U24">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V24">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK24">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BL24">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM24">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>17.5</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS24">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>16</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CB24" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
         <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N25">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="O25">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="P25">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="Q25">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="R25">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="S25">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="T25">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U25">
-        <v>1.11</v>
+        <v>2.6</v>
       </c>
       <c r="V25">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK25">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO25">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ25">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS25">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU25">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="CB25" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="F26">
-        <v>2.16</v>
+        <v>1.54</v>
       </c>
       <c r="G26">
-        <v>2.26</v>
+        <v>1.56</v>
       </c>
       <c r="H26">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="I26">
+        <v>6.2</v>
+      </c>
+      <c r="J26">
+        <v>5.4</v>
+      </c>
+      <c r="K26">
+        <v>5.5</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.02</v>
+      </c>
+      <c r="N26">
+        <v>8.6</v>
+      </c>
+      <c r="O26">
+        <v>1.11</v>
+      </c>
+      <c r="P26">
+        <v>3.5</v>
+      </c>
+      <c r="Q26">
+        <v>1.35</v>
+      </c>
+      <c r="R26">
+        <v>2.06</v>
+      </c>
+      <c r="S26">
+        <v>1.86</v>
+      </c>
+      <c r="T26">
+        <v>1.5</v>
+      </c>
+      <c r="U26">
+        <v>2.78</v>
+      </c>
+      <c r="V26">
+        <v>1.2</v>
+      </c>
+      <c r="W26">
+        <v>2.78</v>
+      </c>
+      <c r="X26">
+        <v>140</v>
+      </c>
+      <c r="Y26">
+        <v>48</v>
+      </c>
+      <c r="Z26">
+        <v>65</v>
+      </c>
+      <c r="AA26">
+        <v>150</v>
+      </c>
+      <c r="AB26">
+        <v>19</v>
+      </c>
+      <c r="AC26">
+        <v>14.5</v>
+      </c>
+      <c r="AD26">
+        <v>24</v>
+      </c>
+      <c r="AE26">
+        <v>60</v>
+      </c>
+      <c r="AF26">
+        <v>15</v>
+      </c>
+      <c r="AG26">
+        <v>11.5</v>
+      </c>
+      <c r="AH26">
+        <v>17.5</v>
+      </c>
+      <c r="AI26">
+        <v>48</v>
+      </c>
+      <c r="AJ26">
+        <v>18</v>
+      </c>
+      <c r="AK26">
+        <v>13.5</v>
+      </c>
+      <c r="AL26">
+        <v>22</v>
+      </c>
+      <c r="AM26">
+        <v>55</v>
+      </c>
+      <c r="AN26">
         <v>4.4</v>
       </c>
-      <c r="J26">
-        <v>3</v>
-      </c>
-      <c r="K26">
-        <v>3.35</v>
-      </c>
-      <c r="L26">
-        <v>1.49</v>
-      </c>
-      <c r="M26">
-        <v>1.12</v>
-      </c>
-      <c r="N26">
-        <v>2.56</v>
-      </c>
-      <c r="O26">
-        <v>1.45</v>
-      </c>
-      <c r="P26">
-        <v>1.55</v>
-      </c>
-      <c r="Q26">
-        <v>2.52</v>
-      </c>
-      <c r="R26">
-        <v>1.2</v>
-      </c>
-      <c r="S26">
-        <v>4.6</v>
-      </c>
-      <c r="T26">
-        <v>1.95</v>
-      </c>
-      <c r="U26">
-        <v>1.79</v>
-      </c>
-      <c r="V26">
-        <v>1.29</v>
-      </c>
-      <c r="W26">
-        <v>1.79</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26">
-        <v>0</v>
-      </c>
-      <c r="AI26">
-        <v>0</v>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>0</v>
-      </c>
       <c r="AO26">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BH26">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
         <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E27" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F27">
-        <v>2.06</v>
+        <v>1.35</v>
       </c>
       <c r="G27">
+        <v>1.36</v>
+      </c>
+      <c r="H27">
+        <v>7.8</v>
+      </c>
+      <c r="I27">
+        <v>8.4</v>
+      </c>
+      <c r="J27">
+        <v>6.8</v>
+      </c>
+      <c r="K27">
+        <v>7.2</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.01</v>
+      </c>
+      <c r="N27">
+        <v>1.1</v>
+      </c>
+      <c r="O27">
+        <v>1.09</v>
+      </c>
+      <c r="P27">
+        <v>1.25</v>
+      </c>
+      <c r="Q27">
+        <v>1.27</v>
+      </c>
+      <c r="R27">
         <v>2.14</v>
       </c>
-      <c r="H27">
+      <c r="S27">
+        <v>1.57</v>
+      </c>
+      <c r="T27">
+        <v>1.51</v>
+      </c>
+      <c r="U27">
+        <v>2.58</v>
+      </c>
+      <c r="V27">
+        <v>1.13</v>
+      </c>
+      <c r="W27">
+        <v>3.75</v>
+      </c>
+      <c r="X27">
+        <v>70</v>
+      </c>
+      <c r="Y27">
+        <v>60</v>
+      </c>
+      <c r="Z27">
+        <v>110</v>
+      </c>
+      <c r="AA27">
+        <v>230</v>
+      </c>
+      <c r="AB27">
+        <v>23</v>
+      </c>
+      <c r="AC27">
+        <v>23</v>
+      </c>
+      <c r="AD27">
+        <v>40</v>
+      </c>
+      <c r="AE27">
+        <v>80</v>
+      </c>
+      <c r="AF27">
+        <v>19</v>
+      </c>
+      <c r="AG27">
+        <v>15.5</v>
+      </c>
+      <c r="AH27">
+        <v>25</v>
+      </c>
+      <c r="AI27">
+        <v>70</v>
+      </c>
+      <c r="AJ27">
+        <v>19</v>
+      </c>
+      <c r="AK27">
+        <v>17</v>
+      </c>
+      <c r="AL27">
+        <v>27</v>
+      </c>
+      <c r="AM27">
+        <v>70</v>
+      </c>
+      <c r="AN27">
+        <v>3.45</v>
+      </c>
+      <c r="AO27">
+        <v>48</v>
+      </c>
+      <c r="AP27">
+        <v>5</v>
+      </c>
+      <c r="AQ27">
+        <v>5</v>
+      </c>
+      <c r="AR27">
+        <v>5.1</v>
+      </c>
+      <c r="AS27">
+        <v>5.3</v>
+      </c>
+      <c r="AT27">
         <v>4.4</v>
       </c>
-      <c r="I27">
-        <v>5.8</v>
-      </c>
-      <c r="J27">
-        <v>1.1</v>
-      </c>
-      <c r="K27">
-        <v>3.45</v>
-      </c>
-      <c r="L27">
-        <v>1.01</v>
-      </c>
-      <c r="M27">
-        <v>1.11</v>
-      </c>
-      <c r="N27">
-        <v>2.58</v>
-      </c>
-      <c r="O27">
-        <v>1.4</v>
-      </c>
-      <c r="P27">
-        <v>1.57</v>
-      </c>
-      <c r="Q27">
-        <v>2.06</v>
-      </c>
-      <c r="R27">
-        <v>1.22</v>
-      </c>
-      <c r="S27">
-        <v>4.5</v>
-      </c>
-      <c r="T27">
-        <v>2.04</v>
-      </c>
-      <c r="U27">
-        <v>1.67</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>11.5</v>
-      </c>
-      <c r="Y27">
-        <v>16</v>
-      </c>
-      <c r="Z27">
-        <v>34</v>
-      </c>
-      <c r="AA27">
-        <v>140</v>
-      </c>
-      <c r="AB27">
-        <v>7.4</v>
-      </c>
-      <c r="AC27">
-        <v>8</v>
-      </c>
-      <c r="AD27">
-        <v>21</v>
-      </c>
-      <c r="AE27">
-        <v>85</v>
-      </c>
-      <c r="AF27">
-        <v>13</v>
-      </c>
-      <c r="AG27">
-        <v>12.5</v>
-      </c>
-      <c r="AH27">
-        <v>1000</v>
-      </c>
-      <c r="AI27">
-        <v>1000</v>
-      </c>
-      <c r="AJ27">
-        <v>27</v>
-      </c>
-      <c r="AK27">
-        <v>28</v>
-      </c>
-      <c r="AL27">
-        <v>60</v>
-      </c>
-      <c r="AM27">
-        <v>1000</v>
-      </c>
-      <c r="AN27">
-        <v>24</v>
-      </c>
-      <c r="AO27">
-        <v>130</v>
-      </c>
-      <c r="AP27">
-        <v>3.5</v>
-      </c>
-      <c r="AQ27">
-        <v>11</v>
-      </c>
-      <c r="AR27">
+      <c r="AU27">
         <v>4.4</v>
       </c>
-      <c r="AS27">
+      <c r="AV27">
         <v>4.8</v>
       </c>
-      <c r="AT27">
-        <v>6</v>
-      </c>
-      <c r="AU27">
-        <v>6.6</v>
-      </c>
-      <c r="AV27">
-        <v>16.5</v>
-      </c>
       <c r="AW27">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX27">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="AY27">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="AZ27">
-        <v>19.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA27">
         <v>5</v>
       </c>
       <c r="BB27">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="BC27">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD27">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE27">
         <v>5</v>
       </c>
       <c r="BF27">
-        <v>17</v>
+        <v>2.66</v>
       </c>
       <c r="BG27">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP27">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CA27">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
         <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E28" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F28">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="G28">
-        <v>990</v>
+        <v>2.64</v>
       </c>
       <c r="H28">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="I28">
-        <v>600</v>
+        <v>4.3</v>
       </c>
       <c r="J28">
-        <v>1.06</v>
+        <v>2.88</v>
       </c>
       <c r="K28">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N28">
-        <v>1.26</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="P28">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="Q28">
-        <v>1.16</v>
+        <v>2.46</v>
       </c>
       <c r="R28">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S28">
-        <v>1.05</v>
+        <v>2.8</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V28">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W28">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7631,249 +7664,1217 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" t="s">
+        <v>175</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.01</v>
+      </c>
+      <c r="N29">
+        <v>1.1</v>
+      </c>
+      <c r="O29">
+        <v>1.02</v>
+      </c>
+      <c r="P29">
+        <v>1.25</v>
+      </c>
+      <c r="Q29">
+        <v>1.5</v>
+      </c>
+      <c r="R29">
+        <v>1.18</v>
+      </c>
+      <c r="S29">
+        <v>1.5</v>
+      </c>
+      <c r="T29">
+        <v>1.11</v>
+      </c>
+      <c r="U29">
+        <v>1.11</v>
+      </c>
+      <c r="V29">
+        <v>1.01</v>
+      </c>
+      <c r="W29">
+        <v>1.01</v>
+      </c>
+      <c r="X29">
+        <v>1000</v>
+      </c>
+      <c r="Y29">
+        <v>1000</v>
+      </c>
+      <c r="Z29">
+        <v>1000</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
+        <v>1000</v>
+      </c>
+      <c r="AC29">
+        <v>1000</v>
+      </c>
+      <c r="AD29">
+        <v>1000</v>
+      </c>
+      <c r="AE29">
+        <v>1000</v>
+      </c>
+      <c r="AF29">
+        <v>1000</v>
+      </c>
+      <c r="AG29">
+        <v>1000</v>
+      </c>
+      <c r="AH29">
+        <v>1000</v>
+      </c>
+      <c r="AI29">
+        <v>1000</v>
+      </c>
+      <c r="AJ29">
+        <v>1000</v>
+      </c>
+      <c r="AK29">
+        <v>1000</v>
+      </c>
+      <c r="AL29">
+        <v>1000</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>1000</v>
+      </c>
+      <c r="AO29">
+        <v>1000</v>
+      </c>
+      <c r="AP29">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29">
+        <v>1.01</v>
+      </c>
+      <c r="AR29">
+        <v>1.01</v>
+      </c>
+      <c r="AS29">
+        <v>1.01</v>
+      </c>
+      <c r="AT29">
+        <v>1.01</v>
+      </c>
+      <c r="AU29">
+        <v>1.01</v>
+      </c>
+      <c r="AV29">
+        <v>1.01</v>
+      </c>
+      <c r="AW29">
+        <v>1.01</v>
+      </c>
+      <c r="AX29">
+        <v>1.01</v>
+      </c>
+      <c r="AY29">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29">
+        <v>1.01</v>
+      </c>
+      <c r="BA29">
+        <v>1.01</v>
+      </c>
+      <c r="BB29">
+        <v>1.01</v>
+      </c>
+      <c r="BC29">
+        <v>1.01</v>
+      </c>
+      <c r="BD29">
+        <v>1.01</v>
+      </c>
+      <c r="BE29">
+        <v>1.01</v>
+      </c>
+      <c r="BF29">
+        <v>1.01</v>
+      </c>
+      <c r="BG29">
+        <v>1.01</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>1.04</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>1.04</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.04</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>1.04</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>1.04</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>1.04</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>1.04</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.04</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.04</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>1.04</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
         <v>95</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F30">
+        <v>2.16</v>
+      </c>
+      <c r="G30">
+        <v>2.26</v>
+      </c>
+      <c r="H30">
+        <v>3.9</v>
+      </c>
+      <c r="I30">
+        <v>4.4</v>
+      </c>
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30">
+        <v>3.3</v>
+      </c>
+      <c r="L30">
+        <v>1.49</v>
+      </c>
+      <c r="M30">
+        <v>1.12</v>
+      </c>
+      <c r="N30">
+        <v>2.62</v>
+      </c>
+      <c r="O30">
+        <v>1.52</v>
+      </c>
+      <c r="P30">
+        <v>1.56</v>
+      </c>
+      <c r="Q30">
+        <v>2.52</v>
+      </c>
+      <c r="R30">
+        <v>1.2</v>
+      </c>
+      <c r="S30">
+        <v>5.1</v>
+      </c>
+      <c r="T30">
+        <v>2.08</v>
+      </c>
+      <c r="U30">
+        <v>1.79</v>
+      </c>
+      <c r="V30">
+        <v>1.3</v>
+      </c>
+      <c r="W30">
+        <v>1.79</v>
+      </c>
+      <c r="X30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y30">
+        <v>11.5</v>
+      </c>
+      <c r="Z30">
+        <v>34</v>
+      </c>
+      <c r="AA30">
+        <v>120</v>
+      </c>
+      <c r="AB30">
+        <v>7.2</v>
+      </c>
+      <c r="AC30">
+        <v>8.4</v>
+      </c>
+      <c r="AD30">
+        <v>20</v>
+      </c>
+      <c r="AE30">
+        <v>80</v>
+      </c>
+      <c r="AF30">
+        <v>15.5</v>
+      </c>
+      <c r="AG30">
+        <v>12</v>
+      </c>
+      <c r="AH30">
+        <v>26</v>
+      </c>
+      <c r="AI30">
+        <v>110</v>
+      </c>
+      <c r="AJ30">
+        <v>36</v>
+      </c>
+      <c r="AK30">
+        <v>36</v>
+      </c>
+      <c r="AL30">
+        <v>70</v>
+      </c>
+      <c r="AM30">
+        <v>210</v>
+      </c>
+      <c r="AN30">
+        <v>34</v>
+      </c>
+      <c r="AO30">
+        <v>120</v>
+      </c>
+      <c r="AP30">
+        <v>8</v>
+      </c>
+      <c r="AQ30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR30">
+        <v>6.4</v>
+      </c>
+      <c r="AS30">
+        <v>7.6</v>
+      </c>
+      <c r="AT30">
+        <v>6.4</v>
+      </c>
+      <c r="AU30">
+        <v>6.4</v>
+      </c>
+      <c r="AV30">
+        <v>15.5</v>
+      </c>
+      <c r="AW30">
+        <v>7.2</v>
+      </c>
+      <c r="AX30">
+        <v>11.5</v>
+      </c>
+      <c r="AY30">
+        <v>10</v>
+      </c>
+      <c r="AZ30">
+        <v>6</v>
+      </c>
+      <c r="BA30">
+        <v>7.4</v>
+      </c>
+      <c r="BB30">
+        <v>6.4</v>
+      </c>
+      <c r="BC30">
+        <v>6.4</v>
+      </c>
+      <c r="BD30">
+        <v>7.2</v>
+      </c>
+      <c r="BE30">
+        <v>7.8</v>
+      </c>
+      <c r="BF30">
+        <v>23</v>
+      </c>
+      <c r="BG30">
+        <v>7.6</v>
+      </c>
+      <c r="BH30">
+        <v>3.05</v>
+      </c>
+      <c r="BI30">
+        <v>2.32</v>
+      </c>
+      <c r="BJ30">
+        <v>11.5</v>
+      </c>
+      <c r="BK30">
+        <v>4.2</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>6.4</v>
+      </c>
+      <c r="BN30">
+        <v>5.4</v>
+      </c>
+      <c r="BO30">
+        <v>3.85</v>
+      </c>
+      <c r="BP30">
+        <v>22</v>
+      </c>
+      <c r="BQ30">
+        <v>5.1</v>
+      </c>
+      <c r="BR30">
+        <v>48</v>
+      </c>
+      <c r="BS30">
+        <v>5.9</v>
+      </c>
+      <c r="BT30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU30">
+        <v>5.6</v>
+      </c>
+      <c r="BV30">
+        <v>46</v>
+      </c>
+      <c r="BW30">
+        <v>5.8</v>
+      </c>
+      <c r="BX30">
+        <v>70</v>
+      </c>
+      <c r="BY30">
+        <v>6</v>
+      </c>
+      <c r="BZ30">
+        <v>55</v>
+      </c>
+      <c r="CA30">
+        <v>5.9</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31">
+        <v>2.06</v>
+      </c>
+      <c r="G31">
+        <v>2.14</v>
+      </c>
+      <c r="H31">
+        <v>4.4</v>
+      </c>
+      <c r="I31">
+        <v>4.9</v>
+      </c>
+      <c r="J31">
+        <v>3.25</v>
+      </c>
+      <c r="K31">
+        <v>3.45</v>
+      </c>
+      <c r="L31">
+        <v>1.01</v>
+      </c>
+      <c r="M31">
+        <v>1.11</v>
+      </c>
+      <c r="N31">
+        <v>2.78</v>
+      </c>
+      <c r="O31">
+        <v>1.41</v>
+      </c>
+      <c r="P31">
+        <v>1.57</v>
+      </c>
+      <c r="Q31">
+        <v>2.28</v>
+      </c>
+      <c r="R31">
+        <v>1.22</v>
+      </c>
+      <c r="S31">
+        <v>4.5</v>
+      </c>
+      <c r="T31">
+        <v>2.06</v>
+      </c>
+      <c r="U31">
+        <v>1.79</v>
+      </c>
+      <c r="V31">
+        <v>1.26</v>
+      </c>
+      <c r="W31">
+        <v>1.91</v>
+      </c>
+      <c r="X31">
+        <v>11.5</v>
+      </c>
+      <c r="Y31">
+        <v>14</v>
+      </c>
+      <c r="Z31">
+        <v>34</v>
+      </c>
+      <c r="AA31">
+        <v>140</v>
+      </c>
+      <c r="AB31">
+        <v>7.4</v>
+      </c>
+      <c r="AC31">
+        <v>8</v>
+      </c>
+      <c r="AD31">
+        <v>21</v>
+      </c>
+      <c r="AE31">
+        <v>85</v>
+      </c>
+      <c r="AF31">
+        <v>12</v>
+      </c>
+      <c r="AG31">
+        <v>11.5</v>
+      </c>
+      <c r="AH31">
+        <v>24</v>
+      </c>
+      <c r="AI31">
+        <v>110</v>
+      </c>
+      <c r="AJ31">
+        <v>27</v>
+      </c>
+      <c r="AK31">
+        <v>28</v>
+      </c>
+      <c r="AL31">
+        <v>60</v>
+      </c>
+      <c r="AM31">
+        <v>200</v>
+      </c>
+      <c r="AN31">
+        <v>24</v>
+      </c>
+      <c r="AO31">
+        <v>130</v>
+      </c>
+      <c r="AP31">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ31">
+        <v>11</v>
+      </c>
+      <c r="AR31">
+        <v>6.6</v>
+      </c>
+      <c r="AS31">
+        <v>7.8</v>
+      </c>
+      <c r="AT31">
+        <v>6</v>
+      </c>
+      <c r="AU31">
+        <v>6.6</v>
+      </c>
+      <c r="AV31">
+        <v>16.5</v>
+      </c>
+      <c r="AW31">
+        <v>7.4</v>
+      </c>
+      <c r="AX31">
+        <v>9.6</v>
+      </c>
+      <c r="AY31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ31">
+        <v>19.5</v>
+      </c>
+      <c r="BA31">
+        <v>7.6</v>
+      </c>
+      <c r="BB31">
+        <v>21</v>
+      </c>
+      <c r="BC31">
+        <v>6.2</v>
+      </c>
+      <c r="BD31">
+        <v>7.2</v>
+      </c>
+      <c r="BE31">
+        <v>7.8</v>
+      </c>
+      <c r="BF31">
+        <v>19</v>
+      </c>
+      <c r="BG31">
+        <v>7.6</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>1.04</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.04</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.04</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.04</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.04</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.04</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.04</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.04</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.04</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
+        <v>1.04</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s">
+        <v>115</v>
+      </c>
+      <c r="D32" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" t="s">
+        <v>178</v>
+      </c>
+      <c r="F32">
+        <v>1.7</v>
+      </c>
+      <c r="G32">
+        <v>990</v>
+      </c>
+      <c r="H32">
+        <v>1.75</v>
+      </c>
+      <c r="I32">
+        <v>32</v>
+      </c>
+      <c r="J32">
+        <v>1.09</v>
+      </c>
+      <c r="K32">
+        <v>950</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.01</v>
+      </c>
+      <c r="N32">
+        <v>1.28</v>
+      </c>
+      <c r="O32">
+        <v>1.16</v>
+      </c>
+      <c r="P32">
+        <v>1.28</v>
+      </c>
+      <c r="Q32">
+        <v>1.16</v>
+      </c>
+      <c r="R32">
+        <v>1.18</v>
+      </c>
+      <c r="S32">
+        <v>1.16</v>
+      </c>
+      <c r="T32">
+        <v>1.11</v>
+      </c>
+      <c r="U32">
+        <v>1.11</v>
+      </c>
+      <c r="V32">
+        <v>1.03</v>
+      </c>
+      <c r="W32">
+        <v>1.01</v>
+      </c>
+      <c r="X32">
+        <v>1000</v>
+      </c>
+      <c r="Y32">
+        <v>1000</v>
+      </c>
+      <c r="Z32">
+        <v>1000</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>1000</v>
+      </c>
+      <c r="AC32">
+        <v>1000</v>
+      </c>
+      <c r="AD32">
+        <v>1000</v>
+      </c>
+      <c r="AE32">
+        <v>1000</v>
+      </c>
+      <c r="AF32">
+        <v>1000</v>
+      </c>
+      <c r="AG32">
+        <v>1000</v>
+      </c>
+      <c r="AH32">
+        <v>1000</v>
+      </c>
+      <c r="AI32">
+        <v>1000</v>
+      </c>
+      <c r="AJ32">
+        <v>1000</v>
+      </c>
+      <c r="AK32">
+        <v>1000</v>
+      </c>
+      <c r="AL32">
+        <v>1000</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>1000</v>
+      </c>
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32">
+        <v>1.01</v>
+      </c>
+      <c r="AR32">
+        <v>1.01</v>
+      </c>
+      <c r="AS32">
+        <v>1.01</v>
+      </c>
+      <c r="AT32">
+        <v>1.01</v>
+      </c>
+      <c r="AU32">
+        <v>1.01</v>
+      </c>
+      <c r="AV32">
+        <v>1.01</v>
+      </c>
+      <c r="AW32">
+        <v>1.01</v>
+      </c>
+      <c r="AX32">
+        <v>1.01</v>
+      </c>
+      <c r="AY32">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32">
+        <v>1.01</v>
+      </c>
+      <c r="BA32">
+        <v>1.01</v>
+      </c>
+      <c r="BB32">
+        <v>1.01</v>
+      </c>
+      <c r="BC32">
+        <v>1.01</v>
+      </c>
+      <c r="BD32">
+        <v>1.01</v>
+      </c>
+      <c r="BE32">
+        <v>1.01</v>
+      </c>
+      <c r="BF32">
+        <v>1.01</v>
+      </c>
+      <c r="BG32">
+        <v>1.01</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.04</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.04</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.04</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.04</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.04</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.04</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.04</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.04</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.04</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
         <v>96</v>
       </c>
-      <c r="C29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29" t="s">
-        <v>168</v>
-      </c>
-      <c r="F29">
-        <v>2.06</v>
-      </c>
-      <c r="G29">
+      <c r="B33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" t="s">
+        <v>147</v>
+      </c>
+      <c r="E33" t="s">
+        <v>179</v>
+      </c>
+      <c r="F33">
+        <v>2.02</v>
+      </c>
+      <c r="G33">
         <v>2.14</v>
       </c>
-      <c r="H29">
+      <c r="H33">
         <v>4.2</v>
       </c>
-      <c r="I29">
+      <c r="I33">
+        <v>4.8</v>
+      </c>
+      <c r="J33">
+        <v>3.2</v>
+      </c>
+      <c r="K33">
+        <v>3.45</v>
+      </c>
+      <c r="L33">
+        <v>1.01</v>
+      </c>
+      <c r="M33">
+        <v>1.1</v>
+      </c>
+      <c r="N33">
+        <v>2.94</v>
+      </c>
+      <c r="O33">
+        <v>1.45</v>
+      </c>
+      <c r="P33">
+        <v>1.67</v>
+      </c>
+      <c r="Q33">
+        <v>2.34</v>
+      </c>
+      <c r="R33">
+        <v>1.24</v>
+      </c>
+      <c r="S33">
+        <v>4.5</v>
+      </c>
+      <c r="T33">
+        <v>2.04</v>
+      </c>
+      <c r="U33">
+        <v>1.86</v>
+      </c>
+      <c r="V33">
+        <v>1.27</v>
+      </c>
+      <c r="W33">
+        <v>1.87</v>
+      </c>
+      <c r="X33">
+        <v>12</v>
+      </c>
+      <c r="Y33">
+        <v>15</v>
+      </c>
+      <c r="Z33">
+        <v>38</v>
+      </c>
+      <c r="AA33">
+        <v>130</v>
+      </c>
+      <c r="AB33">
+        <v>8.6</v>
+      </c>
+      <c r="AC33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD33">
+        <v>22</v>
+      </c>
+      <c r="AE33">
+        <v>70</v>
+      </c>
+      <c r="AF33">
+        <v>13.5</v>
+      </c>
+      <c r="AG33">
+        <v>12.5</v>
+      </c>
+      <c r="AH33">
+        <v>26</v>
+      </c>
+      <c r="AI33">
+        <v>95</v>
+      </c>
+      <c r="AJ33">
+        <v>30</v>
+      </c>
+      <c r="AK33">
+        <v>30</v>
+      </c>
+      <c r="AL33">
+        <v>60</v>
+      </c>
+      <c r="AM33">
+        <v>180</v>
+      </c>
+      <c r="AN33">
+        <v>25</v>
+      </c>
+      <c r="AO33">
+        <v>120</v>
+      </c>
+      <c r="AP33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ33">
+        <v>11</v>
+      </c>
+      <c r="AR33">
         <v>4.7</v>
       </c>
-      <c r="J29">
-        <v>3.2</v>
-      </c>
-      <c r="K29">
-        <v>3.6</v>
-      </c>
-      <c r="L29">
-        <v>1.01</v>
-      </c>
-      <c r="M29">
-        <v>1.1</v>
-      </c>
-      <c r="N29">
-        <v>2.94</v>
-      </c>
-      <c r="O29">
-        <v>1.45</v>
-      </c>
-      <c r="P29">
-        <v>1.64</v>
-      </c>
-      <c r="Q29">
-        <v>2.32</v>
-      </c>
-      <c r="R29">
-        <v>1.24</v>
-      </c>
-      <c r="S29">
-        <v>4.5</v>
-      </c>
-      <c r="T29">
-        <v>2.04</v>
-      </c>
-      <c r="U29">
-        <v>1.83</v>
-      </c>
-      <c r="V29">
-        <v>1.27</v>
-      </c>
-      <c r="W29">
-        <v>1.87</v>
-      </c>
-      <c r="X29">
-        <v>12</v>
-      </c>
-      <c r="Y29">
-        <v>15</v>
-      </c>
-      <c r="Z29">
-        <v>38</v>
-      </c>
-      <c r="AA29">
-        <v>130</v>
-      </c>
-      <c r="AB29">
-        <v>8.6</v>
-      </c>
-      <c r="AC29">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD29">
-        <v>22</v>
-      </c>
-      <c r="AE29">
-        <v>70</v>
-      </c>
-      <c r="AF29">
-        <v>13.5</v>
-      </c>
-      <c r="AG29">
-        <v>12.5</v>
-      </c>
-      <c r="AH29">
-        <v>26</v>
-      </c>
-      <c r="AI29">
-        <v>95</v>
-      </c>
-      <c r="AJ29">
-        <v>30</v>
-      </c>
-      <c r="AK29">
-        <v>30</v>
-      </c>
-      <c r="AL29">
-        <v>60</v>
-      </c>
-      <c r="AM29">
+      <c r="AS33">
+        <v>5.1</v>
+      </c>
+      <c r="AT33">
+        <v>6.4</v>
+      </c>
+      <c r="AU33">
+        <v>6.6</v>
+      </c>
+      <c r="AV33">
+        <v>15.5</v>
+      </c>
+      <c r="AW33">
+        <v>4.9</v>
+      </c>
+      <c r="AX33">
+        <v>10</v>
+      </c>
+      <c r="AY33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ33">
+        <v>18.5</v>
+      </c>
+      <c r="BA33">
+        <v>5</v>
+      </c>
+      <c r="BB33">
+        <v>21</v>
+      </c>
+      <c r="BC33">
+        <v>21</v>
+      </c>
+      <c r="BD33">
+        <v>4.9</v>
+      </c>
+      <c r="BE33">
+        <v>5.2</v>
+      </c>
+      <c r="BF33">
+        <v>16.5</v>
+      </c>
+      <c r="BG33">
+        <v>5.1</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.04</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.04</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.04</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.04</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.04</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.04</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.04</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.04</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.04</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.04</v>
+      </c>
+      <c r="CB33" t="s">
         <v>180</v>
-      </c>
-      <c r="AN29">
-        <v>25</v>
-      </c>
-      <c r="AO29">
-        <v>120</v>
-      </c>
-      <c r="AP29">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ29">
-        <v>11</v>
-      </c>
-      <c r="AR29">
-        <v>4.7</v>
-      </c>
-      <c r="AS29">
-        <v>5.1</v>
-      </c>
-      <c r="AT29">
-        <v>6.4</v>
-      </c>
-      <c r="AU29">
-        <v>6.6</v>
-      </c>
-      <c r="AV29">
-        <v>15.5</v>
-      </c>
-      <c r="AW29">
-        <v>4.9</v>
-      </c>
-      <c r="AX29">
-        <v>10</v>
-      </c>
-      <c r="AY29">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ29">
-        <v>18.5</v>
-      </c>
-      <c r="BA29">
-        <v>5</v>
-      </c>
-      <c r="BB29">
-        <v>21</v>
-      </c>
-      <c r="BC29">
-        <v>21</v>
-      </c>
-      <c r="BD29">
-        <v>4.9</v>
-      </c>
-      <c r="BE29">
-        <v>5.2</v>
-      </c>
-      <c r="BF29">
-        <v>16.5</v>
-      </c>
-      <c r="BG29">
-        <v>5.1</v>
-      </c>
-      <c r="BH29">
-        <v>1000</v>
-      </c>
-      <c r="BI29">
-        <v>1.04</v>
-      </c>
-      <c r="BJ29">
-        <v>1000</v>
-      </c>
-      <c r="BK29">
-        <v>1.04</v>
-      </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
-        <v>1.04</v>
-      </c>
-      <c r="BN29">
-        <v>1000</v>
-      </c>
-      <c r="BO29">
-        <v>1.04</v>
-      </c>
-      <c r="BP29">
-        <v>1000</v>
-      </c>
-      <c r="BQ29">
-        <v>1.04</v>
-      </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
-        <v>1.04</v>
-      </c>
-      <c r="BT29">
-        <v>1000</v>
-      </c>
-      <c r="BU29">
-        <v>1.04</v>
-      </c>
-      <c r="BV29">
-        <v>1000</v>
-      </c>
-      <c r="BW29">
-        <v>1.04</v>
-      </c>
-      <c r="BX29">
-        <v>1000</v>
-      </c>
-      <c r="BY29">
-        <v>1.04</v>
-      </c>
-      <c r="BZ29">
-        <v>1000</v>
-      </c>
-      <c r="CA29">
-        <v>1.04</v>
-      </c>
-      <c r="CB29" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -556,7 +556,7 @@
     <t>Aguilas Doradas</t>
   </si>
   <si>
-    <t>2026-08-24 14:54:40</t>
+    <t>2026-08-24 17:16:20</t>
   </si>
 </sst>
 </file>
@@ -1150,55 +1150,55 @@
         <v>148</v>
       </c>
       <c r="F2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G2">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I2">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="M2">
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q2">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U2">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V2">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W2">
         <v>1.37</v>
@@ -1210,13 +1210,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA2">
         <v>38</v>
       </c>
       <c r="AB2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
@@ -1225,7 +1225,7 @@
         <v>12.5</v>
       </c>
       <c r="AE2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AF2">
         <v>25</v>
@@ -1240,37 +1240,37 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM2">
         <v>160</v>
       </c>
       <c r="AN2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AO2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR2">
         <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1288,25 +1288,25 @@
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD2">
         <v>46</v>
       </c>
       <c r="BE2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BG2">
         <v>21</v>
@@ -1315,61 +1315,61 @@
         <v>3.05</v>
       </c>
       <c r="BI2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ2">
         <v>38</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
         <v>180</v>
@@ -1398,13 +1398,13 @@
         <v>2.78</v>
       </c>
       <c r="H3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I3">
         <v>3.35</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K3">
         <v>3.05</v>
@@ -1425,13 +1425,13 @@
         <v>1.52</v>
       </c>
       <c r="Q3">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T3">
         <v>2.2</v>
@@ -1440,7 +1440,7 @@
         <v>1.77</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
         <v>1.56</v>
@@ -1482,7 +1482,7 @@
         <v>110</v>
       </c>
       <c r="AJ3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK3">
         <v>44</v>
@@ -1500,7 +1500,7 @@
         <v>95</v>
       </c>
       <c r="AP3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
         <v>8</v>
@@ -1533,7 +1533,7 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BB3">
         <v>25</v>
@@ -1545,7 +1545,7 @@
         <v>60</v>
       </c>
       <c r="BE3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BF3">
         <v>34</v>
@@ -1554,7 +1554,7 @@
         <v>46</v>
       </c>
       <c r="BH3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI3">
         <v>2.18</v>
@@ -1569,7 +1569,7 @@
         <v>260</v>
       </c>
       <c r="BM3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN3">
         <v>5.4</v>
@@ -1581,7 +1581,7 @@
         <v>30</v>
       </c>
       <c r="BQ3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR3">
         <v>60</v>
@@ -1605,7 +1605,7 @@
         <v>55</v>
       </c>
       <c r="BY3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BZ3">
         <v>65</v>
@@ -1634,10 +1634,10 @@
         <v>150</v>
       </c>
       <c r="F4">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="G4">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1646,52 +1646,52 @@
         <v>3.1</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <v>3.1</v>
       </c>
       <c r="L4">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M4">
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="O4">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q4">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S4">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z4">
         <v>19</v>
@@ -1700,10 +1700,10 @@
         <v>55</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD4">
         <v>14</v>
@@ -1712,7 +1712,7 @@
         <v>42</v>
       </c>
       <c r="AF4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG4">
         <v>13.5</v>
@@ -1721,7 +1721,7 @@
         <v>21</v>
       </c>
       <c r="AI4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
         <v>48</v>
@@ -1733,31 +1733,31 @@
         <v>65</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP4">
+        <v>8.4</v>
+      </c>
+      <c r="AQ4">
         <v>8.6</v>
       </c>
-      <c r="AQ4">
+      <c r="AR4">
+        <v>16.5</v>
+      </c>
+      <c r="AS4">
+        <v>44</v>
+      </c>
+      <c r="AT4">
         <v>8.4</v>
       </c>
-      <c r="AR4">
-        <v>17</v>
-      </c>
-      <c r="AS4">
-        <v>34</v>
-      </c>
-      <c r="AT4">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
         <v>12.5</v>
@@ -1772,13 +1772,13 @@
         <v>12</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA4">
         <v>55</v>
       </c>
       <c r="BB4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BC4">
         <v>34</v>
@@ -1790,28 +1790,28 @@
         <v>46</v>
       </c>
       <c r="BF4">
+        <v>38</v>
+      </c>
+      <c r="BG4">
         <v>36</v>
       </c>
-      <c r="BG4">
-        <v>40</v>
-      </c>
       <c r="BH4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BL4">
         <v>210</v>
       </c>
       <c r="BM4">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BN4">
         <v>6.6</v>
@@ -1823,13 +1823,13 @@
         <v>26</v>
       </c>
       <c r="BQ4">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BR4">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BS4">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BT4">
         <v>7</v>
@@ -1838,22 +1838,22 @@
         <v>5</v>
       </c>
       <c r="BV4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW4">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BX4">
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BZ4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="CA4">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="CB4" t="s">
         <v>180</v>
@@ -1876,52 +1876,52 @@
         <v>151</v>
       </c>
       <c r="F5">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G5">
         <v>1.49</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K5">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="S5">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="U5">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
         <v>1.13</v>
@@ -1930,7 +1930,7 @@
         <v>3</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Y5">
         <v>42</v>
@@ -1939,28 +1939,28 @@
         <v>95</v>
       </c>
       <c r="AA5">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC5">
         <v>12</v>
       </c>
       <c r="AD5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AE5">
         <v>150</v>
       </c>
       <c r="AF5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG5">
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI5">
         <v>110</v>
@@ -1975,49 +1975,49 @@
         <v>40</v>
       </c>
       <c r="AM5">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AN5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO5">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AP5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU5">
         <v>10</v>
       </c>
       <c r="AV5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW5">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="AX5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB5">
         <v>11</v>
@@ -2029,73 +2029,73 @@
         <v>22</v>
       </c>
       <c r="BE5">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="BF5">
+        <v>5</v>
+      </c>
+      <c r="BG5">
+        <v>55</v>
+      </c>
+      <c r="BH5">
+        <v>4.5</v>
+      </c>
+      <c r="BI5">
+        <v>3.6</v>
+      </c>
+      <c r="BJ5">
+        <v>10.5</v>
+      </c>
+      <c r="BK5">
+        <v>5.8</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>11.5</v>
+      </c>
+      <c r="BN5">
+        <v>4.3</v>
+      </c>
+      <c r="BO5">
+        <v>3.7</v>
+      </c>
+      <c r="BP5">
+        <v>8.6</v>
+      </c>
+      <c r="BQ5">
         <v>5.2</v>
       </c>
-      <c r="BG5">
-        <v>9.6</v>
-      </c>
-      <c r="BH5">
-        <v>4.3</v>
-      </c>
-      <c r="BI5">
-        <v>3.4</v>
-      </c>
-      <c r="BJ5">
-        <v>11</v>
-      </c>
-      <c r="BK5">
-        <v>5.6</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
+      <c r="BR5">
+        <v>21</v>
+      </c>
+      <c r="BS5">
+        <v>8</v>
+      </c>
+      <c r="BT5">
+        <v>11.5</v>
+      </c>
+      <c r="BU5">
+        <v>6</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
         <v>10.5</v>
       </c>
-      <c r="BN5">
-        <v>4.2</v>
-      </c>
-      <c r="BO5">
-        <v>3.3</v>
-      </c>
-      <c r="BP5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ5">
-        <v>5</v>
-      </c>
-      <c r="BR5">
-        <v>23</v>
-      </c>
-      <c r="BS5">
-        <v>7.6</v>
-      </c>
-      <c r="BT5">
-        <v>12</v>
-      </c>
-      <c r="BU5">
-        <v>5.9</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="s">
         <v>180</v>
@@ -2121,7 +2121,7 @@
         <v>3.5</v>
       </c>
       <c r="G6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H6">
         <v>2.22</v>
@@ -2133,7 +2133,7 @@
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L6">
         <v>1.35</v>
@@ -2151,7 +2151,7 @@
         <v>1.9</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R6">
         <v>1.35</v>
@@ -2166,7 +2166,7 @@
         <v>2.14</v>
       </c>
       <c r="V6">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W6">
         <v>1.37</v>
@@ -2211,16 +2211,16 @@
         <v>1000</v>
       </c>
       <c r="AK6">
+        <v>100</v>
+      </c>
+      <c r="AL6">
+        <v>270</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
         <v>110</v>
-      </c>
-      <c r="AL6">
-        <v>300</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>120</v>
       </c>
       <c r="AO6">
         <v>18.5</v>
@@ -2244,7 +2244,7 @@
         <v>7</v>
       </c>
       <c r="AV6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
         <v>21</v>
@@ -2274,7 +2274,7 @@
         <v>13.5</v>
       </c>
       <c r="BF6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG6">
         <v>16</v>
@@ -2363,7 +2363,7 @@
         <v>2.52</v>
       </c>
       <c r="G7">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H7">
         <v>3.2</v>
@@ -2375,7 +2375,7 @@
         <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L7">
         <v>1.43</v>
@@ -2390,7 +2390,7 @@
         <v>1.47</v>
       </c>
       <c r="P7">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q7">
         <v>2.42</v>
@@ -2411,7 +2411,7 @@
         <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X7">
         <v>10.5</v>
@@ -2435,7 +2435,7 @@
         <v>14.5</v>
       </c>
       <c r="AE7">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AF7">
         <v>15.5</v>
@@ -2459,10 +2459,10 @@
         <v>60</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO7">
         <v>60</v>
@@ -2477,7 +2477,7 @@
         <v>18</v>
       </c>
       <c r="AS7">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AT7">
         <v>7.6</v>
@@ -2489,7 +2489,7 @@
         <v>13</v>
       </c>
       <c r="AW7">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AX7">
         <v>13</v>
@@ -2501,25 +2501,25 @@
         <v>19</v>
       </c>
       <c r="BA7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB7">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD7">
         <v>29</v>
       </c>
       <c r="BE7">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BF7">
         <v>21</v>
       </c>
       <c r="BG7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2602,7 +2602,7 @@
         <v>154</v>
       </c>
       <c r="F8">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G8">
         <v>1.59</v>
@@ -2632,7 +2632,7 @@
         <v>1.29</v>
       </c>
       <c r="P8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q8">
         <v>1.87</v>
@@ -2647,16 +2647,16 @@
         <v>1.97</v>
       </c>
       <c r="U8">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V8">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W8">
         <v>2.7</v>
       </c>
       <c r="X8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y8">
         <v>23</v>
@@ -2716,10 +2716,10 @@
         <v>18</v>
       </c>
       <c r="AR8">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AS8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT8">
         <v>7.4</v>
@@ -2731,7 +2731,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX8">
         <v>8.199999999999999</v>
@@ -2743,7 +2743,7 @@
         <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="BB8">
         <v>12.5</v>
@@ -2755,13 +2755,13 @@
         <v>32</v>
       </c>
       <c r="BE8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH8">
         <v>3.7</v>
@@ -2779,7 +2779,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN8">
         <v>4.2</v>
@@ -2791,7 +2791,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR8">
         <v>27</v>
@@ -2809,7 +2809,7 @@
         <v>65</v>
       </c>
       <c r="BW8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8">
         <v>70</v>
@@ -2818,7 +2818,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BZ8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA8">
         <v>6.8</v>
@@ -2844,16 +2844,16 @@
         <v>155</v>
       </c>
       <c r="F9">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G9">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H9">
         <v>5.4</v>
       </c>
       <c r="I9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
         <v>3.85</v>
@@ -2874,7 +2874,7 @@
         <v>1.28</v>
       </c>
       <c r="P9">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q9">
         <v>1.82</v>
@@ -2892,10 +2892,10 @@
         <v>2</v>
       </c>
       <c r="V9">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W9">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X9">
         <v>19</v>
@@ -2916,7 +2916,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AE9">
         <v>85</v>
@@ -2952,19 +2952,19 @@
         <v>110</v>
       </c>
       <c r="AP9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR9">
         <v>7.4</v>
       </c>
       <c r="AS9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU9">
         <v>8</v>
@@ -2973,7 +2973,7 @@
         <v>19</v>
       </c>
       <c r="AW9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX9">
         <v>8.800000000000001</v>
@@ -2997,7 +2997,7 @@
         <v>7</v>
       </c>
       <c r="BE9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9">
         <v>4.7</v>
@@ -3089,7 +3089,7 @@
         <v>2.68</v>
       </c>
       <c r="G10">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H10">
         <v>2.6</v>
@@ -3110,16 +3110,16 @@
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O10">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P10">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Q10">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="R10">
         <v>1.3</v>
@@ -3137,7 +3137,7 @@
         <v>1.47</v>
       </c>
       <c r="W10">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X10">
         <v>15</v>
@@ -3170,7 +3170,7 @@
         <v>14</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI10">
         <v>55</v>
@@ -3188,64 +3188,64 @@
         <v>120</v>
       </c>
       <c r="AN10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO10">
         <v>34</v>
       </c>
       <c r="AP10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS10">
+        <v>5.3</v>
+      </c>
+      <c r="AT10">
+        <v>4</v>
+      </c>
+      <c r="AU10">
+        <v>3.5</v>
+      </c>
+      <c r="AV10">
+        <v>4.2</v>
+      </c>
+      <c r="AW10">
         <v>5.1</v>
       </c>
-      <c r="AT10">
-        <v>3.9</v>
-      </c>
-      <c r="AU10">
-        <v>3.45</v>
-      </c>
-      <c r="AV10">
-        <v>4</v>
-      </c>
-      <c r="AW10">
-        <v>5</v>
-      </c>
       <c r="AX10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY10">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ10">
         <v>4.5</v>
       </c>
       <c r="BA10">
+        <v>5.4</v>
+      </c>
+      <c r="BB10">
+        <v>5.4</v>
+      </c>
+      <c r="BC10">
         <v>5.2</v>
       </c>
-      <c r="BB10">
-        <v>5.2</v>
-      </c>
-      <c r="BC10">
-        <v>5</v>
-      </c>
       <c r="BD10">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE10">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF10">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG10">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3328,22 +3328,22 @@
         <v>157</v>
       </c>
       <c r="F11">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="G11">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="H11">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="I11">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J11">
         <v>3.8</v>
       </c>
       <c r="K11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3352,7 +3352,7 @@
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O11">
         <v>1.22</v>
@@ -3361,55 +3361,55 @@
         <v>2.24</v>
       </c>
       <c r="Q11">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R11">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="S11">
         <v>2.62</v>
       </c>
       <c r="T11">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="U11">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="X11">
         <v>22</v>
       </c>
       <c r="Y11">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z11">
         <v>34</v>
       </c>
       <c r="AA11">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC11">
         <v>11.5</v>
       </c>
       <c r="AD11">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE11">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF11">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH11">
         <v>17</v>
@@ -3418,10 +3418,10 @@
         <v>48</v>
       </c>
       <c r="AJ11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AK11">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AL11">
         <v>30</v>
@@ -3430,7 +3430,7 @@
         <v>75</v>
       </c>
       <c r="AN11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AO11">
         <v>36</v>
@@ -3442,22 +3442,22 @@
         <v>13.5</v>
       </c>
       <c r="AR11">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="AS11">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="AT11">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11">
         <v>8.199999999999999</v>
       </c>
       <c r="AV11">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AW11">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="AX11">
         <v>12</v>
@@ -3466,10 +3466,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA11">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB11">
         <v>16</v>
@@ -3481,22 +3481,22 @@
         <v>21</v>
       </c>
       <c r="BE11">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BF11">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG11">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BH11">
         <v>4.2</v>
       </c>
       <c r="BI11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK11">
         <v>5</v>
@@ -3505,31 +3505,31 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO11">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP11">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ11">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS11">
+        <v>7.6</v>
+      </c>
+      <c r="BT11">
         <v>7.4</v>
       </c>
-      <c r="BT11">
-        <v>7.8</v>
-      </c>
       <c r="BU11">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV11">
         <v>1000</v>
@@ -3541,7 +3541,7 @@
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3594,142 +3594,142 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
         <v>1.27</v>
       </c>
       <c r="P12">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q12">
         <v>1.86</v>
       </c>
       <c r="R12">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S12">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T12">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V12">
         <v>1.63</v>
       </c>
       <c r="W12">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC12">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP12">
-        <v>1.13</v>
+        <v>13</v>
       </c>
       <c r="AQ12">
-        <v>1.13</v>
+        <v>9.4</v>
       </c>
       <c r="AR12">
-        <v>1.13</v>
+        <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>1.14</v>
+        <v>4.8</v>
       </c>
       <c r="AT12">
-        <v>1.13</v>
+        <v>11</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW12">
-        <v>1.14</v>
+        <v>21</v>
       </c>
       <c r="AX12">
-        <v>1.14</v>
+        <v>19</v>
       </c>
       <c r="AY12">
-        <v>1.13</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12">
-        <v>1.13</v>
+        <v>14</v>
       </c>
       <c r="BA12">
-        <v>1.14</v>
+        <v>4.8</v>
       </c>
       <c r="BB12">
-        <v>1.14</v>
+        <v>5</v>
       </c>
       <c r="BC12">
-        <v>1.14</v>
+        <v>4.8</v>
       </c>
       <c r="BD12">
-        <v>1.14</v>
+        <v>4.9</v>
       </c>
       <c r="BE12">
-        <v>1.14</v>
+        <v>5.2</v>
       </c>
       <c r="BF12">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="BG12">
-        <v>1.14</v>
+        <v>14.5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3815,7 +3815,7 @@
         <v>1.82</v>
       </c>
       <c r="G13">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H13">
         <v>4.4</v>
@@ -3836,7 +3836,7 @@
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O13">
         <v>1.3</v>
@@ -3869,7 +3869,7 @@
         <v>16</v>
       </c>
       <c r="Y13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z13">
         <v>40</v>
@@ -3902,7 +3902,7 @@
         <v>80</v>
       </c>
       <c r="AJ13">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK13">
         <v>21</v>
@@ -3926,10 +3926,10 @@
         <v>14</v>
       </c>
       <c r="AR13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT13">
         <v>7.8</v>
@@ -3962,16 +3962,16 @@
         <v>16.5</v>
       </c>
       <c r="BD13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF13">
         <v>9.199999999999999</v>
       </c>
       <c r="BG13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4054,10 +4054,10 @@
         <v>160</v>
       </c>
       <c r="F14">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -4066,10 +4066,10 @@
         <v>4.2</v>
       </c>
       <c r="J14">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
         <v>1.28</v>
@@ -4078,7 +4078,7 @@
         <v>1.06</v>
       </c>
       <c r="N14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O14">
         <v>1.28</v>
@@ -4090,7 +4090,7 @@
         <v>1.83</v>
       </c>
       <c r="R14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S14">
         <v>3.1</v>
@@ -4099,13 +4099,13 @@
         <v>1.76</v>
       </c>
       <c r="U14">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V14">
         <v>1.31</v>
       </c>
       <c r="W14">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X14">
         <v>17.5</v>
@@ -4114,22 +4114,22 @@
         <v>16.5</v>
       </c>
       <c r="Z14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB14">
         <v>10.5</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AE14">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="AF14">
         <v>13</v>
@@ -4144,7 +4144,7 @@
         <v>55</v>
       </c>
       <c r="AJ14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK14">
         <v>21</v>
@@ -4153,16 +4153,16 @@
         <v>34</v>
       </c>
       <c r="AM14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN14">
         <v>13</v>
       </c>
       <c r="AO14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AP14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ14">
         <v>15</v>
@@ -4174,7 +4174,7 @@
         <v>36</v>
       </c>
       <c r="AT14">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU14">
         <v>8</v>
@@ -4186,7 +4186,7 @@
         <v>38</v>
       </c>
       <c r="AX14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY14">
         <v>9.4</v>
@@ -4198,10 +4198,10 @@
         <v>44</v>
       </c>
       <c r="BB14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD14">
         <v>29</v>
@@ -4213,7 +4213,7 @@
         <v>11</v>
       </c>
       <c r="BG14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4296,16 +4296,16 @@
         <v>161</v>
       </c>
       <c r="F15">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G15">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H15">
         <v>4.4</v>
       </c>
       <c r="I15">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4329,28 +4329,28 @@
         <v>2.42</v>
       </c>
       <c r="Q15">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R15">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S15">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U15">
         <v>2.38</v>
       </c>
       <c r="V15">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W15">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y15">
         <v>25</v>
@@ -4380,7 +4380,7 @@
         <v>12</v>
       </c>
       <c r="AH15">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI15">
         <v>55</v>
@@ -4392,7 +4392,7 @@
         <v>17.5</v>
       </c>
       <c r="AL15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM15">
         <v>80</v>
@@ -4413,10 +4413,10 @@
         <v>32</v>
       </c>
       <c r="AS15">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT15">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU15">
         <v>8.800000000000001</v>
@@ -4425,7 +4425,7 @@
         <v>14</v>
       </c>
       <c r="AW15">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="AX15">
         <v>10.5</v>
@@ -4437,7 +4437,7 @@
         <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB15">
         <v>15.5</v>
@@ -4538,16 +4538,16 @@
         <v>162</v>
       </c>
       <c r="F16">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G16">
         <v>2.98</v>
       </c>
       <c r="H16">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I16">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J16">
         <v>3.5</v>
@@ -4568,10 +4568,10 @@
         <v>1.27</v>
       </c>
       <c r="P16">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q16">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R16">
         <v>1.41</v>
@@ -4586,7 +4586,7 @@
         <v>2.26</v>
       </c>
       <c r="V16">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W16">
         <v>1.5</v>
@@ -4595,7 +4595,7 @@
         <v>19</v>
       </c>
       <c r="Y16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z16">
         <v>19</v>
@@ -4631,7 +4631,7 @@
         <v>46</v>
       </c>
       <c r="AK16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL16">
         <v>55</v>
@@ -4655,10 +4655,10 @@
         <v>14</v>
       </c>
       <c r="AS16">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU16">
         <v>7.2</v>
@@ -4667,13 +4667,13 @@
         <v>10</v>
       </c>
       <c r="AW16">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX16">
         <v>17</v>
       </c>
       <c r="AY16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
         <v>13.5</v>
@@ -4685,13 +4685,13 @@
         <v>27</v>
       </c>
       <c r="BC16">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BD16">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BE16">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16">
         <v>20</v>
@@ -4780,13 +4780,13 @@
         <v>163</v>
       </c>
       <c r="F17">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G17">
         <v>2.9</v>
       </c>
       <c r="H17">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I17">
         <v>3.65</v>
@@ -4795,7 +4795,7 @@
         <v>2.8</v>
       </c>
       <c r="K17">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <v>1.5</v>
@@ -4804,7 +4804,7 @@
         <v>1.13</v>
       </c>
       <c r="N17">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O17">
         <v>1.55</v>
@@ -4813,16 +4813,16 @@
         <v>1.48</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R17">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S17">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="T17">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U17">
         <v>1.73</v>
@@ -4837,7 +4837,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z17">
         <v>23</v>
@@ -4870,10 +4870,10 @@
         <v>100</v>
       </c>
       <c r="AJ17">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AK17">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL17">
         <v>85</v>
@@ -4888,58 +4888,58 @@
         <v>90</v>
       </c>
       <c r="AP17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ17">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="AR17">
+        <v>18</v>
+      </c>
+      <c r="AS17">
+        <v>6.6</v>
+      </c>
+      <c r="AT17">
+        <v>5.9</v>
+      </c>
+      <c r="AU17">
         <v>5.3</v>
       </c>
-      <c r="AS17">
+      <c r="AV17">
+        <v>13</v>
+      </c>
+      <c r="AW17">
+        <v>6.6</v>
+      </c>
+      <c r="AX17">
+        <v>13.5</v>
+      </c>
+      <c r="AY17">
+        <v>11</v>
+      </c>
+      <c r="AZ17">
+        <v>19.5</v>
+      </c>
+      <c r="BA17">
+        <v>6.8</v>
+      </c>
+      <c r="BB17">
+        <v>6.2</v>
+      </c>
+      <c r="BC17">
+        <v>6.2</v>
+      </c>
+      <c r="BD17">
+        <v>6.6</v>
+      </c>
+      <c r="BE17">
+        <v>7</v>
+      </c>
+      <c r="BF17">
         <v>6.4</v>
       </c>
-      <c r="AT17">
-        <v>3.75</v>
-      </c>
-      <c r="AU17">
-        <v>3.6</v>
-      </c>
-      <c r="AV17">
-        <v>4.8</v>
-      </c>
-      <c r="AW17">
-        <v>6.2</v>
-      </c>
-      <c r="AX17">
-        <v>4.9</v>
-      </c>
-      <c r="AY17">
-        <v>4.6</v>
-      </c>
-      <c r="AZ17">
-        <v>5.4</v>
-      </c>
-      <c r="BA17">
-        <v>6.4</v>
-      </c>
-      <c r="BB17">
-        <v>6</v>
-      </c>
-      <c r="BC17">
-        <v>6</v>
-      </c>
-      <c r="BD17">
-        <v>6.4</v>
-      </c>
-      <c r="BE17">
+      <c r="BG17">
         <v>6.8</v>
-      </c>
-      <c r="BF17">
-        <v>6.2</v>
-      </c>
-      <c r="BG17">
-        <v>6.4</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5031,10 +5031,10 @@
         <v>2.48</v>
       </c>
       <c r="I18">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J18">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K18">
         <v>3.3</v>
@@ -5046,7 +5046,7 @@
         <v>1.12</v>
       </c>
       <c r="N18">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="O18">
         <v>1.53</v>
@@ -5055,22 +5055,22 @@
         <v>1.52</v>
       </c>
       <c r="Q18">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R18">
         <v>1.18</v>
       </c>
       <c r="S18">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="T18">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U18">
         <v>1.78</v>
       </c>
       <c r="V18">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W18">
         <v>1.39</v>
@@ -5130,37 +5130,37 @@
         <v>55</v>
       </c>
       <c r="AP18">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ18">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="AR18">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AS18">
         <v>5.2</v>
       </c>
       <c r="AT18">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="AU18">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AV18">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AW18">
         <v>5.1</v>
       </c>
       <c r="AX18">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="AY18">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="AZ18">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="BA18">
         <v>5.4</v>
@@ -5279,16 +5279,16 @@
         <v>2.9</v>
       </c>
       <c r="K19">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L19">
         <v>1.43</v>
       </c>
       <c r="M19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O19">
         <v>1.23</v>
@@ -5306,7 +5306,7 @@
         <v>2.52</v>
       </c>
       <c r="T19">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U19">
         <v>1.55</v>
@@ -5330,10 +5330,10 @@
         <v>1000</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC19">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD19">
         <v>1000</v>
@@ -5342,7 +5342,7 @@
         <v>1000</v>
       </c>
       <c r="AF19">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG19">
         <v>950</v>
@@ -5372,58 +5372,58 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AQ19">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR19">
-        <v>19.5</v>
+        <v>1.45</v>
       </c>
       <c r="AS19">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AT19">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU19">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AV19">
-        <v>14</v>
+        <v>1.44</v>
       </c>
       <c r="AW19">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AX19">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AY19">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AZ19">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="BA19">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="BB19">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="BC19">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="BD19">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="BE19">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="BF19">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="BG19">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5509,55 +5509,55 @@
         <v>1.32</v>
       </c>
       <c r="G20">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H20">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I20">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="J20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K20">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L20">
         <v>1.35</v>
       </c>
       <c r="M20">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N20">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O20">
         <v>1.39</v>
       </c>
       <c r="P20">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="Q20">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R20">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S20">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T20">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="U20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V20">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W20">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="X20">
         <v>15</v>
@@ -5581,7 +5581,7 @@
         <v>950</v>
       </c>
       <c r="AE20">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="AF20">
         <v>6.8</v>
@@ -5593,7 +5593,7 @@
         <v>950</v>
       </c>
       <c r="AI20">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AJ20">
         <v>11</v>
@@ -5614,10 +5614,10 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AQ20">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AR20">
         <v>8</v>
@@ -5626,7 +5626,7 @@
         <v>8.4</v>
       </c>
       <c r="AT20">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AU20">
         <v>5</v>
@@ -5638,31 +5638,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AX20">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="AY20">
         <v>4.9</v>
       </c>
       <c r="AZ20">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BA20">
         <v>8.199999999999999</v>
       </c>
       <c r="BB20">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC20">
         <v>6</v>
       </c>
       <c r="BD20">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE20">
         <v>8.199999999999999</v>
       </c>
       <c r="BF20">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BG20">
         <v>8.4</v>
@@ -5748,16 +5748,16 @@
         <v>167</v>
       </c>
       <c r="F21">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G21">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="H21">
         <v>1.31</v>
       </c>
       <c r="I21">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J21">
         <v>6.2</v>
@@ -5775,46 +5775,46 @@
         <v>8.4</v>
       </c>
       <c r="O21">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P21">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
         <v>1.34</v>
       </c>
       <c r="R21">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S21">
         <v>1.9</v>
       </c>
       <c r="T21">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="W21">
         <v>1.1</v>
       </c>
       <c r="X21">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="Y21">
         <v>16.5</v>
       </c>
       <c r="Z21">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA21">
         <v>13</v>
       </c>
       <c r="AB21">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AC21">
         <v>17</v>
@@ -5829,7 +5829,7 @@
         <v>120</v>
       </c>
       <c r="AG21">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AH21">
         <v>24</v>
@@ -5838,7 +5838,7 @@
         <v>26</v>
       </c>
       <c r="AJ21">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AK21">
         <v>130</v>
@@ -5853,10 +5853,10 @@
         <v>100</v>
       </c>
       <c r="AO21">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AP21">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ21">
         <v>14</v>
@@ -5868,7 +5868,7 @@
         <v>11</v>
       </c>
       <c r="AT21">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU21">
         <v>14.5</v>
@@ -5880,7 +5880,7 @@
         <v>11.5</v>
       </c>
       <c r="AX21">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY21">
         <v>30</v>
@@ -5889,28 +5889,28 @@
         <v>20</v>
       </c>
       <c r="BA21">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB21">
+        <v>12.5</v>
+      </c>
+      <c r="BC21">
         <v>11.5</v>
       </c>
-      <c r="BC21">
+      <c r="BD21">
         <v>11</v>
       </c>
-      <c r="BD21">
-        <v>10.5</v>
-      </c>
       <c r="BE21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF21">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG21">
         <v>3.1</v>
       </c>
       <c r="BH21">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BI21">
         <v>5.2</v>
@@ -5919,31 +5919,31 @@
         <v>10.5</v>
       </c>
       <c r="BK21">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BO21">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BT21">
         <v>4.6</v>
@@ -5952,19 +5952,19 @@
         <v>4</v>
       </c>
       <c r="BV21">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BW21">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BX21">
         <v>17</v>
       </c>
       <c r="BY21">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ21">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CA21">
         <v>5.7</v>
@@ -5993,13 +5993,13 @@
         <v>1.73</v>
       </c>
       <c r="G22">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H22">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I22">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -6011,25 +6011,25 @@
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N22">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="O22">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P22">
         <v>2.32</v>
       </c>
       <c r="Q22">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="R22">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S22">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T22">
         <v>1.64</v>
@@ -6038,7 +6038,7 @@
         <v>2.28</v>
       </c>
       <c r="V22">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W22">
         <v>2.16</v>
@@ -6232,22 +6232,22 @@
         <v>169</v>
       </c>
       <c r="F23">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="G23">
-        <v>990</v>
+        <v>2.12</v>
       </c>
       <c r="H23">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="I23">
-        <v>990</v>
+        <v>4</v>
       </c>
       <c r="J23">
-        <v>1.09</v>
+        <v>4</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6256,91 +6256,91 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.28</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P23">
-        <v>1.28</v>
+        <v>2.72</v>
       </c>
       <c r="Q23">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="R23">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S23">
-        <v>1.14</v>
+        <v>2.16</v>
       </c>
       <c r="T23">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="U23">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="V23">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ23">
         <v>1.01</v>
@@ -6480,40 +6480,40 @@
         <v>3</v>
       </c>
       <c r="H24">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I24">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="J24">
+        <v>3.35</v>
+      </c>
+      <c r="K24">
         <v>3.4</v>
       </c>
-      <c r="K24">
-        <v>3.45</v>
-      </c>
       <c r="L24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M24">
         <v>1.08</v>
       </c>
       <c r="N24">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P24">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q24">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S24">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T24">
         <v>1.83</v>
@@ -6522,13 +6522,13 @@
         <v>2.16</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W24">
         <v>1.5</v>
       </c>
       <c r="X24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y24">
         <v>10.5</v>
@@ -6543,7 +6543,7 @@
         <v>11.5</v>
       </c>
       <c r="AC24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD24">
         <v>12</v>
@@ -6552,7 +6552,7 @@
         <v>30</v>
       </c>
       <c r="AF24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG24">
         <v>13</v>
@@ -6567,7 +6567,7 @@
         <v>48</v>
       </c>
       <c r="AK24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL24">
         <v>46</v>
@@ -6579,13 +6579,13 @@
         <v>32</v>
       </c>
       <c r="AO24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP24">
         <v>11.5</v>
       </c>
       <c r="AQ24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR24">
         <v>15.5</v>
@@ -6612,13 +6612,13 @@
         <v>12</v>
       </c>
       <c r="AZ24">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA24">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC24">
         <v>30</v>
@@ -6627,22 +6627,22 @@
         <v>42</v>
       </c>
       <c r="BE24">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BF24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI24">
         <v>3.05</v>
       </c>
       <c r="BJ24">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK24">
         <v>8.4</v>
@@ -6651,7 +6651,7 @@
         <v>130</v>
       </c>
       <c r="BM24">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN24">
         <v>5.9</v>
@@ -6669,7 +6669,7 @@
         <v>38</v>
       </c>
       <c r="BS24">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT24">
         <v>5.6</v>
@@ -6681,19 +6681,19 @@
         <v>22</v>
       </c>
       <c r="BW24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BX24">
         <v>36</v>
       </c>
       <c r="BY24">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ24">
         <v>32</v>
       </c>
       <c r="CA24">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB24" t="s">
         <v>180</v>
@@ -6716,16 +6716,16 @@
         <v>171</v>
       </c>
       <c r="F25">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G25">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H25">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I25">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J25">
         <v>4.1</v>
@@ -6734,7 +6734,7 @@
         <v>4.2</v>
       </c>
       <c r="L25">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M25">
         <v>1.04</v>
@@ -6746,46 +6746,46 @@
         <v>1.2</v>
       </c>
       <c r="P25">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="Q25">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R25">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S25">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T25">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U25">
         <v>2.6</v>
       </c>
       <c r="V25">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y25">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z25">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA25">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB25">
         <v>13.5</v>
       </c>
       <c r="AC25">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD25">
         <v>15.5</v>
@@ -6794,7 +6794,7 @@
         <v>38</v>
       </c>
       <c r="AF25">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AG25">
         <v>11</v>
@@ -6806,31 +6806,31 @@
         <v>40</v>
       </c>
       <c r="AJ25">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AK25">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL25">
         <v>28</v>
       </c>
       <c r="AM25">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN25">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO25">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP25">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AQ25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR25">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS25">
         <v>55</v>
@@ -6839,10 +6839,10 @@
         <v>12</v>
       </c>
       <c r="AU25">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV25">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW25">
         <v>32</v>
@@ -6851,7 +6851,7 @@
         <v>13.5</v>
       </c>
       <c r="AY25">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25">
         <v>14</v>
@@ -6863,7 +6863,7 @@
         <v>22</v>
       </c>
       <c r="BC25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD25">
         <v>24</v>
@@ -6875,49 +6875,49 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BJ25">
         <v>11.5</v>
       </c>
       <c r="BK25">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BN25">
         <v>6.6</v>
       </c>
       <c r="BO25">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP25">
         <v>17.5</v>
       </c>
       <c r="BQ25">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BR25">
         <v>30</v>
       </c>
       <c r="BS25">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BT25">
         <v>10</v>
       </c>
       <c r="BU25">
-        <v>5</v>
+        <v>1.78</v>
       </c>
       <c r="BV25">
         <v>38</v>
@@ -6929,10 +6929,10 @@
         <v>44</v>
       </c>
       <c r="BY25">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BZ25">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="CA25">
         <v>1.95</v>
@@ -6958,16 +6958,16 @@
         <v>172</v>
       </c>
       <c r="F26">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G26">
         <v>1.56</v>
       </c>
       <c r="H26">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I26">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J26">
         <v>5.4</v>
@@ -6982,28 +6982,28 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O26">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P26">
         <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="R26">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S26">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="T26">
         <v>1.5</v>
       </c>
       <c r="U26">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="V26">
         <v>1.2</v>
@@ -7012,34 +7012,34 @@
         <v>2.78</v>
       </c>
       <c r="X26">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="Y26">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Z26">
         <v>65</v>
       </c>
       <c r="AA26">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AC26">
+        <v>13.5</v>
+      </c>
+      <c r="AD26">
+        <v>25</v>
+      </c>
+      <c r="AE26">
+        <v>320</v>
+      </c>
+      <c r="AF26">
         <v>14.5</v>
       </c>
-      <c r="AD26">
-        <v>24</v>
-      </c>
-      <c r="AE26">
-        <v>60</v>
-      </c>
-      <c r="AF26">
-        <v>15</v>
-      </c>
       <c r="AG26">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH26">
         <v>17.5</v>
@@ -7048,10 +7048,10 @@
         <v>48</v>
       </c>
       <c r="AJ26">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL26">
         <v>22</v>
@@ -7066,7 +7066,7 @@
         <v>36</v>
       </c>
       <c r="AP26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ26">
         <v>34</v>
@@ -7078,31 +7078,31 @@
         <v>44</v>
       </c>
       <c r="AT26">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU26">
         <v>12.5</v>
       </c>
       <c r="AV26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW26">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX26">
         <v>13</v>
       </c>
       <c r="AY26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ26">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA26">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB26">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC26">
         <v>12.5</v>
@@ -7111,13 +7111,13 @@
         <v>19</v>
       </c>
       <c r="BE26">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BF26">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG26">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7266,19 +7266,19 @@
         <v>230</v>
       </c>
       <c r="AB27">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC27">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AD27">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AE27">
         <v>80</v>
       </c>
       <c r="AF27">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AG27">
         <v>15.5</v>
@@ -7290,7 +7290,7 @@
         <v>70</v>
       </c>
       <c r="AJ27">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AK27">
         <v>17</v>
@@ -7308,58 +7308,58 @@
         <v>48</v>
       </c>
       <c r="AP27">
+        <v>6</v>
+      </c>
+      <c r="AQ27">
+        <v>6</v>
+      </c>
+      <c r="AR27">
+        <v>6.2</v>
+      </c>
+      <c r="AS27">
+        <v>6.4</v>
+      </c>
+      <c r="AT27">
         <v>5</v>
       </c>
-      <c r="AQ27">
+      <c r="AU27">
         <v>5</v>
       </c>
-      <c r="AR27">
-        <v>5.1</v>
-      </c>
-      <c r="AS27">
+      <c r="AV27">
+        <v>5.6</v>
+      </c>
+      <c r="AW27">
+        <v>6.2</v>
+      </c>
+      <c r="AX27">
+        <v>4.8</v>
+      </c>
+      <c r="AY27">
+        <v>4.7</v>
+      </c>
+      <c r="AZ27">
         <v>5.3</v>
       </c>
-      <c r="AT27">
-        <v>4.4</v>
-      </c>
-      <c r="AU27">
-        <v>4.4</v>
-      </c>
-      <c r="AV27">
+      <c r="BA27">
+        <v>6</v>
+      </c>
+      <c r="BB27">
         <v>4.8</v>
       </c>
-      <c r="AW27">
-        <v>5.1</v>
-      </c>
-      <c r="AX27">
-        <v>4.2</v>
-      </c>
-      <c r="AY27">
-        <v>4</v>
-      </c>
-      <c r="AZ27">
-        <v>4.4</v>
-      </c>
-      <c r="BA27">
-        <v>5</v>
-      </c>
-      <c r="BB27">
-        <v>4.2</v>
-      </c>
       <c r="BC27">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BD27">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BF27">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="BG27">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7980,7 +7980,7 @@
         <v>1.79</v>
       </c>
       <c r="X30">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>11.5</v>
@@ -8004,7 +8004,7 @@
         <v>80</v>
       </c>
       <c r="AF30">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG30">
         <v>12</v>
@@ -8040,10 +8040,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR30">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS30">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT30">
         <v>6.4</v>
@@ -8055,7 +8055,7 @@
         <v>15.5</v>
       </c>
       <c r="AW30">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
@@ -8064,28 +8064,28 @@
         <v>10</v>
       </c>
       <c r="AZ30">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA30">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB30">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC30">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BD30">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE30">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF30">
         <v>23</v>
       </c>
       <c r="BG30">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH30">
         <v>3.05</v>
@@ -8121,7 +8121,7 @@
         <v>48</v>
       </c>
       <c r="BS30">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BT30">
         <v>8.199999999999999</v>
@@ -8133,7 +8133,7 @@
         <v>46</v>
       </c>
       <c r="BW30">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX30">
         <v>70</v>
@@ -8192,7 +8192,7 @@
         <v>1.11</v>
       </c>
       <c r="N31">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="O31">
         <v>1.41</v>
@@ -8201,7 +8201,7 @@
         <v>1.57</v>
       </c>
       <c r="Q31">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="R31">
         <v>1.22</v>
@@ -8419,7 +8419,7 @@
         <v>1.75</v>
       </c>
       <c r="I32">
-        <v>32</v>
+        <v>990</v>
       </c>
       <c r="J32">
         <v>1.09</v>
@@ -8458,7 +8458,7 @@
         <v>1.11</v>
       </c>
       <c r="V32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W32">
         <v>1.01</v>
@@ -8652,19 +8652,19 @@
         <v>179</v>
       </c>
       <c r="F33">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G33">
         <v>2.14</v>
       </c>
       <c r="H33">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I33">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J33">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K33">
         <v>3.45</v>
@@ -8700,7 +8700,7 @@
         <v>1.86</v>
       </c>
       <c r="V33">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W33">
         <v>1.87</v>
@@ -8724,7 +8724,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE33">
         <v>70</v>
@@ -8736,7 +8736,7 @@
         <v>12.5</v>
       </c>
       <c r="AH33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI33">
         <v>95</v>
@@ -8757,19 +8757,19 @@
         <v>25</v>
       </c>
       <c r="AO33">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP33">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ33">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR33">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS33">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT33">
         <v>6.4</v>
@@ -8778,10 +8778,10 @@
         <v>6.6</v>
       </c>
       <c r="AV33">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW33">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX33">
         <v>10</v>
@@ -8790,28 +8790,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA33">
+        <v>5.2</v>
+      </c>
+      <c r="BB33">
+        <v>4.6</v>
+      </c>
+      <c r="BC33">
+        <v>4.6</v>
+      </c>
+      <c r="BD33">
         <v>5</v>
       </c>
-      <c r="BB33">
-        <v>21</v>
-      </c>
-      <c r="BC33">
-        <v>21</v>
-      </c>
-      <c r="BD33">
-        <v>4.9</v>
-      </c>
       <c r="BE33">
+        <v>5.3</v>
+      </c>
+      <c r="BF33">
+        <v>17</v>
+      </c>
+      <c r="BG33">
         <v>5.2</v>
-      </c>
-      <c r="BF33">
-        <v>16.5</v>
-      </c>
-      <c r="BG33">
-        <v>5.1</v>
       </c>
       <c r="BH33">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -556,7 +556,7 @@
     <t>Aguilas Doradas</t>
   </si>
   <si>
-    <t>2026-08-24 17:16:20</t>
+    <t>2026-08-24 19:35:23</t>
   </si>
 </sst>
 </file>
@@ -1150,25 +1150,25 @@
         <v>148</v>
       </c>
       <c r="F2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H2">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="I2">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="J2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
         <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M2">
         <v>1.1</v>
@@ -1177,13 +1177,13 @@
         <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R2">
         <v>1.25</v>
@@ -1192,19 +1192,19 @@
         <v>4.7</v>
       </c>
       <c r="T2">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="U2">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V2">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y2">
         <v>8.800000000000001</v>
@@ -1216,16 +1216,16 @@
         <v>38</v>
       </c>
       <c r="AB2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
         <v>12.5</v>
       </c>
       <c r="AE2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF2">
         <v>25</v>
@@ -1246,13 +1246,13 @@
         <v>50</v>
       </c>
       <c r="AL2">
+        <v>70</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
         <v>65</v>
-      </c>
-      <c r="AM2">
-        <v>160</v>
-      </c>
-      <c r="AN2">
-        <v>60</v>
       </c>
       <c r="AO2">
         <v>29</v>
@@ -1264,7 +1264,7 @@
         <v>7.8</v>
       </c>
       <c r="AR2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS2">
         <v>26</v>
@@ -1279,22 +1279,22 @@
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY2">
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA2">
         <v>38</v>
       </c>
       <c r="BB2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BC2">
         <v>34</v>
@@ -1303,7 +1303,7 @@
         <v>46</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BF2">
         <v>44</v>
@@ -1312,22 +1312,22 @@
         <v>21</v>
       </c>
       <c r="BH2">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI2">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
@@ -1339,13 +1339,13 @@
         <v>34</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR2">
         <v>50</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
         <v>5.2</v>
@@ -1357,19 +1357,19 @@
         <v>19.5</v>
       </c>
       <c r="BW2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>180</v>
@@ -1392,22 +1392,22 @@
         <v>149</v>
       </c>
       <c r="F3">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G3">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I3">
         <v>3.35</v>
       </c>
       <c r="J3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>1.64</v>
@@ -1422,55 +1422,55 @@
         <v>1.6</v>
       </c>
       <c r="P3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U3">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V3">
         <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG3">
         <v>13.5</v>
@@ -1479,7 +1479,7 @@
         <v>25</v>
       </c>
       <c r="AI3">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AJ3">
         <v>46</v>
@@ -1488,16 +1488,16 @@
         <v>44</v>
       </c>
       <c r="AL3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM3">
-        <v>660</v>
+        <v>440</v>
       </c>
       <c r="AN3">
         <v>55</v>
       </c>
       <c r="AO3">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP3">
         <v>7.4</v>
@@ -1506,112 +1506,112 @@
         <v>8</v>
       </c>
       <c r="AR3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW3">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BB3">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BC3">
         <v>36</v>
       </c>
       <c r="BD3">
+        <v>55</v>
+      </c>
+      <c r="BE3">
+        <v>48</v>
+      </c>
+      <c r="BF3">
+        <v>44</v>
+      </c>
+      <c r="BG3">
         <v>60</v>
       </c>
-      <c r="BE3">
+      <c r="BH3">
+        <v>2.76</v>
+      </c>
+      <c r="BI3">
+        <v>2.42</v>
+      </c>
+      <c r="BJ3">
         <v>14</v>
       </c>
-      <c r="BF3">
-        <v>34</v>
-      </c>
-      <c r="BG3">
-        <v>46</v>
-      </c>
-      <c r="BH3">
-        <v>2.98</v>
-      </c>
-      <c r="BI3">
-        <v>2.18</v>
-      </c>
-      <c r="BJ3">
-        <v>13.5</v>
-      </c>
       <c r="BK3">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="BL3">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BN3">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ3">
+        <v>4.4</v>
+      </c>
+      <c r="BR3">
+        <v>65</v>
+      </c>
+      <c r="BS3">
+        <v>4.7</v>
+      </c>
+      <c r="BT3">
+        <v>7.4</v>
+      </c>
+      <c r="BU3">
         <v>5.5</v>
       </c>
-      <c r="BR3">
-        <v>60</v>
-      </c>
-      <c r="BS3">
-        <v>6</v>
-      </c>
-      <c r="BT3">
-        <v>7.2</v>
-      </c>
-      <c r="BU3">
-        <v>4.7</v>
-      </c>
       <c r="BV3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BW3">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BY3">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BZ3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="CA3">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="CB3" t="s">
         <v>180</v>
@@ -1634,19 +1634,19 @@
         <v>150</v>
       </c>
       <c r="F4">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="G4">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I4">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K4">
         <v>3.1</v>
@@ -1658,19 +1658,19 @@
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O4">
         <v>1.51</v>
       </c>
       <c r="P4">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q4">
         <v>2.58</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S4">
         <v>5.3</v>
@@ -1679,43 +1679,43 @@
         <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
+        <v>1.51</v>
+      </c>
+      <c r="W4">
         <v>1.48</v>
-      </c>
-      <c r="W4">
-        <v>1.51</v>
       </c>
       <c r="X4">
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC4">
         <v>6.8</v>
       </c>
       <c r="AD4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE4">
         <v>42</v>
       </c>
       <c r="AF4">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH4">
         <v>21</v>
@@ -1724,61 +1724,61 @@
         <v>65</v>
       </c>
       <c r="AJ4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK4">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AL4">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AM4">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AO4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4">
+        <v>8</v>
+      </c>
+      <c r="AR4">
+        <v>15.5</v>
+      </c>
+      <c r="AS4">
+        <v>42</v>
+      </c>
+      <c r="AT4">
         <v>8.6</v>
-      </c>
-      <c r="AR4">
-        <v>16.5</v>
-      </c>
-      <c r="AS4">
-        <v>44</v>
-      </c>
-      <c r="AT4">
-        <v>8.4</v>
       </c>
       <c r="AU4">
         <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW4">
         <v>36</v>
       </c>
       <c r="AX4">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY4">
         <v>12</v>
       </c>
       <c r="AZ4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA4">
         <v>55</v>
       </c>
       <c r="BB4">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BC4">
         <v>34</v>
@@ -1790,70 +1790,70 @@
         <v>46</v>
       </c>
       <c r="BF4">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BG4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH4">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BI4">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BL4">
         <v>210</v>
       </c>
       <c r="BM4">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN4">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BO4">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP4">
         <v>26</v>
       </c>
       <c r="BQ4">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR4">
         <v>46</v>
       </c>
       <c r="BS4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BT4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
         <v>27</v>
       </c>
       <c r="BW4">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BX4">
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="CA4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="s">
         <v>180</v>
@@ -1876,10 +1876,10 @@
         <v>151</v>
       </c>
       <c r="F5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H5">
         <v>7.2</v>
@@ -1888,40 +1888,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J5">
+        <v>4.7</v>
+      </c>
+      <c r="K5">
+        <v>5.5</v>
+      </c>
+      <c r="L5">
+        <v>1.3</v>
+      </c>
+      <c r="M5">
+        <v>1.04</v>
+      </c>
+      <c r="N5">
         <v>4.8</v>
       </c>
-      <c r="K5">
-        <v>5.4</v>
-      </c>
-      <c r="L5">
-        <v>1.29</v>
-      </c>
-      <c r="M5">
-        <v>1.04</v>
-      </c>
-      <c r="N5">
-        <v>5.3</v>
-      </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q5">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="R5">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="V5">
         <v>1.13</v>
@@ -1930,22 +1930,22 @@
         <v>3</v>
       </c>
       <c r="X5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Y5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Z5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA5">
         <v>250</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
         <v>38</v>
@@ -1954,70 +1954,70 @@
         <v>150</v>
       </c>
       <c r="AF5">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG5">
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI5">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AJ5">
         <v>13.5</v>
       </c>
       <c r="AK5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM5">
         <v>170</v>
       </c>
       <c r="AN5">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AO5">
         <v>170</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR5">
         <v>50</v>
       </c>
       <c r="AS5">
+        <v>10.5</v>
+      </c>
+      <c r="AT5">
+        <v>7.6</v>
+      </c>
+      <c r="AU5">
         <v>9.800000000000001</v>
       </c>
-      <c r="AT5">
-        <v>9</v>
-      </c>
-      <c r="AU5">
-        <v>10</v>
-      </c>
       <c r="AV5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW5">
         <v>10</v>
       </c>
       <c r="AX5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY5">
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB5">
         <v>11</v>
@@ -2026,19 +2026,19 @@
         <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE5">
         <v>10</v>
       </c>
       <c r="BF5">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BG5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
         <v>3.6</v>
@@ -2047,13 +2047,13 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN5">
         <v>4.3</v>
@@ -2065,37 +2065,37 @@
         <v>8.6</v>
       </c>
       <c r="BQ5">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BR5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU5">
         <v>6</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
         <v>180</v>
@@ -2124,7 +2124,7 @@
         <v>3.7</v>
       </c>
       <c r="H6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I6">
         <v>2.3</v>
@@ -2133,7 +2133,7 @@
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L6">
         <v>1.35</v>
@@ -2148,7 +2148,7 @@
         <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q6">
         <v>2.04</v>
@@ -2157,7 +2157,7 @@
         <v>1.35</v>
       </c>
       <c r="S6">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T6">
         <v>1.82</v>
@@ -2220,7 +2220,7 @@
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AO6">
         <v>18.5</v>
@@ -2235,7 +2235,7 @@
         <v>12.5</v>
       </c>
       <c r="AS6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AT6">
         <v>12</v>
@@ -2250,7 +2250,7 @@
         <v>21</v>
       </c>
       <c r="AX6">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY6">
         <v>13.5</v>
@@ -2262,7 +2262,7 @@
         <v>32</v>
       </c>
       <c r="BB6">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BC6">
         <v>32</v>
@@ -2271,7 +2271,7 @@
         <v>28</v>
       </c>
       <c r="BE6">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="BF6">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>2.52</v>
       </c>
       <c r="G7">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H7">
         <v>3.2</v>
@@ -2378,13 +2378,13 @@
         <v>3.3</v>
       </c>
       <c r="L7">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O7">
         <v>1.47</v>
@@ -2393,37 +2393,37 @@
         <v>1.69</v>
       </c>
       <c r="Q7">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
         <v>1.25</v>
       </c>
       <c r="S7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U7">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V7">
         <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB7">
         <v>8.4</v>
@@ -2435,13 +2435,13 @@
         <v>14.5</v>
       </c>
       <c r="AE7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF7">
         <v>15.5</v>
       </c>
       <c r="AG7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH7">
         <v>22</v>
@@ -2450,7 +2450,7 @@
         <v>70</v>
       </c>
       <c r="AJ7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK7">
         <v>34</v>
@@ -2477,7 +2477,7 @@
         <v>18</v>
       </c>
       <c r="AS7">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AT7">
         <v>7.6</v>
@@ -2489,7 +2489,7 @@
         <v>13</v>
       </c>
       <c r="AW7">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AX7">
         <v>13</v>
@@ -2498,88 +2498,88 @@
         <v>11</v>
       </c>
       <c r="AZ7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
+        <v>44</v>
+      </c>
+      <c r="BB7">
+        <v>30</v>
+      </c>
+      <c r="BC7">
+        <v>25</v>
+      </c>
+      <c r="BD7">
+        <v>40</v>
+      </c>
+      <c r="BE7">
+        <v>15.5</v>
+      </c>
+      <c r="BF7">
+        <v>25</v>
+      </c>
+      <c r="BG7">
+        <v>36</v>
+      </c>
+      <c r="BH7">
+        <v>2.98</v>
+      </c>
+      <c r="BI7">
+        <v>2.44</v>
+      </c>
+      <c r="BJ7">
+        <v>11</v>
+      </c>
+      <c r="BK7">
+        <v>5.4</v>
+      </c>
+      <c r="BL7">
+        <v>180</v>
+      </c>
+      <c r="BM7">
+        <v>10</v>
+      </c>
+      <c r="BN7">
+        <v>5.5</v>
+      </c>
+      <c r="BO7">
+        <v>4.2</v>
+      </c>
+      <c r="BP7">
+        <v>23</v>
+      </c>
+      <c r="BQ7">
+        <v>7.2</v>
+      </c>
+      <c r="BR7">
+        <v>42</v>
+      </c>
+      <c r="BS7">
+        <v>8.4</v>
+      </c>
+      <c r="BT7">
+        <v>6.6</v>
+      </c>
+      <c r="BU7">
+        <v>4.9</v>
+      </c>
+      <c r="BV7">
         <v>32</v>
       </c>
-      <c r="BB7">
-        <v>23</v>
-      </c>
-      <c r="BC7">
-        <v>21</v>
-      </c>
-      <c r="BD7">
-        <v>29</v>
-      </c>
-      <c r="BE7">
-        <v>12.5</v>
-      </c>
-      <c r="BF7">
-        <v>21</v>
-      </c>
-      <c r="BG7">
-        <v>27</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>1.04</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.04</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
-      <c r="BO7">
-        <v>1.04</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>1.04</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>1.04</v>
-      </c>
-      <c r="BT7">
-        <v>1000</v>
-      </c>
-      <c r="BU7">
-        <v>1.04</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="s">
         <v>180</v>
@@ -2602,10 +2602,10 @@
         <v>154</v>
       </c>
       <c r="F8">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H8">
         <v>6.6</v>
@@ -2614,7 +2614,7 @@
         <v>7.4</v>
       </c>
       <c r="J8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K8">
         <v>4.6</v>
@@ -2626,49 +2626,49 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q8">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R8">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S8">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T8">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U8">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V8">
         <v>1.15</v>
       </c>
       <c r="W8">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="X8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y8">
         <v>23</v>
       </c>
       <c r="Z8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA8">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB8">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC8">
         <v>10</v>
@@ -2686,7 +2686,7 @@
         <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI8">
         <v>110</v>
@@ -2695,25 +2695,25 @@
         <v>14.5</v>
       </c>
       <c r="AK8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM8">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO8">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP8">
         <v>14.5</v>
       </c>
       <c r="AQ8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR8">
         <v>10</v>
@@ -2731,7 +2731,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX8">
         <v>8.199999999999999</v>
@@ -2743,7 +2743,7 @@
         <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB8">
         <v>12.5</v>
@@ -2752,13 +2752,13 @@
         <v>15</v>
       </c>
       <c r="BD8">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BE8">
         <v>11</v>
       </c>
       <c r="BF8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG8">
         <v>11</v>
@@ -2773,7 +2773,7 @@
         <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2812,7 +2812,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BX8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY8">
         <v>9.199999999999999</v>
@@ -2850,7 +2850,7 @@
         <v>1.77</v>
       </c>
       <c r="H9">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I9">
         <v>6.4</v>
@@ -2898,16 +2898,16 @@
         <v>2.28</v>
       </c>
       <c r="X9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y9">
         <v>21</v>
       </c>
       <c r="Z9">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AA9">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB9">
         <v>9.199999999999999</v>
@@ -2919,7 +2919,7 @@
         <v>30</v>
       </c>
       <c r="AE9">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AF9">
         <v>11</v>
@@ -2931,7 +2931,7 @@
         <v>22</v>
       </c>
       <c r="AI9">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AJ9">
         <v>17.5</v>
@@ -2943,28 +2943,28 @@
         <v>38</v>
       </c>
       <c r="AM9">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN9">
         <v>10.5</v>
       </c>
       <c r="AO9">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AP9">
         <v>6</v>
       </c>
       <c r="AQ9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR9">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU9">
         <v>8</v>
@@ -2973,7 +2973,7 @@
         <v>19</v>
       </c>
       <c r="AW9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX9">
         <v>8.800000000000001</v>
@@ -2985,25 +2985,25 @@
         <v>15.5</v>
       </c>
       <c r="BA9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC9">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD9">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE9">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF9">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BG9">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3095,10 +3095,10 @@
         <v>2.6</v>
       </c>
       <c r="I10">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="K10">
         <v>3.8</v>
@@ -3134,22 +3134,22 @@
         <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
         <v>1.46</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z10">
         <v>19.5</v>
       </c>
       <c r="AA10">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="AB10">
         <v>12</v>
@@ -3158,10 +3158,10 @@
         <v>8.6</v>
       </c>
       <c r="AD10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF10">
         <v>21</v>
@@ -3173,79 +3173,79 @@
         <v>19</v>
       </c>
       <c r="AI10">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AJ10">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK10">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AL10">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AM10">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN10">
         <v>34</v>
       </c>
       <c r="AO10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP10">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ10">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AR10">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS10">
+        <v>6</v>
+      </c>
+      <c r="AT10">
+        <v>5.6</v>
+      </c>
+      <c r="AU10">
+        <v>4.4</v>
+      </c>
+      <c r="AV10">
+        <v>4.6</v>
+      </c>
+      <c r="AW10">
+        <v>5.9</v>
+      </c>
+      <c r="AX10">
         <v>5.3</v>
       </c>
-      <c r="AT10">
-        <v>4</v>
-      </c>
-      <c r="AU10">
-        <v>3.5</v>
-      </c>
-      <c r="AV10">
-        <v>4.2</v>
-      </c>
-      <c r="AW10">
+      <c r="AY10">
+        <v>4.7</v>
+      </c>
+      <c r="AZ10">
         <v>5.1</v>
       </c>
-      <c r="AX10">
-        <v>4.6</v>
-      </c>
-      <c r="AY10">
-        <v>4.2</v>
-      </c>
-      <c r="AZ10">
-        <v>4.5</v>
-      </c>
       <c r="BA10">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB10">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC10">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BD10">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE10">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF10">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BG10">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3328,61 +3328,61 @@
         <v>157</v>
       </c>
       <c r="F11">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G11">
         <v>2.22</v>
       </c>
       <c r="H11">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I11">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O11">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P11">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q11">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="S11">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T11">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="U11">
         <v>2.36</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y11">
         <v>970</v>
@@ -3391,49 +3391,49 @@
         <v>34</v>
       </c>
       <c r="AA11">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB11">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD11">
         <v>16</v>
       </c>
       <c r="AE11">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AF11">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG11">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI11">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ11">
-        <v>27</v>
+        <v>900</v>
       </c>
       <c r="AK11">
         <v>25</v>
       </c>
       <c r="AL11">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AM11">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AO11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP11">
         <v>15</v>
@@ -3442,22 +3442,22 @@
         <v>13.5</v>
       </c>
       <c r="AR11">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS11">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AT11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU11">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV11">
         <v>11</v>
       </c>
       <c r="AW11">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AX11">
         <v>12</v>
@@ -3469,7 +3469,7 @@
         <v>13</v>
       </c>
       <c r="BA11">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB11">
         <v>16</v>
@@ -3481,49 +3481,49 @@
         <v>21</v>
       </c>
       <c r="BE11">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BF11">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG11">
         <v>21</v>
       </c>
       <c r="BH11">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI11">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BJ11">
         <v>9.199999999999999</v>
       </c>
       <c r="BK11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN11">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP11">
         <v>14.5</v>
       </c>
       <c r="BQ11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR11">
         <v>25</v>
       </c>
       <c r="BS11">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT11">
         <v>7.4</v>
@@ -3535,13 +3535,13 @@
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3573,7 +3573,7 @@
         <v>3</v>
       </c>
       <c r="G12">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H12">
         <v>2.34</v>
@@ -3585,7 +3585,7 @@
         <v>3.4</v>
       </c>
       <c r="K12">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3594,28 +3594,28 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="O12">
         <v>1.27</v>
       </c>
       <c r="P12">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q12">
         <v>1.86</v>
       </c>
       <c r="R12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T12">
         <v>1.69</v>
       </c>
       <c r="U12">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
         <v>1.63</v>
@@ -3624,70 +3624,70 @@
         <v>1.43</v>
       </c>
       <c r="X12">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y12">
         <v>13</v>
       </c>
       <c r="Z12">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AA12">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AB12">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC12">
         <v>8.6</v>
       </c>
       <c r="AD12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE12">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AF12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG12">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH12">
         <v>17.5</v>
       </c>
       <c r="AI12">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AJ12">
         <v>65</v>
       </c>
       <c r="AK12">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AL12">
         <v>55</v>
       </c>
       <c r="AM12">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AN12">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AO12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP12">
         <v>13</v>
       </c>
       <c r="AQ12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR12">
         <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="AT12">
         <v>11</v>
@@ -3711,22 +3711,22 @@
         <v>14</v>
       </c>
       <c r="BA12">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC12">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BD12">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE12">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF12">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG12">
         <v>14.5</v>
@@ -3812,7 +3812,7 @@
         <v>159</v>
       </c>
       <c r="F13">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G13">
         <v>1.94</v>
@@ -3848,7 +3848,7 @@
         <v>1.89</v>
       </c>
       <c r="R13">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S13">
         <v>3.25</v>
@@ -3875,7 +3875,7 @@
         <v>40</v>
       </c>
       <c r="AA13">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB13">
         <v>9.4</v>
@@ -3887,7 +3887,7 @@
         <v>23</v>
       </c>
       <c r="AE13">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AF13">
         <v>12</v>
@@ -3899,7 +3899,7 @@
         <v>21</v>
       </c>
       <c r="AI13">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ13">
         <v>22</v>
@@ -3911,13 +3911,13 @@
         <v>40</v>
       </c>
       <c r="AM13">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN13">
         <v>13</v>
       </c>
       <c r="AO13">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP13">
         <v>13</v>
@@ -3941,7 +3941,7 @@
         <v>16</v>
       </c>
       <c r="AW13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX13">
         <v>10</v>
@@ -4057,16 +4057,16 @@
         <v>1.94</v>
       </c>
       <c r="G14">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K14">
         <v>4.1</v>
@@ -4078,40 +4078,40 @@
         <v>1.06</v>
       </c>
       <c r="N14">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O14">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P14">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q14">
         <v>1.83</v>
       </c>
       <c r="R14">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S14">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T14">
         <v>1.76</v>
       </c>
       <c r="U14">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V14">
         <v>1.31</v>
       </c>
       <c r="W14">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X14">
         <v>17.5</v>
       </c>
       <c r="Y14">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z14">
         <v>32</v>
@@ -4123,19 +4123,19 @@
         <v>10.5</v>
       </c>
       <c r="AC14">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE14">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="AF14">
         <v>13</v>
       </c>
       <c r="AG14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH14">
         <v>18.5</v>
@@ -4144,22 +4144,22 @@
         <v>55</v>
       </c>
       <c r="AJ14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK14">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL14">
         <v>34</v>
       </c>
       <c r="AM14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO14">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP14">
         <v>15</v>
@@ -4171,13 +4171,13 @@
         <v>25</v>
       </c>
       <c r="AS14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14">
         <v>14.5</v>
@@ -4186,7 +4186,7 @@
         <v>38</v>
       </c>
       <c r="AX14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY14">
         <v>9.4</v>
@@ -4207,7 +4207,7 @@
         <v>29</v>
       </c>
       <c r="BE14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BF14">
         <v>11</v>
@@ -4296,10 +4296,10 @@
         <v>161</v>
       </c>
       <c r="F15">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G15">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H15">
         <v>4.4</v>
@@ -4326,7 +4326,7 @@
         <v>1.21</v>
       </c>
       <c r="P15">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
         <v>1.63</v>
@@ -4347,16 +4347,16 @@
         <v>1.27</v>
       </c>
       <c r="W15">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z15">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA15">
         <v>110</v>
@@ -4365,10 +4365,10 @@
         <v>13.5</v>
       </c>
       <c r="AC15">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE15">
         <v>60</v>
@@ -4377,10 +4377,10 @@
         <v>13.5</v>
       </c>
       <c r="AG15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI15">
         <v>55</v>
@@ -4395,7 +4395,7 @@
         <v>28</v>
       </c>
       <c r="AM15">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN15">
         <v>8.6</v>
@@ -4413,7 +4413,7 @@
         <v>32</v>
       </c>
       <c r="AS15">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT15">
         <v>10.5</v>
@@ -4437,7 +4437,7 @@
         <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB15">
         <v>15.5</v>
@@ -4449,13 +4449,13 @@
         <v>20</v>
       </c>
       <c r="BE15">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15">
         <v>7.4</v>
       </c>
       <c r="BG15">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4538,16 +4538,16 @@
         <v>162</v>
       </c>
       <c r="F16">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="G16">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="H16">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="I16">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="J16">
         <v>3.5</v>
@@ -4565,13 +4565,13 @@
         <v>4</v>
       </c>
       <c r="O16">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P16">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q16">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R16">
         <v>1.41</v>
@@ -4583,79 +4583,79 @@
         <v>1.67</v>
       </c>
       <c r="U16">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V16">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W16">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X16">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y16">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z16">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA16">
         <v>50</v>
       </c>
       <c r="AB16">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC16">
         <v>8.4</v>
       </c>
       <c r="AD16">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE16">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AF16">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AG16">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH16">
         <v>17</v>
       </c>
       <c r="AI16">
+        <v>95</v>
+      </c>
+      <c r="AJ16">
+        <v>100</v>
+      </c>
+      <c r="AK16">
         <v>40</v>
       </c>
-      <c r="AJ16">
-        <v>46</v>
-      </c>
-      <c r="AK16">
-        <v>34</v>
-      </c>
       <c r="AL16">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AM16">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AN16">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AO16">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AP16">
         <v>12.5</v>
       </c>
       <c r="AQ16">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR16">
         <v>14</v>
       </c>
       <c r="AS16">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="AT16">
         <v>11</v>
@@ -4667,7 +4667,7 @@
         <v>10</v>
       </c>
       <c r="AW16">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AX16">
         <v>17</v>
@@ -4691,13 +4691,13 @@
         <v>32</v>
       </c>
       <c r="BE16">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF16">
         <v>20</v>
       </c>
       <c r="BG16">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4810,7 +4810,7 @@
         <v>1.55</v>
       </c>
       <c r="P17">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q17">
         <v>2.64</v>
@@ -4843,7 +4843,7 @@
         <v>23</v>
       </c>
       <c r="AA17">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB17">
         <v>8.199999999999999</v>
@@ -4855,7 +4855,7 @@
         <v>16</v>
       </c>
       <c r="AE17">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF17">
         <v>17</v>
@@ -4876,10 +4876,10 @@
         <v>44</v>
       </c>
       <c r="AL17">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM17">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AN17">
         <v>60</v>
@@ -4897,10 +4897,10 @@
         <v>18</v>
       </c>
       <c r="AS17">
+        <v>6.8</v>
+      </c>
+      <c r="AT17">
         <v>6.6</v>
-      </c>
-      <c r="AT17">
-        <v>5.9</v>
       </c>
       <c r="AU17">
         <v>5.3</v>
@@ -4921,25 +4921,25 @@
         <v>19.5</v>
       </c>
       <c r="BA17">
+        <v>7</v>
+      </c>
+      <c r="BB17">
+        <v>6.4</v>
+      </c>
+      <c r="BC17">
+        <v>6.4</v>
+      </c>
+      <c r="BD17">
         <v>6.8</v>
       </c>
-      <c r="BB17">
-        <v>6.2</v>
-      </c>
-      <c r="BC17">
-        <v>6.2</v>
-      </c>
-      <c r="BD17">
+      <c r="BE17">
+        <v>7.2</v>
+      </c>
+      <c r="BF17">
         <v>6.6</v>
       </c>
-      <c r="BE17">
+      <c r="BG17">
         <v>7</v>
-      </c>
-      <c r="BF17">
-        <v>6.4</v>
-      </c>
-      <c r="BG17">
-        <v>6.8</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5034,7 +5034,7 @@
         <v>2.82</v>
       </c>
       <c r="J18">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K18">
         <v>3.3</v>
@@ -5061,13 +5061,13 @@
         <v>1.18</v>
       </c>
       <c r="S18">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T18">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U18">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V18">
         <v>1.55</v>
@@ -5076,7 +5076,7 @@
         <v>1.39</v>
       </c>
       <c r="X18">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>8.4</v>
@@ -5088,7 +5088,7 @@
         <v>55</v>
       </c>
       <c r="AB18">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC18">
         <v>7.4</v>
@@ -5100,88 +5100,88 @@
         <v>48</v>
       </c>
       <c r="AF18">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AG18">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AH18">
         <v>24</v>
       </c>
       <c r="AI18">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AJ18">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK18">
         <v>65</v>
       </c>
       <c r="AL18">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AM18">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN18">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AO18">
         <v>55</v>
       </c>
       <c r="AP18">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ18">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR18">
         <v>13</v>
       </c>
       <c r="AS18">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AT18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU18">
         <v>6</v>
       </c>
       <c r="AV18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW18">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AX18">
         <v>18</v>
       </c>
       <c r="AY18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ18">
         <v>19</v>
       </c>
       <c r="BA18">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB18">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC18">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BD18">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE18">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF18">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG18">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5279,7 +5279,7 @@
         <v>2.9</v>
       </c>
       <c r="K19">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
         <v>1.43</v>
@@ -5315,31 +5315,31 @@
         <v>1.16</v>
       </c>
       <c r="W19">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB19">
         <v>970</v>
       </c>
       <c r="AC19">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF19">
         <v>970</v>
@@ -5348,82 +5348,82 @@
         <v>950</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO19">
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.44</v>
+        <v>4.4</v>
       </c>
       <c r="AQ19">
-        <v>8.6</v>
+        <v>1.71</v>
       </c>
       <c r="AR19">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AS19">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AT19">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU19">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AV19">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AW19">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AX19">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="AY19">
-        <v>7.2</v>
+        <v>1.69</v>
       </c>
       <c r="AZ19">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="BA19">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="BB19">
-        <v>1.45</v>
+        <v>9</v>
       </c>
       <c r="BC19">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="BD19">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="BE19">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="BF19">
-        <v>1.45</v>
+        <v>4.7</v>
       </c>
       <c r="BG19">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5506,22 +5506,22 @@
         <v>166</v>
       </c>
       <c r="F20">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H20">
         <v>13</v>
       </c>
       <c r="I20">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="J20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K20">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L20">
         <v>1.35</v>
@@ -5530,13 +5530,13 @@
         <v>1.06</v>
       </c>
       <c r="N20">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="O20">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="P20">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q20">
         <v>2.2</v>
@@ -5548,37 +5548,37 @@
         <v>3.6</v>
       </c>
       <c r="T20">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U20">
         <v>1.48</v>
       </c>
       <c r="V20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W20">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="X20">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y20">
         <v>34</v>
       </c>
       <c r="Z20">
-        <v>190</v>
+        <v>540</v>
       </c>
       <c r="AA20">
         <v>1000</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC20">
         <v>12.5</v>
       </c>
       <c r="AD20">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="AE20">
         <v>520</v>
@@ -5590,19 +5590,19 @@
         <v>12</v>
       </c>
       <c r="AH20">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="AI20">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="AJ20">
         <v>11</v>
       </c>
       <c r="AK20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL20">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="AM20">
         <v>530</v>
@@ -5614,58 +5614,58 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ20">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR20">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS20">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT20">
         <v>5</v>
       </c>
       <c r="AU20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AV20">
-        <v>18</v>
+        <v>8.4</v>
       </c>
       <c r="AW20">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX20">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY20">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA20">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB20">
         <v>8.800000000000001</v>
       </c>
       <c r="BC20">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BD20">
-        <v>19</v>
+        <v>8.6</v>
       </c>
       <c r="BE20">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF20">
         <v>6.6</v>
       </c>
       <c r="BG20">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5754,25 +5754,25 @@
         <v>10.5</v>
       </c>
       <c r="H21">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I21">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J21">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="K21">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L21">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="M21">
         <v>1.02</v>
       </c>
       <c r="N21">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>1.11</v>
@@ -5796,58 +5796,58 @@
         <v>2.3</v>
       </c>
       <c r="V21">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="W21">
         <v>1.1</v>
       </c>
       <c r="X21">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Y21">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Z21">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA21">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB21">
         <v>55</v>
       </c>
       <c r="AC21">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AD21">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE21">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF21">
         <v>120</v>
       </c>
       <c r="AG21">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AH21">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AI21">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AJ21">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AK21">
         <v>130</v>
       </c>
       <c r="AL21">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AM21">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AN21">
         <v>100</v>
@@ -5856,19 +5856,19 @@
         <v>3.45</v>
       </c>
       <c r="AP21">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AQ21">
         <v>14</v>
       </c>
       <c r="AR21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS21">
         <v>11</v>
       </c>
       <c r="AT21">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU21">
         <v>14.5</v>
@@ -5880,37 +5880,37 @@
         <v>11.5</v>
       </c>
       <c r="AX21">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AY21">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="AZ21">
         <v>20</v>
       </c>
       <c r="BA21">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BB21">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC21">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BD21">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BE21">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BF21">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BG21">
         <v>3.1</v>
       </c>
       <c r="BH21">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BI21">
         <v>5.2</v>
@@ -5919,31 +5919,31 @@
         <v>10.5</v>
       </c>
       <c r="BK21">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BO21">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT21">
         <v>4.6</v>
@@ -5955,13 +5955,13 @@
         <v>7.4</v>
       </c>
       <c r="BW21">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BX21">
         <v>17</v>
       </c>
       <c r="BY21">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ21">
         <v>7.6</v>
@@ -6017,16 +6017,16 @@
         <v>1.1</v>
       </c>
       <c r="O22">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P22">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q22">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="R22">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="S22">
         <v>2.58</v>
@@ -6047,22 +6047,22 @@
         <v>23</v>
       </c>
       <c r="Y22">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z22">
         <v>42</v>
       </c>
       <c r="AA22">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB22">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC22">
         <v>10.5</v>
       </c>
       <c r="AD22">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE22">
         <v>55</v>
@@ -6077,7 +6077,7 @@
         <v>18</v>
       </c>
       <c r="AI22">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AJ22">
         <v>21</v>
@@ -6086,16 +6086,16 @@
         <v>18</v>
       </c>
       <c r="AL22">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AM22">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="AN22">
         <v>9</v>
       </c>
       <c r="AO22">
-        <v>50</v>
+        <v>280</v>
       </c>
       <c r="AP22">
         <v>18.5</v>
@@ -6104,10 +6104,10 @@
         <v>17.5</v>
       </c>
       <c r="AR22">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS22">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT22">
         <v>9.800000000000001</v>
@@ -6119,7 +6119,7 @@
         <v>15.5</v>
       </c>
       <c r="AW22">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX22">
         <v>10.5</v>
@@ -6131,7 +6131,7 @@
         <v>14.5</v>
       </c>
       <c r="BA22">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB22">
         <v>16.5</v>
@@ -6140,16 +6140,16 @@
         <v>14.5</v>
       </c>
       <c r="BD22">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BE22">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF22">
         <v>7.4</v>
       </c>
       <c r="BG22">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6232,28 +6232,28 @@
         <v>169</v>
       </c>
       <c r="F23">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="G23">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H23">
-        <v>3.45</v>
+        <v>2.54</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="K23">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23">
         <v>6</v>
@@ -6268,7 +6268,7 @@
         <v>1.48</v>
       </c>
       <c r="R23">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="S23">
         <v>2.16</v>
@@ -6277,40 +6277,40 @@
         <v>1.49</v>
       </c>
       <c r="U23">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V23">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W23">
         <v>1.89</v>
       </c>
       <c r="X23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y23">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z23">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AA23">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB23">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AC23">
         <v>11.5</v>
       </c>
       <c r="AD23">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE23">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF23">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG23">
         <v>13</v>
@@ -6319,7 +6319,7 @@
         <v>17</v>
       </c>
       <c r="AI23">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ23">
         <v>28</v>
@@ -6328,70 +6328,70 @@
         <v>21</v>
       </c>
       <c r="AL23">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AM23">
         <v>60</v>
       </c>
       <c r="AN23">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO23">
         <v>26</v>
       </c>
       <c r="AP23">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6474,7 +6474,7 @@
         <v>170</v>
       </c>
       <c r="F24">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -6486,10 +6486,10 @@
         <v>2.72</v>
       </c>
       <c r="J24">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K24">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L24">
         <v>1.45</v>
@@ -6504,7 +6504,7 @@
         <v>1.37</v>
       </c>
       <c r="P24">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q24">
         <v>2.1</v>
@@ -6513,13 +6513,13 @@
         <v>1.34</v>
       </c>
       <c r="S24">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T24">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U24">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V24">
         <v>1.58</v>
@@ -6528,7 +6528,7 @@
         <v>1.5</v>
       </c>
       <c r="X24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y24">
         <v>10.5</v>
@@ -6543,7 +6543,7 @@
         <v>11.5</v>
       </c>
       <c r="AC24">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD24">
         <v>12</v>
@@ -6558,10 +6558,10 @@
         <v>13</v>
       </c>
       <c r="AH24">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI24">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ24">
         <v>48</v>
@@ -6585,7 +6585,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ24">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR24">
         <v>15.5</v>
@@ -6615,7 +6615,7 @@
         <v>16.5</v>
       </c>
       <c r="BA24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB24">
         <v>44</v>
@@ -6627,13 +6627,13 @@
         <v>42</v>
       </c>
       <c r="BE24">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BG24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH24">
         <v>3.2</v>
@@ -6642,7 +6642,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ24">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK24">
         <v>8.4</v>
@@ -6651,7 +6651,7 @@
         <v>130</v>
       </c>
       <c r="BM24">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BN24">
         <v>5.9</v>
@@ -6666,10 +6666,10 @@
         <v>17.5</v>
       </c>
       <c r="BR24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT24">
         <v>5.6</v>
@@ -6681,19 +6681,19 @@
         <v>22</v>
       </c>
       <c r="BW24">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BX24">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY24">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BZ24">
         <v>32</v>
       </c>
       <c r="CA24">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="CB24" t="s">
         <v>180</v>
@@ -6716,13 +6716,13 @@
         <v>171</v>
       </c>
       <c r="F25">
+        <v>2.02</v>
+      </c>
+      <c r="G25">
         <v>2.04</v>
       </c>
-      <c r="G25">
-        <v>2.08</v>
-      </c>
       <c r="H25">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I25">
         <v>3.75</v>
@@ -6734,52 +6734,52 @@
         <v>4.2</v>
       </c>
       <c r="L25">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M25">
         <v>1.04</v>
       </c>
       <c r="N25">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O25">
         <v>1.2</v>
       </c>
       <c r="P25">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q25">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R25">
+        <v>1.63</v>
+      </c>
+      <c r="S25">
+        <v>2.4</v>
+      </c>
+      <c r="T25">
         <v>1.6</v>
       </c>
-      <c r="S25">
-        <v>2.52</v>
-      </c>
-      <c r="T25">
-        <v>1.58</v>
-      </c>
       <c r="U25">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V25">
         <v>1.36</v>
       </c>
       <c r="W25">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X25">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y25">
         <v>20</v>
       </c>
       <c r="Z25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA25">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB25">
         <v>13.5</v>
@@ -6788,16 +6788,16 @@
         <v>10</v>
       </c>
       <c r="AD25">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE25">
         <v>38</v>
       </c>
       <c r="AF25">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH25">
         <v>15.5</v>
@@ -6806,28 +6806,28 @@
         <v>40</v>
       </c>
       <c r="AJ25">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AK25">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM25">
         <v>60</v>
       </c>
       <c r="AN25">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO25">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP25">
         <v>20</v>
       </c>
       <c r="AQ25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR25">
         <v>27</v>
@@ -6836,43 +6836,43 @@
         <v>55</v>
       </c>
       <c r="AT25">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU25">
         <v>8.800000000000001</v>
       </c>
       <c r="AV25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW25">
         <v>32</v>
       </c>
       <c r="AX25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY25">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA25">
         <v>34</v>
       </c>
       <c r="BB25">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC25">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD25">
         <v>24</v>
       </c>
       <c r="BE25">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF25">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG25">
         <v>22</v>
@@ -6881,61 +6881,61 @@
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BJ25">
         <v>11.5</v>
       </c>
       <c r="BK25">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BN25">
         <v>6.6</v>
       </c>
       <c r="BO25">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP25">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ25">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BR25">
         <v>30</v>
       </c>
       <c r="BS25">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BT25">
         <v>10</v>
       </c>
       <c r="BU25">
-        <v>1.78</v>
+        <v>5</v>
       </c>
       <c r="BV25">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW25">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BX25">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BZ25">
         <v>20</v>
       </c>
       <c r="CA25">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="CB25" t="s">
         <v>180</v>
@@ -6958,22 +6958,22 @@
         <v>172</v>
       </c>
       <c r="F26">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G26">
         <v>1.56</v>
       </c>
       <c r="H26">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I26">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J26">
+        <v>5.3</v>
+      </c>
+      <c r="K26">
         <v>5.4</v>
-      </c>
-      <c r="K26">
-        <v>5.5</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -6982,124 +6982,124 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P26">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q26">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="R26">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="T26">
         <v>1.5</v>
       </c>
       <c r="U26">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="V26">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W26">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X26">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="Y26">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Z26">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB26">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE26">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="AF26">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG26">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH26">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI26">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ26">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK26">
         <v>14</v>
       </c>
       <c r="AL26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM26">
         <v>55</v>
       </c>
       <c r="AN26">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO26">
         <v>36</v>
       </c>
       <c r="AP26">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AQ26">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AR26">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS26">
         <v>44</v>
       </c>
       <c r="AT26">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV26">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW26">
         <v>48</v>
       </c>
       <c r="AX26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ26">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BA26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB26">
         <v>16</v>
@@ -7108,16 +7108,16 @@
         <v>12.5</v>
       </c>
       <c r="BD26">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE26">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BF26">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BG26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7209,10 +7209,10 @@
         <v>7.8</v>
       </c>
       <c r="I27">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J27">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K27">
         <v>7.2</v>
@@ -7224,19 +7224,19 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>1.09</v>
       </c>
       <c r="P27">
-        <v>1.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q27">
         <v>1.27</v>
       </c>
       <c r="R27">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
         <v>1.57</v>
@@ -7248,16 +7248,16 @@
         <v>2.58</v>
       </c>
       <c r="V27">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W27">
         <v>3.75</v>
       </c>
       <c r="X27">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Y27">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z27">
         <v>110</v>
@@ -7275,7 +7275,7 @@
         <v>34</v>
       </c>
       <c r="AE27">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="AF27">
         <v>16.5</v>
@@ -7284,82 +7284,82 @@
         <v>15.5</v>
       </c>
       <c r="AH27">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI27">
         <v>70</v>
       </c>
       <c r="AJ27">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK27">
         <v>17</v>
       </c>
       <c r="AL27">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AM27">
         <v>70</v>
       </c>
       <c r="AN27">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AO27">
         <v>48</v>
       </c>
       <c r="AP27">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ27">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR27">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS27">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT27">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AU27">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="AV27">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="AW27">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX27">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AY27">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27">
-        <v>5.3</v>
+        <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB27">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="BC27">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="BD27">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="BE27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF27">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BG27">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7442,22 +7442,22 @@
         <v>174</v>
       </c>
       <c r="F28">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="G28">
         <v>2.64</v>
       </c>
       <c r="H28">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="I28">
         <v>4.3</v>
       </c>
       <c r="J28">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="K28">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7466,16 +7466,16 @@
         <v>1.07</v>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="O28">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="P28">
         <v>1.4</v>
       </c>
       <c r="Q28">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R28">
         <v>1.13</v>
@@ -7490,10 +7490,10 @@
         <v>1.11</v>
       </c>
       <c r="V28">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W28">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7559,34 +7559,34 @@
         <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="AT28">
         <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="AV28">
         <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AZ28">
         <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BC28">
         <v>1.01</v>
@@ -7684,46 +7684,46 @@
         <v>175</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M29">
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>1.1</v>
+        <v>2.42</v>
       </c>
       <c r="O29">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="P29">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q29">
-        <v>1.5</v>
+        <v>2.44</v>
       </c>
       <c r="R29">
         <v>1.18</v>
       </c>
       <c r="S29">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="T29">
         <v>1.11</v>
@@ -7732,13 +7732,13 @@
         <v>1.11</v>
       </c>
       <c r="V29">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W29">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X29">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y29">
         <v>1000</v>
@@ -7792,58 +7792,58 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AQ29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AR29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AS29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AT29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AU29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AV29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AW29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AX29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AY29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AZ29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BA29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BB29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BC29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BD29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BE29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BF29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
         <v>4.4</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K30">
         <v>3.3</v>
@@ -7950,7 +7950,7 @@
         <v>1.12</v>
       </c>
       <c r="N30">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O30">
         <v>1.52</v>
@@ -7959,7 +7959,7 @@
         <v>1.56</v>
       </c>
       <c r="Q30">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R30">
         <v>1.2</v>
@@ -7989,13 +7989,13 @@
         <v>34</v>
       </c>
       <c r="AA30">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB30">
         <v>7.2</v>
       </c>
       <c r="AC30">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD30">
         <v>20</v>
@@ -8004,16 +8004,16 @@
         <v>80</v>
       </c>
       <c r="AF30">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG30">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH30">
         <v>26</v>
       </c>
       <c r="AI30">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ30">
         <v>36</v>
@@ -8025,13 +8025,13 @@
         <v>70</v>
       </c>
       <c r="AM30">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO30">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AP30">
         <v>8</v>
@@ -8040,10 +8040,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR30">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS30">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AT30">
         <v>6.4</v>
@@ -8055,7 +8055,7 @@
         <v>15.5</v>
       </c>
       <c r="AW30">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
@@ -8064,28 +8064,28 @@
         <v>10</v>
       </c>
       <c r="AZ30">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BA30">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB30">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC30">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BD30">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BE30">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF30">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BG30">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BH30">
         <v>3.05</v>
@@ -8133,7 +8133,7 @@
         <v>46</v>
       </c>
       <c r="BW30">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BX30">
         <v>70</v>
@@ -8145,7 +8145,7 @@
         <v>55</v>
       </c>
       <c r="CA30">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CB30" t="s">
         <v>180</v>
@@ -8168,85 +8168,85 @@
         <v>177</v>
       </c>
       <c r="F31">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G31">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="H31">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I31">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J31">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K31">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M31">
         <v>1.11</v>
       </c>
       <c r="N31">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="O31">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="P31">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Q31">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R31">
         <v>1.22</v>
       </c>
       <c r="S31">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T31">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U31">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V31">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W31">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="X31">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y31">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z31">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA31">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AB31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD31">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE31">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG31">
         <v>11.5</v>
@@ -8255,31 +8255,31 @@
         <v>24</v>
       </c>
       <c r="AI31">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ31">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AL31">
         <v>60</v>
       </c>
       <c r="AM31">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AO31">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AP31">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ31">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AR31">
         <v>6.6</v>
@@ -8288,46 +8288,46 @@
         <v>7.8</v>
       </c>
       <c r="AT31">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU31">
         <v>6.6</v>
       </c>
       <c r="AV31">
-        <v>16.5</v>
+        <v>5.9</v>
       </c>
       <c r="AW31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX31">
+        <v>10</v>
+      </c>
+      <c r="AY31">
         <v>9.6</v>
-      </c>
-      <c r="AY31">
-        <v>9.199999999999999</v>
       </c>
       <c r="AZ31">
         <v>19.5</v>
       </c>
       <c r="BA31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB31">
         <v>21</v>
       </c>
       <c r="BC31">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD31">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE31">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF31">
         <v>19</v>
       </c>
       <c r="BG31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8422,7 +8422,7 @@
         <v>990</v>
       </c>
       <c r="J32">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K32">
         <v>950</v>
@@ -8434,13 +8434,13 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O32">
         <v>1.16</v>
       </c>
       <c r="P32">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q32">
         <v>1.16</v>
@@ -8652,22 +8652,22 @@
         <v>179</v>
       </c>
       <c r="F33">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G33">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H33">
         <v>4.1</v>
       </c>
       <c r="I33">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J33">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K33">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -8700,7 +8700,7 @@
         <v>1.86</v>
       </c>
       <c r="V33">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W33">
         <v>1.87</v>
@@ -8709,7 +8709,7 @@
         <v>12</v>
       </c>
       <c r="Y33">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z33">
         <v>38</v>
@@ -8718,13 +8718,13 @@
         <v>130</v>
       </c>
       <c r="AB33">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC33">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD33">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE33">
         <v>70</v>
@@ -8742,10 +8742,10 @@
         <v>95</v>
       </c>
       <c r="AJ33">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK33">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL33">
         <v>60</v>
@@ -8766,10 +8766,10 @@
         <v>10.5</v>
       </c>
       <c r="AR33">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AS33">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT33">
         <v>6.4</v>
@@ -8781,7 +8781,7 @@
         <v>15</v>
       </c>
       <c r="AW33">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AX33">
         <v>10</v>
@@ -8793,25 +8793,25 @@
         <v>18</v>
       </c>
       <c r="BA33">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB33">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BC33">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BD33">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BE33">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BF33">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BG33">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH33">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -556,7 +556,7 @@
     <t>Aguilas Doradas</t>
   </si>
   <si>
-    <t>2026-08-24 19:35:23</t>
+    <t>2026-08-24 21:52:52</t>
   </si>
 </sst>
 </file>
@@ -1150,226 +1150,226 @@
         <v>148</v>
       </c>
       <c r="F2">
-        <v>3.45</v>
+        <v>1.79</v>
       </c>
       <c r="G2">
+        <v>1.85</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
+      </c>
+      <c r="I2">
+        <v>6.4</v>
+      </c>
+      <c r="J2">
+        <v>3.35</v>
+      </c>
+      <c r="K2">
         <v>3.6</v>
       </c>
-      <c r="H2">
-        <v>2.42</v>
-      </c>
-      <c r="I2">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.4</v>
+      </c>
+      <c r="O2">
+        <v>1.28</v>
+      </c>
+      <c r="P2">
+        <v>1.73</v>
+      </c>
+      <c r="Q2">
+        <v>2.3</v>
+      </c>
+      <c r="R2">
+        <v>1.2</v>
+      </c>
+      <c r="S2">
+        <v>5.4</v>
+      </c>
+      <c r="T2">
+        <v>1.58</v>
+      </c>
+      <c r="U2">
         <v>2.5</v>
       </c>
-      <c r="J2">
-        <v>3.15</v>
-      </c>
-      <c r="K2">
-        <v>3.3</v>
-      </c>
-      <c r="L2">
-        <v>1.53</v>
-      </c>
-      <c r="M2">
-        <v>1.1</v>
-      </c>
-      <c r="N2">
-        <v>3.05</v>
-      </c>
-      <c r="O2">
-        <v>1.46</v>
-      </c>
-      <c r="P2">
-        <v>1.69</v>
-      </c>
-      <c r="Q2">
-        <v>2.38</v>
-      </c>
-      <c r="R2">
-        <v>1.25</v>
-      </c>
-      <c r="S2">
-        <v>4.7</v>
-      </c>
-      <c r="T2">
-        <v>1.99</v>
-      </c>
-      <c r="U2">
-        <v>1.94</v>
-      </c>
       <c r="V2">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="X2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AE2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF2">
-        <v>25</v>
+        <v>8.6</v>
       </c>
       <c r="AG2">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="AH2">
         <v>21</v>
       </c>
       <c r="AI2">
+        <v>80</v>
+      </c>
+      <c r="AJ2">
+        <v>34</v>
+      </c>
+      <c r="AK2">
+        <v>40</v>
+      </c>
+      <c r="AL2">
+        <v>95</v>
+      </c>
+      <c r="AM2">
+        <v>320</v>
+      </c>
+      <c r="AN2">
+        <v>90</v>
+      </c>
+      <c r="AO2">
+        <v>160</v>
+      </c>
+      <c r="AP2">
+        <v>15.5</v>
+      </c>
+      <c r="AQ2">
+        <v>15.5</v>
+      </c>
+      <c r="AR2">
+        <v>15.5</v>
+      </c>
+      <c r="AS2">
+        <v>15.5</v>
+      </c>
+      <c r="AT2">
+        <v>4.2</v>
+      </c>
+      <c r="AU2">
+        <v>4.3</v>
+      </c>
+      <c r="AV2">
+        <v>9</v>
+      </c>
+      <c r="AW2">
+        <v>34</v>
+      </c>
+      <c r="AX2">
+        <v>7.8</v>
+      </c>
+      <c r="AY2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>17.5</v>
+      </c>
+      <c r="BA2">
         <v>55</v>
       </c>
-      <c r="AJ2">
-        <v>75</v>
-      </c>
-      <c r="AK2">
-        <v>50</v>
-      </c>
-      <c r="AL2">
+      <c r="BB2">
+        <v>28</v>
+      </c>
+      <c r="BC2">
+        <v>32</v>
+      </c>
+      <c r="BD2">
         <v>70</v>
       </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
+      <c r="BE2">
+        <v>170</v>
+      </c>
+      <c r="BF2">
+        <v>60</v>
+      </c>
+      <c r="BG2">
         <v>65</v>
       </c>
-      <c r="AO2">
-        <v>29</v>
-      </c>
-      <c r="AP2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ2">
-        <v>7.8</v>
-      </c>
-      <c r="AR2">
-        <v>12.5</v>
-      </c>
-      <c r="AS2">
-        <v>26</v>
-      </c>
-      <c r="AT2">
-        <v>9.6</v>
-      </c>
-      <c r="AU2">
-        <v>6.4</v>
-      </c>
-      <c r="AV2">
-        <v>10</v>
-      </c>
-      <c r="AW2">
-        <v>24</v>
-      </c>
-      <c r="AX2">
-        <v>20</v>
-      </c>
-      <c r="AY2">
-        <v>13</v>
-      </c>
-      <c r="AZ2">
-        <v>18</v>
-      </c>
-      <c r="BA2">
-        <v>38</v>
-      </c>
-      <c r="BB2">
-        <v>46</v>
-      </c>
-      <c r="BC2">
-        <v>34</v>
-      </c>
-      <c r="BD2">
-        <v>46</v>
-      </c>
-      <c r="BE2">
-        <v>12.5</v>
-      </c>
-      <c r="BF2">
-        <v>44</v>
-      </c>
-      <c r="BG2">
-        <v>21</v>
-      </c>
       <c r="BH2">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.6</v>
+        <v>15.5</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="BK2">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BN2">
-        <v>6.8</v>
+        <v>1.07</v>
       </c>
       <c r="BO2">
-        <v>5.7</v>
+        <v>1.05</v>
       </c>
       <c r="BP2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="BR2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BT2">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="BV2">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BZ2">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="CB2" t="s">
         <v>180</v>
@@ -1392,226 +1392,226 @@
         <v>149</v>
       </c>
       <c r="F3">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="G3">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="H3">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="I3">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="K3">
+        <v>2.8</v>
+      </c>
+      <c r="L3">
+        <v>2.58</v>
+      </c>
+      <c r="M3">
+        <v>1.23</v>
+      </c>
+      <c r="N3">
+        <v>1.98</v>
+      </c>
+      <c r="O3">
+        <v>1.97</v>
+      </c>
+      <c r="P3">
+        <v>1.28</v>
+      </c>
+      <c r="Q3">
+        <v>4.4</v>
+      </c>
+      <c r="R3">
+        <v>1.09</v>
+      </c>
+      <c r="S3">
+        <v>11</v>
+      </c>
+      <c r="T3">
         <v>3</v>
       </c>
-      <c r="L3">
-        <v>1.64</v>
-      </c>
-      <c r="M3">
-        <v>1.14</v>
-      </c>
-      <c r="N3">
-        <v>2.62</v>
-      </c>
-      <c r="O3">
-        <v>1.6</v>
-      </c>
-      <c r="P3">
-        <v>1.51</v>
-      </c>
-      <c r="Q3">
-        <v>2.92</v>
-      </c>
-      <c r="R3">
-        <v>1.17</v>
-      </c>
-      <c r="S3">
-        <v>6.4</v>
-      </c>
-      <c r="T3">
-        <v>2.24</v>
-      </c>
       <c r="U3">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="X3">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Z3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA3">
+        <v>130</v>
+      </c>
+      <c r="AB3">
+        <v>5.8</v>
+      </c>
+      <c r="AC3">
+        <v>7.4</v>
+      </c>
+      <c r="AD3">
+        <v>22</v>
+      </c>
+      <c r="AE3">
+        <v>120</v>
+      </c>
+      <c r="AF3">
+        <v>14</v>
+      </c>
+      <c r="AG3">
+        <v>16.5</v>
+      </c>
+      <c r="AH3">
+        <v>42</v>
+      </c>
+      <c r="AI3">
+        <v>240</v>
+      </c>
+      <c r="AJ3">
+        <v>48</v>
+      </c>
+      <c r="AK3">
         <v>70</v>
       </c>
-      <c r="AB3">
-        <v>7.6</v>
-      </c>
-      <c r="AC3">
-        <v>7</v>
-      </c>
-      <c r="AD3">
-        <v>15.5</v>
-      </c>
-      <c r="AE3">
-        <v>60</v>
-      </c>
-      <c r="AF3">
-        <v>15.5</v>
-      </c>
-      <c r="AG3">
-        <v>13.5</v>
-      </c>
-      <c r="AH3">
-        <v>25</v>
-      </c>
-      <c r="AI3">
-        <v>90</v>
-      </c>
-      <c r="AJ3">
-        <v>46</v>
-      </c>
-      <c r="AK3">
-        <v>44</v>
-      </c>
       <c r="AL3">
+        <v>150</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
         <v>95</v>
       </c>
-      <c r="AM3">
-        <v>440</v>
-      </c>
-      <c r="AN3">
-        <v>55</v>
-      </c>
       <c r="AO3">
+        <v>240</v>
+      </c>
+      <c r="AP3">
+        <v>5.1</v>
+      </c>
+      <c r="AQ3">
+        <v>7.2</v>
+      </c>
+      <c r="AR3">
+        <v>21</v>
+      </c>
+      <c r="AS3">
         <v>80</v>
       </c>
-      <c r="AP3">
-        <v>7.4</v>
-      </c>
-      <c r="AQ3">
-        <v>8</v>
-      </c>
-      <c r="AR3">
-        <v>18</v>
-      </c>
-      <c r="AS3">
-        <v>50</v>
-      </c>
       <c r="AT3">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AW3">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AX3">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AY3">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ3">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BA3">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="BB3">
         <v>40</v>
       </c>
       <c r="BC3">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BD3">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="BE3">
-        <v>48</v>
+        <v>460</v>
       </c>
       <c r="BF3">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="BG3">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="BH3">
-        <v>2.76</v>
+        <v>1.58</v>
       </c>
       <c r="BI3">
-        <v>2.42</v>
+        <v>1.53</v>
       </c>
       <c r="BJ3">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="BK3">
-        <v>3.75</v>
+        <v>27</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="BN3">
         <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP3">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="BQ3">
-        <v>4.4</v>
+        <v>46</v>
       </c>
       <c r="BR3">
-        <v>65</v>
+        <v>910</v>
       </c>
       <c r="BS3">
-        <v>4.7</v>
+        <v>150</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BU3">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BV3">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="BW3">
-        <v>4.5</v>
+        <v>75</v>
       </c>
       <c r="BX3">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="BY3">
-        <v>4.8</v>
+        <v>190</v>
       </c>
       <c r="BZ3">
-        <v>70</v>
+        <v>960</v>
       </c>
       <c r="CA3">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="CB3" t="s">
         <v>180</v>
@@ -1634,226 +1634,226 @@
         <v>150</v>
       </c>
       <c r="F4">
-        <v>2.98</v>
+        <v>1.8</v>
       </c>
       <c r="G4">
-        <v>3.05</v>
+        <v>1.81</v>
       </c>
       <c r="H4">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
-        <v>2.94</v>
+        <v>5.8</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="P4">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="Q4">
-        <v>2.58</v>
+        <v>1.87</v>
       </c>
       <c r="R4">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="S4">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>1.45</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>2.96</v>
       </c>
       <c r="V4">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.48</v>
+        <v>2.24</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>7</v>
+      </c>
+      <c r="AC4">
+        <v>5.7</v>
+      </c>
+      <c r="AD4">
+        <v>11</v>
+      </c>
+      <c r="AE4">
+        <v>40</v>
+      </c>
+      <c r="AF4">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z4">
-        <v>18</v>
-      </c>
-      <c r="AA4">
-        <v>48</v>
-      </c>
-      <c r="AB4">
-        <v>9.6</v>
-      </c>
-      <c r="AC4">
-        <v>6.8</v>
-      </c>
-      <c r="AD4">
+      <c r="AG4">
+        <v>8</v>
+      </c>
+      <c r="AH4">
+        <v>13.5</v>
+      </c>
+      <c r="AI4">
+        <v>46</v>
+      </c>
+      <c r="AJ4">
+        <v>25</v>
+      </c>
+      <c r="AK4">
+        <v>23</v>
+      </c>
+      <c r="AL4">
+        <v>46</v>
+      </c>
+      <c r="AM4">
+        <v>130</v>
+      </c>
+      <c r="AN4">
+        <v>32</v>
+      </c>
+      <c r="AO4">
+        <v>70</v>
+      </c>
+      <c r="AP4">
         <v>13</v>
       </c>
-      <c r="AE4">
-        <v>42</v>
-      </c>
-      <c r="AF4">
-        <v>19</v>
-      </c>
-      <c r="AG4">
-        <v>14</v>
-      </c>
-      <c r="AH4">
+      <c r="AQ4">
+        <v>13</v>
+      </c>
+      <c r="AR4">
+        <v>13</v>
+      </c>
+      <c r="AS4">
+        <v>13</v>
+      </c>
+      <c r="AT4">
+        <v>6.4</v>
+      </c>
+      <c r="AU4">
+        <v>5.4</v>
+      </c>
+      <c r="AV4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW4">
+        <v>32</v>
+      </c>
+      <c r="AX4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY4">
+        <v>7.2</v>
+      </c>
+      <c r="AZ4">
+        <v>12</v>
+      </c>
+      <c r="BA4">
+        <v>36</v>
+      </c>
+      <c r="BB4">
         <v>21</v>
       </c>
-      <c r="AI4">
-        <v>65</v>
-      </c>
-      <c r="AJ4">
-        <v>55</v>
-      </c>
-      <c r="AK4">
-        <v>46</v>
-      </c>
-      <c r="AL4">
-        <v>85</v>
-      </c>
-      <c r="AM4">
-        <v>190</v>
-      </c>
-      <c r="AN4">
-        <v>60</v>
-      </c>
-      <c r="AO4">
-        <v>50</v>
-      </c>
-      <c r="AP4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ4">
-        <v>8</v>
-      </c>
-      <c r="AR4">
-        <v>15.5</v>
-      </c>
-      <c r="AS4">
-        <v>42</v>
-      </c>
-      <c r="AT4">
-        <v>8.6</v>
-      </c>
-      <c r="AU4">
-        <v>6.2</v>
-      </c>
-      <c r="AV4">
-        <v>12</v>
-      </c>
-      <c r="AW4">
+      <c r="BC4">
+        <v>20</v>
+      </c>
+      <c r="BD4">
         <v>36</v>
       </c>
-      <c r="AX4">
-        <v>16.5</v>
-      </c>
-      <c r="AY4">
-        <v>12</v>
-      </c>
-      <c r="AZ4">
-        <v>19</v>
-      </c>
-      <c r="BA4">
-        <v>55</v>
-      </c>
-      <c r="BB4">
-        <v>46</v>
-      </c>
-      <c r="BC4">
-        <v>34</v>
-      </c>
-      <c r="BD4">
-        <v>55</v>
-      </c>
       <c r="BE4">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="BF4">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="BG4">
         <v>40</v>
       </c>
       <c r="BH4">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.28</v>
+        <v>14.5</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="BK4">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BL4">
-        <v>210</v>
+        <v>290</v>
       </c>
       <c r="BM4">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BN4">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="BO4">
-        <v>5.2</v>
+        <v>1.64</v>
       </c>
       <c r="BP4">
-        <v>26</v>
+        <v>8.4</v>
       </c>
       <c r="BQ4">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR4">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="BS4">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="BT4">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BV4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BX4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY4">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="BZ4">
+        <v>70</v>
+      </c>
+      <c r="CA4">
         <v>48</v>
-      </c>
-      <c r="CA4">
-        <v>6</v>
       </c>
       <c r="CB4" t="s">
         <v>180</v>
@@ -1876,187 +1876,187 @@
         <v>151</v>
       </c>
       <c r="F5">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="G5">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="O5">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P5">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="Q5">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="R5">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="S5">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="T5">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U5">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="X5">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Y5">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="Z5">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AA5">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AB5">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE5">
         <v>150</v>
       </c>
       <c r="AF5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI5">
         <v>170</v>
       </c>
       <c r="AJ5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM5">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AN5">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO5">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT5">
         <v>7.6</v>
       </c>
       <c r="AU5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV5">
         <v>24</v>
       </c>
       <c r="AW5">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="AX5">
         <v>8</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA5">
         <v>46</v>
       </c>
       <c r="BB5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC5">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="BF5">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="BN5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BO5">
         <v>3.7</v>
@@ -2065,37 +2065,37 @@
         <v>8.6</v>
       </c>
       <c r="BQ5">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BR5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS5">
+        <v>12</v>
+      </c>
+      <c r="BT5">
+        <v>11</v>
+      </c>
+      <c r="BU5">
+        <v>6.6</v>
+      </c>
+      <c r="BV5">
+        <v>60</v>
+      </c>
+      <c r="BW5">
+        <v>12</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>13.5</v>
+      </c>
+      <c r="BZ5">
+        <v>15</v>
+      </c>
+      <c r="CA5">
         <v>7.8</v>
-      </c>
-      <c r="BT5">
-        <v>12</v>
-      </c>
-      <c r="BU5">
-        <v>6</v>
-      </c>
-      <c r="BV5">
-        <v>65</v>
-      </c>
-      <c r="BW5">
-        <v>10</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>10</v>
-      </c>
-      <c r="BZ5">
-        <v>13</v>
-      </c>
-      <c r="CA5">
-        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
         <v>180</v>
@@ -2118,16 +2118,16 @@
         <v>152</v>
       </c>
       <c r="F6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G6">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H6">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I6">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="J6">
         <v>3.5</v>
@@ -2136,10 +2136,10 @@
         <v>3.55</v>
       </c>
       <c r="L6">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
         <v>3.65</v>
@@ -2148,7 +2148,7 @@
         <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q6">
         <v>2.04</v>
@@ -2157,7 +2157,7 @@
         <v>1.35</v>
       </c>
       <c r="S6">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T6">
         <v>1.82</v>
@@ -2166,10 +2166,10 @@
         <v>2.14</v>
       </c>
       <c r="V6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W6">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X6">
         <v>14</v>
@@ -2178,16 +2178,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA6">
         <v>30</v>
       </c>
       <c r="AB6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
         <v>11</v>
@@ -2196,10 +2196,10 @@
         <v>25</v>
       </c>
       <c r="AF6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH6">
         <v>18</v>
@@ -2208,7 +2208,7 @@
         <v>40</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK6">
         <v>100</v>
@@ -2223,10 +2223,10 @@
         <v>46</v>
       </c>
       <c r="AO6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AP6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ6">
         <v>8.800000000000001</v>
@@ -2238,13 +2238,13 @@
         <v>22</v>
       </c>
       <c r="AT6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
         <v>7</v>
       </c>
       <c r="AV6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW6">
         <v>21</v>
@@ -2262,7 +2262,7 @@
         <v>32</v>
       </c>
       <c r="BB6">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BC6">
         <v>32</v>
@@ -2274,70 +2274,70 @@
         <v>55</v>
       </c>
       <c r="BF6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BG6">
         <v>16</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="s">
         <v>180</v>
@@ -2375,10 +2375,10 @@
         <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>1.1</v>
@@ -2390,7 +2390,7 @@
         <v>1.47</v>
       </c>
       <c r="P7">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q7">
         <v>2.4</v>
@@ -2408,7 +2408,7 @@
         <v>1.94</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
         <v>1.63</v>
@@ -2435,7 +2435,7 @@
         <v>14.5</v>
       </c>
       <c r="AE7">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AF7">
         <v>15.5</v>
@@ -2468,7 +2468,7 @@
         <v>60</v>
       </c>
       <c r="AP7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7">
         <v>9.199999999999999</v>
@@ -2477,7 +2477,7 @@
         <v>18</v>
       </c>
       <c r="AS7">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AT7">
         <v>7.6</v>
@@ -2492,7 +2492,7 @@
         <v>32</v>
       </c>
       <c r="AX7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY7">
         <v>11</v>
@@ -2501,10 +2501,10 @@
         <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BB7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC7">
         <v>25</v>
@@ -2516,49 +2516,49 @@
         <v>15.5</v>
       </c>
       <c r="BF7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG7">
         <v>36</v>
       </c>
       <c r="BH7">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI7">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7">
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL7">
         <v>180</v>
       </c>
       <c r="BM7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN7">
         <v>5.5</v>
       </c>
       <c r="BO7">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP7">
         <v>23</v>
       </c>
       <c r="BQ7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR7">
         <v>42</v>
       </c>
       <c r="BS7">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BT7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU7">
         <v>4.9</v>
@@ -2567,19 +2567,19 @@
         <v>32</v>
       </c>
       <c r="BW7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX7">
         <v>50</v>
       </c>
       <c r="BY7">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7">
         <v>44</v>
       </c>
       <c r="CA7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="s">
         <v>180</v>
@@ -2602,25 +2602,25 @@
         <v>154</v>
       </c>
       <c r="F8">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G8">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
         <v>4.6</v>
       </c>
       <c r="L8">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
         <v>1.06</v>
@@ -2635,7 +2635,7 @@
         <v>2.08</v>
       </c>
       <c r="Q8">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R8">
         <v>1.42</v>
@@ -2644,19 +2644,19 @@
         <v>3.15</v>
       </c>
       <c r="T8">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U8">
         <v>1.93</v>
       </c>
       <c r="V8">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W8">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y8">
         <v>23</v>
@@ -2677,25 +2677,25 @@
         <v>27</v>
       </c>
       <c r="AE8">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ8">
         <v>14.5</v>
       </c>
       <c r="AK8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL8">
         <v>38</v>
@@ -2704,7 +2704,7 @@
         <v>140</v>
       </c>
       <c r="AN8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO8">
         <v>150</v>
@@ -2713,37 +2713,37 @@
         <v>14.5</v>
       </c>
       <c r="AQ8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR8">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="AS8">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AT8">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU8">
+        <v>9</v>
+      </c>
+      <c r="AV8">
+        <v>23</v>
+      </c>
+      <c r="AW8">
+        <v>46</v>
+      </c>
+      <c r="AX8">
+        <v>8.4</v>
+      </c>
+      <c r="AY8">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV8">
-        <v>19.5</v>
-      </c>
-      <c r="AW8">
-        <v>10.5</v>
-      </c>
-      <c r="AX8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY8">
-        <v>9</v>
-      </c>
       <c r="AZ8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA8">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BB8">
         <v>12.5</v>
@@ -2752,16 +2752,16 @@
         <v>15</v>
       </c>
       <c r="BD8">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BE8">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BF8">
         <v>7.4</v>
       </c>
       <c r="BG8">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BH8">
         <v>3.7</v>
@@ -3098,7 +3098,7 @@
         <v>3.05</v>
       </c>
       <c r="J10">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K10">
         <v>3.8</v>
@@ -3242,10 +3242,10 @@
         <v>6.6</v>
       </c>
       <c r="BF10">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG10">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3328,19 +3328,19 @@
         <v>157</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G11">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H11">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J11">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
         <v>4.2</v>
@@ -3364,34 +3364,34 @@
         <v>1.67</v>
       </c>
       <c r="R11">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S11">
         <v>2.68</v>
       </c>
       <c r="T11">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U11">
         <v>2.36</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="X11">
         <v>21</v>
       </c>
       <c r="Y11">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z11">
         <v>34</v>
       </c>
       <c r="AA11">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB11">
         <v>12.5</v>
@@ -3421,7 +3421,7 @@
         <v>900</v>
       </c>
       <c r="AK11">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AL11">
         <v>80</v>
@@ -3433,67 +3433,67 @@
         <v>12.5</v>
       </c>
       <c r="AO11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP11">
         <v>15</v>
       </c>
       <c r="AQ11">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR11">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AS11">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AT11">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU11">
         <v>7.8</v>
       </c>
       <c r="AV11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW11">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX11">
         <v>12</v>
       </c>
       <c r="AY11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
         <v>13</v>
       </c>
       <c r="BA11">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BC11">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BD11">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BE11">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG11">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BH11">
         <v>4.1</v>
       </c>
       <c r="BI11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ11">
         <v>9.199999999999999</v>
@@ -3505,13 +3505,13 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO11">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP11">
         <v>14.5</v>
@@ -3529,7 +3529,7 @@
         <v>7.4</v>
       </c>
       <c r="BU11">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV11">
         <v>1000</v>
@@ -3541,7 +3541,7 @@
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3570,19 +3570,19 @@
         <v>158</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H12">
         <v>2.34</v>
       </c>
       <c r="I12">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K12">
         <v>3.9</v>
@@ -3594,7 +3594,7 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
         <v>1.27</v>
@@ -3621,7 +3621,7 @@
         <v>1.63</v>
       </c>
       <c r="W12">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X12">
         <v>16</v>
@@ -4054,10 +4054,10 @@
         <v>160</v>
       </c>
       <c r="F14">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G14">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H14">
         <v>4.1</v>
@@ -4084,13 +4084,13 @@
         <v>1.27</v>
       </c>
       <c r="P14">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q14">
         <v>1.83</v>
       </c>
       <c r="R14">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S14">
         <v>3.15</v>
@@ -4099,13 +4099,13 @@
         <v>1.76</v>
       </c>
       <c r="U14">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V14">
         <v>1.31</v>
       </c>
       <c r="W14">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X14">
         <v>17.5</v>
@@ -4132,13 +4132,13 @@
         <v>48</v>
       </c>
       <c r="AF14">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AG14">
         <v>10</v>
       </c>
       <c r="AH14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI14">
         <v>55</v>
@@ -4147,7 +4147,7 @@
         <v>22</v>
       </c>
       <c r="AK14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL14">
         <v>34</v>
@@ -4156,7 +4156,7 @@
         <v>90</v>
       </c>
       <c r="AN14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO14">
         <v>46</v>
@@ -4210,7 +4210,7 @@
         <v>46</v>
       </c>
       <c r="BF14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG14">
         <v>38</v>
@@ -4296,22 +4296,22 @@
         <v>161</v>
       </c>
       <c r="F15">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="G15">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="H15">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I15">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4320,109 +4320,109 @@
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O15">
         <v>1.21</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q15">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R15">
         <v>1.57</v>
       </c>
       <c r="S15">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T15">
         <v>1.65</v>
       </c>
       <c r="U15">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V15">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="X15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z15">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AA15">
         <v>110</v>
       </c>
       <c r="AB15">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE15">
         <v>60</v>
       </c>
       <c r="AF15">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG15">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH15">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AI15">
         <v>55</v>
       </c>
       <c r="AJ15">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK15">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM15">
-        <v>580</v>
+        <v>75</v>
       </c>
       <c r="AN15">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO15">
-        <v>46</v>
+        <v>260</v>
       </c>
       <c r="AP15">
         <v>19.5</v>
       </c>
       <c r="AQ15">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AR15">
         <v>32</v>
       </c>
       <c r="AS15">
+        <v>11</v>
+      </c>
+      <c r="AT15">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AT15">
-        <v>10.5</v>
       </c>
       <c r="AU15">
         <v>8.800000000000001</v>
       </c>
       <c r="AV15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AW15">
         <v>36</v>
@@ -4431,16 +4431,16 @@
         <v>10.5</v>
       </c>
       <c r="AY15">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15">
         <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB15">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC15">
         <v>13</v>
@@ -4449,13 +4449,13 @@
         <v>20</v>
       </c>
       <c r="BE15">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF15">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG15">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4538,13 +4538,13 @@
         <v>162</v>
       </c>
       <c r="F16">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I16">
         <v>2.52</v>
@@ -4568,28 +4568,28 @@
         <v>1.28</v>
       </c>
       <c r="P16">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q16">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R16">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T16">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
         <v>1.65</v>
       </c>
       <c r="W16">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X16">
         <v>17</v>
@@ -4601,10 +4601,10 @@
         <v>17</v>
       </c>
       <c r="AA16">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC16">
         <v>8.4</v>
@@ -4613,88 +4613,88 @@
         <v>11.5</v>
       </c>
       <c r="AE16">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AF16">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AG16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH16">
         <v>17</v>
       </c>
       <c r="AI16">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ16">
         <v>100</v>
       </c>
       <c r="AK16">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AL16">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AM16">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO16">
         <v>19</v>
       </c>
       <c r="AP16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ16">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR16">
         <v>14</v>
       </c>
       <c r="AS16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU16">
         <v>7.2</v>
       </c>
       <c r="AV16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW16">
         <v>21</v>
       </c>
       <c r="AX16">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AY16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD16">
         <v>32</v>
       </c>
       <c r="BE16">
-        <v>9.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BF16">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BG16">
         <v>16</v>
@@ -4789,10 +4789,10 @@
         <v>3.15</v>
       </c>
       <c r="I17">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J17">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K17">
         <v>3</v>
@@ -4807,7 +4807,7 @@
         <v>2.46</v>
       </c>
       <c r="O17">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P17">
         <v>1.49</v>
@@ -4828,22 +4828,22 @@
         <v>1.73</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
         <v>1.52</v>
       </c>
       <c r="X17">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA17">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB17">
         <v>8.199999999999999</v>
@@ -4876,7 +4876,7 @@
         <v>44</v>
       </c>
       <c r="AL17">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AM17">
         <v>500</v>
@@ -4897,19 +4897,19 @@
         <v>18</v>
       </c>
       <c r="AS17">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT17">
         <v>6.6</v>
       </c>
       <c r="AU17">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AV17">
         <v>13</v>
       </c>
       <c r="AW17">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX17">
         <v>13.5</v>
@@ -4921,25 +4921,25 @@
         <v>19.5</v>
       </c>
       <c r="BA17">
+        <v>7.2</v>
+      </c>
+      <c r="BB17">
+        <v>6.8</v>
+      </c>
+      <c r="BC17">
+        <v>6.6</v>
+      </c>
+      <c r="BD17">
+        <v>7.2</v>
+      </c>
+      <c r="BE17">
+        <v>7.6</v>
+      </c>
+      <c r="BF17">
         <v>7</v>
       </c>
-      <c r="BB17">
-        <v>6.4</v>
-      </c>
-      <c r="BC17">
-        <v>6.4</v>
-      </c>
-      <c r="BD17">
-        <v>6.8</v>
-      </c>
-      <c r="BE17">
+      <c r="BG17">
         <v>7.2</v>
-      </c>
-      <c r="BF17">
-        <v>6.6</v>
-      </c>
-      <c r="BG17">
-        <v>7</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5022,28 +5022,28 @@
         <v>164</v>
       </c>
       <c r="F18">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="G18">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="H18">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="I18">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="J18">
         <v>2.9</v>
       </c>
       <c r="K18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L18">
         <v>1.47</v>
       </c>
       <c r="M18">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N18">
         <v>2.58</v>
@@ -5058,7 +5058,7 @@
         <v>2.56</v>
       </c>
       <c r="R18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S18">
         <v>5.3</v>
@@ -5067,43 +5067,43 @@
         <v>2.08</v>
       </c>
       <c r="U18">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V18">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W18">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X18">
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA18">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC18">
         <v>7.4</v>
       </c>
       <c r="AD18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE18">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="AF18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG18">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH18">
         <v>24</v>
@@ -5115,10 +5115,10 @@
         <v>900</v>
       </c>
       <c r="AK18">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AL18">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AM18">
         <v>500</v>
@@ -5127,7 +5127,7 @@
         <v>500</v>
       </c>
       <c r="AO18">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AP18">
         <v>7.2</v>
@@ -5139,7 +5139,7 @@
         <v>13</v>
       </c>
       <c r="AS18">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18">
         <v>8</v>
@@ -5151,7 +5151,7 @@
         <v>11</v>
       </c>
       <c r="AW18">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX18">
         <v>18</v>
@@ -5163,25 +5163,25 @@
         <v>19</v>
       </c>
       <c r="BA18">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB18">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BC18">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BD18">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE18">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF18">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BG18">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5285,7 +5285,7 @@
         <v>1.43</v>
       </c>
       <c r="M19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N19">
         <v>2.3</v>
@@ -5306,10 +5306,10 @@
         <v>2.52</v>
       </c>
       <c r="T19">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U19">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V19">
         <v>1.16</v>
@@ -5330,7 +5330,7 @@
         <v>900</v>
       </c>
       <c r="AB19">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC19">
         <v>24</v>
@@ -5372,10 +5372,10 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>4.4</v>
+        <v>1.63</v>
       </c>
       <c r="AQ19">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="AR19">
         <v>1.78</v>
@@ -5387,19 +5387,19 @@
         <v>5.1</v>
       </c>
       <c r="AU19">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV19">
-        <v>1.76</v>
+        <v>11.5</v>
       </c>
       <c r="AW19">
         <v>1.8</v>
       </c>
       <c r="AX19">
-        <v>4.9</v>
+        <v>1.65</v>
       </c>
       <c r="AY19">
-        <v>1.69</v>
+        <v>7.8</v>
       </c>
       <c r="AZ19">
         <v>1.77</v>
@@ -5408,19 +5408,19 @@
         <v>1.8</v>
       </c>
       <c r="BB19">
-        <v>9</v>
+        <v>1.76</v>
       </c>
       <c r="BC19">
         <v>1.76</v>
       </c>
       <c r="BD19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BE19">
         <v>1.8</v>
       </c>
       <c r="BF19">
-        <v>4.7</v>
+        <v>1.75</v>
       </c>
       <c r="BG19">
         <v>1.81</v>
@@ -5515,40 +5515,40 @@
         <v>13</v>
       </c>
       <c r="I20">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J20">
         <v>4.5</v>
       </c>
       <c r="K20">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L20">
         <v>1.35</v>
       </c>
       <c r="M20">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N20">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="O20">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P20">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q20">
         <v>2.2</v>
       </c>
       <c r="R20">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S20">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T20">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U20">
         <v>1.48</v>
@@ -5563,7 +5563,7 @@
         <v>13</v>
       </c>
       <c r="Y20">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Z20">
         <v>540</v>
@@ -5578,10 +5578,10 @@
         <v>12.5</v>
       </c>
       <c r="AD20">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="AE20">
-        <v>520</v>
+        <v>490</v>
       </c>
       <c r="AF20">
         <v>6.8</v>
@@ -5605,7 +5605,7 @@
         <v>250</v>
       </c>
       <c r="AM20">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="AN20">
         <v>9.199999999999999</v>
@@ -5620,22 +5620,22 @@
         <v>11.5</v>
       </c>
       <c r="AR20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS20">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT20">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU20">
         <v>10</v>
       </c>
       <c r="AV20">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="AW20">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX20">
         <v>5.7</v>
@@ -5644,10 +5644,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA20">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB20">
         <v>8.800000000000001</v>
@@ -5656,16 +5656,16 @@
         <v>14</v>
       </c>
       <c r="BD20">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BE20">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF20">
         <v>6.6</v>
       </c>
       <c r="BG20">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5757,13 +5757,13 @@
         <v>1.3</v>
       </c>
       <c r="I21">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J21">
         <v>6.6</v>
       </c>
       <c r="K21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L21">
         <v>1.2</v>
@@ -5784,19 +5784,19 @@
         <v>1.34</v>
       </c>
       <c r="R21">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S21">
         <v>1.9</v>
       </c>
       <c r="T21">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V21">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="W21">
         <v>1.1</v>
@@ -5853,10 +5853,10 @@
         <v>100</v>
       </c>
       <c r="AO21">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AP21">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ21">
         <v>14</v>
@@ -5868,7 +5868,7 @@
         <v>11</v>
       </c>
       <c r="AT21">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU21">
         <v>14.5</v>
@@ -5880,10 +5880,10 @@
         <v>11.5</v>
       </c>
       <c r="AX21">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY21">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ21">
         <v>20</v>
@@ -5892,16 +5892,16 @@
         <v>13</v>
       </c>
       <c r="BB21">
+        <v>6.4</v>
+      </c>
+      <c r="BC21">
         <v>6.2</v>
-      </c>
-      <c r="BC21">
-        <v>6</v>
       </c>
       <c r="BD21">
         <v>6</v>
       </c>
       <c r="BE21">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF21">
         <v>14</v>
@@ -5949,13 +5949,13 @@
         <v>4.6</v>
       </c>
       <c r="BU21">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BV21">
         <v>7.4</v>
       </c>
       <c r="BW21">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BX21">
         <v>17</v>
@@ -5967,7 +5967,7 @@
         <v>7.6</v>
       </c>
       <c r="CA21">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB21" t="s">
         <v>180</v>
@@ -6026,7 +6026,7 @@
         <v>1.62</v>
       </c>
       <c r="R22">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="S22">
         <v>2.58</v>
@@ -6035,7 +6035,7 @@
         <v>1.64</v>
       </c>
       <c r="U22">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
         <v>1.25</v>
@@ -6047,7 +6047,7 @@
         <v>23</v>
       </c>
       <c r="Y22">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="Z22">
         <v>42</v>
@@ -6065,7 +6065,7 @@
         <v>19.5</v>
       </c>
       <c r="AE22">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AF22">
         <v>13.5</v>
@@ -6232,22 +6232,22 @@
         <v>169</v>
       </c>
       <c r="F23">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G23">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H23">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="I23">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J23">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="K23">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6268,7 +6268,7 @@
         <v>1.48</v>
       </c>
       <c r="R23">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S23">
         <v>2.16</v>
@@ -6280,34 +6280,34 @@
         <v>2.66</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X23">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y23">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z23">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA23">
         <v>75</v>
       </c>
       <c r="AB23">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AC23">
         <v>11.5</v>
       </c>
       <c r="AD23">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE23">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF23">
         <v>19.5</v>
@@ -6340,58 +6340,58 @@
         <v>26</v>
       </c>
       <c r="AP23">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ23">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AR23">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS23">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT23">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AU23">
         <v>5.6</v>
       </c>
       <c r="AV23">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AW23">
+        <v>5.9</v>
+      </c>
+      <c r="AX23">
         <v>5.2</v>
-      </c>
-      <c r="AX23">
-        <v>4.5</v>
       </c>
       <c r="AY23">
         <v>6.2</v>
       </c>
       <c r="AZ23">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BA23">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BB23">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC23">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD23">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE23">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF23">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BG23">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6474,7 +6474,7 @@
         <v>170</v>
       </c>
       <c r="F24">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -6501,19 +6501,19 @@
         <v>3.65</v>
       </c>
       <c r="O24">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P24">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q24">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R24">
         <v>1.34</v>
       </c>
       <c r="S24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T24">
         <v>1.81</v>
@@ -6534,7 +6534,7 @@
         <v>10.5</v>
       </c>
       <c r="Z24">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA24">
         <v>40</v>
@@ -6567,7 +6567,7 @@
         <v>48</v>
       </c>
       <c r="AK24">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL24">
         <v>46</v>
@@ -6630,7 +6630,7 @@
         <v>85</v>
       </c>
       <c r="BF24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG24">
         <v>25</v>
@@ -6716,115 +6716,115 @@
         <v>171</v>
       </c>
       <c r="F25">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="G25">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H25">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I25">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="J25">
         <v>4.1</v>
       </c>
       <c r="K25">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M25">
         <v>1.04</v>
       </c>
       <c r="N25">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O25">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P25">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q25">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R25">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S25">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T25">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U25">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W25">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X25">
         <v>26</v>
       </c>
       <c r="Y25">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z25">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA25">
         <v>75</v>
       </c>
       <c r="AB25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD25">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE25">
         <v>38</v>
       </c>
       <c r="AF25">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI25">
         <v>40</v>
       </c>
       <c r="AJ25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK25">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AL25">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM25">
         <v>60</v>
       </c>
       <c r="AN25">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO25">
         <v>26</v>
       </c>
       <c r="AP25">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ25">
         <v>19</v>
@@ -6833,109 +6833,109 @@
         <v>27</v>
       </c>
       <c r="AS25">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT25">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU25">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV25">
+        <v>15</v>
+      </c>
+      <c r="AW25">
+        <v>30</v>
+      </c>
+      <c r="AX25">
+        <v>13.5</v>
+      </c>
+      <c r="AY25">
+        <v>9.6</v>
+      </c>
+      <c r="AZ25">
         <v>14</v>
-      </c>
-      <c r="AW25">
-        <v>32</v>
-      </c>
-      <c r="AX25">
-        <v>14</v>
-      </c>
-      <c r="AY25">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ25">
-        <v>13.5</v>
       </c>
       <c r="BA25">
         <v>34</v>
       </c>
       <c r="BB25">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC25">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE25">
         <v>48</v>
       </c>
       <c r="BF25">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BG25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ25">
         <v>11.5</v>
       </c>
       <c r="BK25">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BN25">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BO25">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BP25">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ25">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BR25">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS25">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BT25">
         <v>10</v>
       </c>
       <c r="BU25">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV25">
         <v>34</v>
       </c>
       <c r="BW25">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY25">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BZ25">
         <v>20</v>
       </c>
       <c r="CA25">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="CB25" t="s">
         <v>180</v>
@@ -6958,16 +6958,16 @@
         <v>172</v>
       </c>
       <c r="F26">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G26">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J26">
         <v>5.3</v>
@@ -6982,28 +6982,28 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="O26">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P26">
         <v>3.75</v>
       </c>
       <c r="Q26">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S26">
         <v>1.86</v>
       </c>
       <c r="T26">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="U26">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="V26">
         <v>1.19</v>
@@ -7021,16 +7021,16 @@
         <v>70</v>
       </c>
       <c r="AA26">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AC26">
         <v>14</v>
       </c>
       <c r="AD26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE26">
         <v>60</v>
@@ -7045,22 +7045,22 @@
         <v>16.5</v>
       </c>
       <c r="AI26">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ26">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK26">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL26">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AM26">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AN26">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO26">
         <v>36</v>
@@ -7072,31 +7072,31 @@
         <v>38</v>
       </c>
       <c r="AR26">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS26">
         <v>44</v>
       </c>
       <c r="AT26">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU26">
         <v>13</v>
       </c>
       <c r="AV26">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW26">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX26">
         <v>14</v>
       </c>
       <c r="AY26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ26">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA26">
         <v>42</v>
@@ -7108,16 +7108,16 @@
         <v>12.5</v>
       </c>
       <c r="BD26">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE26">
         <v>40</v>
       </c>
       <c r="BF26">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BG26">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7209,7 +7209,7 @@
         <v>7.8</v>
       </c>
       <c r="I27">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J27">
         <v>6.6</v>
@@ -7236,7 +7236,7 @@
         <v>1.27</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S27">
         <v>1.57</v>
@@ -7248,7 +7248,7 @@
         <v>2.58</v>
       </c>
       <c r="V27">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W27">
         <v>3.75</v>
@@ -7260,7 +7260,7 @@
         <v>55</v>
       </c>
       <c r="Z27">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AA27">
         <v>230</v>
@@ -7281,13 +7281,13 @@
         <v>16.5</v>
       </c>
       <c r="AG27">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH27">
         <v>22</v>
       </c>
       <c r="AI27">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ27">
         <v>16</v>
@@ -7296,28 +7296,28 @@
         <v>17</v>
       </c>
       <c r="AL27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM27">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN27">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AO27">
         <v>48</v>
       </c>
       <c r="AP27">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ27">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AR27">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS27">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT27">
         <v>16</v>
@@ -7329,7 +7329,7 @@
         <v>16</v>
       </c>
       <c r="AW27">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AX27">
         <v>13</v>
@@ -7341,7 +7341,7 @@
         <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB27">
         <v>13</v>
@@ -7353,13 +7353,13 @@
         <v>18.5</v>
       </c>
       <c r="BE27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF27">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BG27">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7454,7 +7454,7 @@
         <v>4.3</v>
       </c>
       <c r="J28">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="K28">
         <v>3.1</v>
@@ -7463,10 +7463,10 @@
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N28">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="O28">
         <v>1.48</v>
@@ -7484,10 +7484,10 @@
         <v>2.8</v>
       </c>
       <c r="T28">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U28">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="V28">
         <v>1.31</v>
@@ -7499,7 +7499,7 @@
         <v>1000</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z28">
         <v>1000</v>
@@ -7511,7 +7511,7 @@
         <v>1000</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD28">
         <v>1000</v>
@@ -7520,10 +7520,10 @@
         <v>1000</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH28">
         <v>1000</v>
@@ -7550,58 +7550,58 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS28">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU28">
-        <v>1.65</v>
+        <v>4.2</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AW28">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="AX28">
-        <v>1.87</v>
+        <v>7.2</v>
       </c>
       <c r="AY28">
         <v>1.83</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BA28">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="BB28">
         <v>1.94</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7684,22 +7684,22 @@
         <v>175</v>
       </c>
       <c r="F29">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="G29">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H29">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I29">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J29">
         <v>2.72</v>
       </c>
       <c r="K29">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L29">
         <v>1.45</v>
@@ -7717,7 +7717,7 @@
         <v>1.43</v>
       </c>
       <c r="Q29">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R29">
         <v>1.18</v>
@@ -7732,10 +7732,10 @@
         <v>1.11</v>
       </c>
       <c r="V29">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W29">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X29">
         <v>12</v>
@@ -7926,10 +7926,10 @@
         <v>176</v>
       </c>
       <c r="F30">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G30">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="H30">
         <v>3.9</v>
@@ -7941,7 +7941,7 @@
         <v>3.05</v>
       </c>
       <c r="K30">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L30">
         <v>1.49</v>
@@ -7959,13 +7959,13 @@
         <v>1.56</v>
       </c>
       <c r="Q30">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R30">
         <v>1.2</v>
       </c>
       <c r="S30">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="T30">
         <v>2.08</v>
@@ -7974,10 +7974,10 @@
         <v>1.79</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W30">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -7989,16 +7989,16 @@
         <v>34</v>
       </c>
       <c r="AA30">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB30">
+        <v>7.4</v>
+      </c>
+      <c r="AC30">
         <v>7.2</v>
       </c>
-      <c r="AC30">
-        <v>7.4</v>
-      </c>
       <c r="AD30">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE30">
         <v>80</v>
@@ -8013,13 +8013,13 @@
         <v>26</v>
       </c>
       <c r="AI30">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ30">
         <v>36</v>
       </c>
       <c r="AK30">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AL30">
         <v>70</v>
@@ -8040,10 +8040,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR30">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AS30">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT30">
         <v>6.4</v>
@@ -8064,28 +8064,28 @@
         <v>10</v>
       </c>
       <c r="AZ30">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA30">
+        <v>11</v>
+      </c>
+      <c r="BB30">
+        <v>13</v>
+      </c>
+      <c r="BC30">
+        <v>14.5</v>
+      </c>
+      <c r="BD30">
         <v>10.5</v>
       </c>
-      <c r="BB30">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC30">
-        <v>8.6</v>
-      </c>
-      <c r="BD30">
-        <v>10</v>
-      </c>
       <c r="BE30">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF30">
         <v>18.5</v>
       </c>
       <c r="BG30">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH30">
         <v>3.05</v>
@@ -8121,7 +8121,7 @@
         <v>48</v>
       </c>
       <c r="BS30">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BT30">
         <v>8.199999999999999</v>
@@ -8130,7 +8130,7 @@
         <v>5.6</v>
       </c>
       <c r="BV30">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW30">
         <v>5.8</v>
@@ -8145,7 +8145,7 @@
         <v>55</v>
       </c>
       <c r="CA30">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB30" t="s">
         <v>180</v>
@@ -8168,16 +8168,16 @@
         <v>177</v>
       </c>
       <c r="F31">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G31">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I31">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J31">
         <v>3.2</v>
@@ -8192,16 +8192,16 @@
         <v>1.11</v>
       </c>
       <c r="N31">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="O31">
         <v>1.49</v>
       </c>
       <c r="P31">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Q31">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="R31">
         <v>1.22</v>
@@ -8213,13 +8213,13 @@
         <v>2.08</v>
       </c>
       <c r="U31">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V31">
         <v>1.29</v>
       </c>
       <c r="W31">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X31">
         <v>11</v>
@@ -8228,10 +8228,10 @@
         <v>12.5</v>
       </c>
       <c r="Z31">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AA31">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB31">
         <v>7.6</v>
@@ -8240,13 +8240,13 @@
         <v>7.8</v>
       </c>
       <c r="AD31">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE31">
         <v>75</v>
       </c>
       <c r="AF31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG31">
         <v>11.5</v>
@@ -8255,7 +8255,7 @@
         <v>24</v>
       </c>
       <c r="AI31">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AJ31">
         <v>32</v>
@@ -8267,13 +8267,13 @@
         <v>60</v>
       </c>
       <c r="AM31">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN31">
         <v>29</v>
       </c>
       <c r="AO31">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AP31">
         <v>8.6</v>
@@ -8282,10 +8282,10 @@
         <v>9.6</v>
       </c>
       <c r="AR31">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="AS31">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT31">
         <v>6.4</v>
@@ -8294,10 +8294,10 @@
         <v>6.6</v>
       </c>
       <c r="AV31">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AW31">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="AX31">
         <v>10</v>
@@ -8309,85 +8309,85 @@
         <v>19.5</v>
       </c>
       <c r="BA31">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BB31">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC31">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BD31">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BE31">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF31">
         <v>19</v>
       </c>
       <c r="BG31">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI31">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK31">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO31">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ31">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS31">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU31">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW31">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA31">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB31" t="s">
         <v>180</v>
@@ -8410,22 +8410,22 @@
         <v>178</v>
       </c>
       <c r="F32">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="G32">
-        <v>990</v>
+        <v>2.44</v>
       </c>
       <c r="H32">
-        <v>1.75</v>
+        <v>2.96</v>
       </c>
       <c r="I32">
-        <v>990</v>
+        <v>3.3</v>
       </c>
       <c r="J32">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="K32">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8434,142 +8434,142 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.31</v>
+        <v>4.3</v>
       </c>
       <c r="O32">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P32">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q32">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="R32">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="S32">
-        <v>1.16</v>
+        <v>2.48</v>
       </c>
       <c r="T32">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="U32">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V32">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y32">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z32">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA32">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB32">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC32">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD32">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE32">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF32">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG32">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH32">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI32">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ32">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK32">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL32">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM32">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN32">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO32">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP32">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ32">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS32">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT32">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU32">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AV32">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW32">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX32">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY32">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AZ32">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA32">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB32">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC32">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD32">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE32">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG32">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8655,16 +8655,16 @@
         <v>2.02</v>
       </c>
       <c r="G33">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H33">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I33">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J33">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K33">
         <v>3.5</v>
@@ -8676,7 +8676,7 @@
         <v>1.1</v>
       </c>
       <c r="N33">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O33">
         <v>1.45</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -517,7 +517,7 @@
     <t>Aguilas Doradas</t>
   </si>
   <si>
-    <t>2026-08-25 00:09:27</t>
+    <t>2026-08-25 02:26:08</t>
   </si>
 </sst>
 </file>
@@ -1114,10 +1114,10 @@
         <v>3.4</v>
       </c>
       <c r="G2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H2">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I2">
         <v>2.36</v>
@@ -1126,67 +1126,67 @@
         <v>3.5</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U2">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
         <v>1.73</v>
       </c>
       <c r="W2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z2">
         <v>14.5</v>
       </c>
       <c r="AA2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF2">
         <v>24</v>
@@ -1204,34 +1204,34 @@
         <v>65</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
         <v>8.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU2">
         <v>7</v>
@@ -1240,10 +1240,10 @@
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY2">
         <v>13</v>
@@ -1252,85 +1252,85 @@
         <v>16</v>
       </c>
       <c r="BA2">
+        <v>32</v>
+      </c>
+      <c r="BB2">
+        <v>42</v>
+      </c>
+      <c r="BC2">
         <v>34</v>
       </c>
-      <c r="BB2">
-        <v>32</v>
-      </c>
-      <c r="BC2">
-        <v>32</v>
-      </c>
       <c r="BD2">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BF2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BG2">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BI2">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BJ2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL2">
         <v>130</v>
       </c>
       <c r="BM2">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="BN2">
         <v>6.6</v>
       </c>
       <c r="BO2">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BP2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT2">
         <v>5.1</v>
       </c>
       <c r="BU2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX2">
         <v>32</v>
       </c>
       <c r="BY2">
+        <v>12.5</v>
+      </c>
+      <c r="BZ2">
+        <v>29</v>
+      </c>
+      <c r="CA2">
         <v>12</v>
-      </c>
-      <c r="BZ2">
-        <v>28</v>
-      </c>
-      <c r="CA2">
-        <v>11.5</v>
       </c>
       <c r="CB2" t="s">
         <v>167</v>
@@ -1353,16 +1353,16 @@
         <v>140</v>
       </c>
       <c r="F3">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G3">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J3">
         <v>3.25</v>
@@ -1371,34 +1371,34 @@
         <v>3.35</v>
       </c>
       <c r="L3">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="U3">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="V3">
         <v>1.42</v>
@@ -1407,19 +1407,19 @@
         <v>1.64</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y3">
         <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA3">
         <v>65</v>
       </c>
       <c r="AB3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
@@ -1431,7 +1431,7 @@
         <v>46</v>
       </c>
       <c r="AF3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG3">
         <v>12</v>
@@ -1443,49 +1443,49 @@
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO3">
         <v>55</v>
       </c>
       <c r="AP3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3">
         <v>18</v>
       </c>
       <c r="AS3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
+        <v>12.5</v>
+      </c>
+      <c r="AW3">
+        <v>34</v>
+      </c>
+      <c r="AX3">
         <v>13</v>
-      </c>
-      <c r="AW3">
-        <v>32</v>
-      </c>
-      <c r="AX3">
-        <v>13.5</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
@@ -1500,79 +1500,79 @@
         <v>32</v>
       </c>
       <c r="BC3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD3">
+        <v>44</v>
+      </c>
+      <c r="BE3">
+        <v>100</v>
+      </c>
+      <c r="BF3">
+        <v>26</v>
+      </c>
+      <c r="BG3">
+        <v>36</v>
+      </c>
+      <c r="BH3">
+        <v>2.88</v>
+      </c>
+      <c r="BI3">
+        <v>2.76</v>
+      </c>
+      <c r="BJ3">
+        <v>11</v>
+      </c>
+      <c r="BK3">
+        <v>9.4</v>
+      </c>
+      <c r="BL3">
+        <v>170</v>
+      </c>
+      <c r="BM3">
+        <v>130</v>
+      </c>
+      <c r="BN3">
+        <v>5.1</v>
+      </c>
+      <c r="BO3">
+        <v>4.7</v>
+      </c>
+      <c r="BP3">
+        <v>21</v>
+      </c>
+      <c r="BQ3">
+        <v>10</v>
+      </c>
+      <c r="BR3">
         <v>40</v>
       </c>
-      <c r="BE3">
-        <v>14</v>
-      </c>
-      <c r="BF3">
-        <v>28</v>
-      </c>
-      <c r="BG3">
-        <v>38</v>
-      </c>
-      <c r="BH3">
-        <v>2.96</v>
-      </c>
-      <c r="BI3">
-        <v>2.64</v>
-      </c>
-      <c r="BJ3">
-        <v>11.5</v>
-      </c>
-      <c r="BK3">
-        <v>5.6</v>
-      </c>
-      <c r="BL3">
-        <v>180</v>
-      </c>
-      <c r="BM3">
-        <v>10.5</v>
-      </c>
-      <c r="BN3">
-        <v>5.5</v>
-      </c>
-      <c r="BO3">
-        <v>4.5</v>
-      </c>
-      <c r="BP3">
-        <v>22</v>
-      </c>
-      <c r="BQ3">
-        <v>7.4</v>
-      </c>
-      <c r="BR3">
-        <v>44</v>
-      </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU3">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV3">
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BX3">
         <v>50</v>
       </c>
       <c r="BY3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CA3">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="CB3" t="s">
         <v>167</v>
@@ -1595,70 +1595,70 @@
         <v>141</v>
       </c>
       <c r="F4">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="G4">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K4">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L4">
         <v>1.4</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q4">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T4">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="V4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W4">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="X4">
         <v>18</v>
       </c>
       <c r="Y4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z4">
         <v>70</v>
       </c>
       <c r="AA4">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AB4">
         <v>8.6</v>
@@ -1667,19 +1667,19 @@
         <v>10.5</v>
       </c>
       <c r="AD4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE4">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AF4">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AG4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI4">
         <v>110</v>
@@ -1691,19 +1691,19 @@
         <v>16</v>
       </c>
       <c r="AL4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN4">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AO4">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AP4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
         <v>22</v>
@@ -1712,109 +1712,109 @@
         <v>50</v>
       </c>
       <c r="AS4">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AT4">
         <v>7.8</v>
       </c>
       <c r="AU4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW4">
+        <v>85</v>
+      </c>
+      <c r="AX4">
+        <v>7.8</v>
+      </c>
+      <c r="AY4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4">
+        <v>22</v>
+      </c>
+      <c r="BA4">
         <v>46</v>
       </c>
-      <c r="AX4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY4">
-        <v>8.6</v>
-      </c>
-      <c r="AZ4">
-        <v>20</v>
-      </c>
-      <c r="BA4">
-        <v>15.5</v>
-      </c>
       <c r="BB4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD4">
         <v>30</v>
       </c>
       <c r="BE4">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="BF4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG4">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="BH4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK4">
         <v>9.800000000000001</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM4">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="BN4">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP4">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ4">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4">
         <v>26</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BV4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BW4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BY4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BZ4">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA4">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="s">
         <v>167</v>
@@ -1843,7 +1843,7 @@
         <v>1.76</v>
       </c>
       <c r="H5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
         <v>6.4</v>
@@ -1852,7 +1852,7 @@
         <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.37</v>
@@ -1864,7 +1864,7 @@
         <v>3.85</v>
       </c>
       <c r="O5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P5">
         <v>1.98</v>
@@ -1900,7 +1900,7 @@
         <v>100</v>
       </c>
       <c r="AA5">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB5">
         <v>9.199999999999999</v>
@@ -1942,19 +1942,19 @@
         <v>10.5</v>
       </c>
       <c r="AO5">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ5">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR5">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT5">
         <v>5.1</v>
@@ -1978,28 +1978,28 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB5">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC5">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD5">
         <v>7.4</v>
       </c>
       <c r="BE5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG5">
         <v>8.6</v>
       </c>
       <c r="BH5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI5">
         <v>2.96</v>
@@ -2014,7 +2014,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
         <v>4.4</v>
@@ -2032,7 +2032,7 @@
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT5">
         <v>9.6</v>
@@ -2041,22 +2041,22 @@
         <v>7.2</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ5">
         <v>21</v>
       </c>
       <c r="CA5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="s">
         <v>167</v>
@@ -2079,13 +2079,13 @@
         <v>143</v>
       </c>
       <c r="F6">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I6">
         <v>3.9</v>
@@ -2097,7 +2097,7 @@
         <v>4.3</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M6">
         <v>1.05</v>
@@ -2112,25 +2112,25 @@
         <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S6">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T6">
         <v>1.61</v>
       </c>
       <c r="U6">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V6">
         <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X6">
         <v>21</v>
@@ -2139,10 +2139,10 @@
         <v>18</v>
       </c>
       <c r="Z6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA6">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AB6">
         <v>12.5</v>
@@ -2154,7 +2154,7 @@
         <v>16</v>
       </c>
       <c r="AE6">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF6">
         <v>15.5</v>
@@ -2163,31 +2163,31 @@
         <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI6">
+        <v>110</v>
+      </c>
+      <c r="AJ6">
+        <v>30</v>
+      </c>
+      <c r="AK6">
+        <v>32</v>
+      </c>
+      <c r="AL6">
+        <v>46</v>
+      </c>
+      <c r="AM6">
         <v>500</v>
       </c>
-      <c r="AJ6">
-        <v>900</v>
-      </c>
-      <c r="AK6">
-        <v>42</v>
-      </c>
-      <c r="AL6">
-        <v>80</v>
-      </c>
-      <c r="AM6">
-        <v>580</v>
-      </c>
       <c r="AN6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AP6">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6">
         <v>14.5</v>
@@ -2196,19 +2196,19 @@
         <v>23</v>
       </c>
       <c r="AS6">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT6">
         <v>10</v>
       </c>
       <c r="AU6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV6">
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AX6">
         <v>12</v>
@@ -2217,7 +2217,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
         <v>34</v>
@@ -2229,16 +2229,16 @@
         <v>17.5</v>
       </c>
       <c r="BD6">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BE6">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="BF6">
         <v>10</v>
       </c>
       <c r="BG6">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BH6">
         <v>4.1</v>
@@ -2271,7 +2271,7 @@
         <v>6.4</v>
       </c>
       <c r="BR6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
         <v>8</v>
@@ -2280,7 +2280,7 @@
         <v>7.4</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2321,100 +2321,100 @@
         <v>144</v>
       </c>
       <c r="F7">
+        <v>2.3</v>
+      </c>
+      <c r="G7">
         <v>2.68</v>
       </c>
-      <c r="G7">
+      <c r="H7">
+        <v>2.92</v>
+      </c>
+      <c r="I7">
+        <v>3.55</v>
+      </c>
+      <c r="J7">
         <v>3.15</v>
       </c>
-      <c r="H7">
-        <v>2.6</v>
-      </c>
-      <c r="I7">
-        <v>3.05</v>
-      </c>
-      <c r="J7">
-        <v>3.1</v>
-      </c>
       <c r="K7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q7">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="T7">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="U7">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="X7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z7">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AA7">
         <v>220</v>
       </c>
       <c r="AB7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE7">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AF7">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AG7">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
         <v>19</v>
       </c>
       <c r="AI7">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AJ7">
         <v>120</v>
       </c>
       <c r="AK7">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AL7">
         <v>290</v>
@@ -2423,124 +2423,124 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AO7">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AP7">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="AS7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT7">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AU7">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX7">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="AY7">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BA7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB7">
         <v>6.2</v>
       </c>
       <c r="BC7">
+        <v>21</v>
+      </c>
+      <c r="BD7">
+        <v>6.4</v>
+      </c>
+      <c r="BE7">
+        <v>7</v>
+      </c>
+      <c r="BF7">
+        <v>5.8</v>
+      </c>
+      <c r="BG7">
+        <v>6.4</v>
+      </c>
+      <c r="BH7">
+        <v>3.5</v>
+      </c>
+      <c r="BI7">
+        <v>2.74</v>
+      </c>
+      <c r="BJ7">
+        <v>10.5</v>
+      </c>
+      <c r="BK7">
+        <v>4.6</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>7.8</v>
+      </c>
+      <c r="BN7">
+        <v>5.7</v>
+      </c>
+      <c r="BO7">
+        <v>4.3</v>
+      </c>
+      <c r="BP7">
+        <v>20</v>
+      </c>
+      <c r="BQ7">
         <v>5.9</v>
       </c>
-      <c r="BD7">
-        <v>6.2</v>
-      </c>
-      <c r="BE7">
+      <c r="BR7">
+        <v>36</v>
+      </c>
+      <c r="BS7">
+        <v>6.8</v>
+      </c>
+      <c r="BT7">
+        <v>6.8</v>
+      </c>
+      <c r="BU7">
+        <v>5.3</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>6.4</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>7</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
         <v>6.6</v>
-      </c>
-      <c r="BF7">
-        <v>6.8</v>
-      </c>
-      <c r="BG7">
-        <v>6.8</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>1.04</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.04</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
-      <c r="BO7">
-        <v>1.04</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>1.04</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>1.04</v>
-      </c>
-      <c r="BT7">
-        <v>1000</v>
-      </c>
-      <c r="BU7">
-        <v>1.04</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>1.04</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
-      <c r="BY7">
-        <v>1.04</v>
-      </c>
-      <c r="BZ7">
-        <v>1000</v>
-      </c>
-      <c r="CA7">
-        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>167</v>
@@ -2563,88 +2563,88 @@
         <v>145</v>
       </c>
       <c r="F8">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="G8">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="H8">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="I8">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="J8">
         <v>3.45</v>
       </c>
       <c r="K8">
+        <v>3.7</v>
+      </c>
+      <c r="L8">
+        <v>1.33</v>
+      </c>
+      <c r="M8">
+        <v>1.06</v>
+      </c>
+      <c r="N8">
         <v>3.85</v>
       </c>
-      <c r="L8">
-        <v>1.12</v>
-      </c>
-      <c r="M8">
-        <v>1.04</v>
-      </c>
-      <c r="N8">
-        <v>3.7</v>
-      </c>
       <c r="O8">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P8">
         <v>2</v>
       </c>
       <c r="Q8">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R8">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T8">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U8">
         <v>2.18</v>
       </c>
       <c r="V8">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="W8">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="X8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AA8">
         <v>80</v>
       </c>
       <c r="AB8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC8">
         <v>8.6</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
         <v>60</v>
       </c>
       <c r="AF8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH8">
         <v>17.5</v>
@@ -2653,13 +2653,13 @@
         <v>95</v>
       </c>
       <c r="AJ8">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AK8">
         <v>95</v>
       </c>
       <c r="AL8">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AM8">
         <v>500</v>
@@ -2668,22 +2668,22 @@
         <v>46</v>
       </c>
       <c r="AO8">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AP8">
         <v>13</v>
       </c>
       <c r="AQ8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR8">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS8">
-        <v>16</v>
+        <v>7.2</v>
       </c>
       <c r="AT8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU8">
         <v>7</v>
@@ -2692,19 +2692,19 @@
         <v>10</v>
       </c>
       <c r="AW8">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AY8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB8">
         <v>7.6</v>
@@ -2719,70 +2719,70 @@
         <v>8</v>
       </c>
       <c r="BF8">
+        <v>6.8</v>
+      </c>
+      <c r="BG8">
+        <v>17.5</v>
+      </c>
+      <c r="BH8">
+        <v>3.7</v>
+      </c>
+      <c r="BI8">
+        <v>2.92</v>
+      </c>
+      <c r="BJ8">
+        <v>9.6</v>
+      </c>
+      <c r="BK8">
+        <v>4.9</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN8">
+        <v>6.4</v>
+      </c>
+      <c r="BO8">
+        <v>4.9</v>
+      </c>
+      <c r="BP8">
+        <v>23</v>
+      </c>
+      <c r="BQ8">
         <v>7</v>
       </c>
-      <c r="BG8">
-        <v>14.5</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.04</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.04</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>1.04</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>1.04</v>
-      </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="s">
         <v>167</v>
@@ -2808,10 +2808,10 @@
         <v>1.83</v>
       </c>
       <c r="G9">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I9">
         <v>4.9</v>
@@ -2820,22 +2820,22 @@
         <v>3.8</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L9">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M9">
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P9">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Q9">
         <v>1.89</v>
@@ -2844,16 +2844,16 @@
         <v>1.39</v>
       </c>
       <c r="S9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T9">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U9">
         <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W9">
         <v>2.06</v>
@@ -2865,19 +2865,19 @@
         <v>20</v>
       </c>
       <c r="Z9">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AA9">
         <v>900</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>10.5</v>
       </c>
       <c r="AD9">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE9">
         <v>150</v>
@@ -2892,16 +2892,16 @@
         <v>21</v>
       </c>
       <c r="AI9">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AJ9">
+        <v>24</v>
+      </c>
+      <c r="AK9">
         <v>22</v>
       </c>
-      <c r="AK9">
-        <v>21</v>
-      </c>
       <c r="AL9">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM9">
         <v>580</v>
@@ -2913,28 +2913,28 @@
         <v>500</v>
       </c>
       <c r="AP9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR9">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="AS9">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AT9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV9">
         <v>16</v>
       </c>
       <c r="AW9">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2946,85 +2946,85 @@
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="BB9">
         <v>17.5</v>
       </c>
       <c r="BC9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD9">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="BE9">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BG9">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="s">
         <v>167</v>
@@ -3047,13 +3047,13 @@
         <v>147</v>
       </c>
       <c r="F10">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>4.2</v>
@@ -3065,34 +3065,34 @@
         <v>4.1</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M10">
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O10">
         <v>1.27</v>
       </c>
       <c r="P10">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q10">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R10">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S10">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T10">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V10">
         <v>1.31</v>
@@ -3104,13 +3104,13 @@
         <v>17.5</v>
       </c>
       <c r="Y10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z10">
         <v>32</v>
       </c>
       <c r="AA10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AB10">
         <v>10.5</v>
@@ -3119,13 +3119,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AE10">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF10">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -3140,43 +3140,43 @@
         <v>22</v>
       </c>
       <c r="AK10">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AL10">
         <v>34</v>
       </c>
       <c r="AM10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO10">
         <v>46</v>
       </c>
       <c r="AP10">
+        <v>16.5</v>
+      </c>
+      <c r="AQ10">
         <v>15.5</v>
       </c>
-      <c r="AQ10">
+      <c r="AR10">
+        <v>27</v>
+      </c>
+      <c r="AS10">
+        <v>65</v>
+      </c>
+      <c r="AT10">
+        <v>9.6</v>
+      </c>
+      <c r="AU10">
+        <v>8.4</v>
+      </c>
+      <c r="AV10">
         <v>15</v>
       </c>
-      <c r="AR10">
-        <v>25</v>
-      </c>
-      <c r="AS10">
-        <v>34</v>
-      </c>
-      <c r="AT10">
-        <v>9.4</v>
-      </c>
-      <c r="AU10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV10">
-        <v>14.5</v>
-      </c>
       <c r="AW10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX10">
         <v>11.5</v>
@@ -3188,85 +3188,85 @@
         <v>16</v>
       </c>
       <c r="BA10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB10">
         <v>20</v>
       </c>
       <c r="BC10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE10">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="BF10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="CB10" t="s">
         <v>167</v>
@@ -3289,220 +3289,220 @@
         <v>148</v>
       </c>
       <c r="F11">
+        <v>1.74</v>
+      </c>
+      <c r="G11">
         <v>1.76</v>
       </c>
-      <c r="G11">
-        <v>1.78</v>
-      </c>
       <c r="H11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I11">
         <v>4.9</v>
       </c>
       <c r="J11">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O11">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
+        <v>2.66</v>
+      </c>
+      <c r="Q11">
+        <v>1.59</v>
+      </c>
+      <c r="R11">
+        <v>1.63</v>
+      </c>
+      <c r="S11">
         <v>2.44</v>
       </c>
-      <c r="Q11">
-        <v>1.62</v>
-      </c>
-      <c r="R11">
-        <v>1.57</v>
-      </c>
-      <c r="S11">
-        <v>2.58</v>
-      </c>
       <c r="T11">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U11">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V11">
         <v>1.25</v>
       </c>
       <c r="W11">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA11">
         <v>110</v>
       </c>
       <c r="AB11">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE11">
         <v>55</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG11">
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM11">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN11">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AO11">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP11">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS11">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AT11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU11">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV11">
         <v>17</v>
       </c>
       <c r="AW11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB11">
         <v>16.5</v>
       </c>
       <c r="BC11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE11">
+        <v>55</v>
+      </c>
+      <c r="BF11">
+        <v>6.8</v>
+      </c>
+      <c r="BG11">
+        <v>32</v>
+      </c>
+      <c r="BH11">
+        <v>4.4</v>
+      </c>
+      <c r="BI11">
+        <v>3.55</v>
+      </c>
+      <c r="BJ11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK11">
+        <v>6.2</v>
+      </c>
+      <c r="BL11">
+        <v>95</v>
+      </c>
+      <c r="BM11">
+        <v>13.5</v>
+      </c>
+      <c r="BN11">
+        <v>4.8</v>
+      </c>
+      <c r="BO11">
+        <v>4.2</v>
+      </c>
+      <c r="BP11">
+        <v>11</v>
+      </c>
+      <c r="BQ11">
+        <v>6.6</v>
+      </c>
+      <c r="BR11">
+        <v>21</v>
+      </c>
+      <c r="BS11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT11">
+        <v>8.6</v>
+      </c>
+      <c r="BU11">
+        <v>5.8</v>
+      </c>
+      <c r="BV11">
         <v>34</v>
       </c>
-      <c r="BF11">
-        <v>7.6</v>
-      </c>
-      <c r="BG11">
-        <v>26</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.04</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.04</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.04</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>1.04</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>1.04</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>1.04</v>
-      </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
-        <v>1.04</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3531,64 +3531,64 @@
         <v>149</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="G12">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H12">
         <v>2.42</v>
       </c>
       <c r="I12">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K12">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L12">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P12">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="R12">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="U12">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V12">
         <v>1.65</v>
       </c>
       <c r="W12">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X12">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Y12">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z12">
         <v>17</v>
@@ -3597,34 +3597,34 @@
         <v>48</v>
       </c>
       <c r="AB12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE12">
+        <v>34</v>
+      </c>
+      <c r="AF12">
+        <v>25</v>
+      </c>
+      <c r="AG12">
+        <v>14.5</v>
+      </c>
+      <c r="AH12">
+        <v>16</v>
+      </c>
+      <c r="AI12">
         <v>38</v>
-      </c>
-      <c r="AF12">
-        <v>30</v>
-      </c>
-      <c r="AG12">
-        <v>14</v>
-      </c>
-      <c r="AH12">
-        <v>17</v>
-      </c>
-      <c r="AI12">
-        <v>80</v>
       </c>
       <c r="AJ12">
         <v>100</v>
       </c>
       <c r="AK12">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AL12">
         <v>60</v>
@@ -3633,28 +3633,28 @@
         <v>200</v>
       </c>
       <c r="AN12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO12">
         <v>19</v>
       </c>
       <c r="AP12">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS12">
         <v>24</v>
       </c>
       <c r="AT12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU12">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV12">
         <v>10.5</v>
@@ -3663,10 +3663,10 @@
         <v>21</v>
       </c>
       <c r="AX12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12">
         <v>14</v>
@@ -3681,70 +3681,70 @@
         <v>25</v>
       </c>
       <c r="BD12">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BE12">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG12">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>2.6</v>
       </c>
       <c r="G13">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H13">
         <v>3.15</v>
@@ -3785,7 +3785,7 @@
         <v>3.6</v>
       </c>
       <c r="J13">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K13">
         <v>3</v>
@@ -3797,28 +3797,28 @@
         <v>1.13</v>
       </c>
       <c r="N13">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="O13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P13">
         <v>1.49</v>
       </c>
       <c r="Q13">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R13">
         <v>1.17</v>
       </c>
       <c r="S13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T13">
         <v>2.12</v>
       </c>
       <c r="U13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V13">
         <v>1.38</v>
@@ -3836,7 +3836,7 @@
         <v>22</v>
       </c>
       <c r="AA13">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB13">
         <v>9.4</v>
@@ -3863,25 +3863,25 @@
         <v>230</v>
       </c>
       <c r="AJ13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL13">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AM13">
         <v>500</v>
       </c>
       <c r="AN13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO13">
         <v>90</v>
       </c>
       <c r="AP13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ13">
         <v>7.8</v>
@@ -3890,7 +3890,7 @@
         <v>18</v>
       </c>
       <c r="AS13">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AT13">
         <v>6.6</v>
@@ -3902,7 +3902,7 @@
         <v>13</v>
       </c>
       <c r="AW13">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX13">
         <v>13.5</v>
@@ -3917,22 +3917,22 @@
         <v>6.6</v>
       </c>
       <c r="BB13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC13">
         <v>6.2</v>
       </c>
-      <c r="BC13">
-        <v>6</v>
-      </c>
       <c r="BD13">
+        <v>6.6</v>
+      </c>
+      <c r="BE13">
+        <v>7</v>
+      </c>
+      <c r="BF13">
         <v>6.4</v>
       </c>
-      <c r="BE13">
+      <c r="BG13">
         <v>6.8</v>
-      </c>
-      <c r="BF13">
-        <v>6.2</v>
-      </c>
-      <c r="BG13">
-        <v>6.6</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4015,22 +4015,22 @@
         <v>151</v>
       </c>
       <c r="F14">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G14">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H14">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="I14">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J14">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L14">
         <v>1.47</v>
@@ -4045,10 +4045,10 @@
         <v>1.53</v>
       </c>
       <c r="P14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q14">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R14">
         <v>1.19</v>
@@ -4063,7 +4063,7 @@
         <v>1.76</v>
       </c>
       <c r="V14">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W14">
         <v>1.35</v>
@@ -4075,13 +4075,13 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA14">
         <v>220</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC14">
         <v>7.4</v>
@@ -4093,16 +4093,16 @@
         <v>140</v>
       </c>
       <c r="AF14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH14">
         <v>24</v>
       </c>
       <c r="AI14">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="AJ14">
         <v>900</v>
@@ -4129,13 +4129,13 @@
         <v>6.8</v>
       </c>
       <c r="AR14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS14">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="AT14">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU14">
         <v>6</v>
@@ -4144,7 +4144,7 @@
         <v>11</v>
       </c>
       <c r="AW14">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AX14">
         <v>18</v>
@@ -4156,7 +4156,7 @@
         <v>19</v>
       </c>
       <c r="BA14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB14">
         <v>10</v>
@@ -4165,13 +4165,13 @@
         <v>9.6</v>
       </c>
       <c r="BD14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE14">
         <v>10.5</v>
       </c>
       <c r="BF14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG14">
         <v>8.800000000000001</v>
@@ -4260,16 +4260,16 @@
         <v>1.7</v>
       </c>
       <c r="G15">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I15">
         <v>7.4</v>
       </c>
       <c r="J15">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K15">
         <v>3.9</v>
@@ -4278,31 +4278,31 @@
         <v>1.43</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N15">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="O15">
         <v>1.23</v>
       </c>
       <c r="P15">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q15">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="R15">
         <v>1.13</v>
       </c>
       <c r="S15">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T15">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U15">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="V15">
         <v>1.16</v>
@@ -4311,25 +4311,25 @@
         <v>1.86</v>
       </c>
       <c r="X15">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y15">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Z15">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA15">
         <v>900</v>
       </c>
       <c r="AB15">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AD15">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="AE15">
         <v>500</v>
@@ -4338,16 +4338,16 @@
         <v>970</v>
       </c>
       <c r="AG15">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AH15">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="AI15">
         <v>540</v>
       </c>
       <c r="AJ15">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK15">
         <v>500</v>
@@ -4356,25 +4356,25 @@
         <v>500</v>
       </c>
       <c r="AM15">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN15">
         <v>500</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP15">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AR15">
         <v>14.5</v>
       </c>
       <c r="AS15">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AT15">
         <v>5.1</v>
@@ -4383,40 +4383,40 @@
         <v>5.4</v>
       </c>
       <c r="AV15">
-        <v>1.74</v>
+        <v>12</v>
       </c>
       <c r="AW15">
-        <v>1.78</v>
+        <v>28</v>
       </c>
       <c r="AX15">
-        <v>1.63</v>
+        <v>6.6</v>
       </c>
       <c r="AY15">
         <v>7.8</v>
       </c>
       <c r="AZ15">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="BA15">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="BB15">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="BC15">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="BD15">
-        <v>1.77</v>
+        <v>22</v>
       </c>
       <c r="BE15">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="BF15">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="BG15">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4499,13 +4499,13 @@
         <v>153</v>
       </c>
       <c r="F16">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G16">
         <v>1.41</v>
       </c>
       <c r="H16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I16">
         <v>16</v>
@@ -4523,28 +4523,28 @@
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O16">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P16">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q16">
         <v>2.2</v>
       </c>
       <c r="R16">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S16">
         <v>4</v>
       </c>
       <c r="T16">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="U16">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V16">
         <v>1.06</v>
@@ -4574,7 +4574,7 @@
         <v>950</v>
       </c>
       <c r="AE16">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="AF16">
         <v>6.8</v>
@@ -4583,25 +4583,25 @@
         <v>12</v>
       </c>
       <c r="AH16">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AI16">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AJ16">
         <v>11</v>
       </c>
       <c r="AK16">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL16">
         <v>250</v>
       </c>
       <c r="AM16">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AN16">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO16">
         <v>1000</v>
@@ -4613,10 +4613,10 @@
         <v>11.5</v>
       </c>
       <c r="AR16">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS16">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT16">
         <v>5.1</v>
@@ -4625,10 +4625,10 @@
         <v>10</v>
       </c>
       <c r="AV16">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AW16">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX16">
         <v>5.7</v>
@@ -4637,10 +4637,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ16">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BA16">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB16">
         <v>8.800000000000001</v>
@@ -4649,16 +4649,16 @@
         <v>14</v>
       </c>
       <c r="BD16">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="BE16">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF16">
         <v>6.6</v>
       </c>
       <c r="BG16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4741,22 +4741,22 @@
         <v>154</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="G17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H17">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I17">
         <v>1.33</v>
       </c>
       <c r="J17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L17">
         <v>1.2</v>
@@ -4765,13 +4765,13 @@
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O17">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P17">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q17">
         <v>1.33</v>
@@ -4783,10 +4783,10 @@
         <v>1.9</v>
       </c>
       <c r="T17">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V17">
         <v>4</v>
@@ -4798,61 +4798,61 @@
         <v>50</v>
       </c>
       <c r="Y17">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA17">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AB17">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AC17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AD17">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE17">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AF17">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AG17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AH17">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI17">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ17">
-        <v>320</v>
+        <v>430</v>
       </c>
       <c r="AK17">
         <v>130</v>
       </c>
       <c r="AL17">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM17">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="AN17">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AO17">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AP17">
         <v>36</v>
       </c>
       <c r="AQ17">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR17">
         <v>10</v>
@@ -4861,7 +4861,7 @@
         <v>11</v>
       </c>
       <c r="AT17">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AU17">
         <v>16</v>
@@ -4873,10 +4873,10 @@
         <v>11</v>
       </c>
       <c r="AX17">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AY17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AZ17">
         <v>21</v>
@@ -4885,79 +4885,79 @@
         <v>18.5</v>
       </c>
       <c r="BB17">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BC17">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="BD17">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="BE17">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="BF17">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="BG17">
         <v>3.05</v>
       </c>
       <c r="BH17">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BI17">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BJ17">
         <v>10.5</v>
       </c>
       <c r="BK17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN17">
         <v>13.5</v>
       </c>
       <c r="BO17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR17">
         <v>50</v>
       </c>
       <c r="BS17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT17">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU17">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BV17">
         <v>7.4</v>
       </c>
       <c r="BW17">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BX17">
         <v>17</v>
       </c>
       <c r="BY17">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ17">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CA17">
         <v>5.6</v>
@@ -4983,7 +4983,7 @@
         <v>155</v>
       </c>
       <c r="F18">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G18">
         <v>1.85</v>
@@ -5007,7 +5007,7 @@
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="O18">
         <v>1.21</v>
@@ -5019,13 +5019,13 @@
         <v>1.62</v>
       </c>
       <c r="R18">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="S18">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T18">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U18">
         <v>2.3</v>
@@ -5034,7 +5034,7 @@
         <v>1.25</v>
       </c>
       <c r="W18">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X18">
         <v>23</v>
@@ -5061,7 +5061,7 @@
         <v>190</v>
       </c>
       <c r="AF18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG18">
         <v>11</v>
@@ -5073,7 +5073,7 @@
         <v>120</v>
       </c>
       <c r="AJ18">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK18">
         <v>18</v>
@@ -5085,22 +5085,22 @@
         <v>320</v>
       </c>
       <c r="AN18">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO18">
-        <v>280</v>
+        <v>55</v>
       </c>
       <c r="AP18">
         <v>18.5</v>
       </c>
       <c r="AQ18">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR18">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AS18">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT18">
         <v>9.800000000000001</v>
@@ -5109,10 +5109,10 @@
         <v>8.4</v>
       </c>
       <c r="AV18">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW18">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AX18">
         <v>10.5</v>
@@ -5124,7 +5124,7 @@
         <v>14.5</v>
       </c>
       <c r="BA18">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BB18">
         <v>16.5</v>
@@ -5133,10 +5133,10 @@
         <v>14.5</v>
       </c>
       <c r="BD18">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF18">
         <v>7.4</v>
@@ -5231,22 +5231,22 @@
         <v>2.08</v>
       </c>
       <c r="H19">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J19">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K19">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -5470,13 +5470,13 @@
         <v>2.96</v>
       </c>
       <c r="G20">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I20">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J20">
         <v>3.4</v>
@@ -5485,34 +5485,34 @@
         <v>3.45</v>
       </c>
       <c r="L20">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M20">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N20">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O20">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P20">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q20">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S20">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="T20">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U20">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V20">
         <v>1.58</v>
@@ -5521,64 +5521,64 @@
         <v>1.5</v>
       </c>
       <c r="X20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y20">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA20">
         <v>40</v>
       </c>
       <c r="AB20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC20">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD20">
         <v>12</v>
       </c>
       <c r="AE20">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF20">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG20">
         <v>13</v>
       </c>
       <c r="AH20">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI20">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ20">
         <v>48</v>
       </c>
       <c r="AK20">
+        <v>36</v>
+      </c>
+      <c r="AL20">
+        <v>48</v>
+      </c>
+      <c r="AM20">
+        <v>110</v>
+      </c>
+      <c r="AN20">
         <v>34</v>
       </c>
-      <c r="AL20">
-        <v>46</v>
-      </c>
-      <c r="AM20">
-        <v>95</v>
-      </c>
-      <c r="AN20">
-        <v>32</v>
-      </c>
       <c r="AO20">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AP20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR20">
         <v>15.5</v>
@@ -5587,7 +5587,7 @@
         <v>36</v>
       </c>
       <c r="AT20">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU20">
         <v>7</v>
@@ -5596,7 +5596,7 @@
         <v>11</v>
       </c>
       <c r="AW20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX20">
         <v>17.5</v>
@@ -5608,7 +5608,7 @@
         <v>16.5</v>
       </c>
       <c r="BA20">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB20">
         <v>44</v>
@@ -5617,7 +5617,7 @@
         <v>30</v>
       </c>
       <c r="BD20">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE20">
         <v>85</v>
@@ -5626,25 +5626,25 @@
         <v>30</v>
       </c>
       <c r="BG20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH20">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI20">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BJ20">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK20">
         <v>8.4</v>
       </c>
       <c r="BL20">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BM20">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BN20">
         <v>5.9</v>
@@ -5659,10 +5659,10 @@
         <v>17.5</v>
       </c>
       <c r="BR20">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS20">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BT20">
         <v>5.6</v>
@@ -5674,19 +5674,19 @@
         <v>22</v>
       </c>
       <c r="BW20">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BX20">
+        <v>38</v>
+      </c>
+      <c r="BY20">
+        <v>13</v>
+      </c>
+      <c r="BZ20">
         <v>34</v>
       </c>
-      <c r="BY20">
-        <v>14</v>
-      </c>
-      <c r="BZ20">
-        <v>32</v>
-      </c>
       <c r="CA20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CB20" t="s">
         <v>167</v>
@@ -5709,16 +5709,16 @@
         <v>158</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G21">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H21">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I21">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J21">
         <v>4.1</v>
@@ -5727,13 +5727,13 @@
         <v>4.3</v>
       </c>
       <c r="L21">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M21">
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O21">
         <v>1.19</v>
@@ -5742,34 +5742,34 @@
         <v>2.66</v>
       </c>
       <c r="Q21">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R21">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S21">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T21">
         <v>1.58</v>
       </c>
       <c r="U21">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X21">
         <v>25</v>
       </c>
       <c r="Y21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z21">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA21">
         <v>75</v>
@@ -5784,10 +5784,10 @@
         <v>17</v>
       </c>
       <c r="AE21">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF21">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG21">
         <v>11</v>
@@ -5802,7 +5802,7 @@
         <v>24</v>
       </c>
       <c r="AK21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL21">
         <v>26</v>
@@ -5811,10 +5811,10 @@
         <v>60</v>
       </c>
       <c r="AN21">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO21">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AP21">
         <v>22</v>
@@ -5826,7 +5826,7 @@
         <v>29</v>
       </c>
       <c r="AS21">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT21">
         <v>13</v>
@@ -5850,7 +5850,7 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB21">
         <v>21</v>
@@ -5865,70 +5865,70 @@
         <v>48</v>
       </c>
       <c r="BF21">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG21">
+        <v>23</v>
+      </c>
+      <c r="BH21">
+        <v>5.2</v>
+      </c>
+      <c r="BI21">
+        <v>3.65</v>
+      </c>
+      <c r="BJ21">
+        <v>9</v>
+      </c>
+      <c r="BK21">
+        <v>4.3</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>7.6</v>
+      </c>
+      <c r="BN21">
+        <v>5.4</v>
+      </c>
+      <c r="BO21">
+        <v>4.5</v>
+      </c>
+      <c r="BP21">
+        <v>13</v>
+      </c>
+      <c r="BQ21">
+        <v>5.1</v>
+      </c>
+      <c r="BR21">
         <v>22</v>
       </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>2.14</v>
-      </c>
-      <c r="BJ21">
-        <v>11.5</v>
-      </c>
-      <c r="BK21">
-        <v>1.81</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>2.1</v>
-      </c>
-      <c r="BN21">
-        <v>7</v>
-      </c>
-      <c r="BO21">
-        <v>3.8</v>
-      </c>
-      <c r="BP21">
-        <v>17.5</v>
-      </c>
-      <c r="BQ21">
-        <v>1.92</v>
-      </c>
-      <c r="BR21">
-        <v>29</v>
-      </c>
       <c r="BS21">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BT21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BU21">
-        <v>1.77</v>
+        <v>4.1</v>
       </c>
       <c r="BV21">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BW21">
-        <v>2.02</v>
+        <v>6.4</v>
       </c>
       <c r="BX21">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BY21">
-        <v>2.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ21">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CA21">
-        <v>1.94</v>
+        <v>5.4</v>
       </c>
       <c r="CB21" t="s">
         <v>167</v>
@@ -5951,85 +5951,85 @@
         <v>159</v>
       </c>
       <c r="F22">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="G22">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I22">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J22">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K22">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M22">
         <v>1.02</v>
       </c>
       <c r="N22">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O22">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P22">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q22">
         <v>1.34</v>
       </c>
       <c r="R22">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="T22">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U22">
         <v>2.94</v>
       </c>
       <c r="V22">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W22">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="X22">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Y22">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z22">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA22">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB22">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE22">
         <v>60</v>
       </c>
       <c r="AF22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG22">
         <v>11.5</v>
@@ -6041,61 +6041,61 @@
         <v>44</v>
       </c>
       <c r="AJ22">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK22">
         <v>13.5</v>
       </c>
       <c r="AL22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM22">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AN22">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AO22">
+        <v>36</v>
+      </c>
+      <c r="AP22">
+        <v>42</v>
+      </c>
+      <c r="AQ22">
         <v>34</v>
       </c>
-      <c r="AP22">
-        <v>40</v>
-      </c>
-      <c r="AQ22">
-        <v>36</v>
-      </c>
       <c r="AR22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS22">
         <v>46</v>
       </c>
       <c r="AT22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW22">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY22">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ22">
         <v>15.5</v>
       </c>
       <c r="BA22">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BB22">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC22">
         <v>12.5</v>
@@ -6104,73 +6104,73 @@
         <v>19.5</v>
       </c>
       <c r="BE22">
+        <v>40</v>
+      </c>
+      <c r="BF22">
+        <v>4</v>
+      </c>
+      <c r="BG22">
         <v>29</v>
       </c>
-      <c r="BF22">
-        <v>3.85</v>
-      </c>
-      <c r="BG22">
-        <v>30</v>
-      </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI22">
-        <v>1.18</v>
+        <v>4.7</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK22">
-        <v>1.18</v>
+        <v>5</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.16</v>
+        <v>9.4</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO22">
-        <v>1.18</v>
+        <v>4</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ22">
-        <v>1.18</v>
+        <v>5.1</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS22">
-        <v>1.13</v>
+        <v>6.6</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU22">
-        <v>1.18</v>
+        <v>5.4</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.18</v>
+        <v>8.6</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY22">
-        <v>1.14</v>
+        <v>8.4</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="CA22">
-        <v>1.09</v>
+        <v>4.9</v>
       </c>
       <c r="CB22" t="s">
         <v>167</v>
@@ -6199,16 +6199,16 @@
         <v>1.36</v>
       </c>
       <c r="H23">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J23">
         <v>6.8</v>
       </c>
       <c r="K23">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6217,7 +6217,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O23">
         <v>1.09</v>
@@ -6226,16 +6226,16 @@
         <v>4</v>
       </c>
       <c r="Q23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R23">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S23">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="T23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U23">
         <v>2.58</v>
@@ -6247,10 +6247,10 @@
         <v>3.75</v>
       </c>
       <c r="X23">
+        <v>70</v>
+      </c>
+      <c r="Y23">
         <v>65</v>
-      </c>
-      <c r="Y23">
-        <v>55</v>
       </c>
       <c r="Z23">
         <v>540</v>
@@ -6271,7 +6271,7 @@
         <v>95</v>
       </c>
       <c r="AF23">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG23">
         <v>12.5</v>
@@ -6295,7 +6295,7 @@
         <v>70</v>
       </c>
       <c r="AN23">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AO23">
         <v>55</v>
@@ -6304,10 +6304,10 @@
         <v>10</v>
       </c>
       <c r="AQ23">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="AR23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS23">
         <v>11.5</v>
@@ -6435,28 +6435,28 @@
         <v>161</v>
       </c>
       <c r="F24">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G24">
         <v>2.64</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="I24">
         <v>4.3</v>
       </c>
       <c r="J24">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K24">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="L24">
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N24">
         <v>2.44</v>
@@ -6477,7 +6477,7 @@
         <v>2.8</v>
       </c>
       <c r="T24">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U24">
         <v>1.55</v>
@@ -6486,7 +6486,7 @@
         <v>1.31</v>
       </c>
       <c r="W24">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X24">
         <v>970</v>
@@ -6501,7 +6501,7 @@
         <v>900</v>
       </c>
       <c r="AB24">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC24">
         <v>42</v>
@@ -6519,7 +6519,7 @@
         <v>970</v>
       </c>
       <c r="AH24">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="AI24">
         <v>500</v>
@@ -6543,16 +6543,16 @@
         <v>500</v>
       </c>
       <c r="AP24">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AQ24">
         <v>5.1</v>
       </c>
       <c r="AR24">
-        <v>11</v>
+        <v>1.81</v>
       </c>
       <c r="AS24">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="AT24">
         <v>5.1</v>
@@ -6561,10 +6561,10 @@
         <v>4.2</v>
       </c>
       <c r="AV24">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AW24">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="AX24">
         <v>7.2</v>
@@ -6573,22 +6573,22 @@
         <v>1.83</v>
       </c>
       <c r="AZ24">
-        <v>2.5</v>
+        <v>17</v>
       </c>
       <c r="BA24">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="BB24">
         <v>1.94</v>
       </c>
       <c r="BC24">
-        <v>1.27</v>
+        <v>1.79</v>
       </c>
       <c r="BD24">
-        <v>26</v>
+        <v>2.5</v>
       </c>
       <c r="BE24">
-        <v>1.99</v>
+        <v>1.54</v>
       </c>
       <c r="BF24">
         <v>1.55</v>
@@ -6677,22 +6677,22 @@
         <v>162</v>
       </c>
       <c r="F25">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="G25">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H25">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I25">
         <v>3.4</v>
       </c>
       <c r="J25">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="K25">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L25">
         <v>1.45</v>
@@ -6701,22 +6701,22 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="O25">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P25">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q25">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R25">
         <v>1.18</v>
       </c>
       <c r="S25">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T25">
         <v>1.11</v>
@@ -6728,7 +6728,7 @@
         <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X25">
         <v>12</v>
@@ -6785,7 +6785,7 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
         <v>1.09</v>
@@ -6919,16 +6919,16 @@
         <v>163</v>
       </c>
       <c r="F26">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G26">
         <v>2.26</v>
       </c>
       <c r="H26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I26">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J26">
         <v>3.05</v>
@@ -6937,37 +6937,37 @@
         <v>3.25</v>
       </c>
       <c r="L26">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M26">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N26">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O26">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P26">
         <v>1.56</v>
       </c>
       <c r="Q26">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="R26">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S26">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="T26">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U26">
         <v>1.79</v>
       </c>
       <c r="V26">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W26">
         <v>1.79</v>
@@ -6979,19 +6979,19 @@
         <v>12</v>
       </c>
       <c r="Z26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA26">
         <v>900</v>
       </c>
       <c r="AB26">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>7.2</v>
       </c>
       <c r="AD26">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AE26">
         <v>85</v>
@@ -7003,7 +7003,7 @@
         <v>11.5</v>
       </c>
       <c r="AH26">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AI26">
         <v>460</v>
@@ -7039,19 +7039,19 @@
         <v>11.5</v>
       </c>
       <c r="AT26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU26">
         <v>6.4</v>
       </c>
       <c r="AV26">
+        <v>16</v>
+      </c>
+      <c r="AW26">
+        <v>12</v>
+      </c>
+      <c r="AX26">
         <v>10.5</v>
-      </c>
-      <c r="AW26">
-        <v>11.5</v>
-      </c>
-      <c r="AX26">
-        <v>11</v>
       </c>
       <c r="AY26">
         <v>10</v>
@@ -7060,7 +7060,7 @@
         <v>13</v>
       </c>
       <c r="BA26">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB26">
         <v>21</v>
@@ -7069,7 +7069,7 @@
         <v>14.5</v>
       </c>
       <c r="BD26">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE26">
         <v>13</v>
@@ -7084,40 +7084,40 @@
         <v>3.05</v>
       </c>
       <c r="BI26">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ26">
         <v>11.5</v>
       </c>
       <c r="BK26">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN26">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO26">
         <v>3.8</v>
       </c>
       <c r="BP26">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BQ26">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR26">
         <v>48</v>
       </c>
       <c r="BS26">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT26">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU26">
         <v>5.6</v>
@@ -7126,7 +7126,7 @@
         <v>48</v>
       </c>
       <c r="BW26">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX26">
         <v>75</v>
@@ -7138,7 +7138,7 @@
         <v>55</v>
       </c>
       <c r="CA26">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB26" t="s">
         <v>167</v>
@@ -7161,34 +7161,34 @@
         <v>164</v>
       </c>
       <c r="F27">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G27">
         <v>2.16</v>
       </c>
       <c r="H27">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I27">
         <v>4.6</v>
       </c>
       <c r="J27">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K27">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L27">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M27">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N27">
         <v>2.86</v>
       </c>
       <c r="O27">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P27">
         <v>1.61</v>
@@ -7209,7 +7209,7 @@
         <v>1.83</v>
       </c>
       <c r="V27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W27">
         <v>1.86</v>
@@ -7221,19 +7221,19 @@
         <v>12.5</v>
       </c>
       <c r="Z27">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AA27">
         <v>900</v>
       </c>
       <c r="AB27">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC27">
         <v>7.8</v>
       </c>
       <c r="AD27">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE27">
         <v>75</v>
@@ -7263,10 +7263,10 @@
         <v>580</v>
       </c>
       <c r="AN27">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO27">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AP27">
         <v>8.6</v>
@@ -7278,7 +7278,7 @@
         <v>22</v>
       </c>
       <c r="AS27">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT27">
         <v>6.4</v>
@@ -7302,19 +7302,19 @@
         <v>19.5</v>
       </c>
       <c r="BA27">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BB27">
         <v>11.5</v>
       </c>
       <c r="BC27">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BD27">
         <v>23</v>
       </c>
       <c r="BE27">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF27">
         <v>21</v>
@@ -7323,7 +7323,7 @@
         <v>8.4</v>
       </c>
       <c r="BH27">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI27">
         <v>2.38</v>
@@ -7332,13 +7332,13 @@
         <v>13</v>
       </c>
       <c r="BK27">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BN27">
         <v>5.2</v>
@@ -7350,37 +7350,37 @@
         <v>19.5</v>
       </c>
       <c r="BQ27">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR27">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS27">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BT27">
         <v>8.4</v>
       </c>
       <c r="BU27">
-        <v>5.8</v>
+        <v>3.65</v>
       </c>
       <c r="BV27">
         <v>50</v>
       </c>
       <c r="BW27">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
+        <v>5.9</v>
+      </c>
+      <c r="BZ27">
+        <v>46</v>
+      </c>
+      <c r="CA27">
         <v>5.6</v>
-      </c>
-      <c r="BZ27">
-        <v>48</v>
-      </c>
-      <c r="CA27">
-        <v>5.4</v>
       </c>
       <c r="CB27" t="s">
         <v>167</v>
@@ -7403,22 +7403,22 @@
         <v>165</v>
       </c>
       <c r="F28">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="G28">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H28">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I28">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J28">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K28">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7430,73 +7430,73 @@
         <v>4.8</v>
       </c>
       <c r="O28">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P28">
         <v>2.2</v>
       </c>
       <c r="Q28">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R28">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S28">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="T28">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U28">
         <v>2.46</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="W28">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X28">
         <v>23</v>
       </c>
       <c r="Y28">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z28">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA28">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB28">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC28">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD28">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE28">
         <v>32</v>
       </c>
       <c r="AF28">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH28">
         <v>16</v>
       </c>
       <c r="AI28">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ28">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AK28">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AL28">
         <v>32</v>
@@ -7508,43 +7508,43 @@
         <v>15</v>
       </c>
       <c r="AO28">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP28">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ28">
-        <v>14</v>
+        <v>5.5</v>
       </c>
       <c r="AR28">
         <v>6.2</v>
       </c>
       <c r="AS28">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT28">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU28">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AV28">
         <v>5.3</v>
       </c>
       <c r="AW28">
+        <v>6.4</v>
+      </c>
+      <c r="AX28">
+        <v>5.6</v>
+      </c>
+      <c r="AY28">
+        <v>4.8</v>
+      </c>
+      <c r="AZ28">
+        <v>5.4</v>
+      </c>
+      <c r="BA28">
         <v>6.6</v>
-      </c>
-      <c r="AX28">
-        <v>5.8</v>
-      </c>
-      <c r="AY28">
-        <v>5</v>
-      </c>
-      <c r="AZ28">
-        <v>13</v>
-      </c>
-      <c r="BA28">
-        <v>6.8</v>
       </c>
       <c r="BB28">
         <v>6.6</v>
@@ -7553,16 +7553,16 @@
         <v>6.2</v>
       </c>
       <c r="BD28">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE28">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF28">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="BG28">
-        <v>18.5</v>
+        <v>6</v>
       </c>
       <c r="BH28">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -517,7 +517,7 @@
     <t>Aguilas Doradas</t>
   </si>
   <si>
-    <t>2026-08-25 02:26:08</t>
+    <t>2026-08-25 04:44:01</t>
   </si>
 </sst>
 </file>
@@ -1111,37 +1111,37 @@
         <v>139</v>
       </c>
       <c r="F2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H2">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J2">
         <v>3.5</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
@@ -1150,25 +1150,25 @@
         <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X2">
         <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z2">
         <v>14.5</v>
@@ -1177,16 +1177,16 @@
         <v>30</v>
       </c>
       <c r="AB2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF2">
         <v>24</v>
@@ -1204,16 +1204,16 @@
         <v>65</v>
       </c>
       <c r="AK2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL2">
         <v>50</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO2">
         <v>21</v>
@@ -1222,7 +1222,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR2">
         <v>13</v>
@@ -1231,10 +1231,10 @@
         <v>27</v>
       </c>
       <c r="AT2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
         <v>10</v>
@@ -1243,25 +1243,25 @@
         <v>23</v>
       </c>
       <c r="AX2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY2">
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BC2">
         <v>34</v>
       </c>
       <c r="BD2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BE2">
         <v>85</v>
@@ -1270,16 +1270,16 @@
         <v>34</v>
       </c>
       <c r="BG2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
         <v>3</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK2">
         <v>7.6</v>
@@ -1306,7 +1306,7 @@
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BT2">
         <v>5.1</v>
@@ -1315,10 +1315,10 @@
         <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>32</v>
@@ -1327,7 +1327,7 @@
         <v>12.5</v>
       </c>
       <c r="BZ2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA2">
         <v>12</v>
@@ -1353,61 +1353,61 @@
         <v>140</v>
       </c>
       <c r="F3">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G3">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H3">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
         <v>3.35</v>
       </c>
       <c r="L3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y3">
         <v>10.5</v>
@@ -1416,10 +1416,10 @@
         <v>22</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
@@ -1428,112 +1428,112 @@
         <v>14.5</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
         <v>12</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI3">
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK3">
         <v>32</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN3">
         <v>32</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP3">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AS3">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AT3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU3">
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AX3">
         <v>13</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC3">
         <v>27</v>
       </c>
       <c r="BD3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE3">
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BG3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH3">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BI3">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL3">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BM3">
         <v>130</v>
       </c>
       <c r="BN3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO3">
         <v>4.7</v>
@@ -1542,37 +1542,37 @@
         <v>21</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR3">
         <v>40</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BT3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
         <v>5.7</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW3">
+        <v>11</v>
+      </c>
+      <c r="BX3">
+        <v>55</v>
+      </c>
+      <c r="BY3">
+        <v>12.5</v>
+      </c>
+      <c r="BZ3">
+        <v>42</v>
+      </c>
+      <c r="CA3">
         <v>12</v>
-      </c>
-      <c r="BX3">
-        <v>50</v>
-      </c>
-      <c r="BY3">
-        <v>14</v>
-      </c>
-      <c r="BZ3">
-        <v>40</v>
-      </c>
-      <c r="CA3">
-        <v>13</v>
       </c>
       <c r="CB3" t="s">
         <v>167</v>
@@ -1595,46 +1595,46 @@
         <v>141</v>
       </c>
       <c r="F4">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="G4">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J4">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q4">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R4">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T4">
         <v>2</v>
@@ -1646,37 +1646,37 @@
         <v>1.13</v>
       </c>
       <c r="W4">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="X4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA4">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE4">
         <v>130</v>
       </c>
       <c r="AF4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
         <v>25</v>
@@ -1685,10 +1685,10 @@
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AK4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL4">
         <v>38</v>
@@ -1697,100 +1697,100 @@
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO4">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP4">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
         <v>22</v>
       </c>
       <c r="AR4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AS4">
         <v>20</v>
       </c>
       <c r="AT4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV4">
         <v>26</v>
       </c>
       <c r="AW4">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AX4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY4">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
         <v>22</v>
       </c>
       <c r="BA4">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="BB4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC4">
         <v>14</v>
       </c>
       <c r="BD4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE4">
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BG4">
         <v>100</v>
       </c>
       <c r="BH4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI4">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
         <v>9.800000000000001</v>
       </c>
       <c r="BL4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BM4">
         <v>130</v>
       </c>
       <c r="BN4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO4">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BS4">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BT4">
         <v>11.5</v>
@@ -1802,19 +1802,19 @@
         <v>75</v>
       </c>
       <c r="BW4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BX4">
         <v>75</v>
       </c>
       <c r="BY4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BZ4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA4">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="CB4" t="s">
         <v>167</v>
@@ -1837,19 +1837,19 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G5">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I5">
         <v>6.4</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>4.4</v>
@@ -1858,43 +1858,43 @@
         <v>1.37</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q5">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R5">
         <v>1.39</v>
       </c>
       <c r="S5">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T5">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V5">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="X5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5">
         <v>100</v>
@@ -1903,16 +1903,16 @@
         <v>900</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
         <v>30</v>
       </c>
       <c r="AE5">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF5">
         <v>11</v>
@@ -1942,10 +1942,10 @@
         <v>10.5</v>
       </c>
       <c r="AO5">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AP5">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AQ5">
         <v>8.4</v>
@@ -1954,10 +1954,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT5">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AU5">
         <v>8</v>
@@ -1966,7 +1966,7 @@
         <v>19</v>
       </c>
       <c r="AW5">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX5">
         <v>8.800000000000001</v>
@@ -1978,25 +1978,25 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB5">
         <v>6.8</v>
       </c>
       <c r="BC5">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF5">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5">
         <v>3.7</v>
@@ -2014,7 +2014,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN5">
         <v>4.4</v>
@@ -2026,16 +2026,16 @@
         <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU5">
         <v>7.2</v>
@@ -2044,19 +2044,19 @@
         <v>55</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5">
         <v>21</v>
       </c>
       <c r="CA5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB5" t="s">
         <v>167</v>
@@ -2079,19 +2079,19 @@
         <v>143</v>
       </c>
       <c r="F6">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="G6">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="H6">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="I6">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K6">
         <v>4.3</v>
@@ -2103,46 +2103,46 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>1.23</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q6">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R6">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S6">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="T6">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U6">
         <v>2.38</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W6">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="X6">
         <v>21</v>
       </c>
       <c r="Y6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z6">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AA6">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB6">
         <v>12.5</v>
@@ -2151,52 +2151,52 @@
         <v>9.4</v>
       </c>
       <c r="AD6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE6">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH6">
         <v>16</v>
       </c>
       <c r="AI6">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ6">
-        <v>30</v>
+        <v>900</v>
       </c>
       <c r="AK6">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AM6">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO6">
-        <v>36</v>
+        <v>600</v>
       </c>
       <c r="AP6">
         <v>17.5</v>
       </c>
       <c r="AQ6">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AR6">
         <v>23</v>
       </c>
       <c r="AS6">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="AT6">
         <v>10</v>
@@ -2208,7 +2208,7 @@
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="AX6">
         <v>12</v>
@@ -2220,79 +2220,79 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="BB6">
         <v>21</v>
       </c>
       <c r="BC6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE6">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="BF6">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG6">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH6">
         <v>4.1</v>
       </c>
       <c r="BI6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN6">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BO6">
         <v>4</v>
       </c>
       <c r="BP6">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BQ6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU6">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW6">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2324,13 +2324,13 @@
         <v>2.3</v>
       </c>
       <c r="G7">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H7">
         <v>2.92</v>
       </c>
       <c r="I7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J7">
         <v>3.15</v>
@@ -2342,22 +2342,22 @@
         <v>1.4</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P7">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
         <v>3.45</v>
@@ -2366,13 +2366,13 @@
         <v>1.73</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V7">
         <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X7">
         <v>14.5</v>
@@ -2405,7 +2405,7 @@
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
         <v>120</v>
@@ -2423,13 +2423,13 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO7">
         <v>75</v>
       </c>
       <c r="AP7">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AQ7">
         <v>9.4</v>
@@ -2438,10 +2438,10 @@
         <v>17</v>
       </c>
       <c r="AS7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU7">
         <v>6.6</v>
@@ -2450,7 +2450,7 @@
         <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX7">
         <v>12</v>
@@ -2459,28 +2459,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>14.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA7">
+        <v>7</v>
+      </c>
+      <c r="BB7">
         <v>6.6</v>
-      </c>
-      <c r="BB7">
-        <v>6.2</v>
       </c>
       <c r="BC7">
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF7">
-        <v>5.8</v>
+        <v>18.5</v>
       </c>
       <c r="BG7">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BH7">
         <v>3.5</v>
@@ -2537,7 +2537,7 @@
         <v>7</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA7">
         <v>6.6</v>
@@ -2563,46 +2563,46 @@
         <v>145</v>
       </c>
       <c r="F8">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="G8">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H8">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="I8">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J8">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
         <v>3.7</v>
       </c>
       <c r="L8">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q8">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R8">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S8">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T8">
         <v>1.7</v>
@@ -2611,25 +2611,25 @@
         <v>2.18</v>
       </c>
       <c r="V8">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y8">
         <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA8">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AB8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC8">
         <v>8.6</v>
@@ -2641,13 +2641,13 @@
         <v>60</v>
       </c>
       <c r="AF8">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI8">
         <v>95</v>
@@ -2659,7 +2659,7 @@
         <v>95</v>
       </c>
       <c r="AL8">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AM8">
         <v>500</v>
@@ -2668,7 +2668,7 @@
         <v>46</v>
       </c>
       <c r="AO8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP8">
         <v>13</v>
@@ -2677,10 +2677,10 @@
         <v>10</v>
       </c>
       <c r="AR8">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AS8">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="AT8">
         <v>10.5</v>
@@ -2695,7 +2695,7 @@
         <v>13</v>
       </c>
       <c r="AX8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY8">
         <v>11</v>
@@ -2704,76 +2704,76 @@
         <v>13.5</v>
       </c>
       <c r="BA8">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BB8">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BC8">
         <v>14.5</v>
       </c>
       <c r="BD8">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BE8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF8">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BG8">
         <v>17.5</v>
       </c>
       <c r="BH8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI8">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8">
         <v>9.6</v>
       </c>
       <c r="BK8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ8">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT8">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU8">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BW8">
         <v>6.6</v>
       </c>
       <c r="BX8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY8">
         <v>7.6</v>
@@ -2782,7 +2782,7 @@
         <v>26</v>
       </c>
       <c r="CA8">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="s">
         <v>167</v>
@@ -2805,67 +2805,67 @@
         <v>146</v>
       </c>
       <c r="F9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G9">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="H9">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
         <v>4.1</v>
       </c>
       <c r="L9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M9">
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="R9">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S9">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T9">
         <v>1.82</v>
       </c>
       <c r="U9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V9">
         <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X9">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Y9">
         <v>20</v>
       </c>
       <c r="Z9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA9">
         <v>900</v>
@@ -2874,10 +2874,10 @@
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE9">
         <v>150</v>
@@ -2892,7 +2892,7 @@
         <v>21</v>
       </c>
       <c r="AI9">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AJ9">
         <v>24</v>
@@ -2910,7 +2910,7 @@
         <v>13</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP9">
         <v>13.5</v>
@@ -2919,13 +2919,13 @@
         <v>14.5</v>
       </c>
       <c r="AR9">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS9">
         <v>9</v>
       </c>
       <c r="AT9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU9">
         <v>7.6</v>
@@ -2934,7 +2934,7 @@
         <v>16</v>
       </c>
       <c r="AW9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2946,7 +2946,7 @@
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB9">
         <v>17.5</v>
@@ -2955,34 +2955,34 @@
         <v>17</v>
       </c>
       <c r="BD9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF9">
         <v>11</v>
       </c>
       <c r="BG9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI9">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ9">
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
@@ -2991,7 +2991,7 @@
         <v>4</v>
       </c>
       <c r="BP9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ9">
         <v>9.6</v>
@@ -3000,7 +3000,7 @@
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
         <v>8.199999999999999</v>
@@ -3012,19 +3012,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
         <v>24</v>
       </c>
       <c r="CA9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB9" t="s">
         <v>167</v>
@@ -3047,10 +3047,10 @@
         <v>147</v>
       </c>
       <c r="F10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G10">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H10">
         <v>4</v>
@@ -3071,25 +3071,25 @@
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O10">
         <v>1.27</v>
       </c>
       <c r="P10">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R10">
         <v>1.45</v>
       </c>
       <c r="S10">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T10">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U10">
         <v>2.28</v>
@@ -3098,76 +3098,76 @@
         <v>1.31</v>
       </c>
       <c r="W10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X10">
         <v>17.5</v>
       </c>
       <c r="Y10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z10">
         <v>32</v>
       </c>
       <c r="AA10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC10">
         <v>8.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE10">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG10">
         <v>10</v>
       </c>
       <c r="AH10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI10">
         <v>55</v>
       </c>
       <c r="AJ10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM10">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO10">
         <v>46</v>
       </c>
       <c r="AP10">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR10">
         <v>27</v>
       </c>
       <c r="AS10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10">
         <v>8.4</v>
@@ -3185,7 +3185,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA10">
         <v>46</v>
@@ -3197,16 +3197,16 @@
         <v>17</v>
       </c>
       <c r="BD10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BE10">
         <v>65</v>
       </c>
       <c r="BF10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH10">
         <v>4.4</v>
@@ -3218,16 +3218,16 @@
         <v>11.5</v>
       </c>
       <c r="BK10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BL10">
         <v>130</v>
       </c>
       <c r="BM10">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BN10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO10">
         <v>4.2</v>
@@ -3236,22 +3236,22 @@
         <v>16</v>
       </c>
       <c r="BQ10">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BR10">
         <v>32</v>
       </c>
       <c r="BS10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT10">
         <v>9</v>
       </c>
       <c r="BU10">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BV10">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BW10">
         <v>4.2</v>
@@ -3260,13 +3260,13 @@
         <v>48</v>
       </c>
       <c r="BY10">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BZ10">
         <v>25</v>
       </c>
       <c r="CA10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="CB10" t="s">
         <v>167</v>
@@ -3289,16 +3289,16 @@
         <v>148</v>
       </c>
       <c r="F11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G11">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>4.4</v>
@@ -3313,43 +3313,43 @@
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P11">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q11">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R11">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S11">
         <v>2.44</v>
       </c>
       <c r="T11">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V11">
         <v>1.25</v>
       </c>
       <c r="W11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y11">
         <v>25</v>
       </c>
       <c r="Z11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA11">
         <v>110</v>
@@ -3361,7 +3361,7 @@
         <v>10.5</v>
       </c>
       <c r="AD11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE11">
         <v>55</v>
@@ -3373,31 +3373,31 @@
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI11">
         <v>50</v>
       </c>
       <c r="AJ11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK11">
         <v>16</v>
       </c>
       <c r="AL11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM11">
         <v>70</v>
       </c>
       <c r="AN11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO11">
         <v>40</v>
       </c>
       <c r="AP11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ11">
         <v>22</v>
@@ -3406,7 +3406,7 @@
         <v>38</v>
       </c>
       <c r="AS11">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AT11">
         <v>11.5</v>
@@ -3415,13 +3415,13 @@
         <v>9.4</v>
       </c>
       <c r="AV11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW11">
         <v>44</v>
       </c>
       <c r="AX11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY11">
         <v>9.4</v>
@@ -3430,7 +3430,7 @@
         <v>15</v>
       </c>
       <c r="BA11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB11">
         <v>16.5</v>
@@ -3454,7 +3454,7 @@
         <v>4.4</v>
       </c>
       <c r="BI11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ11">
         <v>9.199999999999999</v>
@@ -3463,10 +3463,10 @@
         <v>6.2</v>
       </c>
       <c r="BL11">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN11">
         <v>4.8</v>
@@ -3484,7 +3484,7 @@
         <v>21</v>
       </c>
       <c r="BS11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT11">
         <v>8.6</v>
@@ -3496,13 +3496,13 @@
         <v>34</v>
       </c>
       <c r="BW11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX11">
         <v>48</v>
       </c>
       <c r="BY11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>149</v>
       </c>
       <c r="F12">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G12">
         <v>3.1</v>
@@ -3540,10 +3540,10 @@
         <v>2.42</v>
       </c>
       <c r="I12">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J12">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K12">
         <v>3.8</v>
@@ -3555,28 +3555,28 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O12">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P12">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q12">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R12">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T12">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U12">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
         <v>1.65</v>
@@ -3585,10 +3585,10 @@
         <v>1.47</v>
       </c>
       <c r="X12">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z12">
         <v>17</v>
@@ -3597,7 +3597,7 @@
         <v>48</v>
       </c>
       <c r="AB12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC12">
         <v>8.6</v>
@@ -3612,7 +3612,7 @@
         <v>25</v>
       </c>
       <c r="AG12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH12">
         <v>16</v>
@@ -3621,7 +3621,7 @@
         <v>38</v>
       </c>
       <c r="AJ12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK12">
         <v>50</v>
@@ -3630,19 +3630,19 @@
         <v>60</v>
       </c>
       <c r="AM12">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN12">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AO12">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AP12">
         <v>15.5</v>
       </c>
       <c r="AQ12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR12">
         <v>15</v>
@@ -3651,10 +3651,10 @@
         <v>24</v>
       </c>
       <c r="AT12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
         <v>10.5</v>
@@ -3663,52 +3663,52 @@
         <v>21</v>
       </c>
       <c r="AX12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY12">
         <v>11.5</v>
       </c>
       <c r="AZ12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB12">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BC12">
         <v>25</v>
       </c>
       <c r="BD12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE12">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH12">
         <v>3.95</v>
       </c>
       <c r="BI12">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ12">
         <v>9.199999999999999</v>
       </c>
       <c r="BK12">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN12">
         <v>6.6</v>
@@ -3717,16 +3717,16 @@
         <v>5.4</v>
       </c>
       <c r="BP12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ12">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR12">
         <v>32</v>
       </c>
       <c r="BS12">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT12">
         <v>5.8</v>
@@ -3735,16 +3735,16 @@
         <v>4.8</v>
       </c>
       <c r="BV12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX12">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BY12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3773,40 +3773,40 @@
         <v>150</v>
       </c>
       <c r="F13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G13">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H13">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I13">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J13">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K13">
         <v>3</v>
       </c>
       <c r="L13">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="M13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="O13">
         <v>1.57</v>
       </c>
       <c r="P13">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q13">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="R13">
         <v>1.17</v>
@@ -3818,16 +3818,16 @@
         <v>2.12</v>
       </c>
       <c r="U13">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X13">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13">
         <v>9.4</v>
@@ -3839,7 +3839,7 @@
         <v>900</v>
       </c>
       <c r="AB13">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13">
         <v>7.4</v>
@@ -3851,7 +3851,7 @@
         <v>60</v>
       </c>
       <c r="AF13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG13">
         <v>14</v>
@@ -3863,13 +3863,13 @@
         <v>230</v>
       </c>
       <c r="AJ13">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AK13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL13">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AM13">
         <v>500</v>
@@ -3878,10 +3878,10 @@
         <v>55</v>
       </c>
       <c r="AO13">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AP13">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13">
         <v>7.8</v>
@@ -3893,7 +3893,7 @@
         <v>21</v>
       </c>
       <c r="AT13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU13">
         <v>6</v>
@@ -3902,7 +3902,7 @@
         <v>13</v>
       </c>
       <c r="AW13">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AX13">
         <v>13.5</v>
@@ -3914,85 +3914,85 @@
         <v>19.5</v>
       </c>
       <c r="BA13">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB13">
+        <v>15.5</v>
+      </c>
+      <c r="BC13">
+        <v>18.5</v>
+      </c>
+      <c r="BD13">
+        <v>9</v>
+      </c>
+      <c r="BE13">
+        <v>9.4</v>
+      </c>
+      <c r="BF13">
+        <v>8.4</v>
+      </c>
+      <c r="BG13">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC13">
-        <v>6.2</v>
-      </c>
-      <c r="BD13">
-        <v>6.6</v>
-      </c>
-      <c r="BE13">
-        <v>7</v>
-      </c>
-      <c r="BF13">
-        <v>6.4</v>
-      </c>
-      <c r="BG13">
-        <v>6.8</v>
-      </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB13" t="s">
         <v>167</v>
@@ -4015,73 +4015,73 @@
         <v>151</v>
       </c>
       <c r="F14">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G14">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H14">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I14">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="J14">
         <v>2.94</v>
       </c>
       <c r="K14">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L14">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M14">
         <v>1.13</v>
       </c>
       <c r="N14">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P14">
         <v>1.53</v>
       </c>
       <c r="Q14">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R14">
         <v>1.19</v>
       </c>
       <c r="S14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T14">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U14">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V14">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W14">
         <v>1.35</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z14">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA14">
         <v>220</v>
       </c>
       <c r="AB14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>7.4</v>
@@ -4093,40 +4093,40 @@
         <v>140</v>
       </c>
       <c r="AF14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH14">
         <v>24</v>
       </c>
       <c r="AI14">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="AJ14">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK14">
         <v>290</v>
       </c>
       <c r="AL14">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM14">
         <v>500</v>
       </c>
       <c r="AN14">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO14">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AP14">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR14">
         <v>12</v>
@@ -4138,7 +4138,7 @@
         <v>8.6</v>
       </c>
       <c r="AU14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV14">
         <v>11</v>
@@ -4156,85 +4156,85 @@
         <v>19</v>
       </c>
       <c r="BA14">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BB14">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BC14">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="BD14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF14">
         <v>10.5</v>
       </c>
       <c r="BG14">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB14" t="s">
         <v>167</v>
@@ -4257,64 +4257,64 @@
         <v>152</v>
       </c>
       <c r="F15">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="G15">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="J15">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="K15">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L15">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="M15">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N15">
-        <v>2.22</v>
+        <v>2.88</v>
       </c>
       <c r="O15">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="P15">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="Q15">
-        <v>1.96</v>
+        <v>2.48</v>
       </c>
       <c r="R15">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="S15">
-        <v>2.54</v>
+        <v>4.9</v>
       </c>
       <c r="T15">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U15">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="V15">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="W15">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="X15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="Z15">
         <v>120</v>
@@ -4323,160 +4323,160 @@
         <v>900</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AC15">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD15">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="AE15">
         <v>500</v>
       </c>
       <c r="AF15">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG15">
+        <v>12.5</v>
+      </c>
+      <c r="AH15">
+        <v>32</v>
+      </c>
+      <c r="AI15">
         <v>500</v>
       </c>
-      <c r="AH15">
-        <v>120</v>
-      </c>
-      <c r="AI15">
-        <v>540</v>
-      </c>
       <c r="AJ15">
-        <v>900</v>
+        <v>26</v>
       </c>
       <c r="AK15">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL15">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM15">
         <v>580</v>
       </c>
       <c r="AN15">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AO15">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AP15">
-        <v>1.73</v>
+        <v>7.6</v>
       </c>
       <c r="AQ15">
+        <v>12</v>
+      </c>
+      <c r="AR15">
+        <v>32</v>
+      </c>
+      <c r="AS15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT15">
+        <v>5.8</v>
+      </c>
+      <c r="AU15">
+        <v>6.8</v>
+      </c>
+      <c r="AV15">
+        <v>17</v>
+      </c>
+      <c r="AW15">
+        <v>44</v>
+      </c>
+      <c r="AX15">
+        <v>9</v>
+      </c>
+      <c r="AY15">
         <v>9.4</v>
       </c>
-      <c r="AR15">
-        <v>14.5</v>
-      </c>
-      <c r="AS15">
-        <v>2</v>
-      </c>
-      <c r="AT15">
-        <v>5.1</v>
-      </c>
-      <c r="AU15">
-        <v>5.4</v>
-      </c>
-      <c r="AV15">
-        <v>12</v>
-      </c>
-      <c r="AW15">
-        <v>28</v>
-      </c>
-      <c r="AX15">
-        <v>6.6</v>
-      </c>
-      <c r="AY15">
-        <v>7.8</v>
-      </c>
       <c r="AZ15">
-        <v>1.94</v>
+        <v>21</v>
       </c>
       <c r="BA15">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="BB15">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="BC15">
-        <v>1.96</v>
+        <v>21</v>
       </c>
       <c r="BD15">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BE15">
-        <v>2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15">
-        <v>1.95</v>
+        <v>17.5</v>
       </c>
       <c r="BG15">
-        <v>2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB15" t="s">
         <v>167</v>
@@ -4499,64 +4499,64 @@
         <v>153</v>
       </c>
       <c r="F16">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G16">
         <v>1.41</v>
       </c>
       <c r="H16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J16">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K16">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L16">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M16">
+        <v>1.08</v>
+      </c>
+      <c r="N16">
+        <v>3.45</v>
+      </c>
+      <c r="O16">
+        <v>1.36</v>
+      </c>
+      <c r="P16">
+        <v>1.83</v>
+      </c>
+      <c r="Q16">
+        <v>2.08</v>
+      </c>
+      <c r="R16">
+        <v>1.31</v>
+      </c>
+      <c r="S16">
+        <v>3.8</v>
+      </c>
+      <c r="T16">
+        <v>2.48</v>
+      </c>
+      <c r="U16">
+        <v>1.56</v>
+      </c>
+      <c r="V16">
         <v>1.07</v>
-      </c>
-      <c r="N16">
-        <v>3.15</v>
-      </c>
-      <c r="O16">
-        <v>1.38</v>
-      </c>
-      <c r="P16">
-        <v>1.72</v>
-      </c>
-      <c r="Q16">
-        <v>2.2</v>
-      </c>
-      <c r="R16">
-        <v>1.26</v>
-      </c>
-      <c r="S16">
-        <v>4</v>
-      </c>
-      <c r="T16">
-        <v>2.6</v>
-      </c>
-      <c r="U16">
-        <v>1.52</v>
-      </c>
-      <c r="V16">
-        <v>1.06</v>
       </c>
       <c r="W16">
         <v>3.4</v>
       </c>
       <c r="X16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y16">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Z16">
         <v>540</v>
@@ -4565,160 +4565,160 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AC16">
         <v>12.5</v>
       </c>
       <c r="AD16">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="AE16">
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="AF16">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AG16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH16">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AI16">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="AJ16">
         <v>11</v>
       </c>
       <c r="AK16">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL16">
         <v>250</v>
       </c>
       <c r="AM16">
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="AN16">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
         <v>11.5</v>
       </c>
       <c r="AR16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS16">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT16">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AU16">
         <v>10</v>
       </c>
       <c r="AV16">
-        <v>40</v>
+        <v>8.4</v>
       </c>
       <c r="AW16">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX16">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AY16">
         <v>9.6</v>
       </c>
       <c r="AZ16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BA16">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB16">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC16">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD16">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="BE16">
+        <v>9.4</v>
+      </c>
+      <c r="BF16">
+        <v>6.8</v>
+      </c>
+      <c r="BG16">
+        <v>10</v>
+      </c>
+      <c r="BH16">
+        <v>3.5</v>
+      </c>
+      <c r="BI16">
+        <v>2.7</v>
+      </c>
+      <c r="BJ16">
+        <v>15</v>
+      </c>
+      <c r="BK16">
         <v>10.5</v>
-      </c>
-      <c r="BF16">
-        <v>6.6</v>
-      </c>
-      <c r="BG16">
-        <v>11</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="s">
         <v>167</v>
@@ -4741,22 +4741,22 @@
         <v>154</v>
       </c>
       <c r="F17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I17">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="J17">
         <v>6.8</v>
       </c>
       <c r="K17">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L17">
         <v>1.2</v>
@@ -4771,34 +4771,34 @@
         <v>1.11</v>
       </c>
       <c r="P17">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q17">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R17">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S17">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="T17">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U17">
         <v>2.26</v>
       </c>
       <c r="V17">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z17">
         <v>12</v>
@@ -4816,13 +4816,13 @@
         <v>11.5</v>
       </c>
       <c r="AE17">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF17">
         <v>140</v>
       </c>
       <c r="AG17">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH17">
         <v>25</v>
@@ -4834,31 +4834,31 @@
         <v>430</v>
       </c>
       <c r="AK17">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AL17">
+        <v>210</v>
+      </c>
+      <c r="AM17">
+        <v>95</v>
+      </c>
+      <c r="AN17">
         <v>100</v>
       </c>
-      <c r="AM17">
-        <v>260</v>
-      </c>
-      <c r="AN17">
-        <v>85</v>
-      </c>
       <c r="AO17">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AP17">
         <v>36</v>
       </c>
       <c r="AQ17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR17">
         <v>10</v>
       </c>
       <c r="AS17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT17">
         <v>46</v>
@@ -4870,10 +4870,10 @@
         <v>10</v>
       </c>
       <c r="AW17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX17">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="AY17">
         <v>32</v>
@@ -4882,25 +4882,25 @@
         <v>21</v>
       </c>
       <c r="BA17">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BB17">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC17">
-        <v>15.5</v>
+        <v>80</v>
       </c>
       <c r="BD17">
-        <v>14.5</v>
+        <v>46</v>
       </c>
       <c r="BE17">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BF17">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="BG17">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BH17">
         <v>6</v>
@@ -4912,52 +4912,52 @@
         <v>10.5</v>
       </c>
       <c r="BK17">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN17">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BO17">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BP17">
         <v>65</v>
       </c>
       <c r="BQ17">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BR17">
         <v>50</v>
       </c>
       <c r="BS17">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT17">
         <v>4.5</v>
       </c>
       <c r="BU17">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BV17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BW17">
         <v>5.5</v>
       </c>
       <c r="BX17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BY17">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CA17">
         <v>5.6</v>
@@ -4983,31 +4983,31 @@
         <v>155</v>
       </c>
       <c r="F18">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G18">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="H18">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I18">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K18">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N18">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O18">
         <v>1.21</v>
@@ -5022,28 +5022,28 @@
         <v>1.56</v>
       </c>
       <c r="S18">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T18">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U18">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V18">
         <v>1.25</v>
       </c>
       <c r="W18">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X18">
         <v>23</v>
       </c>
       <c r="Y18">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Z18">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AA18">
         <v>900</v>
@@ -5058,7 +5058,7 @@
         <v>19.5</v>
       </c>
       <c r="AE18">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AF18">
         <v>13</v>
@@ -5070,25 +5070,25 @@
         <v>18</v>
       </c>
       <c r="AI18">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AJ18">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL18">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AM18">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN18">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO18">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP18">
         <v>18.5</v>
@@ -5097,25 +5097,25 @@
         <v>18</v>
       </c>
       <c r="AR18">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AS18">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="AT18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU18">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV18">
         <v>16</v>
       </c>
       <c r="AW18">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AX18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY18">
         <v>8.800000000000001</v>
@@ -5124,22 +5124,22 @@
         <v>14.5</v>
       </c>
       <c r="BA18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BB18">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC18">
         <v>14.5</v>
       </c>
       <c r="BD18">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BE18">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BF18">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG18">
         <v>34</v>
@@ -5225,25 +5225,25 @@
         <v>156</v>
       </c>
       <c r="F19">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="G19">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H19">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I19">
+        <v>4</v>
+      </c>
+      <c r="J19">
         <v>4.1</v>
-      </c>
-      <c r="J19">
-        <v>3.75</v>
       </c>
       <c r="K19">
         <v>4.5</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M19">
         <v>1.03</v>
@@ -5255,16 +5255,16 @@
         <v>1.16</v>
       </c>
       <c r="P19">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q19">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R19">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="S19">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="T19">
         <v>1.49</v>
@@ -5276,7 +5276,7 @@
         <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X19">
         <v>30</v>
@@ -5303,10 +5303,10 @@
         <v>36</v>
       </c>
       <c r="AF19">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH19">
         <v>17</v>
@@ -5315,10 +5315,10 @@
         <v>38</v>
       </c>
       <c r="AJ19">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AK19">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL19">
         <v>26</v>
@@ -5330,115 +5330,115 @@
         <v>8.6</v>
       </c>
       <c r="AO19">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP19">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AQ19">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR19">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AS19">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT19">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AU19">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AW19">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX19">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AY19">
         <v>6.2</v>
       </c>
       <c r="AZ19">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BA19">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BB19">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC19">
+        <v>9</v>
+      </c>
+      <c r="BD19">
+        <v>6.8</v>
+      </c>
+      <c r="BE19">
+        <v>8</v>
+      </c>
+      <c r="BF19">
+        <v>4.5</v>
+      </c>
+      <c r="BG19">
+        <v>6.6</v>
+      </c>
+      <c r="BH19">
         <v>5.3</v>
       </c>
-      <c r="BD19">
-        <v>5.5</v>
-      </c>
-      <c r="BE19">
-        <v>6.2</v>
-      </c>
-      <c r="BF19">
-        <v>3.85</v>
-      </c>
-      <c r="BG19">
-        <v>5.5</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
       <c r="BI19">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5467,16 +5467,16 @@
         <v>157</v>
       </c>
       <c r="F20">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H20">
+        <v>2.68</v>
+      </c>
+      <c r="I20">
         <v>2.7</v>
-      </c>
-      <c r="I20">
-        <v>2.72</v>
       </c>
       <c r="J20">
         <v>3.4</v>
@@ -5485,16 +5485,16 @@
         <v>3.45</v>
       </c>
       <c r="L20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M20">
         <v>1.09</v>
       </c>
       <c r="N20">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O20">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P20">
         <v>1.84</v>
@@ -5503,22 +5503,22 @@
         <v>2.16</v>
       </c>
       <c r="R20">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S20">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T20">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U20">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W20">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X20">
         <v>12</v>
@@ -5527,7 +5527,7 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA20">
         <v>40</v>
@@ -5542,7 +5542,7 @@
         <v>12</v>
       </c>
       <c r="AE20">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF20">
         <v>19</v>
@@ -5566,10 +5566,10 @@
         <v>48</v>
       </c>
       <c r="AM20">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN20">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO20">
         <v>29</v>
@@ -5608,43 +5608,43 @@
         <v>16.5</v>
       </c>
       <c r="BA20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB20">
         <v>44</v>
       </c>
       <c r="BC20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD20">
         <v>44</v>
       </c>
       <c r="BE20">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG20">
         <v>26</v>
       </c>
       <c r="BH20">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI20">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BJ20">
         <v>9.800000000000001</v>
       </c>
       <c r="BK20">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL20">
         <v>140</v>
       </c>
       <c r="BM20">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BN20">
         <v>5.9</v>
@@ -5656,16 +5656,16 @@
         <v>24</v>
       </c>
       <c r="BQ20">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BR20">
         <v>38</v>
       </c>
       <c r="BS20">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BT20">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU20">
         <v>5.1</v>
@@ -5674,19 +5674,19 @@
         <v>22</v>
       </c>
       <c r="BW20">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BX20">
         <v>38</v>
       </c>
       <c r="BY20">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="BZ20">
         <v>34</v>
       </c>
       <c r="CA20">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="CB20" t="s">
         <v>167</v>
@@ -5709,82 +5709,82 @@
         <v>158</v>
       </c>
       <c r="F21">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="G21">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="H21">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I21">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J21">
         <v>4.1</v>
       </c>
       <c r="K21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M21">
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>1.19</v>
       </c>
       <c r="P21">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q21">
         <v>1.57</v>
       </c>
       <c r="R21">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S21">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T21">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U21">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="V21">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="X21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y21">
         <v>22</v>
       </c>
       <c r="Z21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA21">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB21">
         <v>14</v>
       </c>
       <c r="AC21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE21">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AF21">
         <v>16</v>
@@ -5793,16 +5793,16 @@
         <v>11</v>
       </c>
       <c r="AH21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI21">
         <v>38</v>
       </c>
       <c r="AJ21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK21">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL21">
         <v>26</v>
@@ -5811,10 +5811,10 @@
         <v>60</v>
       </c>
       <c r="AN21">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO21">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AP21">
         <v>22</v>
@@ -5826,109 +5826,109 @@
         <v>29</v>
       </c>
       <c r="AS21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT21">
         <v>13</v>
       </c>
       <c r="AU21">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW21">
         <v>32</v>
       </c>
       <c r="AX21">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY21">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ21">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA21">
         <v>32</v>
       </c>
       <c r="BB21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC21">
         <v>16</v>
       </c>
       <c r="BD21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE21">
         <v>48</v>
       </c>
       <c r="BF21">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG21">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH21">
         <v>5.2</v>
       </c>
       <c r="BI21">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BJ21">
         <v>9</v>
       </c>
       <c r="BK21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BN21">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO21">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP21">
         <v>13</v>
       </c>
       <c r="BQ21">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BR21">
         <v>22</v>
       </c>
       <c r="BS21">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BT21">
         <v>8</v>
       </c>
       <c r="BU21">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BV21">
         <v>28</v>
       </c>
       <c r="BW21">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BX21">
         <v>32</v>
       </c>
       <c r="BY21">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BZ21">
         <v>15</v>
       </c>
       <c r="CA21">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="CB21" t="s">
         <v>167</v>
@@ -5951,19 +5951,19 @@
         <v>159</v>
       </c>
       <c r="F22">
+        <v>1.56</v>
+      </c>
+      <c r="G22">
         <v>1.57</v>
       </c>
-      <c r="G22">
-        <v>1.58</v>
-      </c>
       <c r="H22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I22">
         <v>5.9</v>
       </c>
       <c r="J22">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K22">
         <v>5.4</v>
@@ -5984,43 +5984,43 @@
         <v>3.7</v>
       </c>
       <c r="Q22">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R22">
         <v>2.1</v>
       </c>
       <c r="S22">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="T22">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U22">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="V22">
         <v>1.2</v>
       </c>
       <c r="W22">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X22">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="Y22">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA22">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD22">
         <v>24</v>
@@ -6041,7 +6041,7 @@
         <v>44</v>
       </c>
       <c r="AJ22">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK22">
         <v>13.5</v>
@@ -6053,13 +6053,13 @@
         <v>50</v>
       </c>
       <c r="AN22">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP22">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AQ22">
         <v>34</v>
@@ -6071,28 +6071,28 @@
         <v>46</v>
       </c>
       <c r="AT22">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV22">
         <v>21</v>
       </c>
       <c r="AW22">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX22">
         <v>14</v>
       </c>
       <c r="AY22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA22">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BB22">
         <v>16.5</v>
@@ -6107,70 +6107,70 @@
         <v>40</v>
       </c>
       <c r="BF22">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG22">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH22">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BI22">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BJ22">
         <v>9.199999999999999</v>
       </c>
       <c r="BK22">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN22">
         <v>5.2</v>
       </c>
       <c r="BO22">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP22">
         <v>9.6</v>
       </c>
       <c r="BQ22">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR22">
         <v>17</v>
       </c>
       <c r="BS22">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT22">
         <v>10.5</v>
       </c>
       <c r="BU22">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY22">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ22">
         <v>9</v>
       </c>
       <c r="CA22">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB22" t="s">
         <v>167</v>
@@ -6193,97 +6193,97 @@
         <v>160</v>
       </c>
       <c r="F23">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="G23">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="H23">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="I23">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="J23">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="K23">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M23">
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="O23">
+        <v>1.08</v>
+      </c>
+      <c r="P23">
+        <v>4.6</v>
+      </c>
+      <c r="Q23">
+        <v>1.24</v>
+      </c>
+      <c r="R23">
+        <v>2.46</v>
+      </c>
+      <c r="S23">
+        <v>1.62</v>
+      </c>
+      <c r="T23">
+        <v>1.56</v>
+      </c>
+      <c r="U23">
+        <v>2.48</v>
+      </c>
+      <c r="V23">
         <v>1.09</v>
       </c>
-      <c r="P23">
-        <v>4</v>
-      </c>
-      <c r="Q23">
-        <v>1.26</v>
-      </c>
-      <c r="R23">
-        <v>2.24</v>
-      </c>
-      <c r="S23">
-        <v>1.65</v>
-      </c>
-      <c r="T23">
-        <v>1.53</v>
-      </c>
-      <c r="U23">
-        <v>2.58</v>
-      </c>
-      <c r="V23">
-        <v>1.12</v>
-      </c>
       <c r="W23">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="X23">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Y23">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="Z23">
-        <v>540</v>
+        <v>160</v>
       </c>
       <c r="AA23">
-        <v>230</v>
+        <v>420</v>
       </c>
       <c r="AB23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC23">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AD23">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AE23">
-        <v>95</v>
+        <v>240</v>
       </c>
       <c r="AF23">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG23">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH23">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI23">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ23">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK23">
         <v>14</v>
@@ -6292,121 +6292,121 @@
         <v>22</v>
       </c>
       <c r="AM23">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN23">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="AO23">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP23">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AR23">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AS23">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="AT23">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU23">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AV23">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AW23">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="AX23">
         <v>13</v>
       </c>
       <c r="AY23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ23">
+        <v>20</v>
+      </c>
+      <c r="BA23">
+        <v>60</v>
+      </c>
+      <c r="BB23">
+        <v>12.5</v>
+      </c>
+      <c r="BC23">
+        <v>11</v>
+      </c>
+      <c r="BD23">
         <v>19</v>
       </c>
-      <c r="BA23">
-        <v>50</v>
-      </c>
-      <c r="BB23">
-        <v>13</v>
-      </c>
-      <c r="BC23">
-        <v>11.5</v>
-      </c>
-      <c r="BD23">
-        <v>18.5</v>
-      </c>
       <c r="BE23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF23">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="BG23">
         <v>34</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6435,64 +6435,64 @@
         <v>161</v>
       </c>
       <c r="F24">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="G24">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="H24">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I24">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J24">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="K24">
         <v>3.1</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M24">
         <v>1.13</v>
       </c>
       <c r="N24">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="O24">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="P24">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="Q24">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="R24">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S24">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="T24">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U24">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="V24">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W24">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X24">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="Y24">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Z24">
         <v>500</v>
@@ -6501,100 +6501,100 @@
         <v>900</v>
       </c>
       <c r="AB24">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="AC24">
-        <v>42</v>
+        <v>7.2</v>
       </c>
       <c r="AD24">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE24">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AF24">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG24">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH24">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AI24">
         <v>500</v>
       </c>
       <c r="AJ24">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK24">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AL24">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AM24">
         <v>500</v>
       </c>
       <c r="AN24">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AO24">
         <v>500</v>
       </c>
       <c r="AP24">
-        <v>1.54</v>
+        <v>6.4</v>
       </c>
       <c r="AQ24">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR24">
-        <v>1.81</v>
+        <v>12</v>
       </c>
       <c r="AS24">
-        <v>1.83</v>
+        <v>27</v>
       </c>
       <c r="AT24">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AU24">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV24">
+        <v>14.5</v>
+      </c>
+      <c r="AW24">
+        <v>9.4</v>
+      </c>
+      <c r="AX24">
         <v>12</v>
       </c>
-      <c r="AW24">
-        <v>1.83</v>
-      </c>
-      <c r="AX24">
-        <v>7.2</v>
-      </c>
       <c r="AY24">
-        <v>1.83</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA24">
-        <v>1.83</v>
+        <v>10</v>
       </c>
       <c r="BB24">
-        <v>1.94</v>
+        <v>8.6</v>
       </c>
       <c r="BC24">
-        <v>1.79</v>
+        <v>15.5</v>
       </c>
       <c r="BD24">
-        <v>2.5</v>
+        <v>28</v>
       </c>
       <c r="BE24">
-        <v>1.54</v>
+        <v>10.5</v>
       </c>
       <c r="BF24">
-        <v>1.55</v>
+        <v>32</v>
       </c>
       <c r="BG24">
-        <v>1.55</v>
+        <v>10</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6677,226 +6677,226 @@
         <v>162</v>
       </c>
       <c r="F25">
+        <v>3.1</v>
+      </c>
+      <c r="G25">
+        <v>3.4</v>
+      </c>
+      <c r="H25">
         <v>2.62</v>
       </c>
-      <c r="G25">
-        <v>3.45</v>
-      </c>
-      <c r="H25">
-        <v>2.58</v>
-      </c>
       <c r="I25">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J25">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="K25">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="L25">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N25">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O25">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="P25">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="Q25">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="R25">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S25">
-        <v>2.34</v>
+        <v>5.1</v>
       </c>
       <c r="T25">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U25">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="V25">
+        <v>1.55</v>
+      </c>
+      <c r="W25">
         <v>1.42</v>
       </c>
-      <c r="W25">
-        <v>1.41</v>
-      </c>
       <c r="X25">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ25">
-        <v>1.09</v>
+        <v>6.4</v>
       </c>
       <c r="AR25">
-        <v>1.09</v>
+        <v>12.5</v>
       </c>
       <c r="AS25">
-        <v>1.09</v>
+        <v>30</v>
       </c>
       <c r="AT25">
-        <v>1.09</v>
+        <v>8.4</v>
       </c>
       <c r="AU25">
-        <v>1.09</v>
+        <v>5.4</v>
       </c>
       <c r="AV25">
-        <v>1.09</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW25">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="AX25">
-        <v>1.09</v>
+        <v>14</v>
       </c>
       <c r="AY25">
-        <v>1.09</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25">
-        <v>1.09</v>
+        <v>16</v>
       </c>
       <c r="BA25">
-        <v>1.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB25">
-        <v>1.09</v>
+        <v>40</v>
       </c>
       <c r="BC25">
-        <v>1.09</v>
+        <v>32</v>
       </c>
       <c r="BD25">
-        <v>1.09</v>
+        <v>8.4</v>
       </c>
       <c r="BE25">
-        <v>1.09</v>
+        <v>9</v>
       </c>
       <c r="BF25">
-        <v>1.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG25">
-        <v>1.09</v>
+        <v>8</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI25">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK25">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO25">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ25">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS25">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU25">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB25" t="s">
         <v>167</v>
@@ -6919,31 +6919,31 @@
         <v>163</v>
       </c>
       <c r="F26">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G26">
         <v>2.26</v>
       </c>
       <c r="H26">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I26">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J26">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K26">
         <v>3.25</v>
       </c>
       <c r="L26">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M26">
         <v>1.13</v>
       </c>
       <c r="N26">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O26">
         <v>1.53</v>
@@ -6952,22 +6952,22 @@
         <v>1.56</v>
       </c>
       <c r="Q26">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="R26">
         <v>1.2</v>
       </c>
       <c r="S26">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T26">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U26">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
         <v>1.79</v>
@@ -6976,7 +6976,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z26">
         <v>32</v>
@@ -6985,7 +6985,7 @@
         <v>900</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC26">
         <v>7.2</v>
@@ -7006,7 +7006,7 @@
         <v>34</v>
       </c>
       <c r="AI26">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="AJ26">
         <v>36</v>
@@ -7027,7 +7027,7 @@
         <v>500</v>
       </c>
       <c r="AP26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ26">
         <v>10</v>
@@ -7036,19 +7036,19 @@
         <v>24</v>
       </c>
       <c r="AS26">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU26">
         <v>6.4</v>
       </c>
       <c r="AV26">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX26">
         <v>10.5</v>
@@ -7060,7 +7060,7 @@
         <v>13</v>
       </c>
       <c r="BA26">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BB26">
         <v>21</v>
@@ -7069,55 +7069,55 @@
         <v>14.5</v>
       </c>
       <c r="BD26">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE26">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF26">
         <v>18.5</v>
       </c>
       <c r="BG26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH26">
         <v>3.05</v>
       </c>
       <c r="BI26">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BJ26">
         <v>11.5</v>
       </c>
       <c r="BK26">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN26">
         <v>4.7</v>
       </c>
       <c r="BO26">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP26">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BQ26">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BR26">
         <v>48</v>
       </c>
       <c r="BS26">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BT26">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BU26">
         <v>5.6</v>
@@ -7126,19 +7126,19 @@
         <v>48</v>
       </c>
       <c r="BW26">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BX26">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY26">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BZ26">
         <v>55</v>
       </c>
       <c r="CA26">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB26" t="s">
         <v>167</v>
@@ -7161,61 +7161,61 @@
         <v>164</v>
       </c>
       <c r="F27">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G27">
         <v>2.16</v>
       </c>
       <c r="H27">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I27">
         <v>4.6</v>
       </c>
       <c r="J27">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K27">
         <v>3.35</v>
       </c>
       <c r="L27">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="M27">
         <v>1.12</v>
       </c>
       <c r="N27">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="O27">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P27">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q27">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R27">
         <v>1.22</v>
       </c>
       <c r="S27">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T27">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U27">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V27">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
         <v>1.86</v>
       </c>
       <c r="X27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y27">
         <v>12.5</v>
@@ -7227,7 +7227,7 @@
         <v>900</v>
       </c>
       <c r="AB27">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>7.8</v>
@@ -7236,7 +7236,7 @@
         <v>20</v>
       </c>
       <c r="AE27">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AF27">
         <v>12.5</v>
@@ -7248,7 +7248,7 @@
         <v>24</v>
       </c>
       <c r="AI27">
-        <v>380</v>
+        <v>200</v>
       </c>
       <c r="AJ27">
         <v>32</v>
@@ -7269,7 +7269,7 @@
         <v>500</v>
       </c>
       <c r="AP27">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AQ27">
         <v>9.6</v>
@@ -7278,7 +7278,7 @@
         <v>22</v>
       </c>
       <c r="AS27">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT27">
         <v>6.4</v>
@@ -7302,28 +7302,28 @@
         <v>19.5</v>
       </c>
       <c r="BA27">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB27">
         <v>11.5</v>
       </c>
       <c r="BC27">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BD27">
         <v>23</v>
       </c>
       <c r="BE27">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF27">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BG27">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI27">
         <v>2.38</v>
@@ -7332,13 +7332,13 @@
         <v>13</v>
       </c>
       <c r="BK27">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BN27">
         <v>5.2</v>
@@ -7350,37 +7350,37 @@
         <v>19.5</v>
       </c>
       <c r="BQ27">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BR27">
         <v>44</v>
       </c>
       <c r="BS27">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BT27">
         <v>8.4</v>
       </c>
       <c r="BU27">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BV27">
         <v>50</v>
       </c>
       <c r="BW27">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BZ27">
         <v>46</v>
       </c>
       <c r="CA27">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="CB27" t="s">
         <v>167</v>
@@ -7403,58 +7403,58 @@
         <v>165</v>
       </c>
       <c r="F28">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G28">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H28">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="I28">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J28">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K28">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M28">
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O28">
         <v>1.22</v>
       </c>
       <c r="P28">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q28">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="R28">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S28">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T28">
         <v>1.58</v>
       </c>
       <c r="U28">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V28">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="X28">
         <v>23</v>
@@ -7466,7 +7466,7 @@
         <v>28</v>
       </c>
       <c r="AA28">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AB28">
         <v>14</v>
@@ -7487,91 +7487,91 @@
         <v>12</v>
       </c>
       <c r="AH28">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AI28">
         <v>38</v>
       </c>
       <c r="AJ28">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK28">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AL28">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM28">
         <v>70</v>
       </c>
       <c r="AN28">
+        <v>13.5</v>
+      </c>
+      <c r="AO28">
+        <v>23</v>
+      </c>
+      <c r="AP28">
+        <v>7</v>
+      </c>
+      <c r="AQ28">
+        <v>14.5</v>
+      </c>
+      <c r="AR28">
+        <v>20</v>
+      </c>
+      <c r="AS28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT28">
+        <v>5.9</v>
+      </c>
+      <c r="AU28">
+        <v>4.9</v>
+      </c>
+      <c r="AV28">
+        <v>12</v>
+      </c>
+      <c r="AW28">
+        <v>7.8</v>
+      </c>
+      <c r="AX28">
         <v>15</v>
       </c>
-      <c r="AO28">
-        <v>25</v>
-      </c>
-      <c r="AP28">
-        <v>6</v>
-      </c>
-      <c r="AQ28">
-        <v>5.5</v>
-      </c>
-      <c r="AR28">
-        <v>6.2</v>
-      </c>
-      <c r="AS28">
-        <v>6.8</v>
-      </c>
-      <c r="AT28">
-        <v>5.1</v>
-      </c>
-      <c r="AU28">
-        <v>4.3</v>
-      </c>
-      <c r="AV28">
-        <v>5.3</v>
-      </c>
-      <c r="AW28">
-        <v>6.4</v>
-      </c>
-      <c r="AX28">
-        <v>5.6</v>
-      </c>
       <c r="AY28">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AZ28">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="BA28">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BB28">
-        <v>6.6</v>
+        <v>26</v>
       </c>
       <c r="BC28">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD28">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BE28">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BF28">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="BG28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI28">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK28">
         <v>1.04</v>
@@ -7583,37 +7583,37 @@
         <v>1.04</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO28">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ28">
         <v>1.04</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS28">
         <v>1.04</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU28">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW28">
         <v>1.04</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY28">
         <v>1.04</v>
@@ -7663,7 +7663,7 @@
         <v>3.5</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M29">
         <v>1.1</v>
@@ -7702,10 +7702,10 @@
         <v>12</v>
       </c>
       <c r="Y29">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z29">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA29">
         <v>130</v>
@@ -7717,7 +7717,7 @@
         <v>8</v>
       </c>
       <c r="AD29">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE29">
         <v>70</v>
@@ -7726,7 +7726,7 @@
         <v>13.5</v>
       </c>
       <c r="AG29">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH29">
         <v>25</v>
@@ -7741,10 +7741,10 @@
         <v>27</v>
       </c>
       <c r="AL29">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM29">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN29">
         <v>25</v>
@@ -7753,28 +7753,28 @@
         <v>110</v>
       </c>
       <c r="AP29">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR29">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS29">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT29">
         <v>6.4</v>
       </c>
       <c r="AU29">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV29">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW29">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX29">
         <v>10</v>
@@ -7786,85 +7786,85 @@
         <v>18</v>
       </c>
       <c r="BA29">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB29">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="BC29">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="BD29">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE29">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF29">
-        <v>18.5</v>
+        <v>6</v>
       </c>
       <c r="BG29">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI29">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK29">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO29">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ29">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU29">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB29" t="s">
         <v>167</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -517,7 +517,7 @@
     <t>Aguilas Doradas</t>
   </si>
   <si>
-    <t>2026-08-25 04:44:01</t>
+    <t>2026-08-25 06:53:18</t>
   </si>
 </sst>
 </file>
@@ -1117,46 +1117,46 @@
         <v>3.55</v>
       </c>
       <c r="H2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I2">
         <v>2.34</v>
       </c>
       <c r="J2">
+        <v>3.45</v>
+      </c>
+      <c r="K2">
         <v>3.5</v>
       </c>
-      <c r="K2">
-        <v>3.55</v>
-      </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O2">
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="T2">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U2">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
         <v>1.74</v>
@@ -1165,10 +1165,10 @@
         <v>1.39</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z2">
         <v>14.5</v>
@@ -1177,10 +1177,10 @@
         <v>30</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD2">
         <v>11</v>
@@ -1189,40 +1189,40 @@
         <v>25</v>
       </c>
       <c r="AF2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ2">
         <v>65</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
         <v>13</v>
@@ -1231,16 +1231,16 @@
         <v>27</v>
       </c>
       <c r="AT2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV2">
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX2">
         <v>21</v>
@@ -1249,31 +1249,31 @@
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BC2">
         <v>34</v>
       </c>
       <c r="BD2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE2">
         <v>85</v>
       </c>
       <c r="BF2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG2">
         <v>18</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI2">
         <v>3</v>
@@ -1282,7 +1282,7 @@
         <v>9.6</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL2">
         <v>130</v>
@@ -1291,22 +1291,22 @@
         <v>110</v>
       </c>
       <c r="BN2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BP2">
         <v>28</v>
       </c>
       <c r="BQ2">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BT2">
         <v>5.1</v>
@@ -1315,22 +1315,22 @@
         <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BX2">
         <v>32</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="BZ2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA2">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="CB2" t="s">
         <v>167</v>
@@ -1353,22 +1353,22 @@
         <v>140</v>
       </c>
       <c r="F3">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
+        <v>3.25</v>
+      </c>
+      <c r="K3">
         <v>3.3</v>
-      </c>
-      <c r="K3">
-        <v>3.35</v>
       </c>
       <c r="L3">
         <v>1.55</v>
@@ -1377,13 +1377,13 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q3">
         <v>2.42</v>
@@ -1395,67 +1395,67 @@
         <v>4.8</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
         <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI3">
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL3">
         <v>55</v>
       </c>
       <c r="AM3">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO3">
         <v>60</v>
@@ -1467,40 +1467,40 @@
         <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AS3">
         <v>50</v>
       </c>
       <c r="AT3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY3">
         <v>11</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
         <v>50</v>
       </c>
       <c r="BB3">
+        <v>34</v>
+      </c>
+      <c r="BC3">
         <v>30</v>
-      </c>
-      <c r="BC3">
-        <v>27</v>
       </c>
       <c r="BD3">
         <v>46</v>
@@ -1509,22 +1509,22 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BG3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BH3">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BI3">
         <v>2.68</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL3">
         <v>180</v>
@@ -1533,46 +1533,46 @@
         <v>130</v>
       </c>
       <c r="BN3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BR3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU3">
         <v>5.7</v>
       </c>
       <c r="BV3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
         <v>42</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB3" t="s">
         <v>167</v>
@@ -1595,226 +1595,226 @@
         <v>141</v>
       </c>
       <c r="F4">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="G4">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q4">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S4">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
         <v>1.92</v>
       </c>
       <c r="V4">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W4">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="X4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z4">
         <v>75</v>
       </c>
       <c r="AA4">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AB4">
         <v>9</v>
       </c>
       <c r="AC4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD4">
         <v>30</v>
       </c>
       <c r="AE4">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI4">
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL4">
         <v>38</v>
       </c>
       <c r="AM4">
+        <v>140</v>
+      </c>
+      <c r="AN4">
+        <v>5.7</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>19</v>
+      </c>
+      <c r="AQ4">
+        <v>27</v>
+      </c>
+      <c r="AR4">
+        <v>65</v>
+      </c>
+      <c r="AS4">
         <v>150</v>
       </c>
-      <c r="AN4">
-        <v>6.4</v>
-      </c>
-      <c r="AO4">
-        <v>160</v>
-      </c>
-      <c r="AP4">
-        <v>17.5</v>
-      </c>
-      <c r="AQ4">
-        <v>22</v>
-      </c>
-      <c r="AR4">
-        <v>60</v>
-      </c>
-      <c r="AS4">
-        <v>20</v>
-      </c>
       <c r="AT4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AW4">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AX4">
         <v>8</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BB4">
         <v>10.5</v>
       </c>
       <c r="BC4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD4">
         <v>32</v>
       </c>
       <c r="BE4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF4">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BG4">
         <v>100</v>
       </c>
       <c r="BH4">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BI4">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BL4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BM4">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="BN4">
         <v>3.85</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP4">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR4">
         <v>24</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BT4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU4">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BV4">
         <v>75</v>
       </c>
       <c r="BW4">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BX4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY4">
         <v>16</v>
       </c>
       <c r="BZ4">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA4">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>167</v>
@@ -1837,34 +1837,34 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="G5">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="H5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
         <v>1.37</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
         <v>3.9</v>
       </c>
       <c r="O5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P5">
         <v>2</v>
@@ -1879,25 +1879,25 @@
         <v>3.2</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U5">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V5">
         <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="X5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z5">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AA5">
         <v>900</v>
@@ -1906,142 +1906,142 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AE5">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AF5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI5">
         <v>320</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL5">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AM5">
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO5">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AP5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ5">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AR5">
         <v>8.800000000000001</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AX5">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY5">
         <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BB5">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BC5">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BF5">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BG5">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH5">
         <v>3.7</v>
       </c>
       <c r="BI5">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO5">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BP5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BV5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
         <v>8.6</v>
@@ -2050,13 +2050,13 @@
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="s">
         <v>167</v>
@@ -2079,16 +2079,16 @@
         <v>143</v>
       </c>
       <c r="F6">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="G6">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="H6">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="I6">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="J6">
         <v>3.85</v>
@@ -2103,172 +2103,172 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O6">
         <v>1.23</v>
       </c>
       <c r="P6">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q6">
         <v>1.69</v>
       </c>
       <c r="R6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S6">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T6">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U6">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V6">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="X6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Z6">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AA6">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="AB6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD6">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AF6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
         <v>16</v>
       </c>
       <c r="AI6">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AJ6">
-        <v>900</v>
+        <v>29</v>
       </c>
       <c r="AK6">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AL6">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM6">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO6">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AP6">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR6">
         <v>23</v>
       </c>
       <c r="AS6">
+        <v>46</v>
+      </c>
+      <c r="AT6">
         <v>11</v>
       </c>
-      <c r="AT6">
-        <v>10</v>
-      </c>
       <c r="AU6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6">
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AX6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="BB6">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BC6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD6">
         <v>23</v>
       </c>
       <c r="BE6">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="BF6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6">
         <v>9</v>
       </c>
       <c r="BK6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN6">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BO6">
         <v>4</v>
       </c>
       <c r="BP6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BQ6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2277,22 +2277,22 @@
         <v>8.4</v>
       </c>
       <c r="BT6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU6">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV6">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2321,85 +2321,85 @@
         <v>144</v>
       </c>
       <c r="F7">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="G7">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H7">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
         <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="T7">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="U7">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X7">
+        <v>13</v>
+      </c>
+      <c r="Y7">
+        <v>12.5</v>
+      </c>
+      <c r="Z7">
+        <v>970</v>
+      </c>
+      <c r="AA7">
+        <v>900</v>
+      </c>
+      <c r="AB7">
+        <v>10.5</v>
+      </c>
+      <c r="AC7">
+        <v>8</v>
+      </c>
+      <c r="AD7">
         <v>14.5</v>
       </c>
-      <c r="Y7">
-        <v>13</v>
-      </c>
-      <c r="Z7">
-        <v>24</v>
-      </c>
-      <c r="AA7">
-        <v>220</v>
-      </c>
-      <c r="AB7">
-        <v>11</v>
-      </c>
-      <c r="AC7">
-        <v>8.4</v>
-      </c>
-      <c r="AD7">
-        <v>15</v>
-      </c>
       <c r="AE7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
@@ -2423,85 +2423,85 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO7">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AP7">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
         <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT7">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU7">
         <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW7">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY7">
         <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>5.6</v>
+        <v>15</v>
       </c>
       <c r="BA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB7">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BC7">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BD7">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE7">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF7">
         <v>18.5</v>
       </c>
       <c r="BG7">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BH7">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BI7">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BN7">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO7">
         <v>4.3</v>
@@ -2510,37 +2510,37 @@
         <v>20</v>
       </c>
       <c r="BQ7">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BR7">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BT7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU7">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW7">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA7">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="s">
         <v>167</v>
@@ -2569,10 +2569,10 @@
         <v>2.9</v>
       </c>
       <c r="H8">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I8">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J8">
         <v>3.55</v>
@@ -2587,28 +2587,28 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O8">
         <v>1.3</v>
       </c>
       <c r="P8">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q8">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R8">
         <v>1.41</v>
       </c>
       <c r="S8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T8">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U8">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
         <v>1.57</v>
@@ -2620,28 +2620,28 @@
         <v>16</v>
       </c>
       <c r="Y8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA8">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="AB8">
         <v>13</v>
       </c>
       <c r="AC8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AF8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG8">
         <v>13</v>
@@ -2650,139 +2650,139 @@
         <v>17</v>
       </c>
       <c r="AI8">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="AK8">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AL8">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN8">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AO8">
         <v>24</v>
       </c>
       <c r="AP8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AT8">
         <v>10.5</v>
       </c>
       <c r="AU8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AX8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY8">
         <v>11</v>
       </c>
       <c r="AZ8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA8">
         <v>32</v>
       </c>
       <c r="BB8">
+        <v>30</v>
+      </c>
+      <c r="BC8">
+        <v>23</v>
+      </c>
+      <c r="BD8">
+        <v>30</v>
+      </c>
+      <c r="BE8">
+        <v>60</v>
+      </c>
+      <c r="BF8">
+        <v>21</v>
+      </c>
+      <c r="BG8">
         <v>20</v>
-      </c>
-      <c r="BC8">
-        <v>14.5</v>
-      </c>
-      <c r="BD8">
-        <v>18.5</v>
-      </c>
-      <c r="BE8">
-        <v>9</v>
-      </c>
-      <c r="BF8">
-        <v>20</v>
-      </c>
-      <c r="BG8">
-        <v>17.5</v>
       </c>
       <c r="BH8">
         <v>3.65</v>
       </c>
       <c r="BI8">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ8">
         <v>9.6</v>
       </c>
       <c r="BK8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN8">
         <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP8">
         <v>22</v>
       </c>
       <c r="BQ8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU8">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BV8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX8">
         <v>34</v>
       </c>
       <c r="BY8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
         <v>26</v>
       </c>
       <c r="CA8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
         <v>167</v>
@@ -2805,10 +2805,10 @@
         <v>146</v>
       </c>
       <c r="F9">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G9">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H9">
         <v>4.5</v>
@@ -2823,67 +2823,67 @@
         <v>4.1</v>
       </c>
       <c r="L9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M9">
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O9">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q9">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R9">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S9">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T9">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V9">
         <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X9">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y9">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA9">
         <v>900</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE9">
         <v>150</v>
       </c>
       <c r="AF9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
@@ -2895,19 +2895,19 @@
         <v>170</v>
       </c>
       <c r="AJ9">
+        <v>21</v>
+      </c>
+      <c r="AK9">
         <v>24</v>
       </c>
-      <c r="AK9">
-        <v>22</v>
-      </c>
       <c r="AL9">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AM9">
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO9">
         <v>600</v>
@@ -2916,64 +2916,64 @@
         <v>13.5</v>
       </c>
       <c r="AQ9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS9">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="AT9">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV9">
         <v>16</v>
       </c>
       <c r="AW9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX9">
         <v>10</v>
       </c>
       <c r="AY9">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD9">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE9">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="BF9">
         <v>11</v>
       </c>
       <c r="BG9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH9">
         <v>3.5</v>
       </c>
       <c r="BI9">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BJ9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK9">
         <v>7.6</v>
@@ -2982,7 +2982,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
@@ -2991,7 +2991,7 @@
         <v>4</v>
       </c>
       <c r="BP9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9">
         <v>9.6</v>
@@ -3000,7 +3000,7 @@
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9">
         <v>8.199999999999999</v>
@@ -3012,19 +3012,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ9">
         <v>24</v>
       </c>
       <c r="CA9">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="s">
         <v>167</v>
@@ -3047,16 +3047,16 @@
         <v>147</v>
       </c>
       <c r="F10">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G10">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3068,7 +3068,7 @@
         <v>1.37</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
         <v>4.5</v>
@@ -3077,31 +3077,31 @@
         <v>1.27</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q10">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R10">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S10">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T10">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U10">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W10">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y10">
         <v>17.5</v>
@@ -3116,46 +3116,46 @@
         <v>11</v>
       </c>
       <c r="AC10">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>13</v>
       </c>
       <c r="AG10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH10">
         <v>18.5</v>
       </c>
       <c r="AI10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ10">
         <v>23</v>
       </c>
       <c r="AK10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL10">
         <v>32</v>
       </c>
       <c r="AM10">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP10">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AQ10">
         <v>15</v>
@@ -3164,109 +3164,109 @@
         <v>27</v>
       </c>
       <c r="AS10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT10">
         <v>9.800000000000001</v>
       </c>
       <c r="AU10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY10">
         <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA10">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BB10">
         <v>20</v>
       </c>
       <c r="BC10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF10">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH10">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="BI10">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BJ10">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK10">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL10">
         <v>130</v>
       </c>
       <c r="BM10">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BN10">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP10">
         <v>16</v>
       </c>
       <c r="BQ10">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="BR10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BS10">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT10">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BU10">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="BV10">
         <v>34</v>
       </c>
       <c r="BW10">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BX10">
         <v>48</v>
       </c>
       <c r="BY10">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA10">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="s">
         <v>167</v>
@@ -3289,19 +3289,19 @@
         <v>148</v>
       </c>
       <c r="F11">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G11">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="H11">
+        <v>4.6</v>
+      </c>
+      <c r="I11">
         <v>4.7</v>
       </c>
-      <c r="I11">
-        <v>5</v>
-      </c>
       <c r="J11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
         <v>4.6</v>
@@ -3313,13 +3313,13 @@
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q11">
         <v>1.58</v>
@@ -3331,70 +3331,70 @@
         <v>2.44</v>
       </c>
       <c r="T11">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="U11">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V11">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W11">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z11">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB11">
         <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD11">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF11">
         <v>13</v>
       </c>
       <c r="AG11">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH11">
+        <v>16</v>
+      </c>
+      <c r="AI11">
+        <v>48</v>
+      </c>
+      <c r="AJ11">
+        <v>19</v>
+      </c>
+      <c r="AK11">
         <v>16.5</v>
       </c>
-      <c r="AI11">
-        <v>50</v>
-      </c>
-      <c r="AJ11">
-        <v>18.5</v>
-      </c>
-      <c r="AK11">
-        <v>16</v>
-      </c>
       <c r="AL11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN11">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AO11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP11">
         <v>22</v>
@@ -3403,106 +3403,106 @@
         <v>22</v>
       </c>
       <c r="AR11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS11">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AT11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU11">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV11">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11">
         <v>15</v>
       </c>
       <c r="BA11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB11">
         <v>16.5</v>
       </c>
       <c r="BC11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE11">
         <v>55</v>
       </c>
       <c r="BF11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG11">
         <v>32</v>
       </c>
       <c r="BH11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI11">
         <v>3.6</v>
       </c>
       <c r="BJ11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK11">
         <v>6.2</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO11">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ11">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR11">
         <v>21</v>
       </c>
       <c r="BS11">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT11">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU11">
         <v>5.8</v>
       </c>
       <c r="BV11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3531,100 +3531,100 @@
         <v>149</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H12">
         <v>2.42</v>
       </c>
       <c r="I12">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K12">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M12">
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O12">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
+        <v>1.51</v>
+      </c>
+      <c r="S12">
+        <v>2.84</v>
+      </c>
+      <c r="T12">
+        <v>1.64</v>
+      </c>
+      <c r="U12">
+        <v>2.46</v>
+      </c>
+      <c r="V12">
+        <v>1.68</v>
+      </c>
+      <c r="W12">
         <v>1.48</v>
-      </c>
-      <c r="S12">
-        <v>2.94</v>
-      </c>
-      <c r="T12">
-        <v>1.65</v>
-      </c>
-      <c r="U12">
-        <v>2.4</v>
-      </c>
-      <c r="V12">
-        <v>1.65</v>
-      </c>
-      <c r="W12">
-        <v>1.47</v>
       </c>
       <c r="X12">
         <v>19.5</v>
       </c>
       <c r="Y12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z12">
+        <v>18.5</v>
+      </c>
+      <c r="AA12">
+        <v>40</v>
+      </c>
+      <c r="AB12">
         <v>17</v>
       </c>
-      <c r="AA12">
-        <v>48</v>
-      </c>
-      <c r="AB12">
-        <v>15</v>
-      </c>
       <c r="AC12">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE12">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AF12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG12">
         <v>14</v>
       </c>
       <c r="AH12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ12">
         <v>95</v>
       </c>
       <c r="AK12">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AL12">
         <v>60</v>
@@ -3633,13 +3633,13 @@
         <v>190</v>
       </c>
       <c r="AN12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO12">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP12">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12">
         <v>11.5</v>
@@ -3648,28 +3648,28 @@
         <v>15</v>
       </c>
       <c r="AS12">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT12">
         <v>13</v>
       </c>
       <c r="AU12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX12">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AY12">
         <v>11.5</v>
       </c>
       <c r="AZ12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA12">
         <v>26</v>
@@ -3678,55 +3678,55 @@
         <v>32</v>
       </c>
       <c r="BC12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE12">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF12">
         <v>20</v>
       </c>
       <c r="BG12">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BH12">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ12">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK12">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO12">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP12">
         <v>22</v>
       </c>
       <c r="BQ12">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BR12">
         <v>32</v>
       </c>
       <c r="BS12">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT12">
         <v>5.8</v>
@@ -3735,16 +3735,16 @@
         <v>4.8</v>
       </c>
       <c r="BV12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW12">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BX12">
         <v>27</v>
       </c>
       <c r="BY12">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3773,13 +3773,13 @@
         <v>150</v>
       </c>
       <c r="F13">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G13">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="H13">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I13">
         <v>3.55</v>
@@ -3788,25 +3788,25 @@
         <v>2.84</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M13">
         <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O13">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="P13">
         <v>1.47</v>
       </c>
       <c r="Q13">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R13">
         <v>1.17</v>
@@ -3818,16 +3818,16 @@
         <v>2.12</v>
       </c>
       <c r="U13">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V13">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y13">
         <v>9.4</v>
@@ -3836,7 +3836,7 @@
         <v>22</v>
       </c>
       <c r="AA13">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB13">
         <v>8.199999999999999</v>
@@ -3863,13 +3863,13 @@
         <v>230</v>
       </c>
       <c r="AJ13">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AK13">
         <v>44</v>
       </c>
       <c r="AL13">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AM13">
         <v>500</v>
@@ -3881,16 +3881,16 @@
         <v>600</v>
       </c>
       <c r="AP13">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ13">
         <v>7.8</v>
       </c>
       <c r="AR13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS13">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="AT13">
         <v>6.8</v>
@@ -3902,7 +3902,7 @@
         <v>13</v>
       </c>
       <c r="AW13">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AX13">
         <v>13.5</v>
@@ -3914,25 +3914,25 @@
         <v>19.5</v>
       </c>
       <c r="BA13">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BB13">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="BC13">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="BD13">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BE13">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF13">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BG13">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BH13">
         <v>2.7</v>
@@ -3974,7 +3974,7 @@
         <v>6.4</v>
       </c>
       <c r="BU13">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV13">
         <v>34</v>
@@ -4021,19 +4021,19 @@
         <v>3.8</v>
       </c>
       <c r="H14">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="I14">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J14">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K14">
         <v>3.15</v>
       </c>
       <c r="L14">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M14">
         <v>1.13</v>
@@ -4048,40 +4048,40 @@
         <v>1.53</v>
       </c>
       <c r="Q14">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R14">
         <v>1.19</v>
       </c>
       <c r="S14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T14">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U14">
         <v>1.77</v>
       </c>
       <c r="V14">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W14">
         <v>1.35</v>
       </c>
       <c r="X14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA14">
         <v>220</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC14">
         <v>7.4</v>
@@ -4090,7 +4090,7 @@
         <v>13</v>
       </c>
       <c r="AE14">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AF14">
         <v>24</v>
@@ -4102,13 +4102,13 @@
         <v>24</v>
       </c>
       <c r="AI14">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="AJ14">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AK14">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="AL14">
         <v>460</v>
@@ -4120,13 +4120,13 @@
         <v>600</v>
       </c>
       <c r="AO14">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AP14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR14">
         <v>12</v>
@@ -4165,25 +4165,25 @@
         <v>20</v>
       </c>
       <c r="BD14">
+        <v>34</v>
+      </c>
+      <c r="BE14">
+        <v>12</v>
+      </c>
+      <c r="BF14">
         <v>11</v>
-      </c>
-      <c r="BE14">
-        <v>11.5</v>
-      </c>
-      <c r="BF14">
-        <v>10.5</v>
       </c>
       <c r="BG14">
         <v>9.6</v>
       </c>
       <c r="BH14">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BI14">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK14">
         <v>5.7</v>
@@ -4192,7 +4192,7 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN14">
         <v>6.8</v>
@@ -4204,37 +4204,37 @@
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT14">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV14">
         <v>23</v>
       </c>
       <c r="BW14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB14" t="s">
         <v>167</v>
@@ -4257,7 +4257,7 @@
         <v>152</v>
       </c>
       <c r="F15">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G15">
         <v>1.95</v>
@@ -4266,13 +4266,13 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J15">
         <v>3.3</v>
       </c>
       <c r="K15">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L15">
         <v>1.54</v>
@@ -4281,28 +4281,28 @@
         <v>1.11</v>
       </c>
       <c r="N15">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O15">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P15">
         <v>1.6</v>
       </c>
       <c r="Q15">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R15">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S15">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U15">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V15">
         <v>1.21</v>
@@ -4311,10 +4311,10 @@
         <v>2.04</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Y15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z15">
         <v>120</v>
@@ -4323,13 +4323,13 @@
         <v>900</v>
       </c>
       <c r="AB15">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE15">
         <v>500</v>
@@ -4338,7 +4338,7 @@
         <v>10.5</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH15">
         <v>32</v>
@@ -4350,7 +4350,7 @@
         <v>26</v>
       </c>
       <c r="AK15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL15">
         <v>160</v>
@@ -4374,34 +4374,34 @@
         <v>32</v>
       </c>
       <c r="AS15">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT15">
         <v>5.8</v>
       </c>
       <c r="AU15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW15">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AX15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY15">
         <v>9.4</v>
       </c>
       <c r="AZ15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA15">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BB15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BC15">
         <v>21</v>
@@ -4410,13 +4410,13 @@
         <v>34</v>
       </c>
       <c r="BE15">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF15">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BG15">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH15">
         <v>3.15</v>
@@ -4434,7 +4434,7 @@
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BN15">
         <v>4.9</v>
@@ -4452,7 +4452,7 @@
         <v>44</v>
       </c>
       <c r="BS15">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT15">
         <v>9.4</v>
@@ -4467,7 +4467,7 @@
         <v>5.5</v>
       </c>
       <c r="BX15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
         <v>5.7</v>
@@ -4476,7 +4476,7 @@
         <v>44</v>
       </c>
       <c r="CA15">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB15" t="s">
         <v>167</v>
@@ -4499,22 +4499,22 @@
         <v>153</v>
       </c>
       <c r="F16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G16">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="H16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="J16">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K16">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L16">
         <v>1.43</v>
@@ -4538,25 +4538,25 @@
         <v>1.31</v>
       </c>
       <c r="S16">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T16">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V16">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W16">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="X16">
         <v>15</v>
       </c>
       <c r="Y16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z16">
         <v>540</v>
@@ -4565,19 +4565,19 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC16">
         <v>12.5</v>
       </c>
       <c r="AD16">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AE16">
         <v>370</v>
       </c>
       <c r="AF16">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AG16">
         <v>11.5</v>
@@ -4601,7 +4601,7 @@
         <v>370</v>
       </c>
       <c r="AN16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO16">
         <v>1000</v>
@@ -4610,13 +4610,13 @@
         <v>12</v>
       </c>
       <c r="AQ16">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="AR16">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS16">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT16">
         <v>5.6</v>
@@ -4625,10 +4625,10 @@
         <v>10</v>
       </c>
       <c r="AV16">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW16">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX16">
         <v>6</v>
@@ -4640,10 +4640,10 @@
         <v>32</v>
       </c>
       <c r="BA16">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB16">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC16">
         <v>15.5</v>
@@ -4652,7 +4652,7 @@
         <v>42</v>
       </c>
       <c r="BE16">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF16">
         <v>6.8</v>
@@ -4670,55 +4670,55 @@
         <v>15</v>
       </c>
       <c r="BK16">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN16">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BO16">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="BP16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BQ16">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BR16">
         <v>34</v>
       </c>
       <c r="BS16">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT16">
         <v>16</v>
       </c>
       <c r="BU16">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ16">
         <v>18</v>
       </c>
       <c r="CA16">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB16" t="s">
         <v>167</v>
@@ -4750,13 +4750,13 @@
         <v>1.3</v>
       </c>
       <c r="I17">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="J17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L17">
         <v>1.2</v>
@@ -4765,49 +4765,49 @@
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P17">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q17">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R17">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="S17">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="T17">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U17">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V17">
         <v>4.1</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>48</v>
       </c>
       <c r="Y17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA17">
         <v>12.5</v>
       </c>
       <c r="AB17">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AC17">
         <v>18</v>
@@ -4816,16 +4816,16 @@
         <v>11.5</v>
       </c>
       <c r="AE17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AF17">
         <v>140</v>
       </c>
       <c r="AG17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AH17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI17">
         <v>26</v>
@@ -4834,31 +4834,31 @@
         <v>430</v>
       </c>
       <c r="AK17">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="AL17">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="AM17">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO17">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AP17">
         <v>36</v>
       </c>
       <c r="AQ17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT17">
         <v>46</v>
@@ -4867,13 +4867,13 @@
         <v>16</v>
       </c>
       <c r="AV17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW17">
         <v>11.5</v>
       </c>
       <c r="AX17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AY17">
         <v>32</v>
@@ -4885,82 +4885,82 @@
         <v>22</v>
       </c>
       <c r="BB17">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BC17">
         <v>80</v>
       </c>
       <c r="BD17">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE17">
+        <v>70</v>
+      </c>
+      <c r="BF17">
         <v>55</v>
-      </c>
-      <c r="BF17">
-        <v>50</v>
       </c>
       <c r="BG17">
         <v>3.1</v>
       </c>
       <c r="BH17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BI17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ17">
         <v>10.5</v>
       </c>
       <c r="BK17">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN17">
         <v>14</v>
       </c>
       <c r="BO17">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BP17">
         <v>65</v>
       </c>
       <c r="BQ17">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR17">
         <v>50</v>
       </c>
       <c r="BS17">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT17">
         <v>4.5</v>
       </c>
       <c r="BU17">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BV17">
         <v>7.2</v>
       </c>
       <c r="BW17">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BX17">
         <v>16.5</v>
       </c>
       <c r="BY17">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ17">
         <v>7.2</v>
       </c>
       <c r="CA17">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="CB17" t="s">
         <v>167</v>
@@ -4983,28 +4983,28 @@
         <v>155</v>
       </c>
       <c r="F18">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G18">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="H18">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I18">
         <v>5.2</v>
       </c>
       <c r="J18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K18">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18">
         <v>4.9</v>
@@ -5022,25 +5022,25 @@
         <v>1.56</v>
       </c>
       <c r="S18">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T18">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U18">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W18">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X18">
         <v>23</v>
       </c>
       <c r="Y18">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="Z18">
         <v>55</v>
@@ -5055,7 +5055,7 @@
         <v>10.5</v>
       </c>
       <c r="AD18">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE18">
         <v>120</v>
@@ -5073,31 +5073,31 @@
         <v>65</v>
       </c>
       <c r="AJ18">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK18">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM18">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN18">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO18">
-        <v>600</v>
+        <v>280</v>
       </c>
       <c r="AP18">
         <v>18.5</v>
       </c>
       <c r="AQ18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR18">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS18">
         <v>28</v>
@@ -5109,13 +5109,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW18">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY18">
         <v>8.800000000000001</v>
@@ -5124,10 +5124,10 @@
         <v>14.5</v>
       </c>
       <c r="BA18">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB18">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC18">
         <v>14.5</v>
@@ -5225,220 +5225,220 @@
         <v>156</v>
       </c>
       <c r="F19">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G19">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J19">
         <v>4.1</v>
       </c>
       <c r="K19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L19">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M19">
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O19">
         <v>1.16</v>
       </c>
       <c r="P19">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q19">
         <v>1.51</v>
       </c>
       <c r="R19">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S19">
         <v>2.28</v>
       </c>
       <c r="T19">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="U19">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X19">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z19">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA19">
         <v>75</v>
       </c>
       <c r="AB19">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AC19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE19">
         <v>36</v>
       </c>
       <c r="AF19">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AI19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ19">
         <v>25</v>
       </c>
       <c r="AK19">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM19">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AN19">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP19">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AQ19">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="AR19">
+        <v>30</v>
+      </c>
+      <c r="AS19">
+        <v>46</v>
+      </c>
+      <c r="AT19">
+        <v>12.5</v>
+      </c>
+      <c r="AU19">
+        <v>9.6</v>
+      </c>
+      <c r="AV19">
+        <v>14.5</v>
+      </c>
+      <c r="AW19">
+        <v>32</v>
+      </c>
+      <c r="AX19">
+        <v>13.5</v>
+      </c>
+      <c r="AY19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ19">
+        <v>13.5</v>
+      </c>
+      <c r="BA19">
+        <v>30</v>
+      </c>
+      <c r="BB19">
+        <v>22</v>
+      </c>
+      <c r="BC19">
+        <v>16</v>
+      </c>
+      <c r="BD19">
+        <v>21</v>
+      </c>
+      <c r="BE19">
+        <v>44</v>
+      </c>
+      <c r="BF19">
         <v>7.4</v>
       </c>
-      <c r="AS19">
-        <v>8.4</v>
-      </c>
-      <c r="AT19">
-        <v>7.6</v>
-      </c>
-      <c r="AU19">
-        <v>7.4</v>
-      </c>
-      <c r="AV19">
-        <v>9</v>
-      </c>
-      <c r="AW19">
-        <v>7.4</v>
-      </c>
-      <c r="AX19">
-        <v>8.4</v>
-      </c>
-      <c r="AY19">
-        <v>6.2</v>
-      </c>
-      <c r="AZ19">
-        <v>8.4</v>
-      </c>
-      <c r="BA19">
-        <v>7.4</v>
-      </c>
-      <c r="BB19">
-        <v>6.8</v>
-      </c>
-      <c r="BC19">
-        <v>9</v>
-      </c>
-      <c r="BD19">
-        <v>6.8</v>
-      </c>
-      <c r="BE19">
-        <v>8</v>
-      </c>
-      <c r="BF19">
-        <v>4.5</v>
-      </c>
       <c r="BG19">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BH19">
         <v>5.3</v>
       </c>
       <c r="BI19">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="BJ19">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="BL19">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN19">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BO19">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP19">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ19">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="BR19">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BS19">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BT19">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU19">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="BV19">
         <v>29</v>
       </c>
       <c r="BW19">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BX19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY19">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5467,25 +5467,25 @@
         <v>157</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G20">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H20">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I20">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J20">
+        <v>3.35</v>
+      </c>
+      <c r="K20">
         <v>3.4</v>
       </c>
-      <c r="K20">
-        <v>3.45</v>
-      </c>
       <c r="L20">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M20">
         <v>1.09</v>
@@ -5497,28 +5497,28 @@
         <v>1.39</v>
       </c>
       <c r="P20">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q20">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R20">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T20">
         <v>1.86</v>
       </c>
       <c r="U20">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V20">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W20">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X20">
         <v>12</v>
@@ -5527,22 +5527,22 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA20">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AB20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC20">
         <v>7.2</v>
       </c>
       <c r="AD20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE20">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF20">
         <v>19</v>
@@ -5560,7 +5560,7 @@
         <v>48</v>
       </c>
       <c r="AK20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL20">
         <v>48</v>
@@ -5572,7 +5572,7 @@
         <v>36</v>
       </c>
       <c r="AO20">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP20">
         <v>11.5</v>
@@ -5584,7 +5584,7 @@
         <v>15.5</v>
       </c>
       <c r="AS20">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AT20">
         <v>10</v>
@@ -5593,16 +5593,16 @@
         <v>7</v>
       </c>
       <c r="AV20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW20">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AX20">
         <v>17.5</v>
       </c>
       <c r="AY20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20">
         <v>16.5</v>
@@ -5611,28 +5611,28 @@
         <v>40</v>
       </c>
       <c r="BB20">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC20">
         <v>32</v>
       </c>
       <c r="BD20">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE20">
         <v>90</v>
       </c>
       <c r="BF20">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG20">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BH20">
         <v>3.1</v>
       </c>
       <c r="BI20">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BJ20">
         <v>9.800000000000001</v>
@@ -5644,13 +5644,13 @@
         <v>140</v>
       </c>
       <c r="BM20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BN20">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO20">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP20">
         <v>24</v>
@@ -5662,10 +5662,10 @@
         <v>38</v>
       </c>
       <c r="BS20">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BT20">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU20">
         <v>5.1</v>
@@ -5680,7 +5680,7 @@
         <v>38</v>
       </c>
       <c r="BY20">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BZ20">
         <v>34</v>
@@ -5709,58 +5709,58 @@
         <v>158</v>
       </c>
       <c r="F21">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="G21">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="H21">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I21">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L21">
         <v>1.29</v>
       </c>
       <c r="M21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O21">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P21">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="Q21">
+        <v>1.56</v>
+      </c>
+      <c r="R21">
+        <v>1.69</v>
+      </c>
+      <c r="S21">
+        <v>2.38</v>
+      </c>
+      <c r="T21">
         <v>1.57</v>
-      </c>
-      <c r="R21">
-        <v>1.67</v>
-      </c>
-      <c r="S21">
-        <v>2.44</v>
-      </c>
-      <c r="T21">
-        <v>1.56</v>
       </c>
       <c r="U21">
         <v>2.68</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="X21">
         <v>26</v>
@@ -5772,13 +5772,13 @@
         <v>32</v>
       </c>
       <c r="AA21">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB21">
         <v>14</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD21">
         <v>16</v>
@@ -5790,16 +5790,16 @@
         <v>16</v>
       </c>
       <c r="AG21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI21">
         <v>38</v>
       </c>
       <c r="AJ21">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK21">
         <v>18</v>
@@ -5811,40 +5811,40 @@
         <v>60</v>
       </c>
       <c r="AN21">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO21">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP21">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR21">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS21">
         <v>55</v>
       </c>
       <c r="AT21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU21">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW21">
         <v>32</v>
       </c>
       <c r="AX21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ21">
         <v>13.5</v>
@@ -5853,43 +5853,43 @@
         <v>32</v>
       </c>
       <c r="BB21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC21">
         <v>16</v>
       </c>
       <c r="BD21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE21">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF21">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH21">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BI21">
         <v>4.1</v>
       </c>
       <c r="BJ21">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BK21">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM21">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BN21">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BO21">
         <v>4.8</v>
@@ -5898,37 +5898,37 @@
         <v>13</v>
       </c>
       <c r="BQ21">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BR21">
         <v>22</v>
       </c>
       <c r="BS21">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="BT21">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BU21">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV21">
         <v>28</v>
       </c>
       <c r="BW21">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BX21">
         <v>32</v>
       </c>
       <c r="BY21">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ21">
         <v>15</v>
       </c>
       <c r="CA21">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB21" t="s">
         <v>167</v>
@@ -5951,16 +5951,16 @@
         <v>159</v>
       </c>
       <c r="F22">
+        <v>1.55</v>
+      </c>
+      <c r="G22">
         <v>1.56</v>
       </c>
-      <c r="G22">
-        <v>1.57</v>
-      </c>
       <c r="H22">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J22">
         <v>5.3</v>
@@ -5975,49 +5975,49 @@
         <v>1.02</v>
       </c>
       <c r="N22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O22">
         <v>1.11</v>
       </c>
       <c r="P22">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q22">
         <v>1.35</v>
       </c>
       <c r="R22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S22">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="T22">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U22">
         <v>2.98</v>
       </c>
       <c r="V22">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W22">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X22">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Y22">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z22">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB22">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC22">
         <v>14</v>
@@ -6026,10 +6026,10 @@
         <v>24</v>
       </c>
       <c r="AE22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG22">
         <v>11.5</v>
@@ -6041,10 +6041,10 @@
         <v>44</v>
       </c>
       <c r="AJ22">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL22">
         <v>21</v>
@@ -6053,7 +6053,7 @@
         <v>50</v>
       </c>
       <c r="AN22">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO22">
         <v>34</v>
@@ -6062,7 +6062,7 @@
         <v>40</v>
       </c>
       <c r="AQ22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AR22">
         <v>55</v>
@@ -6071,7 +6071,7 @@
         <v>46</v>
       </c>
       <c r="AT22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU22">
         <v>12.5</v>
@@ -6080,7 +6080,7 @@
         <v>21</v>
       </c>
       <c r="AW22">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX22">
         <v>14</v>
@@ -6089,13 +6089,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ22">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA22">
         <v>36</v>
       </c>
       <c r="BB22">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC22">
         <v>12.5</v>
@@ -6104,73 +6104,73 @@
         <v>19.5</v>
       </c>
       <c r="BE22">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BF22">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BG22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH22">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BI22">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BJ22">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK22">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM22">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BN22">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BO22">
         <v>4.6</v>
       </c>
       <c r="BP22">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BQ22">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BR22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS22">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BT22">
         <v>10.5</v>
       </c>
       <c r="BU22">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BX22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY22">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ22">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CA22">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="CB22" t="s">
         <v>167</v>
@@ -6193,25 +6193,25 @@
         <v>160</v>
       </c>
       <c r="F23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G23">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="H23">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="I23">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J23">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="K23">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="M23">
         <v>1.01</v>
@@ -6229,31 +6229,31 @@
         <v>1.24</v>
       </c>
       <c r="R23">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="S23">
         <v>1.62</v>
       </c>
       <c r="T23">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U23">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="V23">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W23">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="X23">
         <v>75</v>
       </c>
       <c r="Y23">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="Z23">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AA23">
         <v>420</v>
@@ -6265,22 +6265,22 @@
         <v>23</v>
       </c>
       <c r="AD23">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE23">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="AF23">
         <v>15.5</v>
       </c>
       <c r="AG23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH23">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI23">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ23">
         <v>14.5</v>
@@ -6292,22 +6292,22 @@
         <v>22</v>
       </c>
       <c r="AM23">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN23">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="AO23">
         <v>65</v>
       </c>
       <c r="AP23">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ23">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AR23">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AS23">
         <v>38</v>
@@ -6319,10 +6319,10 @@
         <v>18.5</v>
       </c>
       <c r="AV23">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AW23">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AX23">
         <v>13</v>
@@ -6337,7 +6337,7 @@
         <v>60</v>
       </c>
       <c r="BB23">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC23">
         <v>11</v>
@@ -6349,64 +6349,64 @@
         <v>55</v>
       </c>
       <c r="BF23">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="BG23">
         <v>34</v>
       </c>
       <c r="BH23">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BI23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BJ23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK23">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN23">
         <v>5.1</v>
       </c>
       <c r="BO23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP23">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BQ23">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BR23">
         <v>15.5</v>
       </c>
       <c r="BS23">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BT23">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BU23">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV23">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX23">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6438,7 +6438,7 @@
         <v>2.38</v>
       </c>
       <c r="G24">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H24">
         <v>3.55</v>
@@ -6447,7 +6447,7 @@
         <v>3.95</v>
       </c>
       <c r="J24">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K24">
         <v>3.1</v>
@@ -6456,16 +6456,16 @@
         <v>1.6</v>
       </c>
       <c r="M24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N24">
         <v>2.56</v>
       </c>
       <c r="O24">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P24">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q24">
         <v>2.8</v>
@@ -6480,22 +6480,22 @@
         <v>2.16</v>
       </c>
       <c r="U24">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V24">
         <v>1.34</v>
       </c>
       <c r="W24">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X24">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y24">
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AA24">
         <v>900</v>
@@ -6510,7 +6510,7 @@
         <v>17</v>
       </c>
       <c r="AE24">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="AF24">
         <v>14.5</v>
@@ -6519,16 +6519,16 @@
         <v>12.5</v>
       </c>
       <c r="AH24">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AI24">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AJ24">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AK24">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL24">
         <v>210</v>
@@ -6537,22 +6537,22 @@
         <v>500</v>
       </c>
       <c r="AN24">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AO24">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP24">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ24">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR24">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AS24">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AT24">
         <v>6.4</v>
@@ -6564,7 +6564,7 @@
         <v>14.5</v>
       </c>
       <c r="AW24">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="AX24">
         <v>12</v>
@@ -6573,82 +6573,82 @@
         <v>10.5</v>
       </c>
       <c r="AZ24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA24">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="BB24">
-        <v>8.6</v>
+        <v>26</v>
       </c>
       <c r="BC24">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="BD24">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BE24">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BF24">
         <v>32</v>
       </c>
       <c r="BG24">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK24">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6677,31 +6677,31 @@
         <v>162</v>
       </c>
       <c r="F25">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G25">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="H25">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="I25">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="J25">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K25">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L25">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M25">
         <v>1.12</v>
       </c>
       <c r="N25">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O25">
         <v>1.51</v>
@@ -6719,46 +6719,46 @@
         <v>5.1</v>
       </c>
       <c r="T25">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U25">
         <v>1.84</v>
       </c>
       <c r="V25">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W25">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y25">
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AA25">
         <v>55</v>
       </c>
       <c r="AB25">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>7</v>
       </c>
       <c r="AD25">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE25">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AF25">
         <v>21</v>
       </c>
       <c r="AG25">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AH25">
         <v>23</v>
@@ -6767,58 +6767,58 @@
         <v>75</v>
       </c>
       <c r="AJ25">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK25">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL25">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM25">
         <v>500</v>
       </c>
       <c r="AN25">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO25">
         <v>55</v>
       </c>
       <c r="AP25">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AQ25">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AR25">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AS25">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="AT25">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU25">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV25">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AW25">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="AX25">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY25">
         <v>10.5</v>
       </c>
       <c r="AZ25">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA25">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25">
         <v>40</v>
@@ -6830,73 +6830,73 @@
         <v>8.4</v>
       </c>
       <c r="BE25">
+        <v>8.6</v>
+      </c>
+      <c r="BF25">
         <v>9</v>
-      </c>
-      <c r="BF25">
-        <v>8.199999999999999</v>
       </c>
       <c r="BG25">
         <v>8</v>
       </c>
       <c r="BH25">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="BI25">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="BJ25">
         <v>13</v>
       </c>
       <c r="BK25">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
+        <v>5.1</v>
+      </c>
+      <c r="BN25">
+        <v>6.8</v>
+      </c>
+      <c r="BO25">
+        <v>4.5</v>
+      </c>
+      <c r="BP25">
+        <v>32</v>
+      </c>
+      <c r="BQ25">
+        <v>4.5</v>
+      </c>
+      <c r="BR25">
+        <v>60</v>
+      </c>
+      <c r="BS25">
+        <v>4.8</v>
+      </c>
+      <c r="BT25">
         <v>6.6</v>
       </c>
-      <c r="BN25">
-        <v>7.2</v>
-      </c>
-      <c r="BO25">
-        <v>4.6</v>
-      </c>
-      <c r="BP25">
-        <v>36</v>
-      </c>
-      <c r="BQ25">
-        <v>5.7</v>
-      </c>
-      <c r="BR25">
-        <v>65</v>
-      </c>
-      <c r="BS25">
-        <v>6</v>
-      </c>
-      <c r="BT25">
-        <v>6.4</v>
-      </c>
       <c r="BU25">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV25">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW25">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="BX25">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY25">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BZ25">
         <v>60</v>
       </c>
       <c r="CA25">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="CB25" t="s">
         <v>167</v>
@@ -6919,7 +6919,7 @@
         <v>163</v>
       </c>
       <c r="F26">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G26">
         <v>2.26</v>
@@ -6964,10 +6964,10 @@
         <v>2.14</v>
       </c>
       <c r="U26">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W26">
         <v>1.79</v>
@@ -7012,7 +7012,7 @@
         <v>36</v>
       </c>
       <c r="AK26">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AL26">
         <v>70</v>
@@ -7027,7 +7027,7 @@
         <v>500</v>
       </c>
       <c r="AP26">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ26">
         <v>10</v>
@@ -7036,10 +7036,10 @@
         <v>24</v>
       </c>
       <c r="AS26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU26">
         <v>6.4</v>
@@ -7048,7 +7048,7 @@
         <v>15.5</v>
       </c>
       <c r="AW26">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AX26">
         <v>10.5</v>
@@ -7057,25 +7057,25 @@
         <v>10</v>
       </c>
       <c r="AZ26">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BA26">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BB26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC26">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD26">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BE26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF26">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG26">
         <v>13.5</v>
@@ -7084,7 +7084,7 @@
         <v>3.05</v>
       </c>
       <c r="BI26">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BJ26">
         <v>11.5</v>
@@ -7096,25 +7096,25 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BN26">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP26">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BQ26">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR26">
         <v>48</v>
       </c>
       <c r="BS26">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT26">
         <v>7.2</v>
@@ -7123,22 +7123,22 @@
         <v>5.6</v>
       </c>
       <c r="BV26">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW26">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX26">
         <v>70</v>
       </c>
       <c r="BY26">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ26">
         <v>55</v>
       </c>
       <c r="CA26">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="CB26" t="s">
         <v>167</v>
@@ -7167,7 +7167,7 @@
         <v>2.16</v>
       </c>
       <c r="H27">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I27">
         <v>4.6</v>
@@ -7185,19 +7185,19 @@
         <v>1.12</v>
       </c>
       <c r="N27">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="O27">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P27">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q27">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S27">
         <v>5.3</v>
@@ -7206,7 +7206,7 @@
         <v>2.16</v>
       </c>
       <c r="U27">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V27">
         <v>1.28</v>
@@ -7221,13 +7221,13 @@
         <v>12.5</v>
       </c>
       <c r="Z27">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AA27">
         <v>900</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AC27">
         <v>7.8</v>
@@ -7236,7 +7236,7 @@
         <v>20</v>
       </c>
       <c r="AE27">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AF27">
         <v>12.5</v>
@@ -7257,7 +7257,7 @@
         <v>32</v>
       </c>
       <c r="AL27">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM27">
         <v>580</v>
@@ -7272,25 +7272,25 @@
         <v>8</v>
       </c>
       <c r="AQ27">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR27">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS27">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT27">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU27">
         <v>6.6</v>
       </c>
       <c r="AV27">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AW27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX27">
         <v>10</v>
@@ -7302,85 +7302,85 @@
         <v>19.5</v>
       </c>
       <c r="BA27">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BB27">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="BC27">
         <v>24</v>
       </c>
       <c r="BD27">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BE27">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF27">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG27">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BH27">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI27">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BJ27">
         <v>13</v>
       </c>
       <c r="BK27">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BN27">
         <v>5.2</v>
       </c>
       <c r="BO27">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP27">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BQ27">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BR27">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BS27">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BT27">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU27">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BV27">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW27">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BZ27">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="CA27">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="CB27" t="s">
         <v>167</v>
@@ -7403,34 +7403,34 @@
         <v>165</v>
       </c>
       <c r="F28">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G28">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H28">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I28">
         <v>3.3</v>
       </c>
       <c r="J28">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L28">
         <v>1.31</v>
       </c>
       <c r="M28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N28">
         <v>5.1</v>
       </c>
       <c r="O28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P28">
         <v>2.38</v>
@@ -7439,103 +7439,103 @@
         <v>1.66</v>
       </c>
       <c r="R28">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S28">
         <v>2.66</v>
       </c>
       <c r="T28">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U28">
         <v>2.48</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y28">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z28">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA28">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB28">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC28">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD28">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE28">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF28">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AG28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH28">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AI28">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ28">
+        <v>34</v>
+      </c>
+      <c r="AK28">
+        <v>25</v>
+      </c>
+      <c r="AL28">
         <v>36</v>
-      </c>
-      <c r="AK28">
-        <v>22</v>
-      </c>
-      <c r="AL28">
-        <v>30</v>
       </c>
       <c r="AM28">
         <v>70</v>
       </c>
       <c r="AN28">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO28">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AP28">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AQ28">
+        <v>15</v>
+      </c>
+      <c r="AR28">
+        <v>22</v>
+      </c>
+      <c r="AS28">
+        <v>5.1</v>
+      </c>
+      <c r="AT28">
+        <v>12</v>
+      </c>
+      <c r="AU28">
+        <v>7.2</v>
+      </c>
+      <c r="AV28">
+        <v>11</v>
+      </c>
+      <c r="AW28">
+        <v>4.7</v>
+      </c>
+      <c r="AX28">
         <v>14.5</v>
-      </c>
-      <c r="AR28">
-        <v>20</v>
-      </c>
-      <c r="AS28">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT28">
-        <v>5.9</v>
-      </c>
-      <c r="AU28">
-        <v>4.9</v>
-      </c>
-      <c r="AV28">
-        <v>12</v>
-      </c>
-      <c r="AW28">
-        <v>7.8</v>
-      </c>
-      <c r="AX28">
-        <v>15</v>
       </c>
       <c r="AY28">
         <v>10</v>
@@ -7544,25 +7544,25 @@
         <v>13</v>
       </c>
       <c r="BA28">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BB28">
-        <v>26</v>
+        <v>4.7</v>
       </c>
       <c r="BC28">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BD28">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BE28">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BF28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG28">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BH28">
         <v>4.7</v>
@@ -7574,49 +7574,49 @@
         <v>10</v>
       </c>
       <c r="BK28">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN28">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO28">
         <v>4.4</v>
       </c>
       <c r="BP28">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ28">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BR28">
         <v>28</v>
       </c>
       <c r="BS28">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT28">
         <v>7.6</v>
       </c>
       <c r="BU28">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV28">
         <v>26</v>
       </c>
       <c r="BW28">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BX28">
         <v>34</v>
       </c>
       <c r="BY28">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ28">
         <v>0</v>
@@ -7669,7 +7669,7 @@
         <v>1.1</v>
       </c>
       <c r="N29">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O29">
         <v>1.45</v>
@@ -7690,7 +7690,7 @@
         <v>2.04</v>
       </c>
       <c r="U29">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V29">
         <v>1.27</v>
@@ -7714,7 +7714,7 @@
         <v>7.8</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD29">
         <v>970</v>
@@ -7723,7 +7723,7 @@
         <v>70</v>
       </c>
       <c r="AF29">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG29">
         <v>11.5</v>
@@ -7732,7 +7732,7 @@
         <v>25</v>
       </c>
       <c r="AI29">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ29">
         <v>27</v>
@@ -7759,10 +7759,10 @@
         <v>10</v>
       </c>
       <c r="AR29">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="AS29">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT29">
         <v>6.4</v>
@@ -7774,7 +7774,7 @@
         <v>15.5</v>
       </c>
       <c r="AW29">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX29">
         <v>10</v>
@@ -7786,7 +7786,7 @@
         <v>18</v>
       </c>
       <c r="BA29">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB29">
         <v>21</v>
@@ -7795,22 +7795,22 @@
         <v>21</v>
       </c>
       <c r="BD29">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE29">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF29">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BG29">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH29">
         <v>3.05</v>
       </c>
       <c r="BI29">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ29">
         <v>11.5</v>
@@ -7831,19 +7831,19 @@
         <v>3.7</v>
       </c>
       <c r="BP29">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ29">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT29">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU29">
         <v>4.5</v>
@@ -7852,7 +7852,7 @@
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX29">
         <v>1000</v>
@@ -7864,7 +7864,7 @@
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB29" t="s">
         <v>167</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-25.xlsx
@@ -517,7 +517,7 @@
     <t>Aguilas Doradas</t>
   </si>
   <si>
-    <t>2026-08-25 06:53:18</t>
+    <t>2026-08-25 09:02:57</t>
   </si>
 </sst>
 </file>
@@ -1111,226 +1111,226 @@
         <v>139</v>
       </c>
       <c r="F2">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="G2">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="H2">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="I2">
-        <v>2.34</v>
+        <v>5.5</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>1.85</v>
       </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.92</v>
       </c>
       <c r="N2">
-        <v>3.8</v>
+        <v>1.24</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="P2">
-        <v>1.94</v>
+        <v>1.03</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>5.5</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>3.65</v>
+        <v>130</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>6.8</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="X2">
+        <v>2.2</v>
+      </c>
+      <c r="Y2">
+        <v>6.8</v>
+      </c>
+      <c r="Z2">
+        <v>46</v>
+      </c>
+      <c r="AA2">
+        <v>570</v>
+      </c>
+      <c r="AB2">
+        <v>5.5</v>
+      </c>
+      <c r="AC2">
+        <v>16</v>
+      </c>
+      <c r="AD2">
+        <v>120</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>36</v>
+      </c>
+      <c r="AG2">
+        <v>120</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>460</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>2.1</v>
+      </c>
+      <c r="AQ2">
+        <v>5.4</v>
+      </c>
+      <c r="AR2">
+        <v>26</v>
+      </c>
+      <c r="AS2">
+        <v>15.5</v>
+      </c>
+      <c r="AT2">
+        <v>4.9</v>
+      </c>
+      <c r="AU2">
         <v>13</v>
       </c>
-      <c r="Y2">
+      <c r="AV2">
+        <v>60</v>
+      </c>
+      <c r="AW2">
         <v>10</v>
       </c>
-      <c r="Z2">
-        <v>14.5</v>
-      </c>
-      <c r="AA2">
-        <v>30</v>
-      </c>
-      <c r="AB2">
+      <c r="AX2">
         <v>12.5</v>
       </c>
-      <c r="AC2">
-        <v>7.4</v>
-      </c>
-      <c r="AD2">
-        <v>11</v>
-      </c>
-      <c r="AE2">
-        <v>25</v>
-      </c>
-      <c r="AF2">
-        <v>23</v>
-      </c>
-      <c r="AG2">
-        <v>14.5</v>
-      </c>
-      <c r="AH2">
-        <v>17.5</v>
-      </c>
-      <c r="AI2">
+      <c r="AY2">
+        <v>55</v>
+      </c>
+      <c r="AZ2">
+        <v>10</v>
+      </c>
+      <c r="BA2">
+        <v>10</v>
+      </c>
+      <c r="BB2">
+        <v>10</v>
+      </c>
+      <c r="BC2">
+        <v>10</v>
+      </c>
+      <c r="BD2">
+        <v>10</v>
+      </c>
+      <c r="BE2">
+        <v>10</v>
+      </c>
+      <c r="BF2">
         <v>38</v>
       </c>
-      <c r="AJ2">
-        <v>65</v>
-      </c>
-      <c r="AK2">
-        <v>40</v>
-      </c>
-      <c r="AL2">
-        <v>48</v>
-      </c>
-      <c r="AM2">
-        <v>95</v>
-      </c>
-      <c r="AN2">
+      <c r="BG2">
         <v>46</v>
       </c>
-      <c r="AO2">
-        <v>20</v>
-      </c>
-      <c r="AP2">
-        <v>12.5</v>
-      </c>
-      <c r="AQ2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR2">
-        <v>13</v>
-      </c>
-      <c r="AS2">
-        <v>27</v>
-      </c>
-      <c r="AT2">
-        <v>11.5</v>
-      </c>
-      <c r="AU2">
-        <v>7</v>
-      </c>
-      <c r="AV2">
-        <v>10</v>
-      </c>
-      <c r="AW2">
-        <v>22</v>
-      </c>
-      <c r="AX2">
-        <v>21</v>
-      </c>
-      <c r="AY2">
-        <v>13</v>
-      </c>
-      <c r="AZ2">
-        <v>16</v>
-      </c>
-      <c r="BA2">
-        <v>32</v>
-      </c>
-      <c r="BB2">
-        <v>55</v>
-      </c>
-      <c r="BC2">
-        <v>34</v>
-      </c>
-      <c r="BD2">
-        <v>42</v>
-      </c>
-      <c r="BE2">
-        <v>85</v>
-      </c>
-      <c r="BF2">
-        <v>36</v>
-      </c>
-      <c r="BG2">
-        <v>18</v>
-      </c>
       <c r="BH2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>167</v>
@@ -1353,226 +1353,226 @@
         <v>140</v>
       </c>
       <c r="F3">
-        <v>2.58</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>2.62</v>
+        <v>220</v>
       </c>
       <c r="H3">
-        <v>3.2</v>
+        <v>1.05</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>1.07</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>19</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1.68</v>
+        <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>2.42</v>
+        <v>1.76</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="T3">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="U3">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>15.5</v>
       </c>
       <c r="W3">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>21</v>
+        <v>2.38</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>5.3</v>
       </c>
       <c r="AE3">
-        <v>44</v>
+        <v>16.5</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
+        <v>270</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>36</v>
+      </c>
+      <c r="AP3">
+        <v>1000</v>
+      </c>
+      <c r="AQ3">
+        <v>7.6</v>
+      </c>
+      <c r="AR3">
+        <v>2.24</v>
+      </c>
+      <c r="AS3">
+        <v>4.7</v>
+      </c>
+      <c r="AT3">
+        <v>1000</v>
+      </c>
+      <c r="AU3">
+        <v>7.6</v>
+      </c>
+      <c r="AV3">
+        <v>3.65</v>
+      </c>
+      <c r="AW3">
+        <v>8.4</v>
+      </c>
+      <c r="AX3">
+        <v>1000</v>
+      </c>
+      <c r="AY3">
+        <v>7.8</v>
+      </c>
+      <c r="AZ3">
+        <v>17.5</v>
+      </c>
+      <c r="BA3">
         <v>55</v>
       </c>
-      <c r="AM3">
-        <v>150</v>
-      </c>
-      <c r="AN3">
-        <v>34</v>
-      </c>
-      <c r="AO3">
-        <v>60</v>
-      </c>
-      <c r="AP3">
-        <v>9.4</v>
-      </c>
-      <c r="AQ3">
-        <v>9.6</v>
-      </c>
-      <c r="AR3">
-        <v>18</v>
-      </c>
-      <c r="AS3">
-        <v>50</v>
-      </c>
-      <c r="AT3">
-        <v>8</v>
-      </c>
-      <c r="AU3">
-        <v>6.6</v>
-      </c>
-      <c r="AV3">
-        <v>12.5</v>
-      </c>
-      <c r="AW3">
-        <v>36</v>
-      </c>
-      <c r="AX3">
-        <v>14</v>
-      </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
-      <c r="AZ3">
-        <v>18.5</v>
-      </c>
-      <c r="BA3">
-        <v>50</v>
-      </c>
       <c r="BB3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BC3">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="BD3">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="BE3">
-        <v>100</v>
+        <v>7.6</v>
       </c>
       <c r="BF3">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="BG3">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="BH3">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>167</v>
@@ -1595,226 +1595,226 @@
         <v>141</v>
       </c>
       <c r="F4">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="G4">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="I4">
-        <v>8.800000000000001</v>
+        <v>330</v>
       </c>
       <c r="J4">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="K4">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>4.9</v>
+        <v>2.06</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="P4">
-        <v>2.36</v>
+        <v>1.2</v>
       </c>
       <c r="Q4">
-        <v>1.72</v>
+        <v>5.5</v>
       </c>
       <c r="R4">
-        <v>1.52</v>
+        <v>1.02</v>
       </c>
       <c r="S4">
-        <v>2.88</v>
+        <v>27</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>4.4</v>
       </c>
       <c r="U4">
-        <v>1.92</v>
+        <v>1.25</v>
       </c>
       <c r="V4">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="X4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
+        <v>2.08</v>
+      </c>
+      <c r="AC4">
         <v>9</v>
       </c>
-      <c r="AC4">
-        <v>12</v>
-      </c>
       <c r="AD4">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="AE4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG4">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>220</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AK4">
-        <v>14.5</v>
+        <v>120</v>
       </c>
       <c r="AL4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>5.7</v>
+        <v>150</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="AR4">
+        <v>17.5</v>
+      </c>
+      <c r="AS4">
+        <v>17.5</v>
+      </c>
+      <c r="AT4">
+        <v>1.98</v>
+      </c>
+      <c r="AU4">
+        <v>7.6</v>
+      </c>
+      <c r="AV4">
+        <v>55</v>
+      </c>
+      <c r="AW4">
+        <v>120</v>
+      </c>
+      <c r="AX4">
+        <v>4</v>
+      </c>
+      <c r="AY4">
+        <v>15.5</v>
+      </c>
+      <c r="AZ4">
+        <v>90</v>
+      </c>
+      <c r="BA4">
+        <v>120</v>
+      </c>
+      <c r="BB4">
+        <v>16.5</v>
+      </c>
+      <c r="BC4">
+        <v>60</v>
+      </c>
+      <c r="BD4">
+        <v>13</v>
+      </c>
+      <c r="BE4">
+        <v>13</v>
+      </c>
+      <c r="BF4">
         <v>65</v>
       </c>
-      <c r="AS4">
-        <v>150</v>
-      </c>
-      <c r="AT4">
-        <v>8.6</v>
-      </c>
-      <c r="AU4">
-        <v>10.5</v>
-      </c>
-      <c r="AV4">
-        <v>29</v>
-      </c>
-      <c r="AW4">
-        <v>75</v>
-      </c>
-      <c r="AX4">
-        <v>8</v>
-      </c>
-      <c r="AY4">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4">
-        <v>23</v>
-      </c>
-      <c r="BA4">
-        <v>95</v>
-      </c>
-      <c r="BB4">
-        <v>10.5</v>
-      </c>
-      <c r="BC4">
-        <v>13.5</v>
-      </c>
-      <c r="BD4">
-        <v>32</v>
-      </c>
-      <c r="BE4">
-        <v>110</v>
-      </c>
-      <c r="BF4">
-        <v>5.5</v>
-      </c>
       <c r="BG4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="BH4">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>167</v>
@@ -1837,13 +1837,13 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="G5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
         <v>6.2</v>
@@ -1852,205 +1852,205 @@
         <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M5">
         <v>1.06</v>
       </c>
       <c r="N5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P5">
+        <v>2.04</v>
+      </c>
+      <c r="Q5">
+        <v>1.92</v>
+      </c>
+      <c r="R5">
+        <v>1.41</v>
+      </c>
+      <c r="S5">
+        <v>3.3</v>
+      </c>
+      <c r="T5">
+        <v>1.86</v>
+      </c>
+      <c r="U5">
         <v>2</v>
       </c>
-      <c r="Q5">
-        <v>1.87</v>
-      </c>
-      <c r="R5">
-        <v>1.39</v>
-      </c>
-      <c r="S5">
-        <v>3.2</v>
-      </c>
-      <c r="T5">
-        <v>1.89</v>
-      </c>
-      <c r="U5">
-        <v>1.94</v>
-      </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="X5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z5">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AA5">
         <v>900</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE5">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI5">
-        <v>320</v>
+        <v>170</v>
       </c>
       <c r="AJ5">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK5">
         <v>18</v>
       </c>
       <c r="AL5">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM5">
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO5">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="AP5">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR5">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AS5">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AT5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AU5">
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW5">
+        <v>15</v>
+      </c>
+      <c r="AX5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY5">
         <v>9</v>
-      </c>
-      <c r="AX5">
-        <v>8.4</v>
-      </c>
-      <c r="AY5">
-        <v>8.6</v>
       </c>
       <c r="AZ5">
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BB5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC5">
         <v>14.5</v>
       </c>
       <c r="BD5">
+        <v>28</v>
+      </c>
+      <c r="BE5">
+        <v>10</v>
+      </c>
+      <c r="BF5">
+        <v>8.6</v>
+      </c>
+      <c r="BG5">
+        <v>10</v>
+      </c>
+      <c r="BH5">
+        <v>3.8</v>
+      </c>
+      <c r="BI5">
+        <v>3</v>
+      </c>
+      <c r="BJ5">
         <v>11</v>
       </c>
-      <c r="BE5">
-        <v>9</v>
-      </c>
-      <c r="BF5">
-        <v>7.8</v>
-      </c>
-      <c r="BG5">
-        <v>9</v>
-      </c>
-      <c r="BH5">
-        <v>3.7</v>
-      </c>
-      <c r="BI5">
-        <v>2.94</v>
-      </c>
-      <c r="BJ5">
+      <c r="BK5">
+        <v>8</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN5">
+        <v>4.5</v>
+      </c>
+      <c r="BO5">
+        <v>3.75</v>
+      </c>
+      <c r="BP5">
         <v>11.5</v>
       </c>
-      <c r="BK5">
-        <v>8.4</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>9.4</v>
-      </c>
-      <c r="BN5">
-        <v>4.3</v>
-      </c>
-      <c r="BO5">
-        <v>3.6</v>
-      </c>
-      <c r="BP5">
-        <v>11</v>
-      </c>
       <c r="BQ5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS5">
         <v>7.2</v>
       </c>
       <c r="BT5">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BU5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5">
         <v>20</v>
@@ -2079,28 +2079,28 @@
         <v>143</v>
       </c>
       <c r="F6">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I6">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J6">
         <v>3.85</v>
       </c>
       <c r="K6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
         <v>1.32</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
         <v>4.8</v>
@@ -2115,7 +2115,7 @@
         <v>1.69</v>
       </c>
       <c r="R6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S6">
         <v>2.8</v>
@@ -2127,28 +2127,28 @@
         <v>2.42</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z6">
         <v>36</v>
       </c>
       <c r="AA6">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AB6">
         <v>13</v>
       </c>
       <c r="AC6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD6">
         <v>15.5</v>
@@ -2169,34 +2169,34 @@
         <v>55</v>
       </c>
       <c r="AJ6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK6">
         <v>26</v>
       </c>
       <c r="AL6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM6">
         <v>200</v>
       </c>
       <c r="AN6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO6">
         <v>34</v>
       </c>
       <c r="AP6">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AQ6">
         <v>15.5</v>
       </c>
       <c r="AR6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT6">
         <v>11</v>
@@ -2208,7 +2208,7 @@
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX6">
         <v>13</v>
@@ -2220,10 +2220,10 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BB6">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC6">
         <v>17</v>
@@ -2238,19 +2238,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG6">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH6">
         <v>4.2</v>
       </c>
       <c r="BI6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6">
         <v>9</v>
       </c>
       <c r="BK6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2259,40 +2259,40 @@
         <v>11</v>
       </c>
       <c r="BN6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO6">
         <v>4</v>
       </c>
       <c r="BP6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT6">
+        <v>7.2</v>
+      </c>
+      <c r="BU6">
+        <v>4.5</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
         <v>8.4</v>
       </c>
-      <c r="BT6">
-        <v>7.4</v>
-      </c>
-      <c r="BU6">
-        <v>5.4</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>8.6</v>
-      </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2321,193 +2321,193 @@
         <v>144</v>
       </c>
       <c r="F7">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="G7">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="I7">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q7">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R7">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T7">
+        <v>1.75</v>
+      </c>
+      <c r="U7">
+        <v>2.12</v>
+      </c>
+      <c r="V7">
+        <v>1.35</v>
+      </c>
+      <c r="W7">
         <v>1.79</v>
       </c>
-      <c r="U7">
-        <v>2.02</v>
-      </c>
-      <c r="V7">
-        <v>1.43</v>
-      </c>
-      <c r="W7">
-        <v>1.61</v>
-      </c>
       <c r="X7">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z7">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AA7">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB7">
         <v>10.5</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE7">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AF7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI7">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AJ7">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="AK7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL7">
-        <v>290</v>
+        <v>50</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="AO7">
-        <v>600</v>
+        <v>230</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AR7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS7">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="AT7">
         <v>8.6</v>
       </c>
       <c r="AU7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
+        <v>13</v>
+      </c>
+      <c r="AW7">
+        <v>30</v>
+      </c>
+      <c r="AX7">
         <v>11</v>
       </c>
-      <c r="AW7">
-        <v>7.6</v>
-      </c>
-      <c r="AX7">
-        <v>13</v>
-      </c>
       <c r="AY7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA7">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BB7">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BC7">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BD7">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="BE7">
-        <v>8.6</v>
+        <v>75</v>
       </c>
       <c r="BF7">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="BH7">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BI7">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="BJ7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN7">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BO7">
         <v>4.3</v>
       </c>
       <c r="BP7">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BQ7">
         <v>6.6</v>
@@ -2516,28 +2516,28 @@
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BV7">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
         <v>7.8</v>
@@ -2563,25 +2563,25 @@
         <v>145</v>
       </c>
       <c r="F8">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G8">
         <v>2.9</v>
       </c>
       <c r="H8">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I8">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2596,10 +2596,10 @@
         <v>2.04</v>
       </c>
       <c r="Q8">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
         <v>3.3</v>
@@ -2608,37 +2608,37 @@
         <v>1.71</v>
       </c>
       <c r="U8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W8">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X8">
         <v>16</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA8">
         <v>44</v>
       </c>
       <c r="AB8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF8">
         <v>20</v>
@@ -2653,7 +2653,7 @@
         <v>55</v>
       </c>
       <c r="AJ8">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AK8">
         <v>40</v>
@@ -2665,10 +2665,10 @@
         <v>320</v>
       </c>
       <c r="AN8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP8">
         <v>13.5</v>
@@ -2680,10 +2680,10 @@
         <v>15.5</v>
       </c>
       <c r="AS8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU8">
         <v>7.2</v>
@@ -2692,7 +2692,7 @@
         <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX8">
         <v>17</v>
@@ -2701,16 +2701,16 @@
         <v>11</v>
       </c>
       <c r="AZ8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB8">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BC8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD8">
         <v>30</v>
@@ -2722,7 +2722,7 @@
         <v>21</v>
       </c>
       <c r="BG8">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH8">
         <v>3.65</v>
@@ -2755,7 +2755,7 @@
         <v>7</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS8">
         <v>8</v>
@@ -2805,22 +2805,22 @@
         <v>146</v>
       </c>
       <c r="F9">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G9">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H9">
         <v>4.5</v>
       </c>
       <c r="I9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
         <v>3.85</v>
       </c>
       <c r="K9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L9">
         <v>1.41</v>
@@ -2844,43 +2844,43 @@
         <v>1.37</v>
       </c>
       <c r="S9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T9">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="U9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V9">
         <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y9">
         <v>17.5</v>
       </c>
       <c r="Z9">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA9">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB9">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD9">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AF9">
         <v>11.5</v>
@@ -2889,142 +2889,142 @@
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI9">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AJ9">
         <v>21</v>
       </c>
       <c r="AK9">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AL9">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AM9">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN9">
         <v>13.5</v>
       </c>
       <c r="AO9">
-        <v>600</v>
+        <v>75</v>
       </c>
       <c r="AP9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS9">
         <v>70</v>
       </c>
       <c r="AT9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU9">
         <v>7.8</v>
       </c>
       <c r="AV9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AX9">
         <v>10</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA9">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB9">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BC9">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE9">
         <v>75</v>
       </c>
       <c r="BF9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG9">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BH9">
         <v>3.5</v>
       </c>
       <c r="BI9">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BJ9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK9">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BP9">
         <v>13.5</v>
       </c>
       <c r="BQ9">
+        <v>7</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
         <v>9.6</v>
       </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BT9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
         <v>24</v>
       </c>
       <c r="CA9">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>167</v>
@@ -3050,10 +3050,10 @@
         <v>1.98</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>4.1</v>
@@ -3065,13 +3065,13 @@
         <v>4.1</v>
       </c>
       <c r="L10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O10">
         <v>1.27</v>
@@ -3089,10 +3089,10 @@
         <v>3.05</v>
       </c>
       <c r="T10">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U10">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V10">
         <v>1.32</v>
@@ -3110,25 +3110,25 @@
         <v>32</v>
       </c>
       <c r="AA10">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB10">
         <v>11</v>
       </c>
       <c r="AC10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE10">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF10">
         <v>13</v>
       </c>
       <c r="AG10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH10">
         <v>18.5</v>
@@ -3140,13 +3140,13 @@
         <v>23</v>
       </c>
       <c r="AK10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN10">
         <v>12</v>
@@ -3158,13 +3158,13 @@
         <v>17</v>
       </c>
       <c r="AQ10">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR10">
         <v>27</v>
       </c>
       <c r="AS10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT10">
         <v>9.800000000000001</v>
@@ -3176,19 +3176,19 @@
         <v>14.5</v>
       </c>
       <c r="AW10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX10">
         <v>12</v>
       </c>
       <c r="AY10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10">
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB10">
         <v>20</v>
@@ -3203,19 +3203,19 @@
         <v>60</v>
       </c>
       <c r="BF10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG10">
         <v>36</v>
       </c>
       <c r="BH10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI10">
         <v>3.45</v>
       </c>
       <c r="BJ10">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BK10">
         <v>8.199999999999999</v>
@@ -3224,49 +3224,49 @@
         <v>130</v>
       </c>
       <c r="BM10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BN10">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP10">
         <v>16</v>
       </c>
       <c r="BQ10">
+        <v>11.5</v>
+      </c>
+      <c r="BR10">
+        <v>32</v>
+      </c>
+      <c r="BS10">
+        <v>5.9</v>
+      </c>
+      <c r="BT10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU10">
         <v>6.8</v>
       </c>
-      <c r="BR10">
-        <v>26</v>
-      </c>
-      <c r="BS10">
-        <v>7.8</v>
-      </c>
-      <c r="BT10">
-        <v>7.6</v>
-      </c>
-      <c r="BU10">
-        <v>6.6</v>
-      </c>
       <c r="BV10">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BW10">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="BX10">
         <v>48</v>
       </c>
       <c r="BY10">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BZ10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA10">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="CB10" t="s">
         <v>167</v>
@@ -3289,82 +3289,82 @@
         <v>148</v>
       </c>
       <c r="F11">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G11">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="H11">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I11">
         <v>4.7</v>
       </c>
       <c r="J11">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L11">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="Q11">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="R11">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="S11">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="T11">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U11">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="V11">
         <v>1.27</v>
       </c>
       <c r="W11">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="X11">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y11">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA11">
-        <v>100</v>
+        <v>890</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE11">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AF11">
         <v>13</v>
@@ -3376,112 +3376,112 @@
         <v>16</v>
       </c>
       <c r="AI11">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ11">
         <v>19</v>
       </c>
       <c r="AK11">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM11">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN11">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO11">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AP11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AQ11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AR11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS11">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AT11">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11">
         <v>16.5</v>
       </c>
       <c r="AW11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
+        <v>15.5</v>
+      </c>
+      <c r="BA11">
+        <v>40</v>
+      </c>
+      <c r="BB11">
+        <v>17</v>
+      </c>
+      <c r="BC11">
         <v>15</v>
       </c>
-      <c r="BA11">
-        <v>42</v>
-      </c>
-      <c r="BB11">
-        <v>16.5</v>
-      </c>
-      <c r="BC11">
-        <v>14.5</v>
-      </c>
       <c r="BD11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BE11">
         <v>55</v>
       </c>
       <c r="BF11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG11">
+        <v>36</v>
+      </c>
+      <c r="BH11">
+        <v>4.1</v>
+      </c>
+      <c r="BI11">
+        <v>3.3</v>
+      </c>
+      <c r="BJ11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK11">
         <v>7</v>
       </c>
-      <c r="BG11">
-        <v>32</v>
-      </c>
-      <c r="BH11">
-        <v>4.5</v>
-      </c>
-      <c r="BI11">
-        <v>3.6</v>
-      </c>
-      <c r="BJ11">
-        <v>9</v>
-      </c>
-      <c r="BK11">
-        <v>6.2</v>
-      </c>
       <c r="BL11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO11">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BP11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ11">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BS11">
         <v>9</v>
@@ -3490,19 +3490,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU11">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW11">
         <v>10.5</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3531,85 +3531,85 @@
         <v>149</v>
       </c>
       <c r="F12">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G12">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H12">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I12">
         <v>2.46</v>
       </c>
       <c r="J12">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L12">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O12">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P12">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R12">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S12">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U12">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
         <v>1.68</v>
       </c>
       <c r="W12">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X12">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z12">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AA12">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB12">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE12">
         <v>24</v>
       </c>
       <c r="AF12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG12">
         <v>14</v>
@@ -3621,130 +3621,130 @@
         <v>36</v>
       </c>
       <c r="AJ12">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="AK12">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL12">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AM12">
         <v>190</v>
       </c>
       <c r="AN12">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AO12">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP12">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR12">
         <v>15</v>
       </c>
       <c r="AS12">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AT12">
         <v>13</v>
       </c>
       <c r="AU12">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW12">
+        <v>21</v>
+      </c>
+      <c r="AX12">
         <v>20</v>
       </c>
-      <c r="AX12">
-        <v>19.5</v>
-      </c>
       <c r="AY12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA12">
+        <v>28</v>
+      </c>
+      <c r="BB12">
+        <v>38</v>
+      </c>
+      <c r="BC12">
         <v>26</v>
       </c>
-      <c r="BB12">
+      <c r="BD12">
         <v>32</v>
       </c>
-      <c r="BC12">
-        <v>23</v>
-      </c>
-      <c r="BD12">
-        <v>30</v>
-      </c>
       <c r="BE12">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BF12">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BG12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH12">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BI12">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BK12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO12">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BQ12">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT12">
+        <v>5.7</v>
+      </c>
+      <c r="BU12">
+        <v>4.7</v>
+      </c>
+      <c r="BV12">
+        <v>18</v>
+      </c>
+      <c r="BW12">
+        <v>6.6</v>
+      </c>
+      <c r="BX12">
+        <v>29</v>
+      </c>
+      <c r="BY12">
         <v>7.8</v>
-      </c>
-      <c r="BT12">
-        <v>5.8</v>
-      </c>
-      <c r="BU12">
-        <v>4.8</v>
-      </c>
-      <c r="BV12">
-        <v>17</v>
-      </c>
-      <c r="BW12">
-        <v>6.4</v>
-      </c>
-      <c r="BX12">
-        <v>27</v>
-      </c>
-      <c r="BY12">
-        <v>7.4</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3776,16 +3776,16 @@
         <v>2.64</v>
       </c>
       <c r="G13">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H13">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I13">
         <v>3.55</v>
       </c>
       <c r="J13">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K13">
         <v>2.98</v>
@@ -3800,52 +3800,52 @@
         <v>2.5</v>
       </c>
       <c r="O13">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P13">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q13">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R13">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S13">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T13">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U13">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V13">
         <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z13">
         <v>22</v>
       </c>
       <c r="AA13">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AB13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>7.4</v>
       </c>
       <c r="AD13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE13">
         <v>60</v>
@@ -3854,37 +3854,37 @@
         <v>16.5</v>
       </c>
       <c r="AG13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH13">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AI13">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AJ13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK13">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM13">
         <v>500</v>
       </c>
       <c r="AN13">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AO13">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AP13">
         <v>6.8</v>
       </c>
       <c r="AQ13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR13">
         <v>17.5</v>
@@ -3893,7 +3893,7 @@
         <v>46</v>
       </c>
       <c r="AT13">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU13">
         <v>6</v>
@@ -3908,10 +3908,10 @@
         <v>13.5</v>
       </c>
       <c r="AY13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA13">
         <v>50</v>
@@ -3920,37 +3920,37 @@
         <v>30</v>
       </c>
       <c r="BC13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD13">
         <v>46</v>
       </c>
       <c r="BE13">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF13">
         <v>40</v>
       </c>
       <c r="BG13">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH13">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BI13">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BJ13">
         <v>12</v>
       </c>
       <c r="BK13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN13">
         <v>5.6</v>
@@ -3959,16 +3959,16 @@
         <v>4.1</v>
       </c>
       <c r="BP13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR13">
         <v>55</v>
       </c>
       <c r="BS13">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT13">
         <v>6.4</v>
@@ -3980,19 +3980,19 @@
         <v>34</v>
       </c>
       <c r="BW13">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB13" t="s">
         <v>167</v>
@@ -4015,13 +4015,13 @@
         <v>151</v>
       </c>
       <c r="F14">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G14">
         <v>3.8</v>
       </c>
       <c r="H14">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="I14">
         <v>2.66</v>
@@ -4039,13 +4039,13 @@
         <v>1.13</v>
       </c>
       <c r="N14">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P14">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q14">
         <v>2.72</v>
@@ -4060,16 +4060,16 @@
         <v>2.08</v>
       </c>
       <c r="U14">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V14">
         <v>1.6</v>
       </c>
       <c r="W14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -4078,7 +4078,7 @@
         <v>15</v>
       </c>
       <c r="AA14">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="AB14">
         <v>10.5</v>
@@ -4087,7 +4087,7 @@
         <v>7.4</v>
       </c>
       <c r="AD14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE14">
         <v>110</v>
@@ -4102,7 +4102,7 @@
         <v>24</v>
       </c>
       <c r="AI14">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="AJ14">
         <v>250</v>
@@ -4120,7 +4120,7 @@
         <v>600</v>
       </c>
       <c r="AO14">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AP14">
         <v>7.4</v>
@@ -4141,16 +4141,16 @@
         <v>6.2</v>
       </c>
       <c r="AV14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX14">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AY14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ14">
         <v>19</v>
@@ -4165,16 +4165,16 @@
         <v>20</v>
       </c>
       <c r="BD14">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BE14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG14">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BH14">
         <v>2.82</v>
@@ -4257,40 +4257,40 @@
         <v>152</v>
       </c>
       <c r="F15">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G15">
         <v>1.95</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I15">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K15">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L15">
         <v>1.54</v>
       </c>
       <c r="M15">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N15">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P15">
         <v>1.6</v>
       </c>
       <c r="Q15">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R15">
         <v>1.21</v>
@@ -4302,34 +4302,34 @@
         <v>2.16</v>
       </c>
       <c r="U15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V15">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W15">
         <v>2.04</v>
       </c>
       <c r="X15">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z15">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AA15">
         <v>900</v>
       </c>
       <c r="AB15">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE15">
         <v>500</v>
@@ -4338,7 +4338,7 @@
         <v>10.5</v>
       </c>
       <c r="AG15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH15">
         <v>32</v>
@@ -4350,46 +4350,46 @@
         <v>26</v>
       </c>
       <c r="AK15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL15">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AM15">
         <v>580</v>
       </c>
       <c r="AN15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO15">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="AP15">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AS15">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT15">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU15">
         <v>7</v>
       </c>
       <c r="AV15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AW15">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AX15">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY15">
         <v>9.4</v>
@@ -4398,31 +4398,31 @@
         <v>20</v>
       </c>
       <c r="BA15">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BB15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC15">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD15">
         <v>34</v>
       </c>
       <c r="BE15">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG15">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH15">
         <v>3.15</v>
       </c>
       <c r="BI15">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ15">
         <v>13.5</v>
@@ -4505,31 +4505,31 @@
         <v>1.39</v>
       </c>
       <c r="H16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J16">
         <v>4.8</v>
       </c>
       <c r="K16">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L16">
         <v>1.43</v>
       </c>
       <c r="M16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P16">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q16">
         <v>2.08</v>
@@ -4538,16 +4538,16 @@
         <v>1.31</v>
       </c>
       <c r="S16">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T16">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="U16">
         <v>1.55</v>
       </c>
       <c r="V16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W16">
         <v>3.55</v>
@@ -4565,7 +4565,7 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC16">
         <v>12.5</v>
@@ -4574,7 +4574,7 @@
         <v>160</v>
       </c>
       <c r="AE16">
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="AF16">
         <v>7</v>
@@ -4586,7 +4586,7 @@
         <v>130</v>
       </c>
       <c r="AI16">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="AJ16">
         <v>11</v>
@@ -4598,7 +4598,7 @@
         <v>250</v>
       </c>
       <c r="AM16">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="AN16">
         <v>8</v>
@@ -4610,55 +4610,55 @@
         <v>12</v>
       </c>
       <c r="AQ16">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="AR16">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS16">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT16">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU16">
         <v>10</v>
       </c>
       <c r="AV16">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AW16">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX16">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AY16">
         <v>9.6</v>
       </c>
       <c r="AZ16">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="BA16">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB16">
         <v>9</v>
       </c>
       <c r="BC16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD16">
-        <v>42</v>
+        <v>9.4</v>
       </c>
       <c r="BE16">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF16">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH16">
         <v>3.5</v>
@@ -4670,55 +4670,55 @@
         <v>15</v>
       </c>
       <c r="BK16">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN16">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BO16">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="BP16">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BQ16">
         <v>6</v>
       </c>
       <c r="BR16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT16">
         <v>16</v>
       </c>
       <c r="BU16">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ16">
         <v>18</v>
       </c>
       <c r="CA16">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="s">
         <v>167</v>
@@ -4741,64 +4741,64 @@
         <v>154</v>
       </c>
       <c r="F17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H17">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I17">
         <v>1.31</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K17">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L17">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M17">
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O17">
         <v>1.1</v>
       </c>
       <c r="P17">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q17">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R17">
         <v>2.14</v>
       </c>
       <c r="S17">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="T17">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="U17">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="W17">
         <v>1.1</v>
       </c>
       <c r="X17">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Y17">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z17">
         <v>12.5</v>
@@ -4807,7 +4807,7 @@
         <v>12.5</v>
       </c>
       <c r="AB17">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AC17">
         <v>18</v>
@@ -4819,7 +4819,7 @@
         <v>13</v>
       </c>
       <c r="AF17">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AG17">
         <v>40</v>
@@ -4828,7 +4828,7 @@
         <v>24</v>
       </c>
       <c r="AI17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ17">
         <v>430</v>
@@ -4837,34 +4837,34 @@
         <v>120</v>
       </c>
       <c r="AL17">
+        <v>80</v>
+      </c>
+      <c r="AM17">
         <v>85</v>
       </c>
-      <c r="AM17">
-        <v>90</v>
-      </c>
       <c r="AN17">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO17">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AP17">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AQ17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT17">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AU17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AV17">
         <v>10.5</v>
@@ -4876,7 +4876,7 @@
         <v>90</v>
       </c>
       <c r="AY17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AZ17">
         <v>21</v>
@@ -4885,19 +4885,19 @@
         <v>22</v>
       </c>
       <c r="BB17">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC17">
         <v>80</v>
       </c>
       <c r="BD17">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BE17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF17">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BG17">
         <v>3.1</v>
@@ -4906,7 +4906,7 @@
         <v>6.2</v>
       </c>
       <c r="BI17">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ17">
         <v>10.5</v>
@@ -4924,7 +4924,7 @@
         <v>14</v>
       </c>
       <c r="BO17">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BP17">
         <v>65</v>
@@ -4933,22 +4933,22 @@
         <v>12.5</v>
       </c>
       <c r="BR17">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS17">
         <v>11.5</v>
       </c>
       <c r="BT17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU17">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BV17">
         <v>7.2</v>
       </c>
       <c r="BW17">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BX17">
         <v>16.5</v>
@@ -4957,10 +4957,10 @@
         <v>8</v>
       </c>
       <c r="BZ17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CA17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="CB17" t="s">
         <v>167</v>
@@ -4983,13 +4983,13 @@
         <v>155</v>
       </c>
       <c r="F18">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G18">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H18">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I18">
         <v>5.2</v>
@@ -5001,46 +5001,46 @@
         <v>4.6</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="O18">
         <v>1.21</v>
       </c>
       <c r="P18">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q18">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R18">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S18">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="T18">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U18">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V18">
         <v>1.24</v>
       </c>
       <c r="W18">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X18">
         <v>23</v>
       </c>
       <c r="Y18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z18">
         <v>55</v>
@@ -5052,22 +5052,22 @@
         <v>12</v>
       </c>
       <c r="AC18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD18">
         <v>21</v>
       </c>
       <c r="AE18">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AF18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG18">
         <v>11</v>
       </c>
       <c r="AH18">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI18">
         <v>65</v>
@@ -5076,22 +5076,22 @@
         <v>18.5</v>
       </c>
       <c r="AK18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AL18">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AM18">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN18">
         <v>8</v>
       </c>
       <c r="AO18">
-        <v>280</v>
+        <v>95</v>
       </c>
       <c r="AP18">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ18">
         <v>20</v>
@@ -5109,7 +5109,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW18">
         <v>38</v>
@@ -5121,88 +5121,88 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ18">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA18">
         <v>34</v>
       </c>
       <c r="BB18">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC18">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE18">
         <v>55</v>
       </c>
       <c r="BF18">
+        <v>6.6</v>
+      </c>
+      <c r="BG18">
+        <v>29</v>
+      </c>
+      <c r="BH18">
+        <v>4.4</v>
+      </c>
+      <c r="BI18">
+        <v>3.4</v>
+      </c>
+      <c r="BJ18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK18">
+        <v>4.9</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN18">
+        <v>4.8</v>
+      </c>
+      <c r="BO18">
+        <v>3.7</v>
+      </c>
+      <c r="BP18">
+        <v>11.5</v>
+      </c>
+      <c r="BQ18">
+        <v>5.3</v>
+      </c>
+      <c r="BR18">
+        <v>23</v>
+      </c>
+      <c r="BS18">
         <v>6.8</v>
       </c>
-      <c r="BG18">
-        <v>34</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.04</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.04</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>1.04</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>1.04</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>1.04</v>
-      </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB18" t="s">
         <v>167</v>
@@ -5225,22 +5225,22 @@
         <v>156</v>
       </c>
       <c r="F19">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="H19">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="J19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
         <v>1.27</v>
@@ -5249,13 +5249,13 @@
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O19">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P19">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q19">
         <v>1.51</v>
@@ -5264,73 +5264,73 @@
         <v>1.73</v>
       </c>
       <c r="S19">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T19">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U19">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W19">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="X19">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y19">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z19">
         <v>42</v>
       </c>
       <c r="AA19">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB19">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AC19">
+        <v>11.5</v>
+      </c>
+      <c r="AD19">
+        <v>21</v>
+      </c>
+      <c r="AE19">
+        <v>42</v>
+      </c>
+      <c r="AF19">
+        <v>18.5</v>
+      </c>
+      <c r="AG19">
         <v>11</v>
       </c>
-      <c r="AD19">
-        <v>16</v>
-      </c>
-      <c r="AE19">
-        <v>36</v>
-      </c>
-      <c r="AF19">
-        <v>17</v>
-      </c>
-      <c r="AG19">
-        <v>11.5</v>
-      </c>
       <c r="AH19">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI19">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ19">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AK19">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL19">
         <v>25</v>
       </c>
       <c r="AM19">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AN19">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AO19">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AP19">
         <v>23</v>
@@ -5339,22 +5339,22 @@
         <v>22</v>
       </c>
       <c r="AR19">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AS19">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="AT19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV19">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW19">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX19">
         <v>13.5</v>
@@ -5366,79 +5366,79 @@
         <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB19">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BC19">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BD19">
         <v>21</v>
       </c>
       <c r="BE19">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF19">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG19">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BH19">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI19">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BJ19">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK19">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM19">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BN19">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BO19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP19">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ19">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BR19">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BS19">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BT19">
         <v>8.4</v>
       </c>
       <c r="BU19">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="BV19">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BW19">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BX19">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BY19">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5467,16 +5467,16 @@
         <v>157</v>
       </c>
       <c r="F20">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H20">
+        <v>2.68</v>
+      </c>
+      <c r="I20">
         <v>2.72</v>
-      </c>
-      <c r="I20">
-        <v>2.74</v>
       </c>
       <c r="J20">
         <v>3.35</v>
@@ -5485,43 +5485,43 @@
         <v>3.4</v>
       </c>
       <c r="L20">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M20">
         <v>1.09</v>
       </c>
       <c r="N20">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O20">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P20">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q20">
         <v>2.2</v>
       </c>
       <c r="R20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S20">
         <v>4.1</v>
       </c>
       <c r="T20">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U20">
         <v>2.12</v>
       </c>
       <c r="V20">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W20">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -5539,10 +5539,10 @@
         <v>7.2</v>
       </c>
       <c r="AD20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF20">
         <v>19</v>
@@ -5551,31 +5551,31 @@
         <v>13</v>
       </c>
       <c r="AH20">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI20">
         <v>44</v>
       </c>
       <c r="AJ20">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK20">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL20">
         <v>48</v>
       </c>
       <c r="AM20">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN20">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO20">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ20">
         <v>9.6</v>
@@ -5584,7 +5584,7 @@
         <v>15.5</v>
       </c>
       <c r="AS20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT20">
         <v>10</v>
@@ -5599,43 +5599,43 @@
         <v>30</v>
       </c>
       <c r="AX20">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20">
         <v>16.5</v>
       </c>
       <c r="BA20">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB20">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BC20">
         <v>32</v>
       </c>
       <c r="BD20">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BF20">
         <v>34</v>
       </c>
       <c r="BG20">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI20">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BJ20">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK20">
         <v>8.800000000000001</v>
@@ -5644,37 +5644,37 @@
         <v>140</v>
       </c>
       <c r="BM20">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BN20">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO20">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP20">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ20">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BR20">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS20">
         <v>34</v>
       </c>
       <c r="BT20">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU20">
         <v>5.1</v>
       </c>
       <c r="BV20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW20">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BX20">
         <v>38</v>
@@ -5683,10 +5683,10 @@
         <v>32</v>
       </c>
       <c r="BZ20">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="CA20">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="CB20" t="s">
         <v>167</v>
@@ -5709,16 +5709,16 @@
         <v>158</v>
       </c>
       <c r="F21">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="G21">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="H21">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I21">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J21">
         <v>4.2</v>
@@ -5727,7 +5727,7 @@
         <v>4.3</v>
       </c>
       <c r="L21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M21">
         <v>1.03</v>
@@ -5739,31 +5739,31 @@
         <v>1.18</v>
       </c>
       <c r="P21">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q21">
         <v>1.56</v>
       </c>
       <c r="R21">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S21">
         <v>2.38</v>
       </c>
       <c r="T21">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U21">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="X21">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y21">
         <v>22</v>
@@ -5772,7 +5772,7 @@
         <v>32</v>
       </c>
       <c r="AA21">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB21">
         <v>14</v>
@@ -5781,43 +5781,43 @@
         <v>10.5</v>
       </c>
       <c r="AD21">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ21">
         <v>23</v>
       </c>
       <c r="AK21">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN21">
         <v>8.6</v>
       </c>
       <c r="AO21">
+        <v>24</v>
+      </c>
+      <c r="AP21">
         <v>25</v>
-      </c>
-      <c r="AP21">
-        <v>24</v>
       </c>
       <c r="AQ21">
         <v>20</v>
@@ -5832,34 +5832,34 @@
         <v>13.5</v>
       </c>
       <c r="AU21">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV21">
+        <v>14</v>
+      </c>
+      <c r="AW21">
+        <v>30</v>
+      </c>
+      <c r="AX21">
         <v>15</v>
       </c>
-      <c r="AW21">
-        <v>32</v>
-      </c>
-      <c r="AX21">
-        <v>14</v>
-      </c>
       <c r="AY21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ21">
         <v>13.5</v>
       </c>
       <c r="BA21">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB21">
         <v>21</v>
       </c>
       <c r="BC21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE21">
         <v>46</v>
@@ -5868,67 +5868,67 @@
         <v>8</v>
       </c>
       <c r="BG21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH21">
         <v>4.5</v>
       </c>
       <c r="BI21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ21">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK21">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL21">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM21">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN21">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO21">
         <v>4.8</v>
       </c>
       <c r="BP21">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BQ21">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BR21">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BS21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BT21">
         <v>7.4</v>
       </c>
       <c r="BU21">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV21">
         <v>28</v>
       </c>
       <c r="BW21">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BX21">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY21">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BZ21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CA21">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="CB21" t="s">
         <v>167</v>
@@ -5951,10 +5951,10 @@
         <v>159</v>
       </c>
       <c r="F22">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="G22">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H22">
         <v>6</v>
@@ -5963,58 +5963,58 @@
         <v>6.2</v>
       </c>
       <c r="J22">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K22">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L22">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M22">
         <v>1.02</v>
       </c>
       <c r="N22">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="O22">
         <v>1.11</v>
       </c>
       <c r="P22">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q22">
         <v>1.35</v>
       </c>
       <c r="R22">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S22">
         <v>1.86</v>
       </c>
       <c r="T22">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="U22">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="V22">
         <v>1.19</v>
       </c>
       <c r="W22">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="X22">
         <v>50</v>
       </c>
       <c r="Y22">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z22">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AA22">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB22">
         <v>18.5</v>
@@ -6023,28 +6023,28 @@
         <v>14</v>
       </c>
       <c r="AD22">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE22">
         <v>55</v>
       </c>
       <c r="AF22">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG22">
         <v>11.5</v>
       </c>
       <c r="AH22">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI22">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK22">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL22">
         <v>21</v>
@@ -6053,31 +6053,31 @@
         <v>50</v>
       </c>
       <c r="AN22">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AO22">
         <v>34</v>
       </c>
       <c r="AP22">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AQ22">
         <v>36</v>
       </c>
       <c r="AR22">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS22">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AT22">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU22">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW22">
         <v>50</v>
@@ -6086,13 +6086,13 @@
         <v>14</v>
       </c>
       <c r="AY22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA22">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB22">
         <v>15.5</v>
@@ -6104,13 +6104,13 @@
         <v>19.5</v>
       </c>
       <c r="BE22">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BF22">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BG22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH22">
         <v>5.9</v>
@@ -6134,19 +6134,19 @@
         <v>5</v>
       </c>
       <c r="BO22">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP22">
         <v>9</v>
       </c>
       <c r="BQ22">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR22">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BS22">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT22">
         <v>10.5</v>
@@ -6155,13 +6155,13 @@
         <v>6.4</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW22">
         <v>11.5</v>
       </c>
       <c r="BX22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY22">
         <v>11</v>
@@ -6170,7 +6170,7 @@
         <v>8.4</v>
       </c>
       <c r="CA22">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB22" t="s">
         <v>167</v>
@@ -6196,19 +6196,19 @@
         <v>1.26</v>
       </c>
       <c r="G23">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>12.5</v>
       </c>
       <c r="J23">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="K23">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L23">
         <v>1.15</v>
@@ -6217,10 +6217,10 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O23">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P23">
         <v>4.6</v>
@@ -6229,16 +6229,16 @@
         <v>1.24</v>
       </c>
       <c r="R23">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="S23">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="T23">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="U23">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="V23">
         <v>1.08</v>
@@ -6250,16 +6250,16 @@
         <v>75</v>
       </c>
       <c r="Y23">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="Z23">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AA23">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="AB23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC23">
         <v>23</v>
@@ -6268,19 +6268,19 @@
         <v>46</v>
       </c>
       <c r="AE23">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="AF23">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG23">
         <v>14</v>
       </c>
       <c r="AH23">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI23">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ23">
         <v>14.5</v>
@@ -6301,7 +6301,7 @@
         <v>65</v>
       </c>
       <c r="AP23">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AQ23">
         <v>23</v>
@@ -6310,28 +6310,28 @@
         <v>28</v>
       </c>
       <c r="AS23">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AT23">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU23">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AV23">
         <v>38</v>
       </c>
       <c r="AW23">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="AX23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY23">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA23">
         <v>60</v>
@@ -6340,25 +6340,25 @@
         <v>12</v>
       </c>
       <c r="BC23">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE23">
         <v>55</v>
       </c>
       <c r="BF23">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="BG23">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BH23">
         <v>7.6</v>
       </c>
       <c r="BI23">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BJ23">
         <v>11</v>
@@ -6370,31 +6370,31 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN23">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP23">
         <v>7.4</v>
       </c>
       <c r="BQ23">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BR23">
         <v>15.5</v>
       </c>
       <c r="BS23">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BT23">
         <v>15.5</v>
       </c>
       <c r="BU23">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BV23">
         <v>1000</v>
@@ -6403,10 +6403,10 @@
         <v>8.6</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY23">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6438,22 +6438,22 @@
         <v>2.38</v>
       </c>
       <c r="G24">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H24">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J24">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K24">
         <v>3.1</v>
       </c>
       <c r="L24">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M24">
         <v>1.14</v>
@@ -6462,40 +6462,40 @@
         <v>2.56</v>
       </c>
       <c r="O24">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P24">
         <v>1.5</v>
       </c>
       <c r="Q24">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R24">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S24">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T24">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U24">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V24">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X24">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z24">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AA24">
         <v>900</v>
@@ -6507,31 +6507,31 @@
         <v>7.2</v>
       </c>
       <c r="AD24">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AE24">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AF24">
         <v>14.5</v>
       </c>
       <c r="AG24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH24">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AI24">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AJ24">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AK24">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AL24">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AM24">
         <v>500</v>
@@ -6543,16 +6543,16 @@
         <v>600</v>
       </c>
       <c r="AP24">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ24">
         <v>8.6</v>
       </c>
       <c r="AR24">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AS24">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AT24">
         <v>6.4</v>
@@ -6564,46 +6564,46 @@
         <v>14.5</v>
       </c>
       <c r="AW24">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AX24">
         <v>12</v>
       </c>
       <c r="AY24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA24">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BB24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC24">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BD24">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="BE24">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="BF24">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="BG24">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="BH24">
         <v>2.64</v>
       </c>
       <c r="BI24">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK24">
         <v>6.6</v>
@@ -6624,13 +6624,13 @@
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT24">
         <v>6.8</v>
@@ -6642,13 +6642,13 @@
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6677,25 +6677,25 @@
         <v>162</v>
       </c>
       <c r="F25">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="G25">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="H25">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="I25">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K25">
         <v>3.15</v>
       </c>
       <c r="L25">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M25">
         <v>1.12</v>
@@ -6704,199 +6704,199 @@
         <v>2.72</v>
       </c>
       <c r="O25">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P25">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q25">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="R25">
         <v>1.21</v>
       </c>
       <c r="S25">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T25">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U25">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V25">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W25">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X25">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z25">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA25">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC25">
         <v>7</v>
       </c>
       <c r="AD25">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE25">
+        <v>55</v>
+      </c>
+      <c r="AF25">
+        <v>20</v>
+      </c>
+      <c r="AG25">
+        <v>16</v>
+      </c>
+      <c r="AH25">
+        <v>22</v>
+      </c>
+      <c r="AI25">
+        <v>85</v>
+      </c>
+      <c r="AJ25">
+        <v>60</v>
+      </c>
+      <c r="AK25">
         <v>50</v>
       </c>
-      <c r="AF25">
-        <v>21</v>
-      </c>
-      <c r="AG25">
-        <v>14</v>
-      </c>
-      <c r="AH25">
-        <v>23</v>
-      </c>
-      <c r="AI25">
+      <c r="AL25">
         <v>75</v>
-      </c>
-      <c r="AJ25">
-        <v>65</v>
-      </c>
-      <c r="AK25">
-        <v>55</v>
-      </c>
-      <c r="AL25">
-        <v>80</v>
       </c>
       <c r="AM25">
         <v>500</v>
       </c>
       <c r="AN25">
+        <v>60</v>
+      </c>
+      <c r="AO25">
         <v>65</v>
       </c>
-      <c r="AO25">
-        <v>55</v>
-      </c>
       <c r="AP25">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ25">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR25">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS25">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="AT25">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU25">
         <v>6.2</v>
       </c>
       <c r="AV25">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW25">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AX25">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY25">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ25">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA25">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BB25">
-        <v>40</v>
+        <v>6.6</v>
       </c>
       <c r="BC25">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="BD25">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE25">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF25">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="BG25">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BH25">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI25">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BJ25">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK25">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BN25">
         <v>6.8</v>
       </c>
       <c r="BO25">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP25">
         <v>32</v>
       </c>
       <c r="BQ25">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BR25">
         <v>60</v>
       </c>
       <c r="BS25">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BT25">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BU25">
         <v>4.4</v>
       </c>
       <c r="BV25">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW25">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BX25">
         <v>60</v>
       </c>
       <c r="BY25">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BZ25">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CA25">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="CB25" t="s">
         <v>167</v>
@@ -6922,10 +6922,10 @@
         <v>2.2</v>
       </c>
       <c r="G26">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H26">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I26">
         <v>4.3</v>
@@ -6946,7 +6946,7 @@
         <v>2.76</v>
       </c>
       <c r="O26">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P26">
         <v>1.56</v>
@@ -6964,43 +6964,43 @@
         <v>2.14</v>
       </c>
       <c r="U26">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V26">
         <v>1.31</v>
       </c>
       <c r="W26">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X26">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y26">
         <v>11.5</v>
       </c>
       <c r="Z26">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA26">
         <v>900</v>
       </c>
       <c r="AB26">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD26">
         <v>22</v>
       </c>
       <c r="AE26">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AF26">
         <v>12.5</v>
       </c>
       <c r="AG26">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH26">
         <v>34</v>
@@ -7012,31 +7012,31 @@
         <v>36</v>
       </c>
       <c r="AK26">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AL26">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AM26">
         <v>500</v>
       </c>
       <c r="AN26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO26">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP26">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ26">
         <v>10</v>
       </c>
       <c r="AR26">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AS26">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AT26">
         <v>6.2</v>
@@ -7045,10 +7045,10 @@
         <v>6.4</v>
       </c>
       <c r="AV26">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW26">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AX26">
         <v>10.5</v>
@@ -7057,46 +7057,46 @@
         <v>10</v>
       </c>
       <c r="AZ26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA26">
         <v>28</v>
       </c>
       <c r="BB26">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC26">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD26">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BE26">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BF26">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BG26">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH26">
         <v>3.05</v>
       </c>
       <c r="BI26">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ26">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BK26">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BN26">
         <v>4.8</v>
@@ -7108,37 +7108,37 @@
         <v>21</v>
       </c>
       <c r="BQ26">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BR26">
         <v>48</v>
       </c>
       <c r="BS26">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BT26">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU26">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV26">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW26">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BX26">
         <v>70</v>
       </c>
       <c r="BY26">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BZ26">
         <v>55</v>
       </c>
       <c r="CA26">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB26" t="s">
         <v>167</v>
@@ -7161,226 +7161,226 @@
         <v>164</v>
       </c>
       <c r="F27">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="G27">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="H27">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="I27">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="J27">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K27">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L27">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M27">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N27">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O27">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P27">
         <v>1.58</v>
       </c>
       <c r="Q27">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R27">
         <v>1.21</v>
       </c>
       <c r="S27">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T27">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U27">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V27">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W27">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="X27">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y27">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z27">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA27">
         <v>900</v>
       </c>
       <c r="AB27">
+        <v>8.6</v>
+      </c>
+      <c r="AC27">
         <v>7.2</v>
-      </c>
-      <c r="AC27">
-        <v>7.8</v>
       </c>
       <c r="AD27">
         <v>20</v>
       </c>
       <c r="AE27">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AF27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG27">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH27">
         <v>24</v>
       </c>
       <c r="AI27">
-        <v>200</v>
+        <v>380</v>
       </c>
       <c r="AJ27">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AK27">
         <v>32</v>
       </c>
       <c r="AL27">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AM27">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN27">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AO27">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AP27">
         <v>8</v>
       </c>
       <c r="AQ27">
+        <v>9.6</v>
+      </c>
+      <c r="AR27">
+        <v>21</v>
+      </c>
+      <c r="AS27">
+        <v>30</v>
+      </c>
+      <c r="AT27">
+        <v>6.8</v>
+      </c>
+      <c r="AU27">
+        <v>6.4</v>
+      </c>
+      <c r="AV27">
+        <v>15.5</v>
+      </c>
+      <c r="AW27">
+        <v>46</v>
+      </c>
+      <c r="AX27">
+        <v>11.5</v>
+      </c>
+      <c r="AY27">
         <v>10.5</v>
       </c>
-      <c r="AR27">
-        <v>20</v>
-      </c>
-      <c r="AS27">
-        <v>8.4</v>
-      </c>
-      <c r="AT27">
-        <v>6.2</v>
-      </c>
-      <c r="AU27">
-        <v>6.6</v>
-      </c>
-      <c r="AV27">
-        <v>16</v>
-      </c>
-      <c r="AW27">
-        <v>29</v>
-      </c>
-      <c r="AX27">
-        <v>10</v>
-      </c>
-      <c r="AY27">
-        <v>9.6</v>
-      </c>
       <c r="AZ27">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA27">
         <v>28</v>
       </c>
       <c r="BB27">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BC27">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BD27">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BE27">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BF27">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BG27">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="BH27">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI27">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BJ27">
         <v>13</v>
       </c>
       <c r="BK27">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BN27">
         <v>5.2</v>
       </c>
       <c r="BO27">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BP27">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BQ27">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BR27">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS27">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT27">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU27">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="BV27">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BW27">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY27">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ27">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB27" t="s">
         <v>167</v>
@@ -7403,7 +7403,7 @@
         <v>165</v>
       </c>
       <c r="F28">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G28">
         <v>2.36</v>
@@ -7412,19 +7412,19 @@
         <v>3.15</v>
       </c>
       <c r="I28">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J28">
         <v>3.7</v>
       </c>
       <c r="K28">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L28">
         <v>1.31</v>
       </c>
       <c r="M28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N28">
         <v>5.1</v>
@@ -7433,25 +7433,25 @@
         <v>1.21</v>
       </c>
       <c r="P28">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q28">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R28">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S28">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T28">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="U28">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W28">
         <v>1.73</v>
@@ -7460,82 +7460,82 @@
         <v>24</v>
       </c>
       <c r="Y28">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z28">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA28">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB28">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AC28">
         <v>10.5</v>
       </c>
       <c r="AD28">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE28">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF28">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH28">
         <v>17.5</v>
       </c>
       <c r="AI28">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AJ28">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL28">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AM28">
         <v>70</v>
       </c>
       <c r="AN28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO28">
         <v>28</v>
       </c>
       <c r="AP28">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="AQ28">
         <v>15</v>
       </c>
       <c r="AR28">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="AS28">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AT28">
         <v>12</v>
       </c>
       <c r="AU28">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW28">
-        <v>4.7</v>
+        <v>25</v>
       </c>
       <c r="AX28">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY28">
         <v>10</v>
@@ -7544,46 +7544,46 @@
         <v>13</v>
       </c>
       <c r="BA28">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BB28">
-        <v>4.7</v>
+        <v>25</v>
       </c>
       <c r="BC28">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="BD28">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="BE28">
-        <v>46</v>
+        <v>6.4</v>
       </c>
       <c r="BF28">
         <v>11</v>
       </c>
       <c r="BG28">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BH28">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI28">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ28">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK28">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BN28">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BO28">
         <v>4.4</v>
@@ -7598,25 +7598,25 @@
         <v>28</v>
       </c>
       <c r="BS28">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BT28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU28">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV28">
         <v>26</v>
       </c>
       <c r="BW28">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BX28">
         <v>34</v>
       </c>
       <c r="BY28">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BZ28">
         <v>0</v>
@@ -7651,10 +7651,10 @@
         <v>2.14</v>
       </c>
       <c r="H29">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I29">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J29">
         <v>3.3</v>
@@ -7663,13 +7663,13 @@
         <v>3.5</v>
       </c>
       <c r="L29">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M29">
         <v>1.1</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O29">
         <v>1.45</v>
@@ -7684,28 +7684,28 @@
         <v>1.24</v>
       </c>
       <c r="S29">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T29">
         <v>2.04</v>
       </c>
       <c r="U29">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V29">
         <v>1.27</v>
       </c>
       <c r="W29">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X29">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y29">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z29">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA29">
         <v>130</v>
@@ -7717,10 +7717,10 @@
         <v>7.8</v>
       </c>
       <c r="AD29">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AE29">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AF29">
         <v>12.5</v>
@@ -7729,31 +7729,31 @@
         <v>11.5</v>
       </c>
       <c r="AH29">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI29">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AJ29">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK29">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AL29">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM29">
         <v>190</v>
       </c>
       <c r="AN29">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO29">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP29">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ29">
         <v>10</v>
@@ -7762,19 +7762,19 @@
         <v>24</v>
       </c>
       <c r="AS29">
-        <v>8.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="AT29">
         <v>6.4</v>
       </c>
       <c r="AU29">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV29">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW29">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="AX29">
         <v>10</v>
@@ -7783,10 +7783,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ29">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA29">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BB29">
         <v>21</v>
@@ -7795,22 +7795,22 @@
         <v>21</v>
       </c>
       <c r="BD29">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BE29">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF29">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG29">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BH29">
         <v>3.05</v>
       </c>
       <c r="BI29">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ29">
         <v>11.5</v>
